--- a/docs/SLMS2026_import_matrix_dot1.xlsx
+++ b/docs/SLMS2026_import_matrix_dot1.xlsx
@@ -401,14 +401,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A8"/>
+  <dimension ref="A1:A9"/>
   <cols>
-    <col min="1" max="1" width="51.83203125" customWidth="1"/>
+    <col min="1" max="1" width="56.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>Hướng dẫn — Ma trận đủ 10 TH onboarding (đợt 1)</v>
+        <v>Hướng dẫn — Ma trận onboarding + căn full NT (đợt 1)</v>
       </c>
     </row>
     <row r="2">
@@ -418,12 +418,12 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>File này cover đủ 10 trường hợp hợp lệ theo logic import SLMS2026.</v>
+        <v>File cover #1–#10 ma trận hợp lệ + #11–#14 nội thất đầy đủ.</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Sheet "0. Ma_Tran_Onboarding": tra cứu STT #1–#10.</v>
+        <v>Sheet "0. Ma_Tran_Onboarding": tra cứu STT.</v>
       </c>
     </row>
     <row r="5">
@@ -438,24 +438,29 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>#1–#2 NORENO: sau đợt 1 tự gửi Host — KHÔNG import file đợt 2.</v>
+        <v>#1–#2, #11 NORENO: sau đợt 1 tự gửi Host — KHÔNG import file đợt 2.</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>#3–#10 RENO: sau đợt 1 ở UNDER_RENOVATION — cần file đợt 2.</v>
+        <v>#3–#10, #12–#14 RENO: sau đợt 1 ở UNDER_RENOVATION — cần file đợt 2.</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>#13–#14 THEO_PHONG: mỗi phòng có 1 Quạt + 1 Giường (sheet TB mua đợt 2).</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:A8"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:A9"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I20"/>
   <cols>
     <col min="1" max="1" width="16.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -788,28 +793,149 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="str">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="str">
+        <v>HD-MTX-11-NORENO-FULL</v>
+      </c>
+      <c r="C12" t="str">
+        <v>NORENO</v>
+      </c>
+      <c r="D12" t="str">
+        <v>Có</v>
+      </c>
+      <c r="E12" t="str">
+        <v>—</v>
+      </c>
+      <c r="F12" t="str">
+        <v>—</v>
+      </c>
+      <c r="G12" t="str">
+        <v>—</v>
+      </c>
+      <c r="H12" t="str">
+        <v>Không</v>
+      </c>
+      <c r="I12" t="str">
+        <v>#11 NORENO | Nguyên căn full NT bàn giao | Đợt 2: —</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="str">
+        <v>HD-MTX-12-RENO-WH-FULL</v>
+      </c>
+      <c r="C13" t="str">
+        <v>RENO</v>
+      </c>
+      <c r="D13" t="str">
+        <v>Có</v>
+      </c>
+      <c r="E13" t="str">
+        <v>NGUYEN_CAN</v>
+      </c>
+      <c r="F13" t="str">
+        <v>Có (≥1 dòng)</v>
+      </c>
+      <c r="G13" t="str">
+        <v>Có</v>
+      </c>
+      <c r="H13" t="str">
+        <v>Có</v>
+      </c>
+      <c r="I13" t="str">
+        <v>#12 RENO | NGUYEN_CAN full NT | TB bàn giao + cải tạo + TB mua khu vực chung</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="str">
+        <v>HD-MTX-13-RENO-RM-FULL</v>
+      </c>
+      <c r="C14" t="str">
+        <v>RENO</v>
+      </c>
+      <c r="D14" t="str">
+        <v>Có</v>
+      </c>
+      <c r="E14" t="str">
+        <v>THEO_PHONG (4)</v>
+      </c>
+      <c r="F14" t="str">
+        <v>Có (≥1 dòng)</v>
+      </c>
+      <c r="G14" t="str">
+        <v>Có</v>
+      </c>
+      <c r="H14" t="str">
+        <v>Có</v>
+      </c>
+      <c r="I14" t="str">
+        <v>#13 RENO | THEO_PHONG (4) full NT | mỗi phòng 1 Quạt + 1 Giường (+ ĐH, nóng lạnh)</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="str">
+        <v>HD-MTX-14-RENO-RM-BEDFAN</v>
+      </c>
+      <c r="C15" t="str">
+        <v>RENO</v>
+      </c>
+      <c r="D15" t="str">
+        <v>Không</v>
+      </c>
+      <c r="E15" t="str">
+        <v>THEO_PHONG (5)</v>
+      </c>
+      <c r="F15" t="str">
+        <v>Có (≥1 dòng)</v>
+      </c>
+      <c r="G15" t="str">
+        <v>Có</v>
+      </c>
+      <c r="H15" t="str">
+        <v>Có</v>
+      </c>
+      <c r="I15" t="str">
+        <v>#14 RENO | THEO_PHONG (5) | mỗi phòng đúng 1 Quạt + 1 Giường</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
         <v/>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>Tổng: 10 trường hợp onboarding hợp lệ (2 NORENO + 8 RENO).</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
+    <row r="17">
+      <c r="A17" t="str">
+        <v>Tổng: 14 HĐ onboarding (#1–#10 ma trận + #11–#14 nội thất đầy đủ).</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
         <v>NORENO: import đợt 1 xong → tự gửi Host. RENO: cần import đợt 2.</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="str">
+    <row r="19">
+      <c r="A19" t="str">
         <v>RENO bắt buộc ≥1 hạng mục cải tạo ở sheet 3 trước khi gửi Host.</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>#11–#14: demo full NT — nguyên căn / theo phòng (mỗi phòng ≥ 1 Quạt + 1 Giường).</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I15"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I20"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -932,7 +1058,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O11"/>
+  <dimension ref="A1:O15"/>
   <cols>
     <col min="1" max="1" width="16.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -1468,16 +1594,204 @@
         <v>Ma trận #10 — RENO THEO_PHONG 3 phòng đầy đủ.</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>HD-MTX-11-NORENO-FULL</v>
+      </c>
+      <c r="B12" t="str">
+        <v>MTX#11 NORENO full NT</v>
+      </c>
+      <c r="C12" t="str">
+        <v>11 Ma Trận Tân Bình</v>
+      </c>
+      <c r="D12" t="str">
+        <v>Tân Bình</v>
+      </c>
+      <c r="E12" t="str">
+        <v>TP. Hồ Chí Minh</v>
+      </c>
+      <c r="F12">
+        <v>95</v>
+      </c>
+      <c r="G12">
+        <v>11.5</v>
+      </c>
+      <c r="H12">
+        <v>8.3</v>
+      </c>
+      <c r="I12">
+        <v>2</v>
+      </c>
+      <c r="J12">
+        <v>4</v>
+      </c>
+      <c r="K12" t="str">
+        <v>Lý Văn L</v>
+      </c>
+      <c r="L12">
+        <v>250000000</v>
+      </c>
+      <c r="M12" t="str">
+        <v>2026-08-01</v>
+      </c>
+      <c r="N12" t="str">
+        <v>2028-07-31</v>
+      </c>
+      <c r="O12" t="str">
+        <v>Ma trận #11 — NORENO nguyên căn, nội thất đầy đủ từ chủ (bàn giao).</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>HD-MTX-12-RENO-WH-FULL</v>
+      </c>
+      <c r="B13" t="str">
+        <v>MTX#12 NGUYEN_CAN full NT</v>
+      </c>
+      <c r="C13" t="str">
+        <v>12 Ma Trận Tân Bình</v>
+      </c>
+      <c r="D13" t="str">
+        <v>Tân Bình</v>
+      </c>
+      <c r="E13" t="str">
+        <v>TP. Hồ Chí Minh</v>
+      </c>
+      <c r="F13">
+        <v>110</v>
+      </c>
+      <c r="G13">
+        <v>12.4</v>
+      </c>
+      <c r="H13">
+        <v>8.9</v>
+      </c>
+      <c r="I13">
+        <v>2</v>
+      </c>
+      <c r="J13">
+        <v>4</v>
+      </c>
+      <c r="K13" t="str">
+        <v>Mai Thị M</v>
+      </c>
+      <c r="L13">
+        <v>280000000</v>
+      </c>
+      <c r="M13" t="str">
+        <v>2026-08-01</v>
+      </c>
+      <c r="N13" t="str">
+        <v>2028-07-31</v>
+      </c>
+      <c r="O13" t="str">
+        <v>Ma trận #12 — RENO NGUYEN_CAN nội thất đầy đủ: TB chủ + cải tạo + mua TB khu vực chung.</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>HD-MTX-13-RENO-RM-FULL</v>
+      </c>
+      <c r="B14" t="str">
+        <v>MTX#13 THEO_PHONG full NT</v>
+      </c>
+      <c r="C14" t="str">
+        <v>13 Ma Trận Thủ Đức</v>
+      </c>
+      <c r="D14" t="str">
+        <v>Thủ Đức</v>
+      </c>
+      <c r="E14" t="str">
+        <v>TP. Hồ Chí Minh</v>
+      </c>
+      <c r="F14">
+        <v>120</v>
+      </c>
+      <c r="G14">
+        <v>13</v>
+      </c>
+      <c r="H14">
+        <v>9.2</v>
+      </c>
+      <c r="I14">
+        <v>3</v>
+      </c>
+      <c r="J14">
+        <v>6</v>
+      </c>
+      <c r="K14" t="str">
+        <v>Phan Văn N</v>
+      </c>
+      <c r="L14">
+        <v>320000000</v>
+      </c>
+      <c r="M14" t="str">
+        <v>2026-09-01</v>
+      </c>
+      <c r="N14" t="str">
+        <v>2028-08-31</v>
+      </c>
+      <c r="O14" t="str">
+        <v>Ma trận #13 — RENO THEO_PHONG 4 phòng, mỗi phòng mua 1 Quạt + 1 Giường (+ ĐH/nóng lạnh).</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>HD-MTX-14-RENO-RM-BEDFAN</v>
+      </c>
+      <c r="B15" t="str">
+        <v>MTX#14 THEO_PHONG giường+quạt</v>
+      </c>
+      <c r="C15" t="str">
+        <v>14 Ma Trận Thủ Đức</v>
+      </c>
+      <c r="D15" t="str">
+        <v>Thủ Đức</v>
+      </c>
+      <c r="E15" t="str">
+        <v>TP. Hồ Chí Minh</v>
+      </c>
+      <c r="F15">
+        <v>90</v>
+      </c>
+      <c r="G15">
+        <v>11.2</v>
+      </c>
+      <c r="H15">
+        <v>8</v>
+      </c>
+      <c r="I15">
+        <v>2</v>
+      </c>
+      <c r="J15">
+        <v>5</v>
+      </c>
+      <c r="K15" t="str">
+        <v>Trịnh Thị O</v>
+      </c>
+      <c r="L15">
+        <v>240000000</v>
+      </c>
+      <c r="M15" t="str">
+        <v>2026-09-01</v>
+      </c>
+      <c r="N15" t="str">
+        <v>2028-08-31</v>
+      </c>
+      <c r="O15" t="str">
+        <v>Ma trận #14 — RENO THEO_PHONG 5 phòng, mỗi phòng đúng 1 Quạt + 1 Giường.</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O15"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G25"/>
   <cols>
     <col min="1" max="1" width="20.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -1672,9 +1986,400 @@
         <v/>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>HD-MTX-11-NORENO-FULL</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Điều hòa</v>
+      </c>
+      <c r="C9" t="str">
+        <v>1.5HP Inverter</v>
+      </c>
+      <c r="D9" t="str">
+        <v>Phòng khách</v>
+      </c>
+      <c r="E9" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>HD-MTX-11-NORENO-FULL</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Điều hòa</v>
+      </c>
+      <c r="C10" t="str">
+        <v>1HP</v>
+      </c>
+      <c r="D10" t="str">
+        <v>Phòng ngủ 1</v>
+      </c>
+      <c r="E10" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>HD-MTX-11-NORENO-FULL</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Tủ lạnh</v>
+      </c>
+      <c r="C11" t="str">
+        <v>Inverter 200L</v>
+      </c>
+      <c r="D11" t="str">
+        <v>Bếp</v>
+      </c>
+      <c r="E11" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>HD-MTX-11-NORENO-FULL</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Máy giặt</v>
+      </c>
+      <c r="C12" t="str">
+        <v>Cửa trước 8kg</v>
+      </c>
+      <c r="D12" t="str">
+        <v>Sân sau</v>
+      </c>
+      <c r="E12" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F12">
+        <v>1</v>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>HD-MTX-11-NORENO-FULL</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Nóng lạnh</v>
+      </c>
+      <c r="C13" t="str">
+        <v>15L</v>
+      </c>
+      <c r="D13" t="str">
+        <v>WC tầng 1</v>
+      </c>
+      <c r="E13" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F13">
+        <v>1</v>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>HD-MTX-11-NORENO-FULL</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Giường</v>
+      </c>
+      <c r="C14" t="str">
+        <v>Giường gỗ 1m6</v>
+      </c>
+      <c r="D14" t="str">
+        <v>Phòng ngủ 1</v>
+      </c>
+      <c r="E14" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F14">
+        <v>1</v>
+      </c>
+      <c r="G14" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>HD-MTX-11-NORENO-FULL</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Giường</v>
+      </c>
+      <c r="C15" t="str">
+        <v>Giường gỗ 1m6</v>
+      </c>
+      <c r="D15" t="str">
+        <v>Phòng ngủ 2</v>
+      </c>
+      <c r="E15" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F15">
+        <v>1</v>
+      </c>
+      <c r="G15" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>HD-MTX-11-NORENO-FULL</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Giường</v>
+      </c>
+      <c r="C16" t="str">
+        <v>Giường gỗ 1m2</v>
+      </c>
+      <c r="D16" t="str">
+        <v>Phòng ngủ 3</v>
+      </c>
+      <c r="E16" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F16">
+        <v>1</v>
+      </c>
+      <c r="G16" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>HD-MTX-11-NORENO-FULL</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Quạt</v>
+      </c>
+      <c r="C17" t="str">
+        <v>Quạt trần</v>
+      </c>
+      <c r="D17" t="str">
+        <v>Phòng khách</v>
+      </c>
+      <c r="E17" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F17">
+        <v>1</v>
+      </c>
+      <c r="G17" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>HD-MTX-11-NORENO-FULL</v>
+      </c>
+      <c r="B18" t="str">
+        <v>Quạt</v>
+      </c>
+      <c r="C18" t="str">
+        <v>Quạt đứng</v>
+      </c>
+      <c r="D18" t="str">
+        <v>Phòng ngủ 1</v>
+      </c>
+      <c r="E18" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F18">
+        <v>1</v>
+      </c>
+      <c r="G18" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>HD-MTX-11-NORENO-FULL</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Quạt</v>
+      </c>
+      <c r="C19" t="str">
+        <v>Quạt đứng</v>
+      </c>
+      <c r="D19" t="str">
+        <v>Phòng ngủ 2</v>
+      </c>
+      <c r="E19" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F19">
+        <v>1</v>
+      </c>
+      <c r="G19" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>HD-MTX-11-NORENO-FULL</v>
+      </c>
+      <c r="B20" t="str">
+        <v>Quạt</v>
+      </c>
+      <c r="C20" t="str">
+        <v>Quạt đứng</v>
+      </c>
+      <c r="D20" t="str">
+        <v>Phòng ngủ 3</v>
+      </c>
+      <c r="E20" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F20">
+        <v>1</v>
+      </c>
+      <c r="G20" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>HD-MTX-12-RENO-WH-FULL</v>
+      </c>
+      <c r="B21" t="str">
+        <v>Giường</v>
+      </c>
+      <c r="C21" t="str">
+        <v>Giường gỗ cũ</v>
+      </c>
+      <c r="D21" t="str">
+        <v>Phòng ngủ chính</v>
+      </c>
+      <c r="E21" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F21">
+        <v>2</v>
+      </c>
+      <c r="G21" t="str">
+        <v>TB chủ giữ lại</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>HD-MTX-12-RENO-WH-FULL</v>
+      </c>
+      <c r="B22" t="str">
+        <v>Quạt</v>
+      </c>
+      <c r="C22" t="str">
+        <v>Quạt trần cũ</v>
+      </c>
+      <c r="D22" t="str">
+        <v>Phòng khách</v>
+      </c>
+      <c r="E22" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F22">
+        <v>1</v>
+      </c>
+      <c r="G22" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>HD-MTX-12-RENO-WH-FULL</v>
+      </c>
+      <c r="B23" t="str">
+        <v>Tủ lạnh</v>
+      </c>
+      <c r="C23" t="str">
+        <v>Tủ 150L cũ</v>
+      </c>
+      <c r="D23" t="str">
+        <v>Bếp</v>
+      </c>
+      <c r="E23" t="str">
+        <v>DAMAGED</v>
+      </c>
+      <c r="F23">
+        <v>1</v>
+      </c>
+      <c r="G23" t="str">
+        <v>Sắp thay</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>HD-MTX-13-RENO-RM-FULL</v>
+      </c>
+      <c r="B24" t="str">
+        <v>Máy giặt</v>
+      </c>
+      <c r="C24" t="str">
+        <v>Máy cũ chung</v>
+      </c>
+      <c r="D24" t="str">
+        <v>Sân phơi</v>
+      </c>
+      <c r="E24" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F24">
+        <v>1</v>
+      </c>
+      <c r="G24" t="str">
+        <v>TB dùng chung</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>HD-MTX-13-RENO-RM-FULL</v>
+      </c>
+      <c r="B25" t="str">
+        <v>Tủ lạnh</v>
+      </c>
+      <c r="C25" t="str">
+        <v>Tủ cũ tầng 1</v>
+      </c>
+      <c r="D25" t="str">
+        <v>Bếp chung</v>
+      </c>
+      <c r="E25" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F25">
+        <v>1</v>
+      </c>
+      <c r="G25" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G8"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G25"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/docs/SLMS2026_import_matrix_dot1.xlsx
+++ b/docs/SLMS2026_import_matrix_dot1.xlsx
@@ -403,12 +403,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:A9"/>
   <cols>
-    <col min="1" max="1" width="56.83203125" customWidth="1"/>
+    <col min="1" max="1" width="110.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>Hướng dẫn — Ma trận onboarding + căn full NT (đợt 1)</v>
+        <v>Hướng dẫn — Ma trận onboarding 50 căn (đợt 1)</v>
       </c>
     </row>
     <row r="2">
@@ -418,7 +418,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>File cover #1–#10 ma trận hợp lệ + #11–#14 nội thất đầy đủ.</v>
+        <v>File cover 50 HĐ: nguyên căn (full / cơ bản / không NT) + theo phòng (cơ bản / không NT / full).</v>
       </c>
     </row>
     <row r="4">
@@ -438,17 +438,17 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>#1–#2, #11 NORENO: sau đợt 1 tự gửi Host — KHÔNG import file đợt 2.</v>
+        <v>NORENO (15 HĐ): sau đợt 1 tự gửi Host — KHÔNG import file đợt 2.</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>#3–#10, #12–#14 RENO: sau đợt 1 ở UNDER_RENOVATION — cần file đợt 2.</v>
+        <v>RENO (35 HĐ): sau đợt 1 ở UNDER_RENOVATION — cần file đợt 2.</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>#13–#14 THEO_PHONG: mỗi phòng có 1 Quạt + 1 Giường (sheet TB mua đợt 2).</v>
+        <v>Zone: chỉ quận đã seed (Q1, Q3, BT, GV, PN, Cầu Giấy).</v>
       </c>
     </row>
   </sheetData>
@@ -460,17 +460,17 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I56"/>
   <cols>
-    <col min="1" max="1" width="16.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="16.83203125" customWidth="1"/>
-    <col min="4" max="4" width="18.83203125" customWidth="1"/>
+    <col min="1" max="1" width="5.83203125" customWidth="1"/>
+    <col min="2" max="2" width="36.83203125" customWidth="1"/>
+    <col min="3" max="3" width="12.83203125" customWidth="1"/>
+    <col min="4" max="4" width="14.83203125" customWidth="1"/>
     <col min="5" max="5" width="16.83203125" customWidth="1"/>
-    <col min="6" max="6" width="16.83203125" customWidth="1"/>
-    <col min="7" max="7" width="16.83203125" customWidth="1"/>
-    <col min="8" max="8" width="16.83203125" customWidth="1"/>
-    <col min="9" max="9" width="16.83203125" customWidth="1"/>
+    <col min="6" max="6" width="12.83203125" customWidth="1"/>
+    <col min="7" max="7" width="10.83203125" customWidth="1"/>
+    <col min="8" max="8" width="10.83203125" customWidth="1"/>
+    <col min="9" max="9" width="60.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -507,7 +507,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="str">
-        <v>HD-MTX-01-NORENO-NOFURN</v>
+        <v>HD-MTX-01-NORENO-WH-NONE</v>
       </c>
       <c r="C2" t="str">
         <v>NORENO</v>
@@ -528,7 +528,7 @@
         <v>Không</v>
       </c>
       <c r="I2" t="str">
-        <v>#1 NORENO | TB bàn giao: Không | Đợt 2: —</v>
+        <v>#1 NORENO | nguyên căn | không nội thất | TB bàn giao: Không</v>
       </c>
     </row>
     <row r="3">
@@ -536,13 +536,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="str">
-        <v>HD-MTX-02-NORENO-FURN</v>
+        <v>HD-MTX-02-NORENO-WH-NONE</v>
       </c>
       <c r="C3" t="str">
         <v>NORENO</v>
       </c>
       <c r="D3" t="str">
-        <v>Có</v>
+        <v>Không</v>
       </c>
       <c r="E3" t="str">
         <v>—</v>
@@ -557,7 +557,7 @@
         <v>Không</v>
       </c>
       <c r="I3" t="str">
-        <v>#2 NORENO | TB bàn giao: Có | Đợt 2: —</v>
+        <v>#2 NORENO | nguyên căn | không nội thất | TB bàn giao: Không</v>
       </c>
     </row>
     <row r="4">
@@ -565,28 +565,28 @@
         <v>3</v>
       </c>
       <c r="B4" t="str">
-        <v>HD-MTX-03-RENO-WH-NOFURN</v>
+        <v>HD-MTX-03-NORENO-WH-NONE</v>
       </c>
       <c r="C4" t="str">
-        <v>RENO</v>
+        <v>NORENO</v>
       </c>
       <c r="D4" t="str">
         <v>Không</v>
       </c>
       <c r="E4" t="str">
-        <v>NGUYEN_CAN</v>
+        <v>—</v>
       </c>
       <c r="F4" t="str">
-        <v>Có (≥1 dòng)</v>
+        <v>—</v>
       </c>
       <c r="G4" t="str">
+        <v>—</v>
+      </c>
+      <c r="H4" t="str">
         <v>Không</v>
       </c>
-      <c r="H4" t="str">
-        <v>Có</v>
-      </c>
       <c r="I4" t="str">
-        <v>#3 RENO | NGUYEN_CAN | TB bàn giao: Không | Cải tạo: Có | TB mua: Không</v>
+        <v>#3 NORENO | nguyên căn | không nội thất | TB bàn giao: Không</v>
       </c>
     </row>
     <row r="5">
@@ -594,28 +594,28 @@
         <v>4</v>
       </c>
       <c r="B5" t="str">
-        <v>HD-MTX-04-RENO-WH-EQUIP</v>
+        <v>HD-MTX-04-NORENO-WH-NONE</v>
       </c>
       <c r="C5" t="str">
-        <v>RENO</v>
+        <v>NORENO</v>
       </c>
       <c r="D5" t="str">
         <v>Không</v>
       </c>
       <c r="E5" t="str">
-        <v>NGUYEN_CAN</v>
+        <v>—</v>
       </c>
       <c r="F5" t="str">
-        <v>Có (≥1 dòng)</v>
+        <v>—</v>
       </c>
       <c r="G5" t="str">
-        <v>Có</v>
+        <v>—</v>
       </c>
       <c r="H5" t="str">
-        <v>Có</v>
+        <v>Không</v>
       </c>
       <c r="I5" t="str">
-        <v>#4 RENO | NGUYEN_CAN | TB bàn giao: Không | Cải tạo: Có | TB mua: Có</v>
+        <v>#4 NORENO | nguyên căn | không nội thất | TB bàn giao: Không</v>
       </c>
     </row>
     <row r="6">
@@ -623,28 +623,28 @@
         <v>5</v>
       </c>
       <c r="B6" t="str">
-        <v>HD-MTX-05-RENO-WH-HO-NOFURN</v>
+        <v>HD-MTX-05-NORENO-WH-NONE</v>
       </c>
       <c r="C6" t="str">
-        <v>RENO</v>
+        <v>NORENO</v>
       </c>
       <c r="D6" t="str">
-        <v>Có</v>
+        <v>Không</v>
       </c>
       <c r="E6" t="str">
-        <v>NGUYEN_CAN</v>
+        <v>—</v>
       </c>
       <c r="F6" t="str">
-        <v>Có (≥1 dòng)</v>
+        <v>—</v>
       </c>
       <c r="G6" t="str">
+        <v>—</v>
+      </c>
+      <c r="H6" t="str">
         <v>Không</v>
       </c>
-      <c r="H6" t="str">
-        <v>Có</v>
-      </c>
       <c r="I6" t="str">
-        <v>#5 RENO | NGUYEN_CAN | TB bàn giao: Có | Cải tạo: Có | TB mua: Không</v>
+        <v>#5 NORENO | nguyên căn | không nội thất | TB bàn giao: Không</v>
       </c>
     </row>
     <row r="7">
@@ -652,28 +652,28 @@
         <v>6</v>
       </c>
       <c r="B7" t="str">
-        <v>HD-MTX-06-RENO-WH-HO-EQUIP</v>
+        <v>HD-MTX-06-NORENO-WH-BASIC</v>
       </c>
       <c r="C7" t="str">
-        <v>RENO</v>
+        <v>NORENO</v>
       </c>
       <c r="D7" t="str">
         <v>Có</v>
       </c>
       <c r="E7" t="str">
-        <v>NGUYEN_CAN</v>
+        <v>—</v>
       </c>
       <c r="F7" t="str">
-        <v>Có (≥1 dòng)</v>
+        <v>—</v>
       </c>
       <c r="G7" t="str">
-        <v>Có</v>
+        <v>—</v>
       </c>
       <c r="H7" t="str">
-        <v>Có</v>
+        <v>Không</v>
       </c>
       <c r="I7" t="str">
-        <v>#6 RENO | NGUYEN_CAN | TB bàn giao: Có | Cải tạo: Có | TB mua: Có</v>
+        <v>#6 NORENO | nguyên căn | nội thất cơ bản | TB bàn giao: Có</v>
       </c>
     </row>
     <row r="8">
@@ -681,28 +681,28 @@
         <v>7</v>
       </c>
       <c r="B8" t="str">
-        <v>HD-MTX-07-RENO-RM-NOFURN</v>
+        <v>HD-MTX-07-NORENO-WH-BASIC</v>
       </c>
       <c r="C8" t="str">
-        <v>RENO</v>
+        <v>NORENO</v>
       </c>
       <c r="D8" t="str">
+        <v>Có</v>
+      </c>
+      <c r="E8" t="str">
+        <v>—</v>
+      </c>
+      <c r="F8" t="str">
+        <v>—</v>
+      </c>
+      <c r="G8" t="str">
+        <v>—</v>
+      </c>
+      <c r="H8" t="str">
         <v>Không</v>
       </c>
-      <c r="E8" t="str">
-        <v>THEO_PHONG (3)</v>
-      </c>
-      <c r="F8" t="str">
-        <v>Có (≥1 dòng)</v>
-      </c>
-      <c r="G8" t="str">
-        <v>Không</v>
-      </c>
-      <c r="H8" t="str">
-        <v>Có</v>
-      </c>
       <c r="I8" t="str">
-        <v>#7 RENO | THEO_PHONG (3) | TB bàn giao: Không | Cải tạo: Có | TB mua: Không</v>
+        <v>#7 NORENO | nguyên căn | nội thất cơ bản | TB bàn giao: Có</v>
       </c>
     </row>
     <row r="9">
@@ -710,28 +710,28 @@
         <v>8</v>
       </c>
       <c r="B9" t="str">
-        <v>HD-MTX-08-RENO-RM-EQUIP</v>
+        <v>HD-MTX-08-NORENO-WH-BASIC</v>
       </c>
       <c r="C9" t="str">
-        <v>RENO</v>
+        <v>NORENO</v>
       </c>
       <c r="D9" t="str">
+        <v>Có</v>
+      </c>
+      <c r="E9" t="str">
+        <v>—</v>
+      </c>
+      <c r="F9" t="str">
+        <v>—</v>
+      </c>
+      <c r="G9" t="str">
+        <v>—</v>
+      </c>
+      <c r="H9" t="str">
         <v>Không</v>
       </c>
-      <c r="E9" t="str">
-        <v>THEO_PHONG (3)</v>
-      </c>
-      <c r="F9" t="str">
-        <v>Có (≥1 dòng)</v>
-      </c>
-      <c r="G9" t="str">
-        <v>Có</v>
-      </c>
-      <c r="H9" t="str">
-        <v>Có</v>
-      </c>
       <c r="I9" t="str">
-        <v>#8 RENO | THEO_PHONG (3) | TB bàn giao: Không | Cải tạo: Có | TB mua: Có</v>
+        <v>#8 NORENO | nguyên căn | nội thất cơ bản | TB bàn giao: Có</v>
       </c>
     </row>
     <row r="10">
@@ -739,28 +739,28 @@
         <v>9</v>
       </c>
       <c r="B10" t="str">
-        <v>HD-MTX-09-RENO-RM-HO-NOFURN</v>
+        <v>HD-MTX-09-NORENO-WH-BASIC</v>
       </c>
       <c r="C10" t="str">
-        <v>RENO</v>
+        <v>NORENO</v>
       </c>
       <c r="D10" t="str">
         <v>Có</v>
       </c>
       <c r="E10" t="str">
-        <v>THEO_PHONG (3)</v>
+        <v>—</v>
       </c>
       <c r="F10" t="str">
-        <v>Có (≥1 dòng)</v>
+        <v>—</v>
       </c>
       <c r="G10" t="str">
+        <v>—</v>
+      </c>
+      <c r="H10" t="str">
         <v>Không</v>
       </c>
-      <c r="H10" t="str">
-        <v>Có</v>
-      </c>
       <c r="I10" t="str">
-        <v>#9 RENO | THEO_PHONG (3) | TB bàn giao: Có | Cải tạo: Có | TB mua: Không</v>
+        <v>#9 NORENO | nguyên căn | nội thất cơ bản | TB bàn giao: Có</v>
       </c>
     </row>
     <row r="11">
@@ -768,28 +768,28 @@
         <v>10</v>
       </c>
       <c r="B11" t="str">
-        <v>HD-MTX-10-RENO-RM-HO-EQUIP</v>
+        <v>HD-MTX-10-NORENO-WH-BASIC</v>
       </c>
       <c r="C11" t="str">
-        <v>RENO</v>
+        <v>NORENO</v>
       </c>
       <c r="D11" t="str">
         <v>Có</v>
       </c>
       <c r="E11" t="str">
-        <v>THEO_PHONG (3)</v>
+        <v>—</v>
       </c>
       <c r="F11" t="str">
-        <v>Có (≥1 dòng)</v>
+        <v>—</v>
       </c>
       <c r="G11" t="str">
-        <v>Có</v>
+        <v>—</v>
       </c>
       <c r="H11" t="str">
-        <v>Có</v>
+        <v>Không</v>
       </c>
       <c r="I11" t="str">
-        <v>#10 RENO | THEO_PHONG (3) | TB bàn giao: Có | Cải tạo: Có | TB mua: Có</v>
+        <v>#10 NORENO | nguyên căn | nội thất cơ bản | TB bàn giao: Có</v>
       </c>
     </row>
     <row r="12">
@@ -797,7 +797,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="str">
-        <v>HD-MTX-11-NORENO-FULL</v>
+        <v>HD-MTX-11-NORENO-WH-FULL</v>
       </c>
       <c r="C12" t="str">
         <v>NORENO</v>
@@ -818,7 +818,7 @@
         <v>Không</v>
       </c>
       <c r="I12" t="str">
-        <v>#11 NORENO | Nguyên căn full NT bàn giao | Đợt 2: —</v>
+        <v>#11 NORENO | nguyên căn | full nội thất | TB bàn giao: Có</v>
       </c>
     </row>
     <row r="13">
@@ -826,28 +826,28 @@
         <v>12</v>
       </c>
       <c r="B13" t="str">
-        <v>HD-MTX-12-RENO-WH-FULL</v>
+        <v>HD-MTX-12-NORENO-WH-FULL</v>
       </c>
       <c r="C13" t="str">
-        <v>RENO</v>
+        <v>NORENO</v>
       </c>
       <c r="D13" t="str">
         <v>Có</v>
       </c>
       <c r="E13" t="str">
-        <v>NGUYEN_CAN</v>
+        <v>—</v>
       </c>
       <c r="F13" t="str">
-        <v>Có (≥1 dòng)</v>
+        <v>—</v>
       </c>
       <c r="G13" t="str">
-        <v>Có</v>
+        <v>—</v>
       </c>
       <c r="H13" t="str">
-        <v>Có</v>
+        <v>Không</v>
       </c>
       <c r="I13" t="str">
-        <v>#12 RENO | NGUYEN_CAN full NT | TB bàn giao + cải tạo + TB mua khu vực chung</v>
+        <v>#12 NORENO | nguyên căn | full nội thất | TB bàn giao: Có</v>
       </c>
     </row>
     <row r="14">
@@ -855,28 +855,28 @@
         <v>13</v>
       </c>
       <c r="B14" t="str">
-        <v>HD-MTX-13-RENO-RM-FULL</v>
+        <v>HD-MTX-13-NORENO-WH-FULL</v>
       </c>
       <c r="C14" t="str">
-        <v>RENO</v>
+        <v>NORENO</v>
       </c>
       <c r="D14" t="str">
         <v>Có</v>
       </c>
       <c r="E14" t="str">
-        <v>THEO_PHONG (4)</v>
+        <v>—</v>
       </c>
       <c r="F14" t="str">
-        <v>Có (≥1 dòng)</v>
+        <v>—</v>
       </c>
       <c r="G14" t="str">
-        <v>Có</v>
+        <v>—</v>
       </c>
       <c r="H14" t="str">
-        <v>Có</v>
+        <v>Không</v>
       </c>
       <c r="I14" t="str">
-        <v>#13 RENO | THEO_PHONG (4) full NT | mỗi phòng 1 Quạt + 1 Giường (+ ĐH, nóng lạnh)</v>
+        <v>#13 NORENO | nguyên căn | full nội thất | TB bàn giao: Có</v>
       </c>
     </row>
     <row r="15">
@@ -884,58 +884,1097 @@
         <v>14</v>
       </c>
       <c r="B15" t="str">
-        <v>HD-MTX-14-RENO-RM-BEDFAN</v>
+        <v>HD-MTX-14-NORENO-WH-FULL</v>
       </c>
       <c r="C15" t="str">
+        <v>NORENO</v>
+      </c>
+      <c r="D15" t="str">
+        <v>Có</v>
+      </c>
+      <c r="E15" t="str">
+        <v>—</v>
+      </c>
+      <c r="F15" t="str">
+        <v>—</v>
+      </c>
+      <c r="G15" t="str">
+        <v>—</v>
+      </c>
+      <c r="H15" t="str">
+        <v>Không</v>
+      </c>
+      <c r="I15" t="str">
+        <v>#14 NORENO | nguyên căn | full nội thất | TB bàn giao: Có</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="str">
+        <v>HD-MTX-15-NORENO-WH-FULL</v>
+      </c>
+      <c r="C16" t="str">
+        <v>NORENO</v>
+      </c>
+      <c r="D16" t="str">
+        <v>Có</v>
+      </c>
+      <c r="E16" t="str">
+        <v>—</v>
+      </c>
+      <c r="F16" t="str">
+        <v>—</v>
+      </c>
+      <c r="G16" t="str">
+        <v>—</v>
+      </c>
+      <c r="H16" t="str">
+        <v>Không</v>
+      </c>
+      <c r="I16" t="str">
+        <v>#15 NORENO | nguyên căn | full nội thất | TB bàn giao: Có</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="str">
+        <v>HD-MTX-16-RENO-WH-NONE</v>
+      </c>
+      <c r="C17" t="str">
         <v>RENO</v>
       </c>
-      <c r="D15" t="str">
+      <c r="D17" t="str">
         <v>Không</v>
       </c>
-      <c r="E15" t="str">
-        <v>THEO_PHONG (5)</v>
-      </c>
-      <c r="F15" t="str">
+      <c r="E17" t="str">
+        <v>NGUYEN_CAN</v>
+      </c>
+      <c r="F17" t="str">
         <v>Có (≥1 dòng)</v>
       </c>
-      <c r="G15" t="str">
-        <v>Có</v>
-      </c>
-      <c r="H15" t="str">
-        <v>Có</v>
-      </c>
-      <c r="I15" t="str">
-        <v>#14 RENO | THEO_PHONG (5) | mỗi phòng đúng 1 Quạt + 1 Giường</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>Tổng: 14 HĐ onboarding (#1–#10 ma trận + #11–#14 nội thất đầy đủ).</v>
+      <c r="G17" t="str">
+        <v>Không</v>
+      </c>
+      <c r="H17" t="str">
+        <v>Có</v>
+      </c>
+      <c r="I17" t="str">
+        <v>#16 RENO | nguyên căn | không nội thất | TB bàn giao: Không</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="str">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="str">
+        <v>HD-MTX-17-RENO-WH-NONE</v>
+      </c>
+      <c r="C18" t="str">
+        <v>RENO</v>
+      </c>
+      <c r="D18" t="str">
+        <v>Không</v>
+      </c>
+      <c r="E18" t="str">
+        <v>NGUYEN_CAN</v>
+      </c>
+      <c r="F18" t="str">
+        <v>Có (≥1 dòng)</v>
+      </c>
+      <c r="G18" t="str">
+        <v>Không</v>
+      </c>
+      <c r="H18" t="str">
+        <v>Có</v>
+      </c>
+      <c r="I18" t="str">
+        <v>#17 RENO | nguyên căn | không nội thất | TB bàn giao: Không</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="str">
+        <v>HD-MTX-18-RENO-WH-NONE</v>
+      </c>
+      <c r="C19" t="str">
+        <v>RENO</v>
+      </c>
+      <c r="D19" t="str">
+        <v>Không</v>
+      </c>
+      <c r="E19" t="str">
+        <v>NGUYEN_CAN</v>
+      </c>
+      <c r="F19" t="str">
+        <v>Có (≥1 dòng)</v>
+      </c>
+      <c r="G19" t="str">
+        <v>Không</v>
+      </c>
+      <c r="H19" t="str">
+        <v>Có</v>
+      </c>
+      <c r="I19" t="str">
+        <v>#18 RENO | nguyên căn | không nội thất | TB bàn giao: Không</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="str">
+        <v>HD-MTX-19-RENO-WH-BASIC-HO</v>
+      </c>
+      <c r="C20" t="str">
+        <v>RENO</v>
+      </c>
+      <c r="D20" t="str">
+        <v>Có</v>
+      </c>
+      <c r="E20" t="str">
+        <v>NGUYEN_CAN</v>
+      </c>
+      <c r="F20" t="str">
+        <v>Có (≥1 dòng)</v>
+      </c>
+      <c r="G20" t="str">
+        <v>Không</v>
+      </c>
+      <c r="H20" t="str">
+        <v>Có</v>
+      </c>
+      <c r="I20" t="str">
+        <v>#19 RENO | nguyên căn | nội thất cơ bản | TB bàn giao: Có</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="str">
+        <v>HD-MTX-20-RENO-WH-BASIC-HO</v>
+      </c>
+      <c r="C21" t="str">
+        <v>RENO</v>
+      </c>
+      <c r="D21" t="str">
+        <v>Có</v>
+      </c>
+      <c r="E21" t="str">
+        <v>NGUYEN_CAN</v>
+      </c>
+      <c r="F21" t="str">
+        <v>Có (≥1 dòng)</v>
+      </c>
+      <c r="G21" t="str">
+        <v>Không</v>
+      </c>
+      <c r="H21" t="str">
+        <v>Có</v>
+      </c>
+      <c r="I21" t="str">
+        <v>#20 RENO | nguyên căn | nội thất cơ bản | TB bàn giao: Có</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" t="str">
+        <v>HD-MTX-21-RENO-WH-BASIC-HO</v>
+      </c>
+      <c r="C22" t="str">
+        <v>RENO</v>
+      </c>
+      <c r="D22" t="str">
+        <v>Có</v>
+      </c>
+      <c r="E22" t="str">
+        <v>NGUYEN_CAN</v>
+      </c>
+      <c r="F22" t="str">
+        <v>Có (≥1 dòng)</v>
+      </c>
+      <c r="G22" t="str">
+        <v>Không</v>
+      </c>
+      <c r="H22" t="str">
+        <v>Có</v>
+      </c>
+      <c r="I22" t="str">
+        <v>#21 RENO | nguyên căn | nội thất cơ bản | TB bàn giao: Có</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" t="str">
+        <v>HD-MTX-22-RENO-WH-BASIC-BUY</v>
+      </c>
+      <c r="C23" t="str">
+        <v>RENO</v>
+      </c>
+      <c r="D23" t="str">
+        <v>Không</v>
+      </c>
+      <c r="E23" t="str">
+        <v>NGUYEN_CAN</v>
+      </c>
+      <c r="F23" t="str">
+        <v>Có (≥1 dòng)</v>
+      </c>
+      <c r="G23" t="str">
+        <v>Có</v>
+      </c>
+      <c r="H23" t="str">
+        <v>Có</v>
+      </c>
+      <c r="I23" t="str">
+        <v>#22 RENO | nguyên căn | nội thất cơ bản | TB bàn giao: Không</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" t="str">
+        <v>HD-MTX-23-RENO-WH-BASIC-BUY</v>
+      </c>
+      <c r="C24" t="str">
+        <v>RENO</v>
+      </c>
+      <c r="D24" t="str">
+        <v>Không</v>
+      </c>
+      <c r="E24" t="str">
+        <v>NGUYEN_CAN</v>
+      </c>
+      <c r="F24" t="str">
+        <v>Có (≥1 dòng)</v>
+      </c>
+      <c r="G24" t="str">
+        <v>Có</v>
+      </c>
+      <c r="H24" t="str">
+        <v>Có</v>
+      </c>
+      <c r="I24" t="str">
+        <v>#23 RENO | nguyên căn | nội thất cơ bản | TB bàn giao: Không</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" t="str">
+        <v>HD-MTX-24-RENO-WH-BASIC-BUY</v>
+      </c>
+      <c r="C25" t="str">
+        <v>RENO</v>
+      </c>
+      <c r="D25" t="str">
+        <v>Không</v>
+      </c>
+      <c r="E25" t="str">
+        <v>NGUYEN_CAN</v>
+      </c>
+      <c r="F25" t="str">
+        <v>Có (≥1 dòng)</v>
+      </c>
+      <c r="G25" t="str">
+        <v>Có</v>
+      </c>
+      <c r="H25" t="str">
+        <v>Có</v>
+      </c>
+      <c r="I25" t="str">
+        <v>#24 RENO | nguyên căn | nội thất cơ bản | TB bàn giao: Không</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" t="str">
+        <v>HD-MTX-25-RENO-WH-FULL</v>
+      </c>
+      <c r="C26" t="str">
+        <v>RENO</v>
+      </c>
+      <c r="D26" t="str">
+        <v>Có</v>
+      </c>
+      <c r="E26" t="str">
+        <v>NGUYEN_CAN</v>
+      </c>
+      <c r="F26" t="str">
+        <v>Có (≥1 dòng)</v>
+      </c>
+      <c r="G26" t="str">
+        <v>Có</v>
+      </c>
+      <c r="H26" t="str">
+        <v>Có</v>
+      </c>
+      <c r="I26" t="str">
+        <v>#25 RENO | nguyên căn | full nội thất | TB bàn giao: Có</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" t="str">
+        <v>HD-MTX-26-RENO-WH-FULL</v>
+      </c>
+      <c r="C27" t="str">
+        <v>RENO</v>
+      </c>
+      <c r="D27" t="str">
+        <v>Có</v>
+      </c>
+      <c r="E27" t="str">
+        <v>NGUYEN_CAN</v>
+      </c>
+      <c r="F27" t="str">
+        <v>Có (≥1 dòng)</v>
+      </c>
+      <c r="G27" t="str">
+        <v>Có</v>
+      </c>
+      <c r="H27" t="str">
+        <v>Có</v>
+      </c>
+      <c r="I27" t="str">
+        <v>#26 RENO | nguyên căn | full nội thất | TB bàn giao: Có</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" t="str">
+        <v>HD-MTX-27-RENO-WH-FULL</v>
+      </c>
+      <c r="C28" t="str">
+        <v>RENO</v>
+      </c>
+      <c r="D28" t="str">
+        <v>Có</v>
+      </c>
+      <c r="E28" t="str">
+        <v>NGUYEN_CAN</v>
+      </c>
+      <c r="F28" t="str">
+        <v>Có (≥1 dòng)</v>
+      </c>
+      <c r="G28" t="str">
+        <v>Có</v>
+      </c>
+      <c r="H28" t="str">
+        <v>Có</v>
+      </c>
+      <c r="I28" t="str">
+        <v>#27 RENO | nguyên căn | full nội thất | TB bàn giao: Có</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" t="str">
+        <v>HD-MTX-28-RENO-WH-HO-NOBUY</v>
+      </c>
+      <c r="C29" t="str">
+        <v>RENO</v>
+      </c>
+      <c r="D29" t="str">
+        <v>Có</v>
+      </c>
+      <c r="E29" t="str">
+        <v>NGUYEN_CAN</v>
+      </c>
+      <c r="F29" t="str">
+        <v>Có (≥1 dòng)</v>
+      </c>
+      <c r="G29" t="str">
+        <v>Không</v>
+      </c>
+      <c r="H29" t="str">
+        <v>Có</v>
+      </c>
+      <c r="I29" t="str">
+        <v>#28 RENO | nguyên căn | không nội thất | TB bàn giao: Có</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" t="str">
+        <v>HD-MTX-29-RENO-WH-HO-NOBUY</v>
+      </c>
+      <c r="C30" t="str">
+        <v>RENO</v>
+      </c>
+      <c r="D30" t="str">
+        <v>Có</v>
+      </c>
+      <c r="E30" t="str">
+        <v>NGUYEN_CAN</v>
+      </c>
+      <c r="F30" t="str">
+        <v>Có (≥1 dòng)</v>
+      </c>
+      <c r="G30" t="str">
+        <v>Không</v>
+      </c>
+      <c r="H30" t="str">
+        <v>Có</v>
+      </c>
+      <c r="I30" t="str">
+        <v>#29 RENO | nguyên căn | không nội thất | TB bàn giao: Có</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31" t="str">
+        <v>HD-MTX-30-RENO-WH-HO-BUY</v>
+      </c>
+      <c r="C31" t="str">
+        <v>RENO</v>
+      </c>
+      <c r="D31" t="str">
+        <v>Có</v>
+      </c>
+      <c r="E31" t="str">
+        <v>NGUYEN_CAN</v>
+      </c>
+      <c r="F31" t="str">
+        <v>Có (≥1 dòng)</v>
+      </c>
+      <c r="G31" t="str">
+        <v>Có</v>
+      </c>
+      <c r="H31" t="str">
+        <v>Có</v>
+      </c>
+      <c r="I31" t="str">
+        <v>#30 RENO | nguyên căn | nội thất cơ bản | TB bàn giao: Có</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32" t="str">
+        <v>HD-MTX-31-RENO-WH-HO-BUY</v>
+      </c>
+      <c r="C32" t="str">
+        <v>RENO</v>
+      </c>
+      <c r="D32" t="str">
+        <v>Có</v>
+      </c>
+      <c r="E32" t="str">
+        <v>NGUYEN_CAN</v>
+      </c>
+      <c r="F32" t="str">
+        <v>Có (≥1 dòng)</v>
+      </c>
+      <c r="G32" t="str">
+        <v>Có</v>
+      </c>
+      <c r="H32" t="str">
+        <v>Có</v>
+      </c>
+      <c r="I32" t="str">
+        <v>#31 RENO | nguyên căn | nội thất cơ bản | TB bàn giao: Có</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33" t="str">
+        <v>HD-MTX-32-RENO-RM-NONE</v>
+      </c>
+      <c r="C33" t="str">
+        <v>RENO</v>
+      </c>
+      <c r="D33" t="str">
+        <v>Không</v>
+      </c>
+      <c r="E33" t="str">
+        <v>THEO_PHONG (3)</v>
+      </c>
+      <c r="F33" t="str">
+        <v>Có (≥1 dòng)</v>
+      </c>
+      <c r="G33" t="str">
+        <v>Không</v>
+      </c>
+      <c r="H33" t="str">
+        <v>Có</v>
+      </c>
+      <c r="I33" t="str">
+        <v>#32 RENO | theo phòng (3p) | không nội thất | TB bàn giao: Không</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34" t="str">
+        <v>HD-MTX-33-RENO-RM-NONE</v>
+      </c>
+      <c r="C34" t="str">
+        <v>RENO</v>
+      </c>
+      <c r="D34" t="str">
+        <v>Không</v>
+      </c>
+      <c r="E34" t="str">
+        <v>THEO_PHONG (3)</v>
+      </c>
+      <c r="F34" t="str">
+        <v>Có (≥1 dòng)</v>
+      </c>
+      <c r="G34" t="str">
+        <v>Không</v>
+      </c>
+      <c r="H34" t="str">
+        <v>Có</v>
+      </c>
+      <c r="I34" t="str">
+        <v>#33 RENO | theo phòng (3p) | không nội thất | TB bàn giao: Không</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35" t="str">
+        <v>HD-MTX-34-RENO-RM-NONE</v>
+      </c>
+      <c r="C35" t="str">
+        <v>RENO</v>
+      </c>
+      <c r="D35" t="str">
+        <v>Không</v>
+      </c>
+      <c r="E35" t="str">
+        <v>THEO_PHONG (3)</v>
+      </c>
+      <c r="F35" t="str">
+        <v>Có (≥1 dòng)</v>
+      </c>
+      <c r="G35" t="str">
+        <v>Không</v>
+      </c>
+      <c r="H35" t="str">
+        <v>Có</v>
+      </c>
+      <c r="I35" t="str">
+        <v>#34 RENO | theo phòng (3p) | không nội thất | TB bàn giao: Không</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36" t="str">
+        <v>HD-MTX-35-RENO-RM-NONE</v>
+      </c>
+      <c r="C36" t="str">
+        <v>RENO</v>
+      </c>
+      <c r="D36" t="str">
+        <v>Không</v>
+      </c>
+      <c r="E36" t="str">
+        <v>THEO_PHONG (3)</v>
+      </c>
+      <c r="F36" t="str">
+        <v>Có (≥1 dòng)</v>
+      </c>
+      <c r="G36" t="str">
+        <v>Không</v>
+      </c>
+      <c r="H36" t="str">
+        <v>Có</v>
+      </c>
+      <c r="I36" t="str">
+        <v>#35 RENO | theo phòng (3p) | không nội thất | TB bàn giao: Không</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37" t="str">
+        <v>HD-MTX-36-RENO-RM-BASIC-HO</v>
+      </c>
+      <c r="C37" t="str">
+        <v>RENO</v>
+      </c>
+      <c r="D37" t="str">
+        <v>Có</v>
+      </c>
+      <c r="E37" t="str">
+        <v>THEO_PHONG (3)</v>
+      </c>
+      <c r="F37" t="str">
+        <v>Có (≥1 dòng)</v>
+      </c>
+      <c r="G37" t="str">
+        <v>Không</v>
+      </c>
+      <c r="H37" t="str">
+        <v>Có</v>
+      </c>
+      <c r="I37" t="str">
+        <v>#36 RENO | theo phòng (3p) | nội thất cơ bản | TB bàn giao: Có</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38" t="str">
+        <v>HD-MTX-37-RENO-RM-BASIC-HO</v>
+      </c>
+      <c r="C38" t="str">
+        <v>RENO</v>
+      </c>
+      <c r="D38" t="str">
+        <v>Có</v>
+      </c>
+      <c r="E38" t="str">
+        <v>THEO_PHONG (3)</v>
+      </c>
+      <c r="F38" t="str">
+        <v>Có (≥1 dòng)</v>
+      </c>
+      <c r="G38" t="str">
+        <v>Không</v>
+      </c>
+      <c r="H38" t="str">
+        <v>Có</v>
+      </c>
+      <c r="I38" t="str">
+        <v>#37 RENO | theo phòng (3p) | nội thất cơ bản | TB bàn giao: Có</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39" t="str">
+        <v>HD-MTX-38-RENO-RM-BASIC-HO</v>
+      </c>
+      <c r="C39" t="str">
+        <v>RENO</v>
+      </c>
+      <c r="D39" t="str">
+        <v>Có</v>
+      </c>
+      <c r="E39" t="str">
+        <v>THEO_PHONG (3)</v>
+      </c>
+      <c r="F39" t="str">
+        <v>Có (≥1 dòng)</v>
+      </c>
+      <c r="G39" t="str">
+        <v>Không</v>
+      </c>
+      <c r="H39" t="str">
+        <v>Có</v>
+      </c>
+      <c r="I39" t="str">
+        <v>#38 RENO | theo phòng (3p) | nội thất cơ bản | TB bàn giao: Có</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="B40" t="str">
+        <v>HD-MTX-39-RENO-RM-BASIC-HO</v>
+      </c>
+      <c r="C40" t="str">
+        <v>RENO</v>
+      </c>
+      <c r="D40" t="str">
+        <v>Có</v>
+      </c>
+      <c r="E40" t="str">
+        <v>THEO_PHONG (3)</v>
+      </c>
+      <c r="F40" t="str">
+        <v>Có (≥1 dòng)</v>
+      </c>
+      <c r="G40" t="str">
+        <v>Không</v>
+      </c>
+      <c r="H40" t="str">
+        <v>Có</v>
+      </c>
+      <c r="I40" t="str">
+        <v>#39 RENO | theo phòng (3p) | nội thất cơ bản | TB bàn giao: Có</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="B41" t="str">
+        <v>HD-MTX-40-RENO-RM-BASIC-BUY</v>
+      </c>
+      <c r="C41" t="str">
+        <v>RENO</v>
+      </c>
+      <c r="D41" t="str">
+        <v>Không</v>
+      </c>
+      <c r="E41" t="str">
+        <v>THEO_PHONG (3)</v>
+      </c>
+      <c r="F41" t="str">
+        <v>Có (≥1 dòng)</v>
+      </c>
+      <c r="G41" t="str">
+        <v>Có</v>
+      </c>
+      <c r="H41" t="str">
+        <v>Có</v>
+      </c>
+      <c r="I41" t="str">
+        <v>#40 RENO | theo phòng (3p) | nội thất cơ bản | TB bàn giao: Không</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>41</v>
+      </c>
+      <c r="B42" t="str">
+        <v>HD-MTX-41-RENO-RM-BASIC-BUY</v>
+      </c>
+      <c r="C42" t="str">
+        <v>RENO</v>
+      </c>
+      <c r="D42" t="str">
+        <v>Không</v>
+      </c>
+      <c r="E42" t="str">
+        <v>THEO_PHONG (4)</v>
+      </c>
+      <c r="F42" t="str">
+        <v>Có (≥1 dòng)</v>
+      </c>
+      <c r="G42" t="str">
+        <v>Có</v>
+      </c>
+      <c r="H42" t="str">
+        <v>Có</v>
+      </c>
+      <c r="I42" t="str">
+        <v>#41 RENO | theo phòng (4p) | nội thất cơ bản | TB bàn giao: Không</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>42</v>
+      </c>
+      <c r="B43" t="str">
+        <v>HD-MTX-42-RENO-RM-BASIC-BUY</v>
+      </c>
+      <c r="C43" t="str">
+        <v>RENO</v>
+      </c>
+      <c r="D43" t="str">
+        <v>Không</v>
+      </c>
+      <c r="E43" t="str">
+        <v>THEO_PHONG (3)</v>
+      </c>
+      <c r="F43" t="str">
+        <v>Có (≥1 dòng)</v>
+      </c>
+      <c r="G43" t="str">
+        <v>Có</v>
+      </c>
+      <c r="H43" t="str">
+        <v>Có</v>
+      </c>
+      <c r="I43" t="str">
+        <v>#42 RENO | theo phòng (3p) | nội thất cơ bản | TB bàn giao: Không</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>43</v>
+      </c>
+      <c r="B44" t="str">
+        <v>HD-MTX-43-RENO-RM-BASIC-BUY</v>
+      </c>
+      <c r="C44" t="str">
+        <v>RENO</v>
+      </c>
+      <c r="D44" t="str">
+        <v>Không</v>
+      </c>
+      <c r="E44" t="str">
+        <v>THEO_PHONG (4)</v>
+      </c>
+      <c r="F44" t="str">
+        <v>Có (≥1 dòng)</v>
+      </c>
+      <c r="G44" t="str">
+        <v>Có</v>
+      </c>
+      <c r="H44" t="str">
+        <v>Có</v>
+      </c>
+      <c r="I44" t="str">
+        <v>#43 RENO | theo phòng (4p) | nội thất cơ bản | TB bàn giao: Không</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>44</v>
+      </c>
+      <c r="B45" t="str">
+        <v>HD-MTX-44-RENO-RM-FULL</v>
+      </c>
+      <c r="C45" t="str">
+        <v>RENO</v>
+      </c>
+      <c r="D45" t="str">
+        <v>Có</v>
+      </c>
+      <c r="E45" t="str">
+        <v>THEO_PHONG (4)</v>
+      </c>
+      <c r="F45" t="str">
+        <v>Có (≥1 dòng)</v>
+      </c>
+      <c r="G45" t="str">
+        <v>Có</v>
+      </c>
+      <c r="H45" t="str">
+        <v>Có</v>
+      </c>
+      <c r="I45" t="str">
+        <v>#44 RENO | theo phòng (4p) | full nội thất | TB bàn giao: Có</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>45</v>
+      </c>
+      <c r="B46" t="str">
+        <v>HD-MTX-45-RENO-RM-FULL</v>
+      </c>
+      <c r="C46" t="str">
+        <v>RENO</v>
+      </c>
+      <c r="D46" t="str">
+        <v>Có</v>
+      </c>
+      <c r="E46" t="str">
+        <v>THEO_PHONG (4)</v>
+      </c>
+      <c r="F46" t="str">
+        <v>Có (≥1 dòng)</v>
+      </c>
+      <c r="G46" t="str">
+        <v>Có</v>
+      </c>
+      <c r="H46" t="str">
+        <v>Có</v>
+      </c>
+      <c r="I46" t="str">
+        <v>#45 RENO | theo phòng (4p) | full nội thất | TB bàn giao: Có</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>46</v>
+      </c>
+      <c r="B47" t="str">
+        <v>HD-MTX-46-RENO-RM-FULL</v>
+      </c>
+      <c r="C47" t="str">
+        <v>RENO</v>
+      </c>
+      <c r="D47" t="str">
+        <v>Có</v>
+      </c>
+      <c r="E47" t="str">
+        <v>THEO_PHONG (4)</v>
+      </c>
+      <c r="F47" t="str">
+        <v>Có (≥1 dòng)</v>
+      </c>
+      <c r="G47" t="str">
+        <v>Có</v>
+      </c>
+      <c r="H47" t="str">
+        <v>Có</v>
+      </c>
+      <c r="I47" t="str">
+        <v>#46 RENO | theo phòng (4p) | full nội thất | TB bàn giao: Có</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>47</v>
+      </c>
+      <c r="B48" t="str">
+        <v>HD-MTX-47-RENO-RM-FULL</v>
+      </c>
+      <c r="C48" t="str">
+        <v>RENO</v>
+      </c>
+      <c r="D48" t="str">
+        <v>Có</v>
+      </c>
+      <c r="E48" t="str">
+        <v>THEO_PHONG (4)</v>
+      </c>
+      <c r="F48" t="str">
+        <v>Có (≥1 dòng)</v>
+      </c>
+      <c r="G48" t="str">
+        <v>Có</v>
+      </c>
+      <c r="H48" t="str">
+        <v>Có</v>
+      </c>
+      <c r="I48" t="str">
+        <v>#47 RENO | theo phòng (4p) | full nội thất | TB bàn giao: Có</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>48</v>
+      </c>
+      <c r="B49" t="str">
+        <v>HD-MTX-48-RENO-RM-HO-BUY</v>
+      </c>
+      <c r="C49" t="str">
+        <v>RENO</v>
+      </c>
+      <c r="D49" t="str">
+        <v>Có</v>
+      </c>
+      <c r="E49" t="str">
+        <v>THEO_PHONG (3)</v>
+      </c>
+      <c r="F49" t="str">
+        <v>Có (≥1 dòng)</v>
+      </c>
+      <c r="G49" t="str">
+        <v>Có</v>
+      </c>
+      <c r="H49" t="str">
+        <v>Có</v>
+      </c>
+      <c r="I49" t="str">
+        <v>#48 RENO | theo phòng (3p) | nội thất cơ bản | TB bàn giao: Có</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>49</v>
+      </c>
+      <c r="B50" t="str">
+        <v>HD-MTX-49-RENO-RM-HO-BUY</v>
+      </c>
+      <c r="C50" t="str">
+        <v>RENO</v>
+      </c>
+      <c r="D50" t="str">
+        <v>Có</v>
+      </c>
+      <c r="E50" t="str">
+        <v>THEO_PHONG (3)</v>
+      </c>
+      <c r="F50" t="str">
+        <v>Có (≥1 dòng)</v>
+      </c>
+      <c r="G50" t="str">
+        <v>Có</v>
+      </c>
+      <c r="H50" t="str">
+        <v>Có</v>
+      </c>
+      <c r="I50" t="str">
+        <v>#49 RENO | theo phòng (3p) | nội thất cơ bản | TB bàn giao: Có</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>50</v>
+      </c>
+      <c r="B51" t="str">
+        <v>HD-MTX-50-RENO-RM-HO-BUY</v>
+      </c>
+      <c r="C51" t="str">
+        <v>RENO</v>
+      </c>
+      <c r="D51" t="str">
+        <v>Có</v>
+      </c>
+      <c r="E51" t="str">
+        <v>THEO_PHONG (3)</v>
+      </c>
+      <c r="F51" t="str">
+        <v>Có (≥1 dòng)</v>
+      </c>
+      <c r="G51" t="str">
+        <v>Có</v>
+      </c>
+      <c r="H51" t="str">
+        <v>Có</v>
+      </c>
+      <c r="I51" t="str">
+        <v>#50 RENO | theo phòng (3p) | nội thất cơ bản | TB bàn giao: Có</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>Tổng: 50 HĐ onboarding (nguyên căn full/cơ bản/không NT + theo phòng cơ bản/không NT).</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
         <v>NORENO: import đợt 1 xong → tự gửi Host. RENO: cần import đợt 2.</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>RENO bắt buộc ≥1 hạng mục cải tạo ở sheet 3 trước khi gửi Host.</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="str">
-        <v>#11–#14: demo full NT — nguyên căn / theo phòng (mỗi phòng ≥ 1 Quạt + 1 Giường).</v>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>Zone chỉ gồm quận trong ZoneDataSeeder: Q1, Q3, Bình Thạnh, Gò Vấp, Phú Nhuận, Cầu Giấy.</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>Catalog thiết bị / hạng mục cải tạo: MasterDataSeeder.</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I20"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I56"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -944,8 +1983,8 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B13"/>
   <cols>
-    <col min="1" max="1" width="26.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="1" max="1" width="28.83203125" customWidth="1"/>
+    <col min="2" max="2" width="40.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1002,11 +2041,6 @@
       </c>
       <c r="B7" t="str">
         <v>Quạt điện / quạt trần</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v/>
       </c>
     </row>
     <row r="9">
@@ -1058,23 +2092,23 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O15"/>
+  <dimension ref="A1:O51"/>
   <cols>
-    <col min="1" max="1" width="16.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="20.83203125" customWidth="1"/>
-    <col min="4" max="4" width="16.83203125" customWidth="1"/>
-    <col min="5" max="5" width="18.83203125" customWidth="1"/>
-    <col min="6" max="6" width="18.83203125" customWidth="1"/>
-    <col min="7" max="7" width="17.83203125" customWidth="1"/>
-    <col min="8" max="8" width="18.83203125" customWidth="1"/>
-    <col min="9" max="9" width="16.83203125" customWidth="1"/>
-    <col min="10" max="10" width="17.83203125" customWidth="1"/>
-    <col min="11" max="11" width="16.83203125" customWidth="1"/>
-    <col min="12" max="12" width="18.83203125" customWidth="1"/>
-    <col min="13" max="13" width="16.83203125" customWidth="1"/>
-    <col min="14" max="14" width="17.83203125" customWidth="1"/>
-    <col min="15" max="15" width="18.83203125" customWidth="1"/>
+    <col min="1" max="1" width="13.83203125" customWidth="1"/>
+    <col min="2" max="2" width="13.83203125" customWidth="1"/>
+    <col min="3" max="3" width="18.83203125" customWidth="1"/>
+    <col min="4" max="4" width="12.83203125" customWidth="1"/>
+    <col min="5" max="5" width="16.83203125" customWidth="1"/>
+    <col min="6" max="6" width="16.83203125" customWidth="1"/>
+    <col min="7" max="7" width="15.83203125" customWidth="1"/>
+    <col min="8" max="8" width="16.83203125" customWidth="1"/>
+    <col min="9" max="9" width="14.83203125" customWidth="1"/>
+    <col min="10" max="10" width="15.83203125" customWidth="1"/>
+    <col min="11" max="11" width="13.83203125" customWidth="1"/>
+    <col min="12" max="12" width="16.83203125" customWidth="1"/>
+    <col min="13" max="13" width="14.83203125" customWidth="1"/>
+    <col min="14" max="14" width="15.83203125" customWidth="1"/>
+    <col min="15" max="15" width="16.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,10 +2160,10 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>HD-MTX-01-NORENO-NOFURN</v>
+        <v>HD-MTX-01-NORENO-WH-NONE</v>
       </c>
       <c r="B2" t="str">
-        <v>MTX#01 NORENO trống</v>
+        <v>MTX#01 NGUYEN_CAN NONE</v>
       </c>
       <c r="C2" t="str">
         <v>1 Ma Trận Quận 1</v>
@@ -1141,151 +2175,151 @@
         <v>TP. Hồ Chí Minh</v>
       </c>
       <c r="F2">
-        <v>50</v>
+        <v>104</v>
       </c>
       <c r="G2">
-        <v>8.4</v>
+        <v>17.6</v>
       </c>
       <c r="H2">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K2" t="str">
         <v>Nguyễn Văn A</v>
       </c>
       <c r="L2">
-        <v>150000000</v>
+        <v>233000000</v>
       </c>
       <c r="M2" t="str">
         <v>2026-03-01</v>
       </c>
       <c r="N2" t="str">
-        <v>2027-02-28</v>
+        <v>2028-04-01</v>
       </c>
       <c r="O2" t="str">
-        <v>Ma trận #1 — NORENO, không TB bàn giao, gửi Host sau đợt 1.</v>
+        <v>Ma trận #1 — NORENO | nguyên căn | không nội thất | TB bàn giao: Không | không đợt 2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>HD-MTX-02-NORENO-FURN</v>
+        <v>HD-MTX-02-NORENO-WH-NONE</v>
       </c>
       <c r="B3" t="str">
-        <v>MTX#02 NORENO có TB</v>
+        <v>MTX#02 NGUYEN_CAN NONE</v>
       </c>
       <c r="C3" t="str">
-        <v>2 Ma Trận Quận 1</v>
+        <v>2 Ma Trận Quận 3</v>
       </c>
       <c r="D3" t="str">
-        <v>Quận 1</v>
+        <v>Quận 3</v>
       </c>
       <c r="E3" t="str">
         <v>TP. Hồ Chí Minh</v>
       </c>
       <c r="F3">
-        <v>65</v>
+        <v>123</v>
       </c>
       <c r="G3">
-        <v>9.5</v>
+        <v>19.5</v>
       </c>
       <c r="H3">
-        <v>6.8</v>
+        <v>6.3</v>
       </c>
       <c r="I3">
         <v>1</v>
       </c>
       <c r="J3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K3" t="str">
         <v>Trần Thị B</v>
       </c>
       <c r="L3">
-        <v>180000000</v>
+        <v>266000000</v>
       </c>
       <c r="M3" t="str">
-        <v>2026-03-01</v>
+        <v>2026-04-01</v>
       </c>
       <c r="N3" t="str">
-        <v>2027-02-28</v>
+        <v>2028-06-01</v>
       </c>
       <c r="O3" t="str">
-        <v>Ma trận #2 — NORENO, có TB bàn giao, gửi Host sau đợt 1.</v>
+        <v>Ma trận #2 — NORENO | nguyên căn | không nội thất | TB bàn giao: Không | không đợt 2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>HD-MTX-03-RENO-WH-NOFURN</v>
+        <v>HD-MTX-03-NORENO-WH-NONE</v>
       </c>
       <c r="B4" t="str">
-        <v>MTX#03 NGUYEN_CAN cải tạo</v>
+        <v>MTX#03 NGUYEN_CAN NONE</v>
       </c>
       <c r="C4" t="str">
-        <v>3 Ma Trận Quận 3</v>
+        <v>3 Ma Trận Bình Thạnh</v>
       </c>
       <c r="D4" t="str">
-        <v>Quận 3</v>
+        <v>Bình Thạnh</v>
       </c>
       <c r="E4" t="str">
         <v>TP. Hồ Chí Minh</v>
       </c>
       <c r="F4">
-        <v>80</v>
+        <v>97</v>
       </c>
       <c r="G4">
-        <v>10.6</v>
+        <v>14.5</v>
       </c>
       <c r="H4">
-        <v>7.5</v>
+        <v>6.7</v>
       </c>
       <c r="I4">
         <v>2</v>
       </c>
       <c r="J4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K4" t="str">
         <v>Lê Văn C</v>
       </c>
       <c r="L4">
-        <v>220000000</v>
+        <v>224000000</v>
       </c>
       <c r="M4" t="str">
-        <v>2026-04-01</v>
+        <v>2026-05-01</v>
       </c>
       <c r="N4" t="str">
-        <v>2028-03-31</v>
+        <v>2028-08-01</v>
       </c>
       <c r="O4" t="str">
-        <v>Ma trận #3 — RENO NGUYEN_CAN, không TB bàn giao, có cải tạo, không mua TB.</v>
+        <v>Ma trận #3 — NORENO | nguyên căn | không nội thất | TB bàn giao: Không | không đợt 2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>HD-MTX-04-RENO-WH-EQUIP</v>
+        <v>HD-MTX-04-NORENO-WH-NONE</v>
       </c>
       <c r="B5" t="str">
-        <v>MTX#04 NGUYEN_CAN mua TB</v>
+        <v>MTX#04 NGUYEN_CAN NONE</v>
       </c>
       <c r="C5" t="str">
-        <v>4 Ma Trận Quận 3</v>
+        <v>4 Ma Trận Gò Vấp</v>
       </c>
       <c r="D5" t="str">
-        <v>Quận 3</v>
+        <v>Gò Vấp</v>
       </c>
       <c r="E5" t="str">
         <v>TP. Hồ Chí Minh</v>
       </c>
       <c r="F5">
-        <v>70</v>
+        <v>116</v>
       </c>
       <c r="G5">
-        <v>9.9</v>
+        <v>16.3</v>
       </c>
       <c r="H5">
         <v>7.1</v>
@@ -1294,192 +2328,192 @@
         <v>1</v>
       </c>
       <c r="J5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K5" t="str">
         <v>Phạm Thị D</v>
       </c>
       <c r="L5">
-        <v>200000000</v>
+        <v>257000000</v>
       </c>
       <c r="M5" t="str">
-        <v>2026-04-01</v>
+        <v>2026-06-01</v>
       </c>
       <c r="N5" t="str">
-        <v>2028-03-31</v>
+        <v>2028-10-01</v>
       </c>
       <c r="O5" t="str">
-        <v>Ma trận #4 — RENO NGUYEN_CAN, không TB bàn giao, cải tạo + mua TB.</v>
+        <v>Ma trận #4 — NORENO | nguyên căn | không nội thất | TB bàn giao: Không | không đợt 2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>HD-MTX-05-RENO-WH-HO-NOFURN</v>
+        <v>HD-MTX-05-NORENO-WH-NONE</v>
       </c>
       <c r="B6" t="str">
-        <v>MTX#05 NGUYEN_CAN TB chủ</v>
+        <v>MTX#05 NGUYEN_CAN NONE</v>
       </c>
       <c r="C6" t="str">
-        <v>5 Ma Trận Bình Thạnh</v>
+        <v>5 Ma Trận Phú Nhuận</v>
       </c>
       <c r="D6" t="str">
-        <v>Bình Thạnh</v>
+        <v>Phú Nhuận</v>
       </c>
       <c r="E6" t="str">
         <v>TP. Hồ Chí Minh</v>
       </c>
       <c r="F6">
-        <v>90</v>
+        <v>135</v>
       </c>
       <c r="G6">
-        <v>11.2</v>
+        <v>24.5</v>
       </c>
       <c r="H6">
-        <v>8</v>
+        <v>5.5</v>
       </c>
       <c r="I6">
         <v>2</v>
       </c>
       <c r="J6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K6" t="str">
         <v>Hoàng Văn E</v>
       </c>
       <c r="L6">
-        <v>240000000</v>
+        <v>290000000</v>
       </c>
       <c r="M6" t="str">
-        <v>2026-05-01</v>
+        <v>2026-07-01</v>
       </c>
       <c r="N6" t="str">
-        <v>2028-04-30</v>
+        <v>2028-12-01</v>
       </c>
       <c r="O6" t="str">
-        <v>Ma trận #5 — RENO NGUYEN_CAN, có TB bàn giao, chỉ cải tạo.</v>
+        <v>Ma trận #5 — NORENO | nguyên căn | không nội thất | TB bàn giao: Không | không đợt 2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>HD-MTX-06-RENO-WH-HO-EQUIP</v>
+        <v>HD-MTX-06-NORENO-WH-BASIC</v>
       </c>
       <c r="B7" t="str">
-        <v>MTX#06 NGUYEN_CAN đủ</v>
+        <v>MTX#06 NGUYEN_CAN BASIC</v>
       </c>
       <c r="C7" t="str">
-        <v>6 Ma Trận Bình Thạnh</v>
+        <v>6 Ma Trận Cầu Giấy</v>
       </c>
       <c r="D7" t="str">
-        <v>Bình Thạnh</v>
+        <v>Cầu Giấy</v>
       </c>
       <c r="E7" t="str">
-        <v>TP. Hồ Chí Minh</v>
+        <v>Hà Nội</v>
       </c>
       <c r="F7">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="G7">
-        <v>11.8</v>
+        <v>18.5</v>
       </c>
       <c r="H7">
-        <v>8.5</v>
+        <v>5.9</v>
       </c>
       <c r="I7">
+        <v>1</v>
+      </c>
+      <c r="J7">
         <v>2</v>
-      </c>
-      <c r="J7">
-        <v>4</v>
       </c>
       <c r="K7" t="str">
         <v>Võ Thị F</v>
       </c>
       <c r="L7">
-        <v>260000000</v>
+        <v>248000000</v>
       </c>
       <c r="M7" t="str">
-        <v>2026-05-01</v>
+        <v>2026-08-01</v>
       </c>
       <c r="N7" t="str">
-        <v>2028-04-30</v>
+        <v>2029-02-01</v>
       </c>
       <c r="O7" t="str">
-        <v>Ma trận #6 — RENO NGUYEN_CAN đầy đủ: TB chủ + cải tạo + mua TB.</v>
+        <v>Ma trận #6 — NORENO | nguyên căn | nội thất cơ bản | TB bàn giao: Có | không đợt 2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>HD-MTX-07-RENO-RM-NOFURN</v>
+        <v>HD-MTX-07-NORENO-WH-BASIC</v>
       </c>
       <c r="B8" t="str">
-        <v>MTX#07 THEO_PHONG cải tạo</v>
+        <v>MTX#07 NGUYEN_CAN BASIC</v>
       </c>
       <c r="C8" t="str">
-        <v>7 Ma Trận Gò Vấp</v>
+        <v>7 Ma Trận Quận 1</v>
       </c>
       <c r="D8" t="str">
-        <v>Gò Vấp</v>
+        <v>Quận 1</v>
       </c>
       <c r="E8" t="str">
         <v>TP. Hồ Chí Minh</v>
       </c>
       <c r="F8">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="G8">
-        <v>10.2</v>
+        <v>15.9</v>
       </c>
       <c r="H8">
-        <v>7.4</v>
+        <v>6.3</v>
       </c>
       <c r="I8">
         <v>2</v>
       </c>
       <c r="J8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K8" t="str">
         <v>Đặng Văn G</v>
       </c>
       <c r="L8">
-        <v>210000000</v>
+        <v>281000000</v>
       </c>
       <c r="M8" t="str">
-        <v>2026-06-01</v>
+        <v>2026-09-01</v>
       </c>
       <c r="N8" t="str">
-        <v>2028-05-31</v>
+        <v>2029-04-01</v>
       </c>
       <c r="O8" t="str">
-        <v>Ma trận #7 — RENO THEO_PHONG 3 phòng, không TB bàn giao, chỉ cải tạo.</v>
+        <v>Ma trận #7 — NORENO | nguyên căn | nội thất cơ bản | TB bàn giao: Có | không đợt 2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>HD-MTX-08-RENO-RM-EQUIP</v>
+        <v>HD-MTX-08-NORENO-WH-BASIC</v>
       </c>
       <c r="B9" t="str">
-        <v>MTX#08 THEO_PHONG mua TB</v>
+        <v>MTX#08 NGUYEN_CAN BASIC</v>
       </c>
       <c r="C9" t="str">
-        <v>8 Ma Trận Gò Vấp</v>
+        <v>8 Ma Trận Quận 3</v>
       </c>
       <c r="D9" t="str">
-        <v>Gò Vấp</v>
+        <v>Quận 3</v>
       </c>
       <c r="E9" t="str">
         <v>TP. Hồ Chí Minh</v>
       </c>
       <c r="F9">
-        <v>78</v>
+        <v>119</v>
       </c>
       <c r="G9">
-        <v>10.4</v>
+        <v>17.8</v>
       </c>
       <c r="H9">
-        <v>7.5</v>
+        <v>6.7</v>
       </c>
       <c r="I9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J9">
         <v>4</v>
@@ -1488,136 +2522,136 @@
         <v>Bùi Thị H</v>
       </c>
       <c r="L9">
-        <v>215000000</v>
+        <v>250000000</v>
       </c>
       <c r="M9" t="str">
-        <v>2026-06-01</v>
+        <v>2026-10-01</v>
       </c>
       <c r="N9" t="str">
-        <v>2028-05-31</v>
+        <v>2029-06-01</v>
       </c>
       <c r="O9" t="str">
-        <v>Ma trận #8 — RENO THEO_PHONG 3 phòng, không TB chủ, cải tạo + mua TB.</v>
+        <v>Ma trận #8 — NORENO | nguyên căn | nội thất cơ bản | TB bàn giao: Có | không đợt 2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>HD-MTX-09-RENO-RM-HO-NOFURN</v>
+        <v>HD-MTX-09-NORENO-WH-BASIC</v>
       </c>
       <c r="B10" t="str">
-        <v>MTX#09 THEO_PHONG TB chủ</v>
+        <v>MTX#09 NGUYEN_CAN BASIC</v>
       </c>
       <c r="C10" t="str">
-        <v>9 Ma Trận Phú Nhuận</v>
+        <v>9 Ma Trận Bình Thạnh</v>
       </c>
       <c r="D10" t="str">
-        <v>Phú Nhuận</v>
+        <v>Bình Thạnh</v>
       </c>
       <c r="E10" t="str">
         <v>TP. Hồ Chí Minh</v>
       </c>
       <c r="F10">
-        <v>72</v>
+        <v>93</v>
       </c>
       <c r="G10">
-        <v>10</v>
+        <v>13.1</v>
       </c>
       <c r="H10">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="I10">
         <v>2</v>
       </c>
       <c r="J10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K10" t="str">
         <v>Ngô Văn I</v>
       </c>
       <c r="L10">
-        <v>205000000</v>
+        <v>208000000</v>
       </c>
       <c r="M10" t="str">
-        <v>2026-07-01</v>
+        <v>2026-03-01</v>
       </c>
       <c r="N10" t="str">
-        <v>2028-06-30</v>
+        <v>2028-12-01</v>
       </c>
       <c r="O10" t="str">
-        <v>Ma trận #9 — RENO THEO_PHONG 3 phòng, có TB chủ, chỉ cải tạo.</v>
+        <v>Ma trận #9 — NORENO | nguyên căn | nội thất cơ bản | TB bàn giao: Có | không đợt 2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>HD-MTX-10-RENO-RM-HO-EQUIP</v>
+        <v>HD-MTX-10-NORENO-WH-BASIC</v>
       </c>
       <c r="B11" t="str">
-        <v>MTX#10 THEO_PHONG đủ</v>
+        <v>MTX#10 NGUYEN_CAN BASIC</v>
       </c>
       <c r="C11" t="str">
-        <v>10 Ma Trận Phú Nhuận</v>
+        <v>10 Ma Trận Gò Vấp</v>
       </c>
       <c r="D11" t="str">
-        <v>Phú Nhuận</v>
+        <v>Gò Vấp</v>
       </c>
       <c r="E11" t="str">
         <v>TP. Hồ Chí Minh</v>
       </c>
       <c r="F11">
-        <v>84</v>
+        <v>112</v>
       </c>
       <c r="G11">
-        <v>10.8</v>
+        <v>20.4</v>
       </c>
       <c r="H11">
-        <v>7.8</v>
+        <v>5.5</v>
       </c>
       <c r="I11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K11" t="str">
         <v>Dương Thị K</v>
       </c>
       <c r="L11">
-        <v>230000000</v>
+        <v>241000000</v>
       </c>
       <c r="M11" t="str">
-        <v>2026-07-01</v>
+        <v>2026-04-01</v>
       </c>
       <c r="N11" t="str">
-        <v>2028-06-30</v>
+        <v>2029-02-01</v>
       </c>
       <c r="O11" t="str">
-        <v>Ma trận #10 — RENO THEO_PHONG 3 phòng đầy đủ.</v>
+        <v>Ma trận #10 — NORENO | nguyên căn | nội thất cơ bản | TB bàn giao: Có | không đợt 2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>HD-MTX-11-NORENO-FULL</v>
+        <v>HD-MTX-11-NORENO-WH-FULL</v>
       </c>
       <c r="B12" t="str">
-        <v>MTX#11 NORENO full NT</v>
+        <v>MTX#11 NGUYEN_CAN FULL</v>
       </c>
       <c r="C12" t="str">
-        <v>11 Ma Trận Tân Bình</v>
+        <v>11 Ma Trận Phú Nhuận</v>
       </c>
       <c r="D12" t="str">
-        <v>Tân Bình</v>
+        <v>Phú Nhuận</v>
       </c>
       <c r="E12" t="str">
         <v>TP. Hồ Chí Minh</v>
       </c>
       <c r="F12">
-        <v>95</v>
+        <v>131</v>
       </c>
       <c r="G12">
-        <v>11.5</v>
+        <v>22.2</v>
       </c>
       <c r="H12">
-        <v>8.3</v>
+        <v>5.9</v>
       </c>
       <c r="I12">
         <v>2</v>
@@ -1629,177 +2663,1869 @@
         <v>Lý Văn L</v>
       </c>
       <c r="L12">
-        <v>250000000</v>
+        <v>274000000</v>
       </c>
       <c r="M12" t="str">
-        <v>2026-08-01</v>
+        <v>2026-05-01</v>
       </c>
       <c r="N12" t="str">
-        <v>2028-07-31</v>
+        <v>2029-04-01</v>
       </c>
       <c r="O12" t="str">
-        <v>Ma trận #11 — NORENO nguyên căn, nội thất đầy đủ từ chủ (bàn giao).</v>
+        <v>Ma trận #11 — NORENO | nguyên căn | full nội thất | TB bàn giao: Có | không đợt 2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>HD-MTX-12-RENO-WH-FULL</v>
+        <v>HD-MTX-12-NORENO-WH-FULL</v>
       </c>
       <c r="B13" t="str">
-        <v>MTX#12 NGUYEN_CAN full NT</v>
+        <v>MTX#12 NGUYEN_CAN FULL</v>
       </c>
       <c r="C13" t="str">
-        <v>12 Ma Trận Tân Bình</v>
+        <v>12 Ma Trận Cầu Giấy</v>
       </c>
       <c r="D13" t="str">
-        <v>Tân Bình</v>
+        <v>Cầu Giấy</v>
       </c>
       <c r="E13" t="str">
-        <v>TP. Hồ Chí Minh</v>
+        <v>Hà Nội</v>
       </c>
       <c r="F13">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="G13">
-        <v>12.4</v>
+        <v>16.7</v>
       </c>
       <c r="H13">
-        <v>8.9</v>
+        <v>6.3</v>
       </c>
       <c r="I13">
+        <v>1</v>
+      </c>
+      <c r="J13">
         <v>2</v>
-      </c>
-      <c r="J13">
-        <v>4</v>
       </c>
       <c r="K13" t="str">
         <v>Mai Thị M</v>
       </c>
       <c r="L13">
-        <v>280000000</v>
+        <v>232000000</v>
       </c>
       <c r="M13" t="str">
-        <v>2026-08-01</v>
+        <v>2026-06-01</v>
       </c>
       <c r="N13" t="str">
-        <v>2028-07-31</v>
+        <v>2028-06-01</v>
       </c>
       <c r="O13" t="str">
-        <v>Ma trận #12 — RENO NGUYEN_CAN nội thất đầy đủ: TB chủ + cải tạo + mua TB khu vực chung.</v>
+        <v>Ma trận #12 — NORENO | nguyên căn | full nội thất | TB bàn giao: Có | không đợt 2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>HD-MTX-13-RENO-RM-FULL</v>
+        <v>HD-MTX-13-NORENO-WH-FULL</v>
       </c>
       <c r="B14" t="str">
-        <v>MTX#13 THEO_PHONG full NT</v>
+        <v>MTX#13 NGUYEN_CAN FULL</v>
       </c>
       <c r="C14" t="str">
-        <v>13 Ma Trận Thủ Đức</v>
+        <v>13 Ma Trận Quận 1</v>
       </c>
       <c r="D14" t="str">
-        <v>Thủ Đức</v>
+        <v>Quận 1</v>
       </c>
       <c r="E14" t="str">
         <v>TP. Hồ Chí Minh</v>
       </c>
       <c r="F14">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="G14">
-        <v>13</v>
+        <v>18.5</v>
       </c>
       <c r="H14">
-        <v>9.2</v>
+        <v>6.7</v>
       </c>
       <c r="I14">
+        <v>2</v>
+      </c>
+      <c r="J14">
         <v>3</v>
-      </c>
-      <c r="J14">
-        <v>6</v>
       </c>
       <c r="K14" t="str">
         <v>Phan Văn N</v>
       </c>
       <c r="L14">
-        <v>320000000</v>
+        <v>265000000</v>
       </c>
       <c r="M14" t="str">
-        <v>2026-09-01</v>
+        <v>2026-07-01</v>
       </c>
       <c r="N14" t="str">
-        <v>2028-08-31</v>
+        <v>2028-08-01</v>
       </c>
       <c r="O14" t="str">
-        <v>Ma trận #13 — RENO THEO_PHONG 4 phòng, mỗi phòng mua 1 Quạt + 1 Giường (+ ĐH/nóng lạnh).</v>
+        <v>Ma trận #13 — NORENO | nguyên căn | full nội thất | TB bàn giao: Có | không đợt 2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>HD-MTX-14-RENO-RM-BEDFAN</v>
+        <v>HD-MTX-14-NORENO-WH-FULL</v>
       </c>
       <c r="B15" t="str">
-        <v>MTX#14 THEO_PHONG giường+quạt</v>
+        <v>MTX#14 NGUYEN_CAN FULL</v>
       </c>
       <c r="C15" t="str">
-        <v>14 Ma Trận Thủ Đức</v>
+        <v>14 Ma Trận Quận 3</v>
       </c>
       <c r="D15" t="str">
-        <v>Thủ Đức</v>
+        <v>Quận 3</v>
       </c>
       <c r="E15" t="str">
         <v>TP. Hồ Chí Minh</v>
       </c>
       <c r="F15">
-        <v>90</v>
+        <v>115</v>
       </c>
       <c r="G15">
-        <v>11.2</v>
+        <v>16.2</v>
       </c>
       <c r="H15">
-        <v>8</v>
+        <v>7.1</v>
       </c>
       <c r="I15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K15" t="str">
         <v>Trịnh Thị O</v>
       </c>
       <c r="L15">
+        <v>298000000</v>
+      </c>
+      <c r="M15" t="str">
+        <v>2026-08-01</v>
+      </c>
+      <c r="N15" t="str">
+        <v>2028-10-01</v>
+      </c>
+      <c r="O15" t="str">
+        <v>Ma trận #14 — NORENO | nguyên căn | full nội thất | TB bàn giao: Có | không đợt 2</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>HD-MTX-15-NORENO-WH-FULL</v>
+      </c>
+      <c r="B16" t="str">
+        <v>MTX#15 NGUYEN_CAN FULL</v>
+      </c>
+      <c r="C16" t="str">
+        <v>15 Ma Trận Bình Thạnh</v>
+      </c>
+      <c r="D16" t="str">
+        <v>Bình Thạnh</v>
+      </c>
+      <c r="E16" t="str">
+        <v>TP. Hồ Chí Minh</v>
+      </c>
+      <c r="F16">
+        <v>89</v>
+      </c>
+      <c r="G16">
+        <v>16.2</v>
+      </c>
+      <c r="H16">
+        <v>5.5</v>
+      </c>
+      <c r="I16">
+        <v>2</v>
+      </c>
+      <c r="J16">
+        <v>2</v>
+      </c>
+      <c r="K16" t="str">
+        <v>Huỳnh Văn P</v>
+      </c>
+      <c r="L16">
+        <v>256000000</v>
+      </c>
+      <c r="M16" t="str">
+        <v>2026-09-01</v>
+      </c>
+      <c r="N16" t="str">
+        <v>2028-12-01</v>
+      </c>
+      <c r="O16" t="str">
+        <v>Ma trận #15 — NORENO | nguyên căn | full nội thất | TB bàn giao: Có | không đợt 2</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>HD-MTX-16-RENO-WH-NONE</v>
+      </c>
+      <c r="B17" t="str">
+        <v>MTX#16 NGUYEN_CAN NONE</v>
+      </c>
+      <c r="C17" t="str">
+        <v>16 Ma Trận Gò Vấp</v>
+      </c>
+      <c r="D17" t="str">
+        <v>Gò Vấp</v>
+      </c>
+      <c r="E17" t="str">
+        <v>TP. Hồ Chí Minh</v>
+      </c>
+      <c r="F17">
+        <v>108</v>
+      </c>
+      <c r="G17">
+        <v>18.3</v>
+      </c>
+      <c r="H17">
+        <v>5.9</v>
+      </c>
+      <c r="I17">
+        <v>1</v>
+      </c>
+      <c r="J17">
+        <v>3</v>
+      </c>
+      <c r="K17" t="str">
+        <v>Nguyễn Văn A</v>
+      </c>
+      <c r="L17">
+        <v>225000000</v>
+      </c>
+      <c r="M17" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="N17" t="str">
+        <v>2029-02-01</v>
+      </c>
+      <c r="O17" t="str">
+        <v>Ma trận #16 — RENO | nguyên căn | không nội thất | TB bàn giao: Không | TB mua đ2: Không</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>HD-MTX-17-RENO-WH-NONE</v>
+      </c>
+      <c r="B18" t="str">
+        <v>MTX#17 NGUYEN_CAN NONE</v>
+      </c>
+      <c r="C18" t="str">
+        <v>17 Ma Trận Phú Nhuận</v>
+      </c>
+      <c r="D18" t="str">
+        <v>Phú Nhuận</v>
+      </c>
+      <c r="E18" t="str">
+        <v>TP. Hồ Chí Minh</v>
+      </c>
+      <c r="F18">
+        <v>127</v>
+      </c>
+      <c r="G18">
+        <v>20.2</v>
+      </c>
+      <c r="H18">
+        <v>6.3</v>
+      </c>
+      <c r="I18">
+        <v>2</v>
+      </c>
+      <c r="J18">
+        <v>4</v>
+      </c>
+      <c r="K18" t="str">
+        <v>Trần Thị B</v>
+      </c>
+      <c r="L18">
+        <v>258000000</v>
+      </c>
+      <c r="M18" t="str">
+        <v>2026-03-01</v>
+      </c>
+      <c r="N18" t="str">
+        <v>2028-08-01</v>
+      </c>
+      <c r="O18" t="str">
+        <v>Ma trận #17 — RENO | nguyên căn | không nội thất | TB bàn giao: Không | TB mua đ2: Không</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>HD-MTX-18-RENO-WH-NONE</v>
+      </c>
+      <c r="B19" t="str">
+        <v>MTX#18 NGUYEN_CAN NONE</v>
+      </c>
+      <c r="C19" t="str">
+        <v>18 Ma Trận Cầu Giấy</v>
+      </c>
+      <c r="D19" t="str">
+        <v>Cầu Giấy</v>
+      </c>
+      <c r="E19" t="str">
+        <v>Hà Nội</v>
+      </c>
+      <c r="F19">
+        <v>101</v>
+      </c>
+      <c r="G19">
+        <v>15.1</v>
+      </c>
+      <c r="H19">
+        <v>6.7</v>
+      </c>
+      <c r="I19">
+        <v>1</v>
+      </c>
+      <c r="J19">
+        <v>2</v>
+      </c>
+      <c r="K19" t="str">
+        <v>Lê Văn C</v>
+      </c>
+      <c r="L19">
+        <v>216000000</v>
+      </c>
+      <c r="M19" t="str">
+        <v>2026-04-01</v>
+      </c>
+      <c r="N19" t="str">
+        <v>2028-10-01</v>
+      </c>
+      <c r="O19" t="str">
+        <v>Ma trận #18 — RENO | nguyên căn | không nội thất | TB bàn giao: Không | TB mua đ2: Không</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>HD-MTX-19-RENO-WH-BASIC-HO</v>
+      </c>
+      <c r="B20" t="str">
+        <v>MTX#19 NGUYEN_CAN BASIC</v>
+      </c>
+      <c r="C20" t="str">
+        <v>19 Ma Trận Quận 1</v>
+      </c>
+      <c r="D20" t="str">
+        <v>Quận 1</v>
+      </c>
+      <c r="E20" t="str">
+        <v>TP. Hồ Chí Minh</v>
+      </c>
+      <c r="F20">
+        <v>120</v>
+      </c>
+      <c r="G20">
+        <v>16.9</v>
+      </c>
+      <c r="H20">
+        <v>7.1</v>
+      </c>
+      <c r="I20">
+        <v>2</v>
+      </c>
+      <c r="J20">
+        <v>3</v>
+      </c>
+      <c r="K20" t="str">
+        <v>Phạm Thị D</v>
+      </c>
+      <c r="L20">
+        <v>249000000</v>
+      </c>
+      <c r="M20" t="str">
+        <v>2026-05-01</v>
+      </c>
+      <c r="N20" t="str">
+        <v>2028-12-01</v>
+      </c>
+      <c r="O20" t="str">
+        <v>Ma trận #19 — RENO | nguyên căn | nội thất cơ bản | TB bàn giao: Có | TB mua đ2: Không</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>HD-MTX-20-RENO-WH-BASIC-HO</v>
+      </c>
+      <c r="B21" t="str">
+        <v>MTX#20 NGUYEN_CAN BASIC</v>
+      </c>
+      <c r="C21" t="str">
+        <v>20 Ma Trận Quận 3</v>
+      </c>
+      <c r="D21" t="str">
+        <v>Quận 3</v>
+      </c>
+      <c r="E21" t="str">
+        <v>TP. Hồ Chí Minh</v>
+      </c>
+      <c r="F21">
+        <v>139</v>
+      </c>
+      <c r="G21">
+        <v>25.3</v>
+      </c>
+      <c r="H21">
+        <v>5.5</v>
+      </c>
+      <c r="I21">
+        <v>1</v>
+      </c>
+      <c r="J21">
+        <v>4</v>
+      </c>
+      <c r="K21" t="str">
+        <v>Hoàng Văn E</v>
+      </c>
+      <c r="L21">
+        <v>282000000</v>
+      </c>
+      <c r="M21" t="str">
+        <v>2026-06-01</v>
+      </c>
+      <c r="N21" t="str">
+        <v>2029-02-01</v>
+      </c>
+      <c r="O21" t="str">
+        <v>Ma trận #20 — RENO | nguyên căn | nội thất cơ bản | TB bàn giao: Có | TB mua đ2: Không</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>HD-MTX-21-RENO-WH-BASIC-HO</v>
+      </c>
+      <c r="B22" t="str">
+        <v>MTX#21 NGUYEN_CAN BASIC</v>
+      </c>
+      <c r="C22" t="str">
+        <v>21 Ma Trận Bình Thạnh</v>
+      </c>
+      <c r="D22" t="str">
+        <v>Bình Thạnh</v>
+      </c>
+      <c r="E22" t="str">
+        <v>TP. Hồ Chí Minh</v>
+      </c>
+      <c r="F22">
+        <v>85</v>
+      </c>
+      <c r="G22">
+        <v>14.4</v>
+      </c>
+      <c r="H22">
+        <v>5.9</v>
+      </c>
+      <c r="I22">
+        <v>2</v>
+      </c>
+      <c r="J22">
+        <v>2</v>
+      </c>
+      <c r="K22" t="str">
+        <v>Võ Thị F</v>
+      </c>
+      <c r="L22">
         <v>240000000</v>
       </c>
-      <c r="M15" t="str">
+      <c r="M22" t="str">
+        <v>2026-07-01</v>
+      </c>
+      <c r="N22" t="str">
+        <v>2029-04-01</v>
+      </c>
+      <c r="O22" t="str">
+        <v>Ma trận #21 — RENO | nguyên căn | nội thất cơ bản | TB bàn giao: Có | TB mua đ2: Không</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>HD-MTX-22-RENO-WH-BASIC-BUY</v>
+      </c>
+      <c r="B23" t="str">
+        <v>MTX#22 NGUYEN_CAN BASIC</v>
+      </c>
+      <c r="C23" t="str">
+        <v>22 Ma Trận Gò Vấp</v>
+      </c>
+      <c r="D23" t="str">
+        <v>Gò Vấp</v>
+      </c>
+      <c r="E23" t="str">
+        <v>TP. Hồ Chí Minh</v>
+      </c>
+      <c r="F23">
+        <v>104</v>
+      </c>
+      <c r="G23">
+        <v>16.5</v>
+      </c>
+      <c r="H23">
+        <v>6.3</v>
+      </c>
+      <c r="I23">
+        <v>1</v>
+      </c>
+      <c r="J23">
+        <v>3</v>
+      </c>
+      <c r="K23" t="str">
+        <v>Đặng Văn G</v>
+      </c>
+      <c r="L23">
+        <v>273000000</v>
+      </c>
+      <c r="M23" t="str">
+        <v>2026-08-01</v>
+      </c>
+      <c r="N23" t="str">
+        <v>2029-06-01</v>
+      </c>
+      <c r="O23" t="str">
+        <v>Ma trận #22 — RENO | nguyên căn | nội thất cơ bản | TB bàn giao: Không | TB mua đ2: Có</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>HD-MTX-23-RENO-WH-BASIC-BUY</v>
+      </c>
+      <c r="B24" t="str">
+        <v>MTX#23 NGUYEN_CAN BASIC</v>
+      </c>
+      <c r="C24" t="str">
+        <v>23 Ma Trận Phú Nhuận</v>
+      </c>
+      <c r="D24" t="str">
+        <v>Phú Nhuận</v>
+      </c>
+      <c r="E24" t="str">
+        <v>TP. Hồ Chí Minh</v>
+      </c>
+      <c r="F24">
+        <v>123</v>
+      </c>
+      <c r="G24">
+        <v>18.4</v>
+      </c>
+      <c r="H24">
+        <v>6.7</v>
+      </c>
+      <c r="I24">
+        <v>2</v>
+      </c>
+      <c r="J24">
+        <v>4</v>
+      </c>
+      <c r="K24" t="str">
+        <v>Bùi Thị H</v>
+      </c>
+      <c r="L24">
+        <v>306000000</v>
+      </c>
+      <c r="M24" t="str">
         <v>2026-09-01</v>
       </c>
-      <c r="N15" t="str">
-        <v>2028-08-31</v>
-      </c>
-      <c r="O15" t="str">
-        <v>Ma trận #14 — RENO THEO_PHONG 5 phòng, mỗi phòng đúng 1 Quạt + 1 Giường.</v>
+      <c r="N24" t="str">
+        <v>2029-08-01</v>
+      </c>
+      <c r="O24" t="str">
+        <v>Ma trận #23 — RENO | nguyên căn | nội thất cơ bản | TB bàn giao: Không | TB mua đ2: Có</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>HD-MTX-24-RENO-WH-BASIC-BUY</v>
+      </c>
+      <c r="B25" t="str">
+        <v>MTX#24 NGUYEN_CAN BASIC</v>
+      </c>
+      <c r="C25" t="str">
+        <v>24 Ma Trận Cầu Giấy</v>
+      </c>
+      <c r="D25" t="str">
+        <v>Cầu Giấy</v>
+      </c>
+      <c r="E25" t="str">
+        <v>Hà Nội</v>
+      </c>
+      <c r="F25">
+        <v>97</v>
+      </c>
+      <c r="G25">
+        <v>13.7</v>
+      </c>
+      <c r="H25">
+        <v>7.1</v>
+      </c>
+      <c r="I25">
+        <v>1</v>
+      </c>
+      <c r="J25">
+        <v>2</v>
+      </c>
+      <c r="K25" t="str">
+        <v>Ngô Văn I</v>
+      </c>
+      <c r="L25">
+        <v>200000000</v>
+      </c>
+      <c r="M25" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="N25" t="str">
+        <v>2028-10-01</v>
+      </c>
+      <c r="O25" t="str">
+        <v>Ma trận #24 — RENO | nguyên căn | nội thất cơ bản | TB bàn giao: Không | TB mua đ2: Có</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>HD-MTX-25-RENO-WH-FULL</v>
+      </c>
+      <c r="B26" t="str">
+        <v>MTX#25 NGUYEN_CAN FULL</v>
+      </c>
+      <c r="C26" t="str">
+        <v>25 Ma Trận Quận 1</v>
+      </c>
+      <c r="D26" t="str">
+        <v>Quận 1</v>
+      </c>
+      <c r="E26" t="str">
+        <v>TP. Hồ Chí Minh</v>
+      </c>
+      <c r="F26">
+        <v>116</v>
+      </c>
+      <c r="G26">
+        <v>21.1</v>
+      </c>
+      <c r="H26">
+        <v>5.5</v>
+      </c>
+      <c r="I26">
+        <v>2</v>
+      </c>
+      <c r="J26">
+        <v>3</v>
+      </c>
+      <c r="K26" t="str">
+        <v>Dương Thị K</v>
+      </c>
+      <c r="L26">
+        <v>233000000</v>
+      </c>
+      <c r="M26" t="str">
+        <v>2026-03-01</v>
+      </c>
+      <c r="N26" t="str">
+        <v>2028-04-01</v>
+      </c>
+      <c r="O26" t="str">
+        <v>Ma trận #25 — RENO | nguyên căn | full nội thất | TB bàn giao: Có | TB mua đ2: Có</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>HD-MTX-26-RENO-WH-FULL</v>
+      </c>
+      <c r="B27" t="str">
+        <v>MTX#26 NGUYEN_CAN FULL</v>
+      </c>
+      <c r="C27" t="str">
+        <v>26 Ma Trận Quận 3</v>
+      </c>
+      <c r="D27" t="str">
+        <v>Quận 3</v>
+      </c>
+      <c r="E27" t="str">
+        <v>TP. Hồ Chí Minh</v>
+      </c>
+      <c r="F27">
+        <v>135</v>
+      </c>
+      <c r="G27">
+        <v>22.9</v>
+      </c>
+      <c r="H27">
+        <v>5.9</v>
+      </c>
+      <c r="I27">
+        <v>1</v>
+      </c>
+      <c r="J27">
+        <v>4</v>
+      </c>
+      <c r="K27" t="str">
+        <v>Lý Văn L</v>
+      </c>
+      <c r="L27">
+        <v>266000000</v>
+      </c>
+      <c r="M27" t="str">
+        <v>2026-04-01</v>
+      </c>
+      <c r="N27" t="str">
+        <v>2028-06-01</v>
+      </c>
+      <c r="O27" t="str">
+        <v>Ma trận #26 — RENO | nguyên căn | full nội thất | TB bàn giao: Có | TB mua đ2: Có</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>HD-MTX-27-RENO-WH-FULL</v>
+      </c>
+      <c r="B28" t="str">
+        <v>MTX#27 NGUYEN_CAN FULL</v>
+      </c>
+      <c r="C28" t="str">
+        <v>27 Ma Trận Bình Thạnh</v>
+      </c>
+      <c r="D28" t="str">
+        <v>Bình Thạnh</v>
+      </c>
+      <c r="E28" t="str">
+        <v>TP. Hồ Chí Minh</v>
+      </c>
+      <c r="F28">
+        <v>109</v>
+      </c>
+      <c r="G28">
+        <v>17.3</v>
+      </c>
+      <c r="H28">
+        <v>6.3</v>
+      </c>
+      <c r="I28">
+        <v>2</v>
+      </c>
+      <c r="J28">
+        <v>2</v>
+      </c>
+      <c r="K28" t="str">
+        <v>Mai Thị M</v>
+      </c>
+      <c r="L28">
+        <v>224000000</v>
+      </c>
+      <c r="M28" t="str">
+        <v>2026-05-01</v>
+      </c>
+      <c r="N28" t="str">
+        <v>2028-08-01</v>
+      </c>
+      <c r="O28" t="str">
+        <v>Ma trận #27 — RENO | nguyên căn | full nội thất | TB bàn giao: Có | TB mua đ2: Có</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>HD-MTX-28-RENO-WH-HO-NOBUY</v>
+      </c>
+      <c r="B29" t="str">
+        <v>MTX#28 NGUYEN_CAN NONE</v>
+      </c>
+      <c r="C29" t="str">
+        <v>28 Ma Trận Gò Vấp</v>
+      </c>
+      <c r="D29" t="str">
+        <v>Gò Vấp</v>
+      </c>
+      <c r="E29" t="str">
+        <v>TP. Hồ Chí Minh</v>
+      </c>
+      <c r="F29">
+        <v>100</v>
+      </c>
+      <c r="G29">
+        <v>14.9</v>
+      </c>
+      <c r="H29">
+        <v>6.7</v>
+      </c>
+      <c r="I29">
+        <v>1</v>
+      </c>
+      <c r="J29">
+        <v>3</v>
+      </c>
+      <c r="K29" t="str">
+        <v>Phan Văn N</v>
+      </c>
+      <c r="L29">
+        <v>257000000</v>
+      </c>
+      <c r="M29" t="str">
+        <v>2026-06-01</v>
+      </c>
+      <c r="N29" t="str">
+        <v>2028-10-01</v>
+      </c>
+      <c r="O29" t="str">
+        <v>Ma trận #28 — RENO | nguyên căn | không nội thất | TB bàn giao: Có | TB mua đ2: Không</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>HD-MTX-29-RENO-WH-HO-NOBUY</v>
+      </c>
+      <c r="B30" t="str">
+        <v>MTX#29 NGUYEN_CAN NONE</v>
+      </c>
+      <c r="C30" t="str">
+        <v>29 Ma Trận Phú Nhuận</v>
+      </c>
+      <c r="D30" t="str">
+        <v>Phú Nhuận</v>
+      </c>
+      <c r="E30" t="str">
+        <v>TP. Hồ Chí Minh</v>
+      </c>
+      <c r="F30">
+        <v>119</v>
+      </c>
+      <c r="G30">
+        <v>16.8</v>
+      </c>
+      <c r="H30">
+        <v>7.1</v>
+      </c>
+      <c r="I30">
+        <v>2</v>
+      </c>
+      <c r="J30">
+        <v>4</v>
+      </c>
+      <c r="K30" t="str">
+        <v>Trịnh Thị O</v>
+      </c>
+      <c r="L30">
+        <v>290000000</v>
+      </c>
+      <c r="M30" t="str">
+        <v>2026-07-01</v>
+      </c>
+      <c r="N30" t="str">
+        <v>2028-12-01</v>
+      </c>
+      <c r="O30" t="str">
+        <v>Ma trận #29 — RENO | nguyên căn | không nội thất | TB bàn giao: Có | TB mua đ2: Không</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>HD-MTX-30-RENO-WH-HO-BUY</v>
+      </c>
+      <c r="B31" t="str">
+        <v>MTX#30 NGUYEN_CAN BASIC</v>
+      </c>
+      <c r="C31" t="str">
+        <v>30 Ma Trận Cầu Giấy</v>
+      </c>
+      <c r="D31" t="str">
+        <v>Cầu Giấy</v>
+      </c>
+      <c r="E31" t="str">
+        <v>Hà Nội</v>
+      </c>
+      <c r="F31">
+        <v>93</v>
+      </c>
+      <c r="G31">
+        <v>16.9</v>
+      </c>
+      <c r="H31">
+        <v>5.5</v>
+      </c>
+      <c r="I31">
+        <v>1</v>
+      </c>
+      <c r="J31">
+        <v>2</v>
+      </c>
+      <c r="K31" t="str">
+        <v>Huỳnh Văn P</v>
+      </c>
+      <c r="L31">
+        <v>248000000</v>
+      </c>
+      <c r="M31" t="str">
+        <v>2026-08-01</v>
+      </c>
+      <c r="N31" t="str">
+        <v>2029-02-01</v>
+      </c>
+      <c r="O31" t="str">
+        <v>Ma trận #30 — RENO | nguyên căn | nội thất cơ bản | TB bàn giao: Có | TB mua đ2: Có</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>HD-MTX-31-RENO-WH-HO-BUY</v>
+      </c>
+      <c r="B32" t="str">
+        <v>MTX#31 NGUYEN_CAN BASIC</v>
+      </c>
+      <c r="C32" t="str">
+        <v>31 Ma Trận Quận 1</v>
+      </c>
+      <c r="D32" t="str">
+        <v>Quận 1</v>
+      </c>
+      <c r="E32" t="str">
+        <v>TP. Hồ Chí Minh</v>
+      </c>
+      <c r="F32">
+        <v>112</v>
+      </c>
+      <c r="G32">
+        <v>19</v>
+      </c>
+      <c r="H32">
+        <v>5.9</v>
+      </c>
+      <c r="I32">
+        <v>2</v>
+      </c>
+      <c r="J32">
+        <v>3</v>
+      </c>
+      <c r="K32" t="str">
+        <v>Nguyễn Văn A</v>
+      </c>
+      <c r="L32">
+        <v>281000000</v>
+      </c>
+      <c r="M32" t="str">
+        <v>2026-09-01</v>
+      </c>
+      <c r="N32" t="str">
+        <v>2029-04-01</v>
+      </c>
+      <c r="O32" t="str">
+        <v>Ma trận #31 — RENO | nguyên căn | nội thất cơ bản | TB bàn giao: Có | TB mua đ2: Có</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>HD-MTX-32-RENO-RM-NONE</v>
+      </c>
+      <c r="B33" t="str">
+        <v>MTX#32 THEO_PHONG NONE</v>
+      </c>
+      <c r="C33" t="str">
+        <v>32 Ma Trận Quận 3</v>
+      </c>
+      <c r="D33" t="str">
+        <v>Quận 3</v>
+      </c>
+      <c r="E33" t="str">
+        <v>TP. Hồ Chí Minh</v>
+      </c>
+      <c r="F33">
+        <v>112</v>
+      </c>
+      <c r="G33">
+        <v>17.8</v>
+      </c>
+      <c r="H33">
+        <v>6.3</v>
+      </c>
+      <c r="I33">
+        <v>2</v>
+      </c>
+      <c r="J33">
+        <v>4</v>
+      </c>
+      <c r="K33" t="str">
+        <v>Trần Thị B</v>
+      </c>
+      <c r="L33">
+        <v>226000000</v>
+      </c>
+      <c r="M33" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="N33" t="str">
+        <v>2029-06-01</v>
+      </c>
+      <c r="O33" t="str">
+        <v>Ma trận #32 — RENO | theo phòng (3p) | không nội thất | TB bàn giao: Không | TB mua đ2: Không</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>HD-MTX-33-RENO-RM-NONE</v>
+      </c>
+      <c r="B34" t="str">
+        <v>MTX#33 THEO_PHONG NONE</v>
+      </c>
+      <c r="C34" t="str">
+        <v>33 Ma Trận Bình Thạnh</v>
+      </c>
+      <c r="D34" t="str">
+        <v>Bình Thạnh</v>
+      </c>
+      <c r="E34" t="str">
+        <v>TP. Hồ Chí Minh</v>
+      </c>
+      <c r="F34">
+        <v>115</v>
+      </c>
+      <c r="G34">
+        <v>17.2</v>
+      </c>
+      <c r="H34">
+        <v>6.7</v>
+      </c>
+      <c r="I34">
+        <v>3</v>
+      </c>
+      <c r="J34">
+        <v>4</v>
+      </c>
+      <c r="K34" t="str">
+        <v>Lê Văn C</v>
+      </c>
+      <c r="L34">
+        <v>231000000</v>
+      </c>
+      <c r="M34" t="str">
+        <v>2026-03-01</v>
+      </c>
+      <c r="N34" t="str">
+        <v>2028-12-01</v>
+      </c>
+      <c r="O34" t="str">
+        <v>Ma trận #33 — RENO | theo phòng (3p) | không nội thất | TB bàn giao: Không | TB mua đ2: Không</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>HD-MTX-34-RENO-RM-NONE</v>
+      </c>
+      <c r="B35" t="str">
+        <v>MTX#34 THEO_PHONG NONE</v>
+      </c>
+      <c r="C35" t="str">
+        <v>34 Ma Trận Gò Vấp</v>
+      </c>
+      <c r="D35" t="str">
+        <v>Gò Vấp</v>
+      </c>
+      <c r="E35" t="str">
+        <v>TP. Hồ Chí Minh</v>
+      </c>
+      <c r="F35">
+        <v>118</v>
+      </c>
+      <c r="G35">
+        <v>16.6</v>
+      </c>
+      <c r="H35">
+        <v>7.1</v>
+      </c>
+      <c r="I35">
+        <v>2</v>
+      </c>
+      <c r="J35">
+        <v>4</v>
+      </c>
+      <c r="K35" t="str">
+        <v>Phạm Thị D</v>
+      </c>
+      <c r="L35">
+        <v>236000000</v>
+      </c>
+      <c r="M35" t="str">
+        <v>2026-04-01</v>
+      </c>
+      <c r="N35" t="str">
+        <v>2029-02-01</v>
+      </c>
+      <c r="O35" t="str">
+        <v>Ma trận #34 — RENO | theo phòng (3p) | không nội thất | TB bàn giao: Không | TB mua đ2: Không</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>HD-MTX-35-RENO-RM-NONE</v>
+      </c>
+      <c r="B36" t="str">
+        <v>MTX#35 THEO_PHONG NONE</v>
+      </c>
+      <c r="C36" t="str">
+        <v>35 Ma Trận Phú Nhuận</v>
+      </c>
+      <c r="D36" t="str">
+        <v>Phú Nhuận</v>
+      </c>
+      <c r="E36" t="str">
+        <v>TP. Hồ Chí Minh</v>
+      </c>
+      <c r="F36">
+        <v>106</v>
+      </c>
+      <c r="G36">
+        <v>19.3</v>
+      </c>
+      <c r="H36">
+        <v>5.5</v>
+      </c>
+      <c r="I36">
+        <v>3</v>
+      </c>
+      <c r="J36">
+        <v>4</v>
+      </c>
+      <c r="K36" t="str">
+        <v>Hoàng Văn E</v>
+      </c>
+      <c r="L36">
+        <v>241000000</v>
+      </c>
+      <c r="M36" t="str">
+        <v>2026-05-01</v>
+      </c>
+      <c r="N36" t="str">
+        <v>2029-04-01</v>
+      </c>
+      <c r="O36" t="str">
+        <v>Ma trận #35 — RENO | theo phòng (3p) | không nội thất | TB bàn giao: Không | TB mua đ2: Không</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>HD-MTX-36-RENO-RM-BASIC-HO</v>
+      </c>
+      <c r="B37" t="str">
+        <v>MTX#36 THEO_PHONG BASIC</v>
+      </c>
+      <c r="C37" t="str">
+        <v>36 Ma Trận Cầu Giấy</v>
+      </c>
+      <c r="D37" t="str">
+        <v>Cầu Giấy</v>
+      </c>
+      <c r="E37" t="str">
+        <v>Hà Nội</v>
+      </c>
+      <c r="F37">
+        <v>109</v>
+      </c>
+      <c r="G37">
+        <v>18.5</v>
+      </c>
+      <c r="H37">
+        <v>5.9</v>
+      </c>
+      <c r="I37">
+        <v>2</v>
+      </c>
+      <c r="J37">
+        <v>4</v>
+      </c>
+      <c r="K37" t="str">
+        <v>Võ Thị F</v>
+      </c>
+      <c r="L37">
+        <v>216000000</v>
+      </c>
+      <c r="M37" t="str">
+        <v>2026-06-01</v>
+      </c>
+      <c r="N37" t="str">
+        <v>2028-06-01</v>
+      </c>
+      <c r="O37" t="str">
+        <v>Ma trận #36 — RENO | theo phòng (3p) | nội thất cơ bản | TB bàn giao: Có | TB mua đ2: Không</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>HD-MTX-37-RENO-RM-BASIC-HO</v>
+      </c>
+      <c r="B38" t="str">
+        <v>MTX#37 THEO_PHONG BASIC</v>
+      </c>
+      <c r="C38" t="str">
+        <v>37 Ma Trận Quận 1</v>
+      </c>
+      <c r="D38" t="str">
+        <v>Quận 1</v>
+      </c>
+      <c r="E38" t="str">
+        <v>TP. Hồ Chí Minh</v>
+      </c>
+      <c r="F38">
+        <v>112</v>
+      </c>
+      <c r="G38">
+        <v>17.8</v>
+      </c>
+      <c r="H38">
+        <v>6.3</v>
+      </c>
+      <c r="I38">
+        <v>3</v>
+      </c>
+      <c r="J38">
+        <v>4</v>
+      </c>
+      <c r="K38" t="str">
+        <v>Đặng Văn G</v>
+      </c>
+      <c r="L38">
+        <v>221000000</v>
+      </c>
+      <c r="M38" t="str">
+        <v>2026-07-01</v>
+      </c>
+      <c r="N38" t="str">
+        <v>2028-08-01</v>
+      </c>
+      <c r="O38" t="str">
+        <v>Ma trận #37 — RENO | theo phòng (3p) | nội thất cơ bản | TB bàn giao: Có | TB mua đ2: Không</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>HD-MTX-38-RENO-RM-BASIC-HO</v>
+      </c>
+      <c r="B39" t="str">
+        <v>MTX#38 THEO_PHONG BASIC</v>
+      </c>
+      <c r="C39" t="str">
+        <v>38 Ma Trận Quận 3</v>
+      </c>
+      <c r="D39" t="str">
+        <v>Quận 3</v>
+      </c>
+      <c r="E39" t="str">
+        <v>TP. Hồ Chí Minh</v>
+      </c>
+      <c r="F39">
+        <v>115</v>
+      </c>
+      <c r="G39">
+        <v>17.2</v>
+      </c>
+      <c r="H39">
+        <v>6.7</v>
+      </c>
+      <c r="I39">
+        <v>2</v>
+      </c>
+      <c r="J39">
+        <v>4</v>
+      </c>
+      <c r="K39" t="str">
+        <v>Bùi Thị H</v>
+      </c>
+      <c r="L39">
+        <v>226000000</v>
+      </c>
+      <c r="M39" t="str">
+        <v>2026-08-01</v>
+      </c>
+      <c r="N39" t="str">
+        <v>2028-10-01</v>
+      </c>
+      <c r="O39" t="str">
+        <v>Ma trận #38 — RENO | theo phòng (3p) | nội thất cơ bản | TB bàn giao: Có | TB mua đ2: Không</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>HD-MTX-39-RENO-RM-BASIC-HO</v>
+      </c>
+      <c r="B40" t="str">
+        <v>MTX#39 THEO_PHONG BASIC</v>
+      </c>
+      <c r="C40" t="str">
+        <v>39 Ma Trận Bình Thạnh</v>
+      </c>
+      <c r="D40" t="str">
+        <v>Bình Thạnh</v>
+      </c>
+      <c r="E40" t="str">
+        <v>TP. Hồ Chí Minh</v>
+      </c>
+      <c r="F40">
+        <v>118</v>
+      </c>
+      <c r="G40">
+        <v>16.6</v>
+      </c>
+      <c r="H40">
+        <v>7.1</v>
+      </c>
+      <c r="I40">
+        <v>3</v>
+      </c>
+      <c r="J40">
+        <v>4</v>
+      </c>
+      <c r="K40" t="str">
+        <v>Ngô Văn I</v>
+      </c>
+      <c r="L40">
+        <v>231000000</v>
+      </c>
+      <c r="M40" t="str">
+        <v>2026-09-01</v>
+      </c>
+      <c r="N40" t="str">
+        <v>2028-12-01</v>
+      </c>
+      <c r="O40" t="str">
+        <v>Ma trận #39 — RENO | theo phòng (3p) | nội thất cơ bản | TB bàn giao: Có | TB mua đ2: Không</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>HD-MTX-40-RENO-RM-BASIC-BUY</v>
+      </c>
+      <c r="B41" t="str">
+        <v>MTX#40 THEO_PHONG BASIC</v>
+      </c>
+      <c r="C41" t="str">
+        <v>40 Ma Trận Gò Vấp</v>
+      </c>
+      <c r="D41" t="str">
+        <v>Gò Vấp</v>
+      </c>
+      <c r="E41" t="str">
+        <v>TP. Hồ Chí Minh</v>
+      </c>
+      <c r="F41">
+        <v>106</v>
+      </c>
+      <c r="G41">
+        <v>19.3</v>
+      </c>
+      <c r="H41">
+        <v>5.5</v>
+      </c>
+      <c r="I41">
+        <v>2</v>
+      </c>
+      <c r="J41">
+        <v>4</v>
+      </c>
+      <c r="K41" t="str">
+        <v>Dương Thị K</v>
+      </c>
+      <c r="L41">
+        <v>236000000</v>
+      </c>
+      <c r="M41" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="N41" t="str">
+        <v>2029-02-01</v>
+      </c>
+      <c r="O41" t="str">
+        <v>Ma trận #40 — RENO | theo phòng (3p) | nội thất cơ bản | TB bàn giao: Không | TB mua đ2: Có</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>HD-MTX-41-RENO-RM-BASIC-BUY</v>
+      </c>
+      <c r="B42" t="str">
+        <v>MTX#41 THEO_PHONG BASIC</v>
+      </c>
+      <c r="C42" t="str">
+        <v>41 Ma Trận Phú Nhuận</v>
+      </c>
+      <c r="D42" t="str">
+        <v>Phú Nhuận</v>
+      </c>
+      <c r="E42" t="str">
+        <v>TP. Hồ Chí Minh</v>
+      </c>
+      <c r="F42">
+        <v>121</v>
+      </c>
+      <c r="G42">
+        <v>20.5</v>
+      </c>
+      <c r="H42">
+        <v>5.9</v>
+      </c>
+      <c r="I42">
+        <v>3</v>
+      </c>
+      <c r="J42">
+        <v>5</v>
+      </c>
+      <c r="K42" t="str">
+        <v>Lý Văn L</v>
+      </c>
+      <c r="L42">
+        <v>253000000</v>
+      </c>
+      <c r="M42" t="str">
+        <v>2026-03-01</v>
+      </c>
+      <c r="N42" t="str">
+        <v>2028-08-01</v>
+      </c>
+      <c r="O42" t="str">
+        <v>Ma trận #41 — RENO | theo phòng (4p) | nội thất cơ bản | TB bàn giao: Không | TB mua đ2: Có</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>HD-MTX-42-RENO-RM-BASIC-BUY</v>
+      </c>
+      <c r="B43" t="str">
+        <v>MTX#42 THEO_PHONG BASIC</v>
+      </c>
+      <c r="C43" t="str">
+        <v>42 Ma Trận Cầu Giấy</v>
+      </c>
+      <c r="D43" t="str">
+        <v>Cầu Giấy</v>
+      </c>
+      <c r="E43" t="str">
+        <v>Hà Nội</v>
+      </c>
+      <c r="F43">
+        <v>112</v>
+      </c>
+      <c r="G43">
+        <v>17.8</v>
+      </c>
+      <c r="H43">
+        <v>6.3</v>
+      </c>
+      <c r="I43">
+        <v>2</v>
+      </c>
+      <c r="J43">
+        <v>4</v>
+      </c>
+      <c r="K43" t="str">
+        <v>Mai Thị M</v>
+      </c>
+      <c r="L43">
+        <v>216000000</v>
+      </c>
+      <c r="M43" t="str">
+        <v>2026-04-01</v>
+      </c>
+      <c r="N43" t="str">
+        <v>2028-10-01</v>
+      </c>
+      <c r="O43" t="str">
+        <v>Ma trận #42 — RENO | theo phòng (3p) | nội thất cơ bản | TB bàn giao: Không | TB mua đ2: Có</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>HD-MTX-43-RENO-RM-BASIC-BUY</v>
+      </c>
+      <c r="B44" t="str">
+        <v>MTX#43 THEO_PHONG BASIC</v>
+      </c>
+      <c r="C44" t="str">
+        <v>43 Ma Trận Quận 1</v>
+      </c>
+      <c r="D44" t="str">
+        <v>Quận 1</v>
+      </c>
+      <c r="E44" t="str">
+        <v>TP. Hồ Chí Minh</v>
+      </c>
+      <c r="F44">
+        <v>127</v>
+      </c>
+      <c r="G44">
+        <v>19</v>
+      </c>
+      <c r="H44">
+        <v>6.7</v>
+      </c>
+      <c r="I44">
+        <v>3</v>
+      </c>
+      <c r="J44">
+        <v>5</v>
+      </c>
+      <c r="K44" t="str">
+        <v>Phan Văn N</v>
+      </c>
+      <c r="L44">
+        <v>233000000</v>
+      </c>
+      <c r="M44" t="str">
+        <v>2026-05-01</v>
+      </c>
+      <c r="N44" t="str">
+        <v>2028-12-01</v>
+      </c>
+      <c r="O44" t="str">
+        <v>Ma trận #43 — RENO | theo phòng (4p) | nội thất cơ bản | TB bàn giao: Không | TB mua đ2: Có</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>HD-MTX-44-RENO-RM-FULL</v>
+      </c>
+      <c r="B45" t="str">
+        <v>MTX#44 THEO_PHONG FULL</v>
+      </c>
+      <c r="C45" t="str">
+        <v>44 Ma Trận Quận 3</v>
+      </c>
+      <c r="D45" t="str">
+        <v>Quận 3</v>
+      </c>
+      <c r="E45" t="str">
+        <v>TP. Hồ Chí Minh</v>
+      </c>
+      <c r="F45">
+        <v>130</v>
+      </c>
+      <c r="G45">
+        <v>18.3</v>
+      </c>
+      <c r="H45">
+        <v>7.1</v>
+      </c>
+      <c r="I45">
+        <v>2</v>
+      </c>
+      <c r="J45">
+        <v>5</v>
+      </c>
+      <c r="K45" t="str">
+        <v>Trịnh Thị O</v>
+      </c>
+      <c r="L45">
+        <v>238000000</v>
+      </c>
+      <c r="M45" t="str">
+        <v>2026-06-01</v>
+      </c>
+      <c r="N45" t="str">
+        <v>2029-02-01</v>
+      </c>
+      <c r="O45" t="str">
+        <v>Ma trận #44 — RENO | theo phòng (4p) | full nội thất | TB bàn giao: Có | TB mua đ2: Có</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>HD-MTX-45-RENO-RM-FULL</v>
+      </c>
+      <c r="B46" t="str">
+        <v>MTX#45 THEO_PHONG FULL</v>
+      </c>
+      <c r="C46" t="str">
+        <v>45 Ma Trận Bình Thạnh</v>
+      </c>
+      <c r="D46" t="str">
+        <v>Bình Thạnh</v>
+      </c>
+      <c r="E46" t="str">
+        <v>TP. Hồ Chí Minh</v>
+      </c>
+      <c r="F46">
+        <v>118</v>
+      </c>
+      <c r="G46">
+        <v>21.5</v>
+      </c>
+      <c r="H46">
+        <v>5.5</v>
+      </c>
+      <c r="I46">
+        <v>3</v>
+      </c>
+      <c r="J46">
+        <v>5</v>
+      </c>
+      <c r="K46" t="str">
+        <v>Huỳnh Văn P</v>
+      </c>
+      <c r="L46">
+        <v>243000000</v>
+      </c>
+      <c r="M46" t="str">
+        <v>2026-07-01</v>
+      </c>
+      <c r="N46" t="str">
+        <v>2029-04-01</v>
+      </c>
+      <c r="O46" t="str">
+        <v>Ma trận #45 — RENO | theo phòng (4p) | full nội thất | TB bàn giao: Có | TB mua đ2: Có</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>HD-MTX-46-RENO-RM-FULL</v>
+      </c>
+      <c r="B47" t="str">
+        <v>MTX#46 THEO_PHONG FULL</v>
+      </c>
+      <c r="C47" t="str">
+        <v>46 Ma Trận Gò Vấp</v>
+      </c>
+      <c r="D47" t="str">
+        <v>Gò Vấp</v>
+      </c>
+      <c r="E47" t="str">
+        <v>TP. Hồ Chí Minh</v>
+      </c>
+      <c r="F47">
+        <v>121</v>
+      </c>
+      <c r="G47">
+        <v>20.5</v>
+      </c>
+      <c r="H47">
+        <v>5.9</v>
+      </c>
+      <c r="I47">
+        <v>2</v>
+      </c>
+      <c r="J47">
+        <v>5</v>
+      </c>
+      <c r="K47" t="str">
+        <v>Nguyễn Văn A</v>
+      </c>
+      <c r="L47">
+        <v>248000000</v>
+      </c>
+      <c r="M47" t="str">
+        <v>2026-08-01</v>
+      </c>
+      <c r="N47" t="str">
+        <v>2029-06-01</v>
+      </c>
+      <c r="O47" t="str">
+        <v>Ma trận #46 — RENO | theo phòng (4p) | full nội thất | TB bàn giao: Có | TB mua đ2: Có</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>HD-MTX-47-RENO-RM-FULL</v>
+      </c>
+      <c r="B48" t="str">
+        <v>MTX#47 THEO_PHONG FULL</v>
+      </c>
+      <c r="C48" t="str">
+        <v>47 Ma Trận Phú Nhuận</v>
+      </c>
+      <c r="D48" t="str">
+        <v>Phú Nhuận</v>
+      </c>
+      <c r="E48" t="str">
+        <v>TP. Hồ Chí Minh</v>
+      </c>
+      <c r="F48">
+        <v>124</v>
+      </c>
+      <c r="G48">
+        <v>19.7</v>
+      </c>
+      <c r="H48">
+        <v>6.3</v>
+      </c>
+      <c r="I48">
+        <v>3</v>
+      </c>
+      <c r="J48">
+        <v>5</v>
+      </c>
+      <c r="K48" t="str">
+        <v>Trần Thị B</v>
+      </c>
+      <c r="L48">
+        <v>253000000</v>
+      </c>
+      <c r="M48" t="str">
+        <v>2026-09-01</v>
+      </c>
+      <c r="N48" t="str">
+        <v>2029-08-01</v>
+      </c>
+      <c r="O48" t="str">
+        <v>Ma trận #47 — RENO | theo phòng (4p) | full nội thất | TB bàn giao: Có | TB mua đ2: Có</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>HD-MTX-48-RENO-RM-HO-BUY</v>
+      </c>
+      <c r="B49" t="str">
+        <v>MTX#48 THEO_PHONG BASIC</v>
+      </c>
+      <c r="C49" t="str">
+        <v>48 Ma Trận Cầu Giấy</v>
+      </c>
+      <c r="D49" t="str">
+        <v>Cầu Giấy</v>
+      </c>
+      <c r="E49" t="str">
+        <v>Hà Nội</v>
+      </c>
+      <c r="F49">
+        <v>115</v>
+      </c>
+      <c r="G49">
+        <v>17.2</v>
+      </c>
+      <c r="H49">
+        <v>6.7</v>
+      </c>
+      <c r="I49">
+        <v>2</v>
+      </c>
+      <c r="J49">
+        <v>4</v>
+      </c>
+      <c r="K49" t="str">
+        <v>Lê Văn C</v>
+      </c>
+      <c r="L49">
+        <v>216000000</v>
+      </c>
+      <c r="M49" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="N49" t="str">
+        <v>2028-10-01</v>
+      </c>
+      <c r="O49" t="str">
+        <v>Ma trận #48 — RENO | theo phòng (3p) | nội thất cơ bản | TB bàn giao: Có | TB mua đ2: Có</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>HD-MTX-49-RENO-RM-HO-BUY</v>
+      </c>
+      <c r="B50" t="str">
+        <v>MTX#49 THEO_PHONG BASIC</v>
+      </c>
+      <c r="C50" t="str">
+        <v>49 Ma Trận Quận 1</v>
+      </c>
+      <c r="D50" t="str">
+        <v>Quận 1</v>
+      </c>
+      <c r="E50" t="str">
+        <v>TP. Hồ Chí Minh</v>
+      </c>
+      <c r="F50">
+        <v>118</v>
+      </c>
+      <c r="G50">
+        <v>16.6</v>
+      </c>
+      <c r="H50">
+        <v>7.1</v>
+      </c>
+      <c r="I50">
+        <v>3</v>
+      </c>
+      <c r="J50">
+        <v>4</v>
+      </c>
+      <c r="K50" t="str">
+        <v>Phạm Thị D</v>
+      </c>
+      <c r="L50">
+        <v>221000000</v>
+      </c>
+      <c r="M50" t="str">
+        <v>2026-03-01</v>
+      </c>
+      <c r="N50" t="str">
+        <v>2028-04-01</v>
+      </c>
+      <c r="O50" t="str">
+        <v>Ma trận #49 — RENO | theo phòng (3p) | nội thất cơ bản | TB bàn giao: Có | TB mua đ2: Có</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>HD-MTX-50-RENO-RM-HO-BUY</v>
+      </c>
+      <c r="B51" t="str">
+        <v>MTX#50 THEO_PHONG BASIC</v>
+      </c>
+      <c r="C51" t="str">
+        <v>50 Ma Trận Quận 3</v>
+      </c>
+      <c r="D51" t="str">
+        <v>Quận 3</v>
+      </c>
+      <c r="E51" t="str">
+        <v>TP. Hồ Chí Minh</v>
+      </c>
+      <c r="F51">
+        <v>106</v>
+      </c>
+      <c r="G51">
+        <v>19.3</v>
+      </c>
+      <c r="H51">
+        <v>5.5</v>
+      </c>
+      <c r="I51">
+        <v>2</v>
+      </c>
+      <c r="J51">
+        <v>4</v>
+      </c>
+      <c r="K51" t="str">
+        <v>Hoàng Văn E</v>
+      </c>
+      <c r="L51">
+        <v>226000000</v>
+      </c>
+      <c r="M51" t="str">
+        <v>2026-04-01</v>
+      </c>
+      <c r="N51" t="str">
+        <v>2028-06-01</v>
+      </c>
+      <c r="O51" t="str">
+        <v>Ma trận #50 — RENO | theo phòng (3p) | nội thất cơ bản | TB bàn giao: Có | TB mua đ2: Có</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O15"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O51"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G112"/>
   <cols>
-    <col min="1" max="1" width="20.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="1" max="1" width="28.83203125" customWidth="1"/>
+    <col min="2" max="2" width="14.83203125" customWidth="1"/>
     <col min="3" max="3" width="18.83203125" customWidth="1"/>
     <col min="4" max="4" width="16.83203125" customWidth="1"/>
-    <col min="5" max="5" width="23.83203125" customWidth="1"/>
-    <col min="6" max="6" width="16.83203125" customWidth="1"/>
-    <col min="7" max="7" width="16.83203125" customWidth="1"/>
+    <col min="5" max="5" width="16.83203125" customWidth="1"/>
+    <col min="6" max="6" width="10.83203125" customWidth="1"/>
+    <col min="7" max="7" width="18.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1827,7 +4553,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>HD-MTX-02-NORENO-FURN</v>
+        <v>HD-MTX-06-NORENO-WH-BASIC</v>
       </c>
       <c r="B2" t="str">
         <v>Điều hòa</v>
@@ -1845,18 +4571,18 @@
         <v>1</v>
       </c>
       <c r="G2" t="str">
-        <v/>
+        <v>NT cơ bản</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>HD-MTX-02-NORENO-FURN</v>
+        <v>HD-MTX-06-NORENO-WH-BASIC</v>
       </c>
       <c r="B3" t="str">
         <v>Giường</v>
       </c>
       <c r="C3" t="str">
-        <v>Giường gỗ</v>
+        <v>Giường gỗ 1m6</v>
       </c>
       <c r="D3" t="str">
         <v>Phòng ngủ</v>
@@ -1873,16 +4599,16 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>HD-MTX-05-RENO-WH-HO-NOFURN</v>
+        <v>HD-MTX-07-NORENO-WH-BASIC</v>
       </c>
       <c r="B4" t="str">
-        <v>Máy giặt</v>
+        <v>Điều hòa</v>
       </c>
       <c r="C4" t="str">
-        <v>Máy cũ</v>
+        <v>Máy 1.5HP</v>
       </c>
       <c r="D4" t="str">
-        <v>Sân sau</v>
+        <v>Phòng khách</v>
       </c>
       <c r="E4" t="str">
         <v>GOOD</v>
@@ -1891,27 +4617,27 @@
         <v>1</v>
       </c>
       <c r="G4" t="str">
-        <v>TB chủ</v>
+        <v>NT cơ bản</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>HD-MTX-06-RENO-WH-HO-EQUIP</v>
+        <v>HD-MTX-07-NORENO-WH-BASIC</v>
       </c>
       <c r="B5" t="str">
-        <v>Quạt</v>
+        <v>Giường</v>
       </c>
       <c r="C5" t="str">
-        <v>Quạt trần</v>
+        <v>Giường gỗ 1m6</v>
       </c>
       <c r="D5" t="str">
-        <v>Phòng khách</v>
+        <v>Phòng ngủ</v>
       </c>
       <c r="E5" t="str">
         <v>GOOD</v>
       </c>
       <c r="F5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -1919,45 +4645,45 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>HD-MTX-06-RENO-WH-HO-EQUIP</v>
+        <v>HD-MTX-08-NORENO-WH-BASIC</v>
       </c>
       <c r="B6" t="str">
-        <v>Tủ lạnh</v>
+        <v>Điều hòa</v>
       </c>
       <c r="C6" t="str">
-        <v>Tủ 180L</v>
+        <v>Máy 1.5HP</v>
       </c>
       <c r="D6" t="str">
-        <v>Bếp</v>
+        <v>Phòng khách</v>
       </c>
       <c r="E6" t="str">
-        <v>DAMAGED</v>
+        <v>GOOD</v>
       </c>
       <c r="F6">
         <v>1</v>
       </c>
       <c r="G6" t="str">
-        <v/>
+        <v>NT cơ bản</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>HD-MTX-09-RENO-RM-HO-NOFURN</v>
+        <v>HD-MTX-08-NORENO-WH-BASIC</v>
       </c>
       <c r="B7" t="str">
         <v>Giường</v>
       </c>
       <c r="C7" t="str">
-        <v>Giường sắt cũ</v>
+        <v>Giường gỗ 1m6</v>
       </c>
       <c r="D7" t="str">
-        <v>Tầng 2</v>
+        <v>Phòng ngủ</v>
       </c>
       <c r="E7" t="str">
         <v>GOOD</v>
       </c>
       <c r="F7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G7" t="str">
         <v/>
@@ -1965,39 +4691,39 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>HD-MTX-10-RENO-RM-HO-EQUIP</v>
+        <v>HD-MTX-09-NORENO-WH-BASIC</v>
       </c>
       <c r="B8" t="str">
-        <v>Nóng lạnh</v>
+        <v>Điều hòa</v>
       </c>
       <c r="C8" t="str">
-        <v>Máy cũ</v>
+        <v>Máy 1.5HP</v>
       </c>
       <c r="D8" t="str">
-        <v>WC chung</v>
+        <v>Phòng khách</v>
       </c>
       <c r="E8" t="str">
-        <v>DAMAGED</v>
+        <v>GOOD</v>
       </c>
       <c r="F8">
         <v>1</v>
       </c>
       <c r="G8" t="str">
-        <v/>
+        <v>NT cơ bản</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>HD-MTX-11-NORENO-FULL</v>
+        <v>HD-MTX-09-NORENO-WH-BASIC</v>
       </c>
       <c r="B9" t="str">
-        <v>Điều hòa</v>
+        <v>Giường</v>
       </c>
       <c r="C9" t="str">
-        <v>1.5HP Inverter</v>
+        <v>Giường gỗ 1m6</v>
       </c>
       <c r="D9" t="str">
-        <v>Phòng khách</v>
+        <v>Phòng ngủ</v>
       </c>
       <c r="E9" t="str">
         <v>GOOD</v>
@@ -2011,16 +4737,16 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>HD-MTX-11-NORENO-FULL</v>
+        <v>HD-MTX-10-NORENO-WH-BASIC</v>
       </c>
       <c r="B10" t="str">
         <v>Điều hòa</v>
       </c>
       <c r="C10" t="str">
-        <v>1HP</v>
+        <v>Máy 1.5HP</v>
       </c>
       <c r="D10" t="str">
-        <v>Phòng ngủ 1</v>
+        <v>Phòng khách</v>
       </c>
       <c r="E10" t="str">
         <v>GOOD</v>
@@ -2029,21 +4755,21 @@
         <v>1</v>
       </c>
       <c r="G10" t="str">
-        <v/>
+        <v>NT cơ bản</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>HD-MTX-11-NORENO-FULL</v>
+        <v>HD-MTX-10-NORENO-WH-BASIC</v>
       </c>
       <c r="B11" t="str">
-        <v>Tủ lạnh</v>
+        <v>Giường</v>
       </c>
       <c r="C11" t="str">
-        <v>Inverter 200L</v>
+        <v>Giường gỗ 1m6</v>
       </c>
       <c r="D11" t="str">
-        <v>Bếp</v>
+        <v>Phòng ngủ</v>
       </c>
       <c r="E11" t="str">
         <v>GOOD</v>
@@ -2057,16 +4783,16 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>HD-MTX-11-NORENO-FULL</v>
+        <v>HD-MTX-11-NORENO-WH-FULL</v>
       </c>
       <c r="B12" t="str">
-        <v>Máy giặt</v>
+        <v>Điều hòa</v>
       </c>
       <c r="C12" t="str">
-        <v>Cửa trước 8kg</v>
+        <v>1.5HP Inverter</v>
       </c>
       <c r="D12" t="str">
-        <v>Sân sau</v>
+        <v>Phòng khách</v>
       </c>
       <c r="E12" t="str">
         <v>GOOD</v>
@@ -2080,16 +4806,16 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>HD-MTX-11-NORENO-FULL</v>
+        <v>HD-MTX-11-NORENO-WH-FULL</v>
       </c>
       <c r="B13" t="str">
-        <v>Nóng lạnh</v>
+        <v>Điều hòa</v>
       </c>
       <c r="C13" t="str">
-        <v>15L</v>
+        <v>1HP</v>
       </c>
       <c r="D13" t="str">
-        <v>WC tầng 1</v>
+        <v>Phòng ngủ 1</v>
       </c>
       <c r="E13" t="str">
         <v>GOOD</v>
@@ -2103,16 +4829,16 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>HD-MTX-11-NORENO-FULL</v>
+        <v>HD-MTX-11-NORENO-WH-FULL</v>
       </c>
       <c r="B14" t="str">
-        <v>Giường</v>
+        <v>Tủ lạnh</v>
       </c>
       <c r="C14" t="str">
-        <v>Giường gỗ 1m6</v>
+        <v>Inverter 200L</v>
       </c>
       <c r="D14" t="str">
-        <v>Phòng ngủ 1</v>
+        <v>Bếp</v>
       </c>
       <c r="E14" t="str">
         <v>GOOD</v>
@@ -2126,16 +4852,16 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>HD-MTX-11-NORENO-FULL</v>
+        <v>HD-MTX-11-NORENO-WH-FULL</v>
       </c>
       <c r="B15" t="str">
-        <v>Giường</v>
+        <v>Máy giặt</v>
       </c>
       <c r="C15" t="str">
-        <v>Giường gỗ 1m6</v>
+        <v>Cửa trước 8kg</v>
       </c>
       <c r="D15" t="str">
-        <v>Phòng ngủ 2</v>
+        <v>Sân sau</v>
       </c>
       <c r="E15" t="str">
         <v>GOOD</v>
@@ -2149,16 +4875,16 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>HD-MTX-11-NORENO-FULL</v>
+        <v>HD-MTX-11-NORENO-WH-FULL</v>
       </c>
       <c r="B16" t="str">
-        <v>Giường</v>
+        <v>Nóng lạnh</v>
       </c>
       <c r="C16" t="str">
-        <v>Giường gỗ 1m2</v>
+        <v>15L</v>
       </c>
       <c r="D16" t="str">
-        <v>Phòng ngủ 3</v>
+        <v>WC tầng 1</v>
       </c>
       <c r="E16" t="str">
         <v>GOOD</v>
@@ -2172,16 +4898,16 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>HD-MTX-11-NORENO-FULL</v>
+        <v>HD-MTX-11-NORENO-WH-FULL</v>
       </c>
       <c r="B17" t="str">
-        <v>Quạt</v>
+        <v>Giường</v>
       </c>
       <c r="C17" t="str">
-        <v>Quạt trần</v>
+        <v>Giường gỗ 1m6</v>
       </c>
       <c r="D17" t="str">
-        <v>Phòng khách</v>
+        <v>Phòng ngủ 1</v>
       </c>
       <c r="E17" t="str">
         <v>GOOD</v>
@@ -2195,16 +4921,16 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>HD-MTX-11-NORENO-FULL</v>
+        <v>HD-MTX-11-NORENO-WH-FULL</v>
       </c>
       <c r="B18" t="str">
-        <v>Quạt</v>
+        <v>Giường</v>
       </c>
       <c r="C18" t="str">
-        <v>Quạt đứng</v>
+        <v>Giường gỗ 1m6</v>
       </c>
       <c r="D18" t="str">
-        <v>Phòng ngủ 1</v>
+        <v>Phòng ngủ 2</v>
       </c>
       <c r="E18" t="str">
         <v>GOOD</v>
@@ -2218,16 +4944,16 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>HD-MTX-11-NORENO-FULL</v>
+        <v>HD-MTX-11-NORENO-WH-FULL</v>
       </c>
       <c r="B19" t="str">
         <v>Quạt</v>
       </c>
       <c r="C19" t="str">
-        <v>Quạt đứng</v>
+        <v>Quạt trần</v>
       </c>
       <c r="D19" t="str">
-        <v>Phòng ngủ 2</v>
+        <v>Phòng khách</v>
       </c>
       <c r="E19" t="str">
         <v>GOOD</v>
@@ -2241,7 +4967,7 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>HD-MTX-11-NORENO-FULL</v>
+        <v>HD-MTX-11-NORENO-WH-FULL</v>
       </c>
       <c r="B20" t="str">
         <v>Quạt</v>
@@ -2250,7 +4976,7 @@
         <v>Quạt đứng</v>
       </c>
       <c r="D20" t="str">
-        <v>Phòng ngủ 3</v>
+        <v>Phòng ngủ 1</v>
       </c>
       <c r="E20" t="str">
         <v>GOOD</v>
@@ -2264,39 +4990,39 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>HD-MTX-12-RENO-WH-FULL</v>
+        <v>HD-MTX-12-NORENO-WH-FULL</v>
       </c>
       <c r="B21" t="str">
-        <v>Giường</v>
+        <v>Điều hòa</v>
       </c>
       <c r="C21" t="str">
-        <v>Giường gỗ cũ</v>
+        <v>1.5HP Inverter</v>
       </c>
       <c r="D21" t="str">
-        <v>Phòng ngủ chính</v>
+        <v>Phòng khách</v>
       </c>
       <c r="E21" t="str">
         <v>GOOD</v>
       </c>
       <c r="F21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G21" t="str">
-        <v>TB chủ giữ lại</v>
+        <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>HD-MTX-12-RENO-WH-FULL</v>
+        <v>HD-MTX-12-NORENO-WH-FULL</v>
       </c>
       <c r="B22" t="str">
-        <v>Quạt</v>
+        <v>Điều hòa</v>
       </c>
       <c r="C22" t="str">
-        <v>Quạt trần cũ</v>
+        <v>1HP</v>
       </c>
       <c r="D22" t="str">
-        <v>Phòng khách</v>
+        <v>Phòng ngủ 1</v>
       </c>
       <c r="E22" t="str">
         <v>GOOD</v>
@@ -2310,39 +5036,39 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>HD-MTX-12-RENO-WH-FULL</v>
+        <v>HD-MTX-12-NORENO-WH-FULL</v>
       </c>
       <c r="B23" t="str">
         <v>Tủ lạnh</v>
       </c>
       <c r="C23" t="str">
-        <v>Tủ 150L cũ</v>
+        <v>Inverter 200L</v>
       </c>
       <c r="D23" t="str">
         <v>Bếp</v>
       </c>
       <c r="E23" t="str">
-        <v>DAMAGED</v>
+        <v>GOOD</v>
       </c>
       <c r="F23">
         <v>1</v>
       </c>
       <c r="G23" t="str">
-        <v>Sắp thay</v>
+        <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>HD-MTX-13-RENO-RM-FULL</v>
+        <v>HD-MTX-12-NORENO-WH-FULL</v>
       </c>
       <c r="B24" t="str">
         <v>Máy giặt</v>
       </c>
       <c r="C24" t="str">
-        <v>Máy cũ chung</v>
+        <v>Cửa trước 8kg</v>
       </c>
       <c r="D24" t="str">
-        <v>Sân phơi</v>
+        <v>Sân sau</v>
       </c>
       <c r="E24" t="str">
         <v>GOOD</v>
@@ -2351,35 +5077,2036 @@
         <v>1</v>
       </c>
       <c r="G24" t="str">
-        <v>TB dùng chung</v>
+        <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>HD-MTX-13-RENO-RM-FULL</v>
+        <v>HD-MTX-12-NORENO-WH-FULL</v>
       </c>
       <c r="B25" t="str">
+        <v>Nóng lạnh</v>
+      </c>
+      <c r="C25" t="str">
+        <v>15L</v>
+      </c>
+      <c r="D25" t="str">
+        <v>WC tầng 1</v>
+      </c>
+      <c r="E25" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F25">
+        <v>1</v>
+      </c>
+      <c r="G25" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>HD-MTX-12-NORENO-WH-FULL</v>
+      </c>
+      <c r="B26" t="str">
+        <v>Giường</v>
+      </c>
+      <c r="C26" t="str">
+        <v>Giường gỗ 1m6</v>
+      </c>
+      <c r="D26" t="str">
+        <v>Phòng ngủ 1</v>
+      </c>
+      <c r="E26" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F26">
+        <v>1</v>
+      </c>
+      <c r="G26" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>HD-MTX-12-NORENO-WH-FULL</v>
+      </c>
+      <c r="B27" t="str">
+        <v>Giường</v>
+      </c>
+      <c r="C27" t="str">
+        <v>Giường gỗ 1m6</v>
+      </c>
+      <c r="D27" t="str">
+        <v>Phòng ngủ 2</v>
+      </c>
+      <c r="E27" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F27">
+        <v>1</v>
+      </c>
+      <c r="G27" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>HD-MTX-12-NORENO-WH-FULL</v>
+      </c>
+      <c r="B28" t="str">
+        <v>Quạt</v>
+      </c>
+      <c r="C28" t="str">
+        <v>Quạt trần</v>
+      </c>
+      <c r="D28" t="str">
+        <v>Phòng khách</v>
+      </c>
+      <c r="E28" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F28">
+        <v>1</v>
+      </c>
+      <c r="G28" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>HD-MTX-12-NORENO-WH-FULL</v>
+      </c>
+      <c r="B29" t="str">
+        <v>Quạt</v>
+      </c>
+      <c r="C29" t="str">
+        <v>Quạt đứng</v>
+      </c>
+      <c r="D29" t="str">
+        <v>Phòng ngủ 1</v>
+      </c>
+      <c r="E29" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F29">
+        <v>1</v>
+      </c>
+      <c r="G29" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>HD-MTX-13-NORENO-WH-FULL</v>
+      </c>
+      <c r="B30" t="str">
+        <v>Điều hòa</v>
+      </c>
+      <c r="C30" t="str">
+        <v>1.5HP Inverter</v>
+      </c>
+      <c r="D30" t="str">
+        <v>Phòng khách</v>
+      </c>
+      <c r="E30" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F30">
+        <v>1</v>
+      </c>
+      <c r="G30" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>HD-MTX-13-NORENO-WH-FULL</v>
+      </c>
+      <c r="B31" t="str">
+        <v>Điều hòa</v>
+      </c>
+      <c r="C31" t="str">
+        <v>1HP</v>
+      </c>
+      <c r="D31" t="str">
+        <v>Phòng ngủ 1</v>
+      </c>
+      <c r="E31" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F31">
+        <v>1</v>
+      </c>
+      <c r="G31" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>HD-MTX-13-NORENO-WH-FULL</v>
+      </c>
+      <c r="B32" t="str">
         <v>Tủ lạnh</v>
       </c>
-      <c r="C25" t="str">
+      <c r="C32" t="str">
+        <v>Inverter 200L</v>
+      </c>
+      <c r="D32" t="str">
+        <v>Bếp</v>
+      </c>
+      <c r="E32" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F32">
+        <v>1</v>
+      </c>
+      <c r="G32" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>HD-MTX-13-NORENO-WH-FULL</v>
+      </c>
+      <c r="B33" t="str">
+        <v>Máy giặt</v>
+      </c>
+      <c r="C33" t="str">
+        <v>Cửa trước 8kg</v>
+      </c>
+      <c r="D33" t="str">
+        <v>Sân sau</v>
+      </c>
+      <c r="E33" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F33">
+        <v>1</v>
+      </c>
+      <c r="G33" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>HD-MTX-13-NORENO-WH-FULL</v>
+      </c>
+      <c r="B34" t="str">
+        <v>Nóng lạnh</v>
+      </c>
+      <c r="C34" t="str">
+        <v>15L</v>
+      </c>
+      <c r="D34" t="str">
+        <v>WC tầng 1</v>
+      </c>
+      <c r="E34" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F34">
+        <v>1</v>
+      </c>
+      <c r="G34" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>HD-MTX-13-NORENO-WH-FULL</v>
+      </c>
+      <c r="B35" t="str">
+        <v>Giường</v>
+      </c>
+      <c r="C35" t="str">
+        <v>Giường gỗ 1m6</v>
+      </c>
+      <c r="D35" t="str">
+        <v>Phòng ngủ 1</v>
+      </c>
+      <c r="E35" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F35">
+        <v>1</v>
+      </c>
+      <c r="G35" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>HD-MTX-13-NORENO-WH-FULL</v>
+      </c>
+      <c r="B36" t="str">
+        <v>Giường</v>
+      </c>
+      <c r="C36" t="str">
+        <v>Giường gỗ 1m6</v>
+      </c>
+      <c r="D36" t="str">
+        <v>Phòng ngủ 2</v>
+      </c>
+      <c r="E36" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F36">
+        <v>1</v>
+      </c>
+      <c r="G36" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>HD-MTX-13-NORENO-WH-FULL</v>
+      </c>
+      <c r="B37" t="str">
+        <v>Quạt</v>
+      </c>
+      <c r="C37" t="str">
+        <v>Quạt trần</v>
+      </c>
+      <c r="D37" t="str">
+        <v>Phòng khách</v>
+      </c>
+      <c r="E37" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F37">
+        <v>1</v>
+      </c>
+      <c r="G37" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>HD-MTX-13-NORENO-WH-FULL</v>
+      </c>
+      <c r="B38" t="str">
+        <v>Quạt</v>
+      </c>
+      <c r="C38" t="str">
+        <v>Quạt đứng</v>
+      </c>
+      <c r="D38" t="str">
+        <v>Phòng ngủ 1</v>
+      </c>
+      <c r="E38" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F38">
+        <v>1</v>
+      </c>
+      <c r="G38" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>HD-MTX-14-NORENO-WH-FULL</v>
+      </c>
+      <c r="B39" t="str">
+        <v>Điều hòa</v>
+      </c>
+      <c r="C39" t="str">
+        <v>1.5HP Inverter</v>
+      </c>
+      <c r="D39" t="str">
+        <v>Phòng khách</v>
+      </c>
+      <c r="E39" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F39">
+        <v>1</v>
+      </c>
+      <c r="G39" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>HD-MTX-14-NORENO-WH-FULL</v>
+      </c>
+      <c r="B40" t="str">
+        <v>Điều hòa</v>
+      </c>
+      <c r="C40" t="str">
+        <v>1HP</v>
+      </c>
+      <c r="D40" t="str">
+        <v>Phòng ngủ 1</v>
+      </c>
+      <c r="E40" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F40">
+        <v>1</v>
+      </c>
+      <c r="G40" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>HD-MTX-14-NORENO-WH-FULL</v>
+      </c>
+      <c r="B41" t="str">
+        <v>Tủ lạnh</v>
+      </c>
+      <c r="C41" t="str">
+        <v>Inverter 200L</v>
+      </c>
+      <c r="D41" t="str">
+        <v>Bếp</v>
+      </c>
+      <c r="E41" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F41">
+        <v>1</v>
+      </c>
+      <c r="G41" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>HD-MTX-14-NORENO-WH-FULL</v>
+      </c>
+      <c r="B42" t="str">
+        <v>Máy giặt</v>
+      </c>
+      <c r="C42" t="str">
+        <v>Cửa trước 8kg</v>
+      </c>
+      <c r="D42" t="str">
+        <v>Sân sau</v>
+      </c>
+      <c r="E42" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F42">
+        <v>1</v>
+      </c>
+      <c r="G42" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>HD-MTX-14-NORENO-WH-FULL</v>
+      </c>
+      <c r="B43" t="str">
+        <v>Nóng lạnh</v>
+      </c>
+      <c r="C43" t="str">
+        <v>15L</v>
+      </c>
+      <c r="D43" t="str">
+        <v>WC tầng 1</v>
+      </c>
+      <c r="E43" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F43">
+        <v>1</v>
+      </c>
+      <c r="G43" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>HD-MTX-14-NORENO-WH-FULL</v>
+      </c>
+      <c r="B44" t="str">
+        <v>Giường</v>
+      </c>
+      <c r="C44" t="str">
+        <v>Giường gỗ 1m6</v>
+      </c>
+      <c r="D44" t="str">
+        <v>Phòng ngủ 1</v>
+      </c>
+      <c r="E44" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F44">
+        <v>1</v>
+      </c>
+      <c r="G44" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>HD-MTX-14-NORENO-WH-FULL</v>
+      </c>
+      <c r="B45" t="str">
+        <v>Giường</v>
+      </c>
+      <c r="C45" t="str">
+        <v>Giường gỗ 1m6</v>
+      </c>
+      <c r="D45" t="str">
+        <v>Phòng ngủ 2</v>
+      </c>
+      <c r="E45" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F45">
+        <v>1</v>
+      </c>
+      <c r="G45" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>HD-MTX-14-NORENO-WH-FULL</v>
+      </c>
+      <c r="B46" t="str">
+        <v>Quạt</v>
+      </c>
+      <c r="C46" t="str">
+        <v>Quạt trần</v>
+      </c>
+      <c r="D46" t="str">
+        <v>Phòng khách</v>
+      </c>
+      <c r="E46" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F46">
+        <v>1</v>
+      </c>
+      <c r="G46" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>HD-MTX-14-NORENO-WH-FULL</v>
+      </c>
+      <c r="B47" t="str">
+        <v>Quạt</v>
+      </c>
+      <c r="C47" t="str">
+        <v>Quạt đứng</v>
+      </c>
+      <c r="D47" t="str">
+        <v>Phòng ngủ 1</v>
+      </c>
+      <c r="E47" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F47">
+        <v>1</v>
+      </c>
+      <c r="G47" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>HD-MTX-15-NORENO-WH-FULL</v>
+      </c>
+      <c r="B48" t="str">
+        <v>Điều hòa</v>
+      </c>
+      <c r="C48" t="str">
+        <v>1.5HP Inverter</v>
+      </c>
+      <c r="D48" t="str">
+        <v>Phòng khách</v>
+      </c>
+      <c r="E48" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F48">
+        <v>1</v>
+      </c>
+      <c r="G48" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>HD-MTX-15-NORENO-WH-FULL</v>
+      </c>
+      <c r="B49" t="str">
+        <v>Điều hòa</v>
+      </c>
+      <c r="C49" t="str">
+        <v>1HP</v>
+      </c>
+      <c r="D49" t="str">
+        <v>Phòng ngủ 1</v>
+      </c>
+      <c r="E49" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F49">
+        <v>1</v>
+      </c>
+      <c r="G49" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>HD-MTX-15-NORENO-WH-FULL</v>
+      </c>
+      <c r="B50" t="str">
+        <v>Tủ lạnh</v>
+      </c>
+      <c r="C50" t="str">
+        <v>Inverter 200L</v>
+      </c>
+      <c r="D50" t="str">
+        <v>Bếp</v>
+      </c>
+      <c r="E50" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F50">
+        <v>1</v>
+      </c>
+      <c r="G50" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>HD-MTX-15-NORENO-WH-FULL</v>
+      </c>
+      <c r="B51" t="str">
+        <v>Máy giặt</v>
+      </c>
+      <c r="C51" t="str">
+        <v>Cửa trước 8kg</v>
+      </c>
+      <c r="D51" t="str">
+        <v>Sân sau</v>
+      </c>
+      <c r="E51" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F51">
+        <v>1</v>
+      </c>
+      <c r="G51" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>HD-MTX-15-NORENO-WH-FULL</v>
+      </c>
+      <c r="B52" t="str">
+        <v>Nóng lạnh</v>
+      </c>
+      <c r="C52" t="str">
+        <v>15L</v>
+      </c>
+      <c r="D52" t="str">
+        <v>WC tầng 1</v>
+      </c>
+      <c r="E52" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F52">
+        <v>1</v>
+      </c>
+      <c r="G52" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>HD-MTX-15-NORENO-WH-FULL</v>
+      </c>
+      <c r="B53" t="str">
+        <v>Giường</v>
+      </c>
+      <c r="C53" t="str">
+        <v>Giường gỗ 1m6</v>
+      </c>
+      <c r="D53" t="str">
+        <v>Phòng ngủ 1</v>
+      </c>
+      <c r="E53" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F53">
+        <v>1</v>
+      </c>
+      <c r="G53" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>HD-MTX-15-NORENO-WH-FULL</v>
+      </c>
+      <c r="B54" t="str">
+        <v>Giường</v>
+      </c>
+      <c r="C54" t="str">
+        <v>Giường gỗ 1m6</v>
+      </c>
+      <c r="D54" t="str">
+        <v>Phòng ngủ 2</v>
+      </c>
+      <c r="E54" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F54">
+        <v>1</v>
+      </c>
+      <c r="G54" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>HD-MTX-15-NORENO-WH-FULL</v>
+      </c>
+      <c r="B55" t="str">
+        <v>Quạt</v>
+      </c>
+      <c r="C55" t="str">
+        <v>Quạt trần</v>
+      </c>
+      <c r="D55" t="str">
+        <v>Phòng khách</v>
+      </c>
+      <c r="E55" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F55">
+        <v>1</v>
+      </c>
+      <c r="G55" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>HD-MTX-15-NORENO-WH-FULL</v>
+      </c>
+      <c r="B56" t="str">
+        <v>Quạt</v>
+      </c>
+      <c r="C56" t="str">
+        <v>Quạt đứng</v>
+      </c>
+      <c r="D56" t="str">
+        <v>Phòng ngủ 1</v>
+      </c>
+      <c r="E56" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F56">
+        <v>1</v>
+      </c>
+      <c r="G56" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>HD-MTX-19-RENO-WH-BASIC-HO</v>
+      </c>
+      <c r="B57" t="str">
+        <v>Điều hòa</v>
+      </c>
+      <c r="C57" t="str">
+        <v>Máy 1.5HP</v>
+      </c>
+      <c r="D57" t="str">
+        <v>Phòng khách</v>
+      </c>
+      <c r="E57" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F57">
+        <v>1</v>
+      </c>
+      <c r="G57" t="str">
+        <v>NT cơ bản</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>HD-MTX-19-RENO-WH-BASIC-HO</v>
+      </c>
+      <c r="B58" t="str">
+        <v>Giường</v>
+      </c>
+      <c r="C58" t="str">
+        <v>Giường gỗ 1m6</v>
+      </c>
+      <c r="D58" t="str">
+        <v>Phòng ngủ</v>
+      </c>
+      <c r="E58" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F58">
+        <v>1</v>
+      </c>
+      <c r="G58" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>HD-MTX-20-RENO-WH-BASIC-HO</v>
+      </c>
+      <c r="B59" t="str">
+        <v>Điều hòa</v>
+      </c>
+      <c r="C59" t="str">
+        <v>Máy 1.5HP</v>
+      </c>
+      <c r="D59" t="str">
+        <v>Phòng khách</v>
+      </c>
+      <c r="E59" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F59">
+        <v>1</v>
+      </c>
+      <c r="G59" t="str">
+        <v>NT cơ bản</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>HD-MTX-20-RENO-WH-BASIC-HO</v>
+      </c>
+      <c r="B60" t="str">
+        <v>Giường</v>
+      </c>
+      <c r="C60" t="str">
+        <v>Giường gỗ 1m6</v>
+      </c>
+      <c r="D60" t="str">
+        <v>Phòng ngủ</v>
+      </c>
+      <c r="E60" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F60">
+        <v>1</v>
+      </c>
+      <c r="G60" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>HD-MTX-21-RENO-WH-BASIC-HO</v>
+      </c>
+      <c r="B61" t="str">
+        <v>Điều hòa</v>
+      </c>
+      <c r="C61" t="str">
+        <v>Máy 1.5HP</v>
+      </c>
+      <c r="D61" t="str">
+        <v>Phòng khách</v>
+      </c>
+      <c r="E61" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F61">
+        <v>1</v>
+      </c>
+      <c r="G61" t="str">
+        <v>NT cơ bản</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>HD-MTX-21-RENO-WH-BASIC-HO</v>
+      </c>
+      <c r="B62" t="str">
+        <v>Giường</v>
+      </c>
+      <c r="C62" t="str">
+        <v>Giường gỗ 1m6</v>
+      </c>
+      <c r="D62" t="str">
+        <v>Phòng ngủ</v>
+      </c>
+      <c r="E62" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F62">
+        <v>1</v>
+      </c>
+      <c r="G62" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>HD-MTX-25-RENO-WH-FULL</v>
+      </c>
+      <c r="B63" t="str">
+        <v>Điều hòa</v>
+      </c>
+      <c r="C63" t="str">
+        <v>1.5HP Inverter</v>
+      </c>
+      <c r="D63" t="str">
+        <v>Phòng khách</v>
+      </c>
+      <c r="E63" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F63">
+        <v>1</v>
+      </c>
+      <c r="G63" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>HD-MTX-25-RENO-WH-FULL</v>
+      </c>
+      <c r="B64" t="str">
+        <v>Điều hòa</v>
+      </c>
+      <c r="C64" t="str">
+        <v>1HP</v>
+      </c>
+      <c r="D64" t="str">
+        <v>Phòng ngủ 1</v>
+      </c>
+      <c r="E64" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F64">
+        <v>1</v>
+      </c>
+      <c r="G64" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>HD-MTX-25-RENO-WH-FULL</v>
+      </c>
+      <c r="B65" t="str">
+        <v>Tủ lạnh</v>
+      </c>
+      <c r="C65" t="str">
+        <v>Inverter 200L</v>
+      </c>
+      <c r="D65" t="str">
+        <v>Bếp</v>
+      </c>
+      <c r="E65" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F65">
+        <v>1</v>
+      </c>
+      <c r="G65" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>HD-MTX-25-RENO-WH-FULL</v>
+      </c>
+      <c r="B66" t="str">
+        <v>Máy giặt</v>
+      </c>
+      <c r="C66" t="str">
+        <v>Cửa trước 8kg</v>
+      </c>
+      <c r="D66" t="str">
+        <v>Sân sau</v>
+      </c>
+      <c r="E66" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F66">
+        <v>1</v>
+      </c>
+      <c r="G66" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>HD-MTX-25-RENO-WH-FULL</v>
+      </c>
+      <c r="B67" t="str">
+        <v>Nóng lạnh</v>
+      </c>
+      <c r="C67" t="str">
+        <v>15L</v>
+      </c>
+      <c r="D67" t="str">
+        <v>WC tầng 1</v>
+      </c>
+      <c r="E67" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F67">
+        <v>1</v>
+      </c>
+      <c r="G67" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>HD-MTX-25-RENO-WH-FULL</v>
+      </c>
+      <c r="B68" t="str">
+        <v>Giường</v>
+      </c>
+      <c r="C68" t="str">
+        <v>Giường gỗ 1m6</v>
+      </c>
+      <c r="D68" t="str">
+        <v>Phòng ngủ 1</v>
+      </c>
+      <c r="E68" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F68">
+        <v>1</v>
+      </c>
+      <c r="G68" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>HD-MTX-25-RENO-WH-FULL</v>
+      </c>
+      <c r="B69" t="str">
+        <v>Giường</v>
+      </c>
+      <c r="C69" t="str">
+        <v>Giường gỗ 1m6</v>
+      </c>
+      <c r="D69" t="str">
+        <v>Phòng ngủ 2</v>
+      </c>
+      <c r="E69" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F69">
+        <v>1</v>
+      </c>
+      <c r="G69" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>HD-MTX-25-RENO-WH-FULL</v>
+      </c>
+      <c r="B70" t="str">
+        <v>Quạt</v>
+      </c>
+      <c r="C70" t="str">
+        <v>Quạt trần</v>
+      </c>
+      <c r="D70" t="str">
+        <v>Phòng khách</v>
+      </c>
+      <c r="E70" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F70">
+        <v>1</v>
+      </c>
+      <c r="G70" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>HD-MTX-25-RENO-WH-FULL</v>
+      </c>
+      <c r="B71" t="str">
+        <v>Quạt</v>
+      </c>
+      <c r="C71" t="str">
+        <v>Quạt đứng</v>
+      </c>
+      <c r="D71" t="str">
+        <v>Phòng ngủ 1</v>
+      </c>
+      <c r="E71" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F71">
+        <v>1</v>
+      </c>
+      <c r="G71" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>HD-MTX-26-RENO-WH-FULL</v>
+      </c>
+      <c r="B72" t="str">
+        <v>Điều hòa</v>
+      </c>
+      <c r="C72" t="str">
+        <v>1.5HP Inverter</v>
+      </c>
+      <c r="D72" t="str">
+        <v>Phòng khách</v>
+      </c>
+      <c r="E72" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F72">
+        <v>1</v>
+      </c>
+      <c r="G72" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>HD-MTX-26-RENO-WH-FULL</v>
+      </c>
+      <c r="B73" t="str">
+        <v>Điều hòa</v>
+      </c>
+      <c r="C73" t="str">
+        <v>1HP</v>
+      </c>
+      <c r="D73" t="str">
+        <v>Phòng ngủ 1</v>
+      </c>
+      <c r="E73" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F73">
+        <v>1</v>
+      </c>
+      <c r="G73" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>HD-MTX-26-RENO-WH-FULL</v>
+      </c>
+      <c r="B74" t="str">
+        <v>Tủ lạnh</v>
+      </c>
+      <c r="C74" t="str">
+        <v>Inverter 200L</v>
+      </c>
+      <c r="D74" t="str">
+        <v>Bếp</v>
+      </c>
+      <c r="E74" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F74">
+        <v>1</v>
+      </c>
+      <c r="G74" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>HD-MTX-26-RENO-WH-FULL</v>
+      </c>
+      <c r="B75" t="str">
+        <v>Máy giặt</v>
+      </c>
+      <c r="C75" t="str">
+        <v>Cửa trước 8kg</v>
+      </c>
+      <c r="D75" t="str">
+        <v>Sân sau</v>
+      </c>
+      <c r="E75" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F75">
+        <v>1</v>
+      </c>
+      <c r="G75" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>HD-MTX-26-RENO-WH-FULL</v>
+      </c>
+      <c r="B76" t="str">
+        <v>Nóng lạnh</v>
+      </c>
+      <c r="C76" t="str">
+        <v>15L</v>
+      </c>
+      <c r="D76" t="str">
+        <v>WC tầng 1</v>
+      </c>
+      <c r="E76" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F76">
+        <v>1</v>
+      </c>
+      <c r="G76" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>HD-MTX-26-RENO-WH-FULL</v>
+      </c>
+      <c r="B77" t="str">
+        <v>Giường</v>
+      </c>
+      <c r="C77" t="str">
+        <v>Giường gỗ 1m6</v>
+      </c>
+      <c r="D77" t="str">
+        <v>Phòng ngủ 1</v>
+      </c>
+      <c r="E77" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F77">
+        <v>1</v>
+      </c>
+      <c r="G77" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>HD-MTX-26-RENO-WH-FULL</v>
+      </c>
+      <c r="B78" t="str">
+        <v>Giường</v>
+      </c>
+      <c r="C78" t="str">
+        <v>Giường gỗ 1m6</v>
+      </c>
+      <c r="D78" t="str">
+        <v>Phòng ngủ 2</v>
+      </c>
+      <c r="E78" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F78">
+        <v>1</v>
+      </c>
+      <c r="G78" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v>HD-MTX-26-RENO-WH-FULL</v>
+      </c>
+      <c r="B79" t="str">
+        <v>Quạt</v>
+      </c>
+      <c r="C79" t="str">
+        <v>Quạt trần</v>
+      </c>
+      <c r="D79" t="str">
+        <v>Phòng khách</v>
+      </c>
+      <c r="E79" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F79">
+        <v>1</v>
+      </c>
+      <c r="G79" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>HD-MTX-26-RENO-WH-FULL</v>
+      </c>
+      <c r="B80" t="str">
+        <v>Quạt</v>
+      </c>
+      <c r="C80" t="str">
+        <v>Quạt đứng</v>
+      </c>
+      <c r="D80" t="str">
+        <v>Phòng ngủ 1</v>
+      </c>
+      <c r="E80" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F80">
+        <v>1</v>
+      </c>
+      <c r="G80" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v>HD-MTX-27-RENO-WH-FULL</v>
+      </c>
+      <c r="B81" t="str">
+        <v>Điều hòa</v>
+      </c>
+      <c r="C81" t="str">
+        <v>1.5HP Inverter</v>
+      </c>
+      <c r="D81" t="str">
+        <v>Phòng khách</v>
+      </c>
+      <c r="E81" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F81">
+        <v>1</v>
+      </c>
+      <c r="G81" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>HD-MTX-27-RENO-WH-FULL</v>
+      </c>
+      <c r="B82" t="str">
+        <v>Điều hòa</v>
+      </c>
+      <c r="C82" t="str">
+        <v>1HP</v>
+      </c>
+      <c r="D82" t="str">
+        <v>Phòng ngủ 1</v>
+      </c>
+      <c r="E82" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F82">
+        <v>1</v>
+      </c>
+      <c r="G82" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>HD-MTX-27-RENO-WH-FULL</v>
+      </c>
+      <c r="B83" t="str">
+        <v>Tủ lạnh</v>
+      </c>
+      <c r="C83" t="str">
+        <v>Inverter 200L</v>
+      </c>
+      <c r="D83" t="str">
+        <v>Bếp</v>
+      </c>
+      <c r="E83" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F83">
+        <v>1</v>
+      </c>
+      <c r="G83" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>HD-MTX-27-RENO-WH-FULL</v>
+      </c>
+      <c r="B84" t="str">
+        <v>Máy giặt</v>
+      </c>
+      <c r="C84" t="str">
+        <v>Cửa trước 8kg</v>
+      </c>
+      <c r="D84" t="str">
+        <v>Sân sau</v>
+      </c>
+      <c r="E84" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F84">
+        <v>1</v>
+      </c>
+      <c r="G84" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>HD-MTX-27-RENO-WH-FULL</v>
+      </c>
+      <c r="B85" t="str">
+        <v>Nóng lạnh</v>
+      </c>
+      <c r="C85" t="str">
+        <v>15L</v>
+      </c>
+      <c r="D85" t="str">
+        <v>WC tầng 1</v>
+      </c>
+      <c r="E85" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F85">
+        <v>1</v>
+      </c>
+      <c r="G85" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v>HD-MTX-27-RENO-WH-FULL</v>
+      </c>
+      <c r="B86" t="str">
+        <v>Giường</v>
+      </c>
+      <c r="C86" t="str">
+        <v>Giường gỗ 1m6</v>
+      </c>
+      <c r="D86" t="str">
+        <v>Phòng ngủ 1</v>
+      </c>
+      <c r="E86" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F86">
+        <v>1</v>
+      </c>
+      <c r="G86" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v>HD-MTX-27-RENO-WH-FULL</v>
+      </c>
+      <c r="B87" t="str">
+        <v>Giường</v>
+      </c>
+      <c r="C87" t="str">
+        <v>Giường gỗ 1m6</v>
+      </c>
+      <c r="D87" t="str">
+        <v>Phòng ngủ 2</v>
+      </c>
+      <c r="E87" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F87">
+        <v>1</v>
+      </c>
+      <c r="G87" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>HD-MTX-27-RENO-WH-FULL</v>
+      </c>
+      <c r="B88" t="str">
+        <v>Quạt</v>
+      </c>
+      <c r="C88" t="str">
+        <v>Quạt trần</v>
+      </c>
+      <c r="D88" t="str">
+        <v>Phòng khách</v>
+      </c>
+      <c r="E88" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F88">
+        <v>1</v>
+      </c>
+      <c r="G88" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>HD-MTX-27-RENO-WH-FULL</v>
+      </c>
+      <c r="B89" t="str">
+        <v>Quạt</v>
+      </c>
+      <c r="C89" t="str">
+        <v>Quạt đứng</v>
+      </c>
+      <c r="D89" t="str">
+        <v>Phòng ngủ 1</v>
+      </c>
+      <c r="E89" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F89">
+        <v>1</v>
+      </c>
+      <c r="G89" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>HD-MTX-30-RENO-WH-HO-BUY</v>
+      </c>
+      <c r="B90" t="str">
+        <v>Điều hòa</v>
+      </c>
+      <c r="C90" t="str">
+        <v>Máy 1.5HP</v>
+      </c>
+      <c r="D90" t="str">
+        <v>Phòng khách</v>
+      </c>
+      <c r="E90" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F90">
+        <v>1</v>
+      </c>
+      <c r="G90" t="str">
+        <v>NT cơ bản</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>HD-MTX-30-RENO-WH-HO-BUY</v>
+      </c>
+      <c r="B91" t="str">
+        <v>Giường</v>
+      </c>
+      <c r="C91" t="str">
+        <v>Giường gỗ 1m6</v>
+      </c>
+      <c r="D91" t="str">
+        <v>Phòng ngủ</v>
+      </c>
+      <c r="E91" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F91">
+        <v>1</v>
+      </c>
+      <c r="G91" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v>HD-MTX-31-RENO-WH-HO-BUY</v>
+      </c>
+      <c r="B92" t="str">
+        <v>Điều hòa</v>
+      </c>
+      <c r="C92" t="str">
+        <v>Máy 1.5HP</v>
+      </c>
+      <c r="D92" t="str">
+        <v>Phòng khách</v>
+      </c>
+      <c r="E92" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F92">
+        <v>1</v>
+      </c>
+      <c r="G92" t="str">
+        <v>NT cơ bản</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v>HD-MTX-31-RENO-WH-HO-BUY</v>
+      </c>
+      <c r="B93" t="str">
+        <v>Giường</v>
+      </c>
+      <c r="C93" t="str">
+        <v>Giường gỗ 1m6</v>
+      </c>
+      <c r="D93" t="str">
+        <v>Phòng ngủ</v>
+      </c>
+      <c r="E93" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F93">
+        <v>1</v>
+      </c>
+      <c r="G93" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v>HD-MTX-36-RENO-RM-BASIC-HO</v>
+      </c>
+      <c r="B94" t="str">
+        <v>Giường</v>
+      </c>
+      <c r="C94" t="str">
+        <v>Giường sắt cũ</v>
+      </c>
+      <c r="D94" t="str">
+        <v>Tầng 2</v>
+      </c>
+      <c r="E94" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F94">
+        <v>2</v>
+      </c>
+      <c r="G94" t="str">
+        <v>TB chủ</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v>HD-MTX-36-RENO-RM-BASIC-HO</v>
+      </c>
+      <c r="B95" t="str">
+        <v>Quạt</v>
+      </c>
+      <c r="C95" t="str">
+        <v>Quạt trần</v>
+      </c>
+      <c r="D95" t="str">
+        <v>Hành lang</v>
+      </c>
+      <c r="E95" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F95">
+        <v>1</v>
+      </c>
+      <c r="G95" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v>HD-MTX-37-RENO-RM-BASIC-HO</v>
+      </c>
+      <c r="B96" t="str">
+        <v>Giường</v>
+      </c>
+      <c r="C96" t="str">
+        <v>Giường sắt cũ</v>
+      </c>
+      <c r="D96" t="str">
+        <v>Tầng 2</v>
+      </c>
+      <c r="E96" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F96">
+        <v>2</v>
+      </c>
+      <c r="G96" t="str">
+        <v>TB chủ</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v>HD-MTX-38-RENO-RM-BASIC-HO</v>
+      </c>
+      <c r="B97" t="str">
+        <v>Giường</v>
+      </c>
+      <c r="C97" t="str">
+        <v>Giường sắt cũ</v>
+      </c>
+      <c r="D97" t="str">
+        <v>Tầng 2</v>
+      </c>
+      <c r="E97" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F97">
+        <v>2</v>
+      </c>
+      <c r="G97" t="str">
+        <v>TB chủ</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
+        <v>HD-MTX-38-RENO-RM-BASIC-HO</v>
+      </c>
+      <c r="B98" t="str">
+        <v>Quạt</v>
+      </c>
+      <c r="C98" t="str">
+        <v>Quạt trần</v>
+      </c>
+      <c r="D98" t="str">
+        <v>Hành lang</v>
+      </c>
+      <c r="E98" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F98">
+        <v>1</v>
+      </c>
+      <c r="G98" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v>HD-MTX-39-RENO-RM-BASIC-HO</v>
+      </c>
+      <c r="B99" t="str">
+        <v>Giường</v>
+      </c>
+      <c r="C99" t="str">
+        <v>Giường sắt cũ</v>
+      </c>
+      <c r="D99" t="str">
+        <v>Tầng 2</v>
+      </c>
+      <c r="E99" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F99">
+        <v>2</v>
+      </c>
+      <c r="G99" t="str">
+        <v>TB chủ</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
+        <v>HD-MTX-44-RENO-RM-FULL</v>
+      </c>
+      <c r="B100" t="str">
+        <v>Máy giặt</v>
+      </c>
+      <c r="C100" t="str">
+        <v>Máy cũ chung</v>
+      </c>
+      <c r="D100" t="str">
+        <v>Sân phơi</v>
+      </c>
+      <c r="E100" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F100">
+        <v>1</v>
+      </c>
+      <c r="G100" t="str">
+        <v>TB dùng chung</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v>HD-MTX-44-RENO-RM-FULL</v>
+      </c>
+      <c r="B101" t="str">
+        <v>Tủ lạnh</v>
+      </c>
+      <c r="C101" t="str">
         <v>Tủ cũ tầng 1</v>
       </c>
-      <c r="D25" t="str">
+      <c r="D101" t="str">
         <v>Bếp chung</v>
       </c>
-      <c r="E25" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F25">
-        <v>1</v>
-      </c>
-      <c r="G25" t="str">
+      <c r="E101" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F101">
+        <v>1</v>
+      </c>
+      <c r="G101" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>HD-MTX-45-RENO-RM-FULL</v>
+      </c>
+      <c r="B102" t="str">
+        <v>Máy giặt</v>
+      </c>
+      <c r="C102" t="str">
+        <v>Máy cũ chung</v>
+      </c>
+      <c r="D102" t="str">
+        <v>Sân phơi</v>
+      </c>
+      <c r="E102" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F102">
+        <v>1</v>
+      </c>
+      <c r="G102" t="str">
+        <v>TB dùng chung</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>HD-MTX-45-RENO-RM-FULL</v>
+      </c>
+      <c r="B103" t="str">
+        <v>Tủ lạnh</v>
+      </c>
+      <c r="C103" t="str">
+        <v>Tủ cũ tầng 1</v>
+      </c>
+      <c r="D103" t="str">
+        <v>Bếp chung</v>
+      </c>
+      <c r="E103" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F103">
+        <v>1</v>
+      </c>
+      <c r="G103" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>HD-MTX-46-RENO-RM-FULL</v>
+      </c>
+      <c r="B104" t="str">
+        <v>Máy giặt</v>
+      </c>
+      <c r="C104" t="str">
+        <v>Máy cũ chung</v>
+      </c>
+      <c r="D104" t="str">
+        <v>Sân phơi</v>
+      </c>
+      <c r="E104" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F104">
+        <v>1</v>
+      </c>
+      <c r="G104" t="str">
+        <v>TB dùng chung</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v>HD-MTX-46-RENO-RM-FULL</v>
+      </c>
+      <c r="B105" t="str">
+        <v>Tủ lạnh</v>
+      </c>
+      <c r="C105" t="str">
+        <v>Tủ cũ tầng 1</v>
+      </c>
+      <c r="D105" t="str">
+        <v>Bếp chung</v>
+      </c>
+      <c r="E105" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F105">
+        <v>1</v>
+      </c>
+      <c r="G105" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
+        <v>HD-MTX-47-RENO-RM-FULL</v>
+      </c>
+      <c r="B106" t="str">
+        <v>Máy giặt</v>
+      </c>
+      <c r="C106" t="str">
+        <v>Máy cũ chung</v>
+      </c>
+      <c r="D106" t="str">
+        <v>Sân phơi</v>
+      </c>
+      <c r="E106" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F106">
+        <v>1</v>
+      </c>
+      <c r="G106" t="str">
+        <v>TB dùng chung</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="str">
+        <v>HD-MTX-47-RENO-RM-FULL</v>
+      </c>
+      <c r="B107" t="str">
+        <v>Tủ lạnh</v>
+      </c>
+      <c r="C107" t="str">
+        <v>Tủ cũ tầng 1</v>
+      </c>
+      <c r="D107" t="str">
+        <v>Bếp chung</v>
+      </c>
+      <c r="E107" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F107">
+        <v>1</v>
+      </c>
+      <c r="G107" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="str">
+        <v>HD-MTX-48-RENO-RM-HO-BUY</v>
+      </c>
+      <c r="B108" t="str">
+        <v>Giường</v>
+      </c>
+      <c r="C108" t="str">
+        <v>Giường sắt cũ</v>
+      </c>
+      <c r="D108" t="str">
+        <v>Tầng 2</v>
+      </c>
+      <c r="E108" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F108">
+        <v>2</v>
+      </c>
+      <c r="G108" t="str">
+        <v>TB chủ</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="str">
+        <v>HD-MTX-48-RENO-RM-HO-BUY</v>
+      </c>
+      <c r="B109" t="str">
+        <v>Quạt</v>
+      </c>
+      <c r="C109" t="str">
+        <v>Quạt trần</v>
+      </c>
+      <c r="D109" t="str">
+        <v>Hành lang</v>
+      </c>
+      <c r="E109" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F109">
+        <v>1</v>
+      </c>
+      <c r="G109" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="str">
+        <v>HD-MTX-49-RENO-RM-HO-BUY</v>
+      </c>
+      <c r="B110" t="str">
+        <v>Giường</v>
+      </c>
+      <c r="C110" t="str">
+        <v>Giường sắt cũ</v>
+      </c>
+      <c r="D110" t="str">
+        <v>Tầng 2</v>
+      </c>
+      <c r="E110" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F110">
+        <v>2</v>
+      </c>
+      <c r="G110" t="str">
+        <v>TB chủ</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="str">
+        <v>HD-MTX-50-RENO-RM-HO-BUY</v>
+      </c>
+      <c r="B111" t="str">
+        <v>Giường</v>
+      </c>
+      <c r="C111" t="str">
+        <v>Giường sắt cũ</v>
+      </c>
+      <c r="D111" t="str">
+        <v>Tầng 2</v>
+      </c>
+      <c r="E111" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F111">
+        <v>2</v>
+      </c>
+      <c r="G111" t="str">
+        <v>TB chủ</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="str">
+        <v>HD-MTX-50-RENO-RM-HO-BUY</v>
+      </c>
+      <c r="B112" t="str">
+        <v>Quạt</v>
+      </c>
+      <c r="C112" t="str">
+        <v>Quạt trần</v>
+      </c>
+      <c r="D112" t="str">
+        <v>Hành lang</v>
+      </c>
+      <c r="E112" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F112">
+        <v>1</v>
+      </c>
+      <c r="G112" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G25"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G112"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/docs/SLMS2026_import_matrix_dot1.xlsx
+++ b/docs/SLMS2026_import_matrix_dot1.xlsx
@@ -4517,7 +4517,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G112"/>
+  <dimension ref="A1:G229"/>
   <cols>
     <col min="1" max="1" width="28.83203125" customWidth="1"/>
     <col min="2" max="2" width="14.83203125" customWidth="1"/>
@@ -4585,7 +4585,7 @@
         <v>Giường gỗ 1m6</v>
       </c>
       <c r="D3" t="str">
-        <v>Phòng ngủ</v>
+        <v>Phòng ngủ 1</v>
       </c>
       <c r="E3" t="str">
         <v>GOOD</v>
@@ -4599,13 +4599,13 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>HD-MTX-07-NORENO-WH-BASIC</v>
+        <v>HD-MTX-06-NORENO-WH-BASIC</v>
       </c>
       <c r="B4" t="str">
-        <v>Điều hòa</v>
+        <v>Quạt</v>
       </c>
       <c r="C4" t="str">
-        <v>Máy 1.5HP</v>
+        <v>Quạt trần</v>
       </c>
       <c r="D4" t="str">
         <v>Phòng khách</v>
@@ -4617,21 +4617,21 @@
         <v>1</v>
       </c>
       <c r="G4" t="str">
-        <v>NT cơ bản</v>
+        <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>HD-MTX-07-NORENO-WH-BASIC</v>
+        <v>HD-MTX-06-NORENO-WH-BASIC</v>
       </c>
       <c r="B5" t="str">
-        <v>Giường</v>
+        <v>Nóng lạnh</v>
       </c>
       <c r="C5" t="str">
-        <v>Giường gỗ 1m6</v>
+        <v>15L</v>
       </c>
       <c r="D5" t="str">
-        <v>Phòng ngủ</v>
+        <v>WC tầng 1</v>
       </c>
       <c r="E5" t="str">
         <v>GOOD</v>
@@ -4645,16 +4645,16 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>HD-MTX-08-NORENO-WH-BASIC</v>
+        <v>HD-MTX-06-NORENO-WH-BASIC</v>
       </c>
       <c r="B6" t="str">
-        <v>Điều hòa</v>
+        <v>Tủ lạnh</v>
       </c>
       <c r="C6" t="str">
-        <v>Máy 1.5HP</v>
+        <v>Tủ 150L</v>
       </c>
       <c r="D6" t="str">
-        <v>Phòng khách</v>
+        <v>Bếp</v>
       </c>
       <c r="E6" t="str">
         <v>GOOD</v>
@@ -4668,16 +4668,16 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>HD-MTX-08-NORENO-WH-BASIC</v>
+        <v>HD-MTX-07-NORENO-WH-BASIC</v>
       </c>
       <c r="B7" t="str">
-        <v>Giường</v>
+        <v>Điều hòa</v>
       </c>
       <c r="C7" t="str">
-        <v>Giường gỗ 1m6</v>
+        <v>Máy 1.5HP</v>
       </c>
       <c r="D7" t="str">
-        <v>Phòng ngủ</v>
+        <v>Phòng khách</v>
       </c>
       <c r="E7" t="str">
         <v>GOOD</v>
@@ -4686,21 +4686,21 @@
         <v>1</v>
       </c>
       <c r="G7" t="str">
-        <v/>
+        <v>NT cơ bản</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>HD-MTX-09-NORENO-WH-BASIC</v>
+        <v>HD-MTX-07-NORENO-WH-BASIC</v>
       </c>
       <c r="B8" t="str">
-        <v>Điều hòa</v>
+        <v>Giường</v>
       </c>
       <c r="C8" t="str">
-        <v>Máy 1.5HP</v>
+        <v>Giường gỗ 1m6</v>
       </c>
       <c r="D8" t="str">
-        <v>Phòng khách</v>
+        <v>Phòng ngủ 1</v>
       </c>
       <c r="E8" t="str">
         <v>GOOD</v>
@@ -4709,21 +4709,21 @@
         <v>1</v>
       </c>
       <c r="G8" t="str">
-        <v>NT cơ bản</v>
+        <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>HD-MTX-09-NORENO-WH-BASIC</v>
+        <v>HD-MTX-07-NORENO-WH-BASIC</v>
       </c>
       <c r="B9" t="str">
         <v>Giường</v>
       </c>
       <c r="C9" t="str">
-        <v>Giường gỗ 1m6</v>
+        <v>Giường gỗ 1m2</v>
       </c>
       <c r="D9" t="str">
-        <v>Phòng ngủ</v>
+        <v>Phòng ngủ 2</v>
       </c>
       <c r="E9" t="str">
         <v>GOOD</v>
@@ -4737,13 +4737,13 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>HD-MTX-10-NORENO-WH-BASIC</v>
+        <v>HD-MTX-07-NORENO-WH-BASIC</v>
       </c>
       <c r="B10" t="str">
-        <v>Điều hòa</v>
+        <v>Quạt</v>
       </c>
       <c r="C10" t="str">
-        <v>Máy 1.5HP</v>
+        <v>Quạt trần</v>
       </c>
       <c r="D10" t="str">
         <v>Phòng khách</v>
@@ -4755,21 +4755,21 @@
         <v>1</v>
       </c>
       <c r="G10" t="str">
-        <v>NT cơ bản</v>
+        <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>HD-MTX-10-NORENO-WH-BASIC</v>
+        <v>HD-MTX-07-NORENO-WH-BASIC</v>
       </c>
       <c r="B11" t="str">
-        <v>Giường</v>
+        <v>Nóng lạnh</v>
       </c>
       <c r="C11" t="str">
-        <v>Giường gỗ 1m6</v>
+        <v>15L</v>
       </c>
       <c r="D11" t="str">
-        <v>Phòng ngủ</v>
+        <v>WC tầng 1</v>
       </c>
       <c r="E11" t="str">
         <v>GOOD</v>
@@ -4783,16 +4783,16 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>HD-MTX-11-NORENO-WH-FULL</v>
+        <v>HD-MTX-07-NORENO-WH-BASIC</v>
       </c>
       <c r="B12" t="str">
-        <v>Điều hòa</v>
+        <v>Tủ lạnh</v>
       </c>
       <c r="C12" t="str">
-        <v>1.5HP Inverter</v>
+        <v>Tủ 150L</v>
       </c>
       <c r="D12" t="str">
-        <v>Phòng khách</v>
+        <v>Bếp</v>
       </c>
       <c r="E12" t="str">
         <v>GOOD</v>
@@ -4801,21 +4801,21 @@
         <v>1</v>
       </c>
       <c r="G12" t="str">
-        <v/>
+        <v>NT cơ bản</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>HD-MTX-11-NORENO-WH-FULL</v>
+        <v>HD-MTX-08-NORENO-WH-BASIC</v>
       </c>
       <c r="B13" t="str">
         <v>Điều hòa</v>
       </c>
       <c r="C13" t="str">
-        <v>1HP</v>
+        <v>Máy 1.5HP</v>
       </c>
       <c r="D13" t="str">
-        <v>Phòng ngủ 1</v>
+        <v>Phòng khách</v>
       </c>
       <c r="E13" t="str">
         <v>GOOD</v>
@@ -4824,21 +4824,21 @@
         <v>1</v>
       </c>
       <c r="G13" t="str">
-        <v/>
+        <v>NT cơ bản</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>HD-MTX-11-NORENO-WH-FULL</v>
+        <v>HD-MTX-08-NORENO-WH-BASIC</v>
       </c>
       <c r="B14" t="str">
-        <v>Tủ lạnh</v>
+        <v>Giường</v>
       </c>
       <c r="C14" t="str">
-        <v>Inverter 200L</v>
+        <v>Giường gỗ 1m6</v>
       </c>
       <c r="D14" t="str">
-        <v>Bếp</v>
+        <v>Phòng ngủ 1</v>
       </c>
       <c r="E14" t="str">
         <v>GOOD</v>
@@ -4852,16 +4852,16 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>HD-MTX-11-NORENO-WH-FULL</v>
+        <v>HD-MTX-08-NORENO-WH-BASIC</v>
       </c>
       <c r="B15" t="str">
-        <v>Máy giặt</v>
+        <v>Giường</v>
       </c>
       <c r="C15" t="str">
-        <v>Cửa trước 8kg</v>
+        <v>Giường gỗ 1m2</v>
       </c>
       <c r="D15" t="str">
-        <v>Sân sau</v>
+        <v>Phòng ngủ 2</v>
       </c>
       <c r="E15" t="str">
         <v>GOOD</v>
@@ -4875,16 +4875,16 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>HD-MTX-11-NORENO-WH-FULL</v>
+        <v>HD-MTX-08-NORENO-WH-BASIC</v>
       </c>
       <c r="B16" t="str">
-        <v>Nóng lạnh</v>
+        <v>Giường</v>
       </c>
       <c r="C16" t="str">
-        <v>15L</v>
+        <v>Giường gỗ 1m2</v>
       </c>
       <c r="D16" t="str">
-        <v>WC tầng 1</v>
+        <v>Phòng ngủ 3</v>
       </c>
       <c r="E16" t="str">
         <v>GOOD</v>
@@ -4898,16 +4898,16 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>HD-MTX-11-NORENO-WH-FULL</v>
+        <v>HD-MTX-08-NORENO-WH-BASIC</v>
       </c>
       <c r="B17" t="str">
-        <v>Giường</v>
+        <v>Quạt</v>
       </c>
       <c r="C17" t="str">
-        <v>Giường gỗ 1m6</v>
+        <v>Quạt trần</v>
       </c>
       <c r="D17" t="str">
-        <v>Phòng ngủ 1</v>
+        <v>Phòng khách</v>
       </c>
       <c r="E17" t="str">
         <v>GOOD</v>
@@ -4921,16 +4921,16 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>HD-MTX-11-NORENO-WH-FULL</v>
+        <v>HD-MTX-08-NORENO-WH-BASIC</v>
       </c>
       <c r="B18" t="str">
-        <v>Giường</v>
+        <v>Nóng lạnh</v>
       </c>
       <c r="C18" t="str">
-        <v>Giường gỗ 1m6</v>
+        <v>15L</v>
       </c>
       <c r="D18" t="str">
-        <v>Phòng ngủ 2</v>
+        <v>WC tầng 1</v>
       </c>
       <c r="E18" t="str">
         <v>GOOD</v>
@@ -4944,16 +4944,16 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>HD-MTX-11-NORENO-WH-FULL</v>
+        <v>HD-MTX-08-NORENO-WH-BASIC</v>
       </c>
       <c r="B19" t="str">
-        <v>Quạt</v>
+        <v>Tủ lạnh</v>
       </c>
       <c r="C19" t="str">
-        <v>Quạt trần</v>
+        <v>Tủ 150L</v>
       </c>
       <c r="D19" t="str">
-        <v>Phòng khách</v>
+        <v>Bếp</v>
       </c>
       <c r="E19" t="str">
         <v>GOOD</v>
@@ -4962,21 +4962,21 @@
         <v>1</v>
       </c>
       <c r="G19" t="str">
-        <v/>
+        <v>NT cơ bản</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>HD-MTX-11-NORENO-WH-FULL</v>
+        <v>HD-MTX-09-NORENO-WH-BASIC</v>
       </c>
       <c r="B20" t="str">
-        <v>Quạt</v>
+        <v>Điều hòa</v>
       </c>
       <c r="C20" t="str">
-        <v>Quạt đứng</v>
+        <v>Máy 1.5HP</v>
       </c>
       <c r="D20" t="str">
-        <v>Phòng ngủ 1</v>
+        <v>Phòng khách</v>
       </c>
       <c r="E20" t="str">
         <v>GOOD</v>
@@ -4985,21 +4985,21 @@
         <v>1</v>
       </c>
       <c r="G20" t="str">
-        <v/>
+        <v>NT cơ bản</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>HD-MTX-12-NORENO-WH-FULL</v>
+        <v>HD-MTX-09-NORENO-WH-BASIC</v>
       </c>
       <c r="B21" t="str">
-        <v>Điều hòa</v>
+        <v>Giường</v>
       </c>
       <c r="C21" t="str">
-        <v>1.5HP Inverter</v>
+        <v>Giường gỗ 1m6</v>
       </c>
       <c r="D21" t="str">
-        <v>Phòng khách</v>
+        <v>Phòng ngủ 1</v>
       </c>
       <c r="E21" t="str">
         <v>GOOD</v>
@@ -5013,16 +5013,16 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>HD-MTX-12-NORENO-WH-FULL</v>
+        <v>HD-MTX-09-NORENO-WH-BASIC</v>
       </c>
       <c r="B22" t="str">
-        <v>Điều hòa</v>
+        <v>Quạt</v>
       </c>
       <c r="C22" t="str">
-        <v>1HP</v>
+        <v>Quạt trần</v>
       </c>
       <c r="D22" t="str">
-        <v>Phòng ngủ 1</v>
+        <v>Phòng khách</v>
       </c>
       <c r="E22" t="str">
         <v>GOOD</v>
@@ -5036,16 +5036,16 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>HD-MTX-12-NORENO-WH-FULL</v>
+        <v>HD-MTX-09-NORENO-WH-BASIC</v>
       </c>
       <c r="B23" t="str">
-        <v>Tủ lạnh</v>
+        <v>Nóng lạnh</v>
       </c>
       <c r="C23" t="str">
-        <v>Inverter 200L</v>
+        <v>15L</v>
       </c>
       <c r="D23" t="str">
-        <v>Bếp</v>
+        <v>WC tầng 1</v>
       </c>
       <c r="E23" t="str">
         <v>GOOD</v>
@@ -5059,16 +5059,16 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>HD-MTX-12-NORENO-WH-FULL</v>
+        <v>HD-MTX-10-NORENO-WH-BASIC</v>
       </c>
       <c r="B24" t="str">
-        <v>Máy giặt</v>
+        <v>Điều hòa</v>
       </c>
       <c r="C24" t="str">
-        <v>Cửa trước 8kg</v>
+        <v>Máy 1.5HP</v>
       </c>
       <c r="D24" t="str">
-        <v>Sân sau</v>
+        <v>Phòng khách</v>
       </c>
       <c r="E24" t="str">
         <v>GOOD</v>
@@ -5077,21 +5077,21 @@
         <v>1</v>
       </c>
       <c r="G24" t="str">
-        <v/>
+        <v>NT cơ bản</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>HD-MTX-12-NORENO-WH-FULL</v>
+        <v>HD-MTX-10-NORENO-WH-BASIC</v>
       </c>
       <c r="B25" t="str">
-        <v>Nóng lạnh</v>
+        <v>Giường</v>
       </c>
       <c r="C25" t="str">
-        <v>15L</v>
+        <v>Giường gỗ 1m6</v>
       </c>
       <c r="D25" t="str">
-        <v>WC tầng 1</v>
+        <v>Phòng ngủ 1</v>
       </c>
       <c r="E25" t="str">
         <v>GOOD</v>
@@ -5105,16 +5105,16 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>HD-MTX-12-NORENO-WH-FULL</v>
+        <v>HD-MTX-10-NORENO-WH-BASIC</v>
       </c>
       <c r="B26" t="str">
         <v>Giường</v>
       </c>
       <c r="C26" t="str">
-        <v>Giường gỗ 1m6</v>
+        <v>Giường gỗ 1m2</v>
       </c>
       <c r="D26" t="str">
-        <v>Phòng ngủ 1</v>
+        <v>Phòng ngủ 2</v>
       </c>
       <c r="E26" t="str">
         <v>GOOD</v>
@@ -5128,16 +5128,16 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>HD-MTX-12-NORENO-WH-FULL</v>
+        <v>HD-MTX-10-NORENO-WH-BASIC</v>
       </c>
       <c r="B27" t="str">
-        <v>Giường</v>
+        <v>Quạt</v>
       </c>
       <c r="C27" t="str">
-        <v>Giường gỗ 1m6</v>
+        <v>Quạt trần</v>
       </c>
       <c r="D27" t="str">
-        <v>Phòng ngủ 2</v>
+        <v>Phòng khách</v>
       </c>
       <c r="E27" t="str">
         <v>GOOD</v>
@@ -5151,16 +5151,16 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>HD-MTX-12-NORENO-WH-FULL</v>
+        <v>HD-MTX-10-NORENO-WH-BASIC</v>
       </c>
       <c r="B28" t="str">
-        <v>Quạt</v>
+        <v>Nóng lạnh</v>
       </c>
       <c r="C28" t="str">
-        <v>Quạt trần</v>
+        <v>15L</v>
       </c>
       <c r="D28" t="str">
-        <v>Phòng khách</v>
+        <v>WC tầng 1</v>
       </c>
       <c r="E28" t="str">
         <v>GOOD</v>
@@ -5174,16 +5174,16 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>HD-MTX-12-NORENO-WH-FULL</v>
+        <v>HD-MTX-10-NORENO-WH-BASIC</v>
       </c>
       <c r="B29" t="str">
-        <v>Quạt</v>
+        <v>Tủ lạnh</v>
       </c>
       <c r="C29" t="str">
-        <v>Quạt đứng</v>
+        <v>Tủ 150L</v>
       </c>
       <c r="D29" t="str">
-        <v>Phòng ngủ 1</v>
+        <v>Bếp</v>
       </c>
       <c r="E29" t="str">
         <v>GOOD</v>
@@ -5192,12 +5192,12 @@
         <v>1</v>
       </c>
       <c r="G29" t="str">
-        <v/>
+        <v>NT cơ bản</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>HD-MTX-13-NORENO-WH-FULL</v>
+        <v>HD-MTX-11-NORENO-WH-FULL</v>
       </c>
       <c r="B30" t="str">
         <v>Điều hòa</v>
@@ -5220,13 +5220,13 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>HD-MTX-13-NORENO-WH-FULL</v>
+        <v>HD-MTX-11-NORENO-WH-FULL</v>
       </c>
       <c r="B31" t="str">
         <v>Điều hòa</v>
       </c>
       <c r="C31" t="str">
-        <v>1HP</v>
+        <v>1HP Inverter</v>
       </c>
       <c r="D31" t="str">
         <v>Phòng ngủ 1</v>
@@ -5243,16 +5243,16 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>HD-MTX-13-NORENO-WH-FULL</v>
+        <v>HD-MTX-11-NORENO-WH-FULL</v>
       </c>
       <c r="B32" t="str">
-        <v>Tủ lạnh</v>
+        <v>Điều hòa</v>
       </c>
       <c r="C32" t="str">
-        <v>Inverter 200L</v>
+        <v>1HP</v>
       </c>
       <c r="D32" t="str">
-        <v>Bếp</v>
+        <v>Phòng ngủ 2</v>
       </c>
       <c r="E32" t="str">
         <v>GOOD</v>
@@ -5266,16 +5266,16 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>HD-MTX-13-NORENO-WH-FULL</v>
+        <v>HD-MTX-11-NORENO-WH-FULL</v>
       </c>
       <c r="B33" t="str">
-        <v>Máy giặt</v>
+        <v>Điều hòa</v>
       </c>
       <c r="C33" t="str">
-        <v>Cửa trước 8kg</v>
+        <v>1HP</v>
       </c>
       <c r="D33" t="str">
-        <v>Sân sau</v>
+        <v>Phòng ngủ 3</v>
       </c>
       <c r="E33" t="str">
         <v>GOOD</v>
@@ -5289,16 +5289,16 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>HD-MTX-13-NORENO-WH-FULL</v>
+        <v>HD-MTX-11-NORENO-WH-FULL</v>
       </c>
       <c r="B34" t="str">
-        <v>Nóng lạnh</v>
+        <v>Tủ lạnh</v>
       </c>
       <c r="C34" t="str">
-        <v>15L</v>
+        <v>Inverter 200L</v>
       </c>
       <c r="D34" t="str">
-        <v>WC tầng 1</v>
+        <v>Bếp</v>
       </c>
       <c r="E34" t="str">
         <v>GOOD</v>
@@ -5312,16 +5312,16 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>HD-MTX-13-NORENO-WH-FULL</v>
+        <v>HD-MTX-11-NORENO-WH-FULL</v>
       </c>
       <c r="B35" t="str">
-        <v>Giường</v>
+        <v>Máy giặt</v>
       </c>
       <c r="C35" t="str">
-        <v>Giường gỗ 1m6</v>
+        <v>Cửa trước 8kg</v>
       </c>
       <c r="D35" t="str">
-        <v>Phòng ngủ 1</v>
+        <v>Sân sau</v>
       </c>
       <c r="E35" t="str">
         <v>GOOD</v>
@@ -5335,16 +5335,16 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>HD-MTX-13-NORENO-WH-FULL</v>
+        <v>HD-MTX-11-NORENO-WH-FULL</v>
       </c>
       <c r="B36" t="str">
-        <v>Giường</v>
+        <v>Nóng lạnh</v>
       </c>
       <c r="C36" t="str">
-        <v>Giường gỗ 1m6</v>
+        <v>15L</v>
       </c>
       <c r="D36" t="str">
-        <v>Phòng ngủ 2</v>
+        <v>WC tầng 1</v>
       </c>
       <c r="E36" t="str">
         <v>GOOD</v>
@@ -5358,16 +5358,16 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>HD-MTX-13-NORENO-WH-FULL</v>
+        <v>HD-MTX-11-NORENO-WH-FULL</v>
       </c>
       <c r="B37" t="str">
-        <v>Quạt</v>
+        <v>Nóng lạnh</v>
       </c>
       <c r="C37" t="str">
-        <v>Quạt trần</v>
+        <v>15L</v>
       </c>
       <c r="D37" t="str">
-        <v>Phòng khách</v>
+        <v>WC tầng 2</v>
       </c>
       <c r="E37" t="str">
         <v>GOOD</v>
@@ -5381,13 +5381,13 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>HD-MTX-13-NORENO-WH-FULL</v>
+        <v>HD-MTX-11-NORENO-WH-FULL</v>
       </c>
       <c r="B38" t="str">
-        <v>Quạt</v>
+        <v>Giường</v>
       </c>
       <c r="C38" t="str">
-        <v>Quạt đứng</v>
+        <v>Giường gỗ 1m6</v>
       </c>
       <c r="D38" t="str">
         <v>Phòng ngủ 1</v>
@@ -5404,16 +5404,16 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>HD-MTX-14-NORENO-WH-FULL</v>
+        <v>HD-MTX-11-NORENO-WH-FULL</v>
       </c>
       <c r="B39" t="str">
-        <v>Điều hòa</v>
+        <v>Giường</v>
       </c>
       <c r="C39" t="str">
-        <v>1.5HP Inverter</v>
+        <v>Giường gỗ 1m6</v>
       </c>
       <c r="D39" t="str">
-        <v>Phòng khách</v>
+        <v>Phòng ngủ 2</v>
       </c>
       <c r="E39" t="str">
         <v>GOOD</v>
@@ -5427,16 +5427,16 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>HD-MTX-14-NORENO-WH-FULL</v>
+        <v>HD-MTX-11-NORENO-WH-FULL</v>
       </c>
       <c r="B40" t="str">
-        <v>Điều hòa</v>
+        <v>Giường</v>
       </c>
       <c r="C40" t="str">
-        <v>1HP</v>
+        <v>Giường gỗ 1m6</v>
       </c>
       <c r="D40" t="str">
-        <v>Phòng ngủ 1</v>
+        <v>Phòng ngủ 3</v>
       </c>
       <c r="E40" t="str">
         <v>GOOD</v>
@@ -5450,16 +5450,16 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>HD-MTX-14-NORENO-WH-FULL</v>
+        <v>HD-MTX-11-NORENO-WH-FULL</v>
       </c>
       <c r="B41" t="str">
-        <v>Tủ lạnh</v>
+        <v>Quạt</v>
       </c>
       <c r="C41" t="str">
-        <v>Inverter 200L</v>
+        <v>Quạt trần</v>
       </c>
       <c r="D41" t="str">
-        <v>Bếp</v>
+        <v>Phòng khách</v>
       </c>
       <c r="E41" t="str">
         <v>GOOD</v>
@@ -5473,16 +5473,16 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>HD-MTX-14-NORENO-WH-FULL</v>
+        <v>HD-MTX-11-NORENO-WH-FULL</v>
       </c>
       <c r="B42" t="str">
-        <v>Máy giặt</v>
+        <v>Quạt</v>
       </c>
       <c r="C42" t="str">
-        <v>Cửa trước 8kg</v>
+        <v>Quạt đứng</v>
       </c>
       <c r="D42" t="str">
-        <v>Sân sau</v>
+        <v>Phòng ngủ 1</v>
       </c>
       <c r="E42" t="str">
         <v>GOOD</v>
@@ -5496,16 +5496,16 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>HD-MTX-14-NORENO-WH-FULL</v>
+        <v>HD-MTX-11-NORENO-WH-FULL</v>
       </c>
       <c r="B43" t="str">
-        <v>Nóng lạnh</v>
+        <v>Quạt</v>
       </c>
       <c r="C43" t="str">
-        <v>15L</v>
+        <v>Quạt đứng</v>
       </c>
       <c r="D43" t="str">
-        <v>WC tầng 1</v>
+        <v>Phòng ngủ 2</v>
       </c>
       <c r="E43" t="str">
         <v>GOOD</v>
@@ -5519,16 +5519,16 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>HD-MTX-14-NORENO-WH-FULL</v>
+        <v>HD-MTX-11-NORENO-WH-FULL</v>
       </c>
       <c r="B44" t="str">
-        <v>Giường</v>
+        <v>Quạt</v>
       </c>
       <c r="C44" t="str">
-        <v>Giường gỗ 1m6</v>
+        <v>Quạt đứng</v>
       </c>
       <c r="D44" t="str">
-        <v>Phòng ngủ 1</v>
+        <v>Phòng ngủ 3</v>
       </c>
       <c r="E44" t="str">
         <v>GOOD</v>
@@ -5542,16 +5542,16 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>HD-MTX-14-NORENO-WH-FULL</v>
+        <v>HD-MTX-12-NORENO-WH-FULL</v>
       </c>
       <c r="B45" t="str">
-        <v>Giường</v>
+        <v>Điều hòa</v>
       </c>
       <c r="C45" t="str">
-        <v>Giường gỗ 1m6</v>
+        <v>1.5HP Inverter</v>
       </c>
       <c r="D45" t="str">
-        <v>Phòng ngủ 2</v>
+        <v>Phòng khách</v>
       </c>
       <c r="E45" t="str">
         <v>GOOD</v>
@@ -5565,16 +5565,16 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>HD-MTX-14-NORENO-WH-FULL</v>
+        <v>HD-MTX-12-NORENO-WH-FULL</v>
       </c>
       <c r="B46" t="str">
-        <v>Quạt</v>
+        <v>Điều hòa</v>
       </c>
       <c r="C46" t="str">
-        <v>Quạt trần</v>
+        <v>1HP Inverter</v>
       </c>
       <c r="D46" t="str">
-        <v>Phòng khách</v>
+        <v>Phòng ngủ 1</v>
       </c>
       <c r="E46" t="str">
         <v>GOOD</v>
@@ -5588,16 +5588,16 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>HD-MTX-14-NORENO-WH-FULL</v>
+        <v>HD-MTX-12-NORENO-WH-FULL</v>
       </c>
       <c r="B47" t="str">
-        <v>Quạt</v>
+        <v>Tủ lạnh</v>
       </c>
       <c r="C47" t="str">
-        <v>Quạt đứng</v>
+        <v>Inverter 200L</v>
       </c>
       <c r="D47" t="str">
-        <v>Phòng ngủ 1</v>
+        <v>Bếp</v>
       </c>
       <c r="E47" t="str">
         <v>GOOD</v>
@@ -5611,16 +5611,16 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>HD-MTX-15-NORENO-WH-FULL</v>
+        <v>HD-MTX-12-NORENO-WH-FULL</v>
       </c>
       <c r="B48" t="str">
-        <v>Điều hòa</v>
+        <v>Máy giặt</v>
       </c>
       <c r="C48" t="str">
-        <v>1.5HP Inverter</v>
+        <v>Cửa trước 8kg</v>
       </c>
       <c r="D48" t="str">
-        <v>Phòng khách</v>
+        <v>Sân sau</v>
       </c>
       <c r="E48" t="str">
         <v>GOOD</v>
@@ -5634,16 +5634,16 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>HD-MTX-15-NORENO-WH-FULL</v>
+        <v>HD-MTX-12-NORENO-WH-FULL</v>
       </c>
       <c r="B49" t="str">
-        <v>Điều hòa</v>
+        <v>Nóng lạnh</v>
       </c>
       <c r="C49" t="str">
-        <v>1HP</v>
+        <v>15L</v>
       </c>
       <c r="D49" t="str">
-        <v>Phòng ngủ 1</v>
+        <v>WC tầng 1</v>
       </c>
       <c r="E49" t="str">
         <v>GOOD</v>
@@ -5657,16 +5657,16 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>HD-MTX-15-NORENO-WH-FULL</v>
+        <v>HD-MTX-12-NORENO-WH-FULL</v>
       </c>
       <c r="B50" t="str">
-        <v>Tủ lạnh</v>
+        <v>Giường</v>
       </c>
       <c r="C50" t="str">
-        <v>Inverter 200L</v>
+        <v>Giường gỗ 1m6</v>
       </c>
       <c r="D50" t="str">
-        <v>Bếp</v>
+        <v>Phòng ngủ 1</v>
       </c>
       <c r="E50" t="str">
         <v>GOOD</v>
@@ -5680,16 +5680,16 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>HD-MTX-15-NORENO-WH-FULL</v>
+        <v>HD-MTX-12-NORENO-WH-FULL</v>
       </c>
       <c r="B51" t="str">
-        <v>Máy giặt</v>
+        <v>Quạt</v>
       </c>
       <c r="C51" t="str">
-        <v>Cửa trước 8kg</v>
+        <v>Quạt trần</v>
       </c>
       <c r="D51" t="str">
-        <v>Sân sau</v>
+        <v>Phòng khách</v>
       </c>
       <c r="E51" t="str">
         <v>GOOD</v>
@@ -5703,16 +5703,16 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>HD-MTX-15-NORENO-WH-FULL</v>
+        <v>HD-MTX-12-NORENO-WH-FULL</v>
       </c>
       <c r="B52" t="str">
-        <v>Nóng lạnh</v>
+        <v>Quạt</v>
       </c>
       <c r="C52" t="str">
-        <v>15L</v>
+        <v>Quạt đứng</v>
       </c>
       <c r="D52" t="str">
-        <v>WC tầng 1</v>
+        <v>Phòng ngủ 1</v>
       </c>
       <c r="E52" t="str">
         <v>GOOD</v>
@@ -5726,16 +5726,16 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>HD-MTX-15-NORENO-WH-FULL</v>
+        <v>HD-MTX-13-NORENO-WH-FULL</v>
       </c>
       <c r="B53" t="str">
-        <v>Giường</v>
+        <v>Điều hòa</v>
       </c>
       <c r="C53" t="str">
-        <v>Giường gỗ 1m6</v>
+        <v>1.5HP Inverter</v>
       </c>
       <c r="D53" t="str">
-        <v>Phòng ngủ 1</v>
+        <v>Phòng khách</v>
       </c>
       <c r="E53" t="str">
         <v>GOOD</v>
@@ -5749,16 +5749,16 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>HD-MTX-15-NORENO-WH-FULL</v>
+        <v>HD-MTX-13-NORENO-WH-FULL</v>
       </c>
       <c r="B54" t="str">
-        <v>Giường</v>
+        <v>Điều hòa</v>
       </c>
       <c r="C54" t="str">
-        <v>Giường gỗ 1m6</v>
+        <v>1HP Inverter</v>
       </c>
       <c r="D54" t="str">
-        <v>Phòng ngủ 2</v>
+        <v>Phòng ngủ 1</v>
       </c>
       <c r="E54" t="str">
         <v>GOOD</v>
@@ -5772,16 +5772,16 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>HD-MTX-15-NORENO-WH-FULL</v>
+        <v>HD-MTX-13-NORENO-WH-FULL</v>
       </c>
       <c r="B55" t="str">
-        <v>Quạt</v>
+        <v>Điều hòa</v>
       </c>
       <c r="C55" t="str">
-        <v>Quạt trần</v>
+        <v>1HP</v>
       </c>
       <c r="D55" t="str">
-        <v>Phòng khách</v>
+        <v>Phòng ngủ 2</v>
       </c>
       <c r="E55" t="str">
         <v>GOOD</v>
@@ -5795,16 +5795,16 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>HD-MTX-15-NORENO-WH-FULL</v>
+        <v>HD-MTX-13-NORENO-WH-FULL</v>
       </c>
       <c r="B56" t="str">
-        <v>Quạt</v>
+        <v>Tủ lạnh</v>
       </c>
       <c r="C56" t="str">
-        <v>Quạt đứng</v>
+        <v>Inverter 200L</v>
       </c>
       <c r="D56" t="str">
-        <v>Phòng ngủ 1</v>
+        <v>Bếp</v>
       </c>
       <c r="E56" t="str">
         <v>GOOD</v>
@@ -5818,16 +5818,16 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>HD-MTX-19-RENO-WH-BASIC-HO</v>
+        <v>HD-MTX-13-NORENO-WH-FULL</v>
       </c>
       <c r="B57" t="str">
-        <v>Điều hòa</v>
+        <v>Máy giặt</v>
       </c>
       <c r="C57" t="str">
-        <v>Máy 1.5HP</v>
+        <v>Cửa trước 8kg</v>
       </c>
       <c r="D57" t="str">
-        <v>Phòng khách</v>
+        <v>Sân sau</v>
       </c>
       <c r="E57" t="str">
         <v>GOOD</v>
@@ -5836,21 +5836,21 @@
         <v>1</v>
       </c>
       <c r="G57" t="str">
-        <v>NT cơ bản</v>
+        <v/>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>HD-MTX-19-RENO-WH-BASIC-HO</v>
+        <v>HD-MTX-13-NORENO-WH-FULL</v>
       </c>
       <c r="B58" t="str">
-        <v>Giường</v>
+        <v>Nóng lạnh</v>
       </c>
       <c r="C58" t="str">
-        <v>Giường gỗ 1m6</v>
+        <v>15L</v>
       </c>
       <c r="D58" t="str">
-        <v>Phòng ngủ</v>
+        <v>WC tầng 1</v>
       </c>
       <c r="E58" t="str">
         <v>GOOD</v>
@@ -5864,16 +5864,16 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>HD-MTX-20-RENO-WH-BASIC-HO</v>
+        <v>HD-MTX-13-NORENO-WH-FULL</v>
       </c>
       <c r="B59" t="str">
-        <v>Điều hòa</v>
+        <v>Nóng lạnh</v>
       </c>
       <c r="C59" t="str">
-        <v>Máy 1.5HP</v>
+        <v>15L</v>
       </c>
       <c r="D59" t="str">
-        <v>Phòng khách</v>
+        <v>WC tầng 2</v>
       </c>
       <c r="E59" t="str">
         <v>GOOD</v>
@@ -5882,12 +5882,12 @@
         <v>1</v>
       </c>
       <c r="G59" t="str">
-        <v>NT cơ bản</v>
+        <v/>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>HD-MTX-20-RENO-WH-BASIC-HO</v>
+        <v>HD-MTX-13-NORENO-WH-FULL</v>
       </c>
       <c r="B60" t="str">
         <v>Giường</v>
@@ -5896,7 +5896,7 @@
         <v>Giường gỗ 1m6</v>
       </c>
       <c r="D60" t="str">
-        <v>Phòng ngủ</v>
+        <v>Phòng ngủ 1</v>
       </c>
       <c r="E60" t="str">
         <v>GOOD</v>
@@ -5910,16 +5910,16 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>HD-MTX-21-RENO-WH-BASIC-HO</v>
+        <v>HD-MTX-13-NORENO-WH-FULL</v>
       </c>
       <c r="B61" t="str">
-        <v>Điều hòa</v>
+        <v>Giường</v>
       </c>
       <c r="C61" t="str">
-        <v>Máy 1.5HP</v>
+        <v>Giường gỗ 1m6</v>
       </c>
       <c r="D61" t="str">
-        <v>Phòng khách</v>
+        <v>Phòng ngủ 2</v>
       </c>
       <c r="E61" t="str">
         <v>GOOD</v>
@@ -5928,21 +5928,21 @@
         <v>1</v>
       </c>
       <c r="G61" t="str">
-        <v>NT cơ bản</v>
+        <v/>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>HD-MTX-21-RENO-WH-BASIC-HO</v>
+        <v>HD-MTX-13-NORENO-WH-FULL</v>
       </c>
       <c r="B62" t="str">
-        <v>Giường</v>
+        <v>Quạt</v>
       </c>
       <c r="C62" t="str">
-        <v>Giường gỗ 1m6</v>
+        <v>Quạt trần</v>
       </c>
       <c r="D62" t="str">
-        <v>Phòng ngủ</v>
+        <v>Phòng khách</v>
       </c>
       <c r="E62" t="str">
         <v>GOOD</v>
@@ -5956,16 +5956,16 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>HD-MTX-25-RENO-WH-FULL</v>
+        <v>HD-MTX-13-NORENO-WH-FULL</v>
       </c>
       <c r="B63" t="str">
-        <v>Điều hòa</v>
+        <v>Quạt</v>
       </c>
       <c r="C63" t="str">
-        <v>1.5HP Inverter</v>
+        <v>Quạt đứng</v>
       </c>
       <c r="D63" t="str">
-        <v>Phòng khách</v>
+        <v>Phòng ngủ 1</v>
       </c>
       <c r="E63" t="str">
         <v>GOOD</v>
@@ -5979,16 +5979,16 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>HD-MTX-25-RENO-WH-FULL</v>
+        <v>HD-MTX-13-NORENO-WH-FULL</v>
       </c>
       <c r="B64" t="str">
-        <v>Điều hòa</v>
+        <v>Quạt</v>
       </c>
       <c r="C64" t="str">
-        <v>1HP</v>
+        <v>Quạt đứng</v>
       </c>
       <c r="D64" t="str">
-        <v>Phòng ngủ 1</v>
+        <v>Phòng ngủ 2</v>
       </c>
       <c r="E64" t="str">
         <v>GOOD</v>
@@ -6002,16 +6002,16 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>HD-MTX-25-RENO-WH-FULL</v>
+        <v>HD-MTX-14-NORENO-WH-FULL</v>
       </c>
       <c r="B65" t="str">
-        <v>Tủ lạnh</v>
+        <v>Điều hòa</v>
       </c>
       <c r="C65" t="str">
-        <v>Inverter 200L</v>
+        <v>1.5HP Inverter</v>
       </c>
       <c r="D65" t="str">
-        <v>Bếp</v>
+        <v>Phòng khách</v>
       </c>
       <c r="E65" t="str">
         <v>GOOD</v>
@@ -6025,16 +6025,16 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>HD-MTX-25-RENO-WH-FULL</v>
+        <v>HD-MTX-14-NORENO-WH-FULL</v>
       </c>
       <c r="B66" t="str">
-        <v>Máy giặt</v>
+        <v>Điều hòa</v>
       </c>
       <c r="C66" t="str">
-        <v>Cửa trước 8kg</v>
+        <v>1HP Inverter</v>
       </c>
       <c r="D66" t="str">
-        <v>Sân sau</v>
+        <v>Phòng ngủ 1</v>
       </c>
       <c r="E66" t="str">
         <v>GOOD</v>
@@ -6048,16 +6048,16 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>HD-MTX-25-RENO-WH-FULL</v>
+        <v>HD-MTX-14-NORENO-WH-FULL</v>
       </c>
       <c r="B67" t="str">
-        <v>Nóng lạnh</v>
+        <v>Điều hòa</v>
       </c>
       <c r="C67" t="str">
-        <v>15L</v>
+        <v>1HP</v>
       </c>
       <c r="D67" t="str">
-        <v>WC tầng 1</v>
+        <v>Phòng ngủ 2</v>
       </c>
       <c r="E67" t="str">
         <v>GOOD</v>
@@ -6071,16 +6071,16 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>HD-MTX-25-RENO-WH-FULL</v>
+        <v>HD-MTX-14-NORENO-WH-FULL</v>
       </c>
       <c r="B68" t="str">
-        <v>Giường</v>
+        <v>Điều hòa</v>
       </c>
       <c r="C68" t="str">
-        <v>Giường gỗ 1m6</v>
+        <v>1HP</v>
       </c>
       <c r="D68" t="str">
-        <v>Phòng ngủ 1</v>
+        <v>Phòng ngủ 3</v>
       </c>
       <c r="E68" t="str">
         <v>GOOD</v>
@@ -6094,16 +6094,16 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>HD-MTX-25-RENO-WH-FULL</v>
+        <v>HD-MTX-14-NORENO-WH-FULL</v>
       </c>
       <c r="B69" t="str">
-        <v>Giường</v>
+        <v>Tủ lạnh</v>
       </c>
       <c r="C69" t="str">
-        <v>Giường gỗ 1m6</v>
+        <v>Inverter 200L</v>
       </c>
       <c r="D69" t="str">
-        <v>Phòng ngủ 2</v>
+        <v>Bếp</v>
       </c>
       <c r="E69" t="str">
         <v>GOOD</v>
@@ -6117,16 +6117,16 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>HD-MTX-25-RENO-WH-FULL</v>
+        <v>HD-MTX-14-NORENO-WH-FULL</v>
       </c>
       <c r="B70" t="str">
-        <v>Quạt</v>
+        <v>Máy giặt</v>
       </c>
       <c r="C70" t="str">
-        <v>Quạt trần</v>
+        <v>Cửa trước 8kg</v>
       </c>
       <c r="D70" t="str">
-        <v>Phòng khách</v>
+        <v>Sân sau</v>
       </c>
       <c r="E70" t="str">
         <v>GOOD</v>
@@ -6140,16 +6140,16 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>HD-MTX-25-RENO-WH-FULL</v>
+        <v>HD-MTX-14-NORENO-WH-FULL</v>
       </c>
       <c r="B71" t="str">
-        <v>Quạt</v>
+        <v>Nóng lạnh</v>
       </c>
       <c r="C71" t="str">
-        <v>Quạt đứng</v>
+        <v>15L</v>
       </c>
       <c r="D71" t="str">
-        <v>Phòng ngủ 1</v>
+        <v>WC tầng 1</v>
       </c>
       <c r="E71" t="str">
         <v>GOOD</v>
@@ -6163,16 +6163,16 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>HD-MTX-26-RENO-WH-FULL</v>
+        <v>HD-MTX-14-NORENO-WH-FULL</v>
       </c>
       <c r="B72" t="str">
-        <v>Điều hòa</v>
+        <v>Giường</v>
       </c>
       <c r="C72" t="str">
-        <v>1.5HP Inverter</v>
+        <v>Giường gỗ 1m6</v>
       </c>
       <c r="D72" t="str">
-        <v>Phòng khách</v>
+        <v>Phòng ngủ 1</v>
       </c>
       <c r="E72" t="str">
         <v>GOOD</v>
@@ -6186,16 +6186,16 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>HD-MTX-26-RENO-WH-FULL</v>
+        <v>HD-MTX-14-NORENO-WH-FULL</v>
       </c>
       <c r="B73" t="str">
-        <v>Điều hòa</v>
+        <v>Giường</v>
       </c>
       <c r="C73" t="str">
-        <v>1HP</v>
+        <v>Giường gỗ 1m6</v>
       </c>
       <c r="D73" t="str">
-        <v>Phòng ngủ 1</v>
+        <v>Phòng ngủ 2</v>
       </c>
       <c r="E73" t="str">
         <v>GOOD</v>
@@ -6209,16 +6209,16 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>HD-MTX-26-RENO-WH-FULL</v>
+        <v>HD-MTX-14-NORENO-WH-FULL</v>
       </c>
       <c r="B74" t="str">
-        <v>Tủ lạnh</v>
+        <v>Giường</v>
       </c>
       <c r="C74" t="str">
-        <v>Inverter 200L</v>
+        <v>Giường gỗ 1m6</v>
       </c>
       <c r="D74" t="str">
-        <v>Bếp</v>
+        <v>Phòng ngủ 3</v>
       </c>
       <c r="E74" t="str">
         <v>GOOD</v>
@@ -6232,16 +6232,16 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>HD-MTX-26-RENO-WH-FULL</v>
+        <v>HD-MTX-14-NORENO-WH-FULL</v>
       </c>
       <c r="B75" t="str">
-        <v>Máy giặt</v>
+        <v>Quạt</v>
       </c>
       <c r="C75" t="str">
-        <v>Cửa trước 8kg</v>
+        <v>Quạt trần</v>
       </c>
       <c r="D75" t="str">
-        <v>Sân sau</v>
+        <v>Phòng khách</v>
       </c>
       <c r="E75" t="str">
         <v>GOOD</v>
@@ -6255,16 +6255,16 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>HD-MTX-26-RENO-WH-FULL</v>
+        <v>HD-MTX-14-NORENO-WH-FULL</v>
       </c>
       <c r="B76" t="str">
-        <v>Nóng lạnh</v>
+        <v>Quạt</v>
       </c>
       <c r="C76" t="str">
-        <v>15L</v>
+        <v>Quạt đứng</v>
       </c>
       <c r="D76" t="str">
-        <v>WC tầng 1</v>
+        <v>Phòng ngủ 1</v>
       </c>
       <c r="E76" t="str">
         <v>GOOD</v>
@@ -6278,16 +6278,16 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>HD-MTX-26-RENO-WH-FULL</v>
+        <v>HD-MTX-14-NORENO-WH-FULL</v>
       </c>
       <c r="B77" t="str">
-        <v>Giường</v>
+        <v>Quạt</v>
       </c>
       <c r="C77" t="str">
-        <v>Giường gỗ 1m6</v>
+        <v>Quạt đứng</v>
       </c>
       <c r="D77" t="str">
-        <v>Phòng ngủ 1</v>
+        <v>Phòng ngủ 2</v>
       </c>
       <c r="E77" t="str">
         <v>GOOD</v>
@@ -6301,16 +6301,16 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>HD-MTX-26-RENO-WH-FULL</v>
+        <v>HD-MTX-14-NORENO-WH-FULL</v>
       </c>
       <c r="B78" t="str">
-        <v>Giường</v>
+        <v>Quạt</v>
       </c>
       <c r="C78" t="str">
-        <v>Giường gỗ 1m6</v>
+        <v>Quạt đứng</v>
       </c>
       <c r="D78" t="str">
-        <v>Phòng ngủ 2</v>
+        <v>Phòng ngủ 3</v>
       </c>
       <c r="E78" t="str">
         <v>GOOD</v>
@@ -6324,13 +6324,13 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>HD-MTX-26-RENO-WH-FULL</v>
+        <v>HD-MTX-15-NORENO-WH-FULL</v>
       </c>
       <c r="B79" t="str">
-        <v>Quạt</v>
+        <v>Điều hòa</v>
       </c>
       <c r="C79" t="str">
-        <v>Quạt trần</v>
+        <v>1.5HP Inverter</v>
       </c>
       <c r="D79" t="str">
         <v>Phòng khách</v>
@@ -6347,13 +6347,13 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>HD-MTX-26-RENO-WH-FULL</v>
+        <v>HD-MTX-15-NORENO-WH-FULL</v>
       </c>
       <c r="B80" t="str">
-        <v>Quạt</v>
+        <v>Điều hòa</v>
       </c>
       <c r="C80" t="str">
-        <v>Quạt đứng</v>
+        <v>1HP Inverter</v>
       </c>
       <c r="D80" t="str">
         <v>Phòng ngủ 1</v>
@@ -6370,16 +6370,16 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>HD-MTX-27-RENO-WH-FULL</v>
+        <v>HD-MTX-15-NORENO-WH-FULL</v>
       </c>
       <c r="B81" t="str">
-        <v>Điều hòa</v>
+        <v>Tủ lạnh</v>
       </c>
       <c r="C81" t="str">
-        <v>1.5HP Inverter</v>
+        <v>Inverter 200L</v>
       </c>
       <c r="D81" t="str">
-        <v>Phòng khách</v>
+        <v>Bếp</v>
       </c>
       <c r="E81" t="str">
         <v>GOOD</v>
@@ -6393,16 +6393,16 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>HD-MTX-27-RENO-WH-FULL</v>
+        <v>HD-MTX-15-NORENO-WH-FULL</v>
       </c>
       <c r="B82" t="str">
-        <v>Điều hòa</v>
+        <v>Máy giặt</v>
       </c>
       <c r="C82" t="str">
-        <v>1HP</v>
+        <v>Cửa trước 8kg</v>
       </c>
       <c r="D82" t="str">
-        <v>Phòng ngủ 1</v>
+        <v>Sân sau</v>
       </c>
       <c r="E82" t="str">
         <v>GOOD</v>
@@ -6416,16 +6416,16 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>HD-MTX-27-RENO-WH-FULL</v>
+        <v>HD-MTX-15-NORENO-WH-FULL</v>
       </c>
       <c r="B83" t="str">
-        <v>Tủ lạnh</v>
+        <v>Nóng lạnh</v>
       </c>
       <c r="C83" t="str">
-        <v>Inverter 200L</v>
+        <v>15L</v>
       </c>
       <c r="D83" t="str">
-        <v>Bếp</v>
+        <v>WC tầng 1</v>
       </c>
       <c r="E83" t="str">
         <v>GOOD</v>
@@ -6439,16 +6439,16 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>HD-MTX-27-RENO-WH-FULL</v>
+        <v>HD-MTX-15-NORENO-WH-FULL</v>
       </c>
       <c r="B84" t="str">
-        <v>Máy giặt</v>
+        <v>Nóng lạnh</v>
       </c>
       <c r="C84" t="str">
-        <v>Cửa trước 8kg</v>
+        <v>15L</v>
       </c>
       <c r="D84" t="str">
-        <v>Sân sau</v>
+        <v>WC tầng 2</v>
       </c>
       <c r="E84" t="str">
         <v>GOOD</v>
@@ -6462,16 +6462,16 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>HD-MTX-27-RENO-WH-FULL</v>
+        <v>HD-MTX-15-NORENO-WH-FULL</v>
       </c>
       <c r="B85" t="str">
-        <v>Nóng lạnh</v>
+        <v>Giường</v>
       </c>
       <c r="C85" t="str">
-        <v>15L</v>
+        <v>Giường gỗ 1m6</v>
       </c>
       <c r="D85" t="str">
-        <v>WC tầng 1</v>
+        <v>Phòng ngủ 1</v>
       </c>
       <c r="E85" t="str">
         <v>GOOD</v>
@@ -6485,16 +6485,16 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>HD-MTX-27-RENO-WH-FULL</v>
+        <v>HD-MTX-15-NORENO-WH-FULL</v>
       </c>
       <c r="B86" t="str">
-        <v>Giường</v>
+        <v>Quạt</v>
       </c>
       <c r="C86" t="str">
-        <v>Giường gỗ 1m6</v>
+        <v>Quạt trần</v>
       </c>
       <c r="D86" t="str">
-        <v>Phòng ngủ 1</v>
+        <v>Phòng khách</v>
       </c>
       <c r="E86" t="str">
         <v>GOOD</v>
@@ -6508,16 +6508,16 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>HD-MTX-27-RENO-WH-FULL</v>
+        <v>HD-MTX-15-NORENO-WH-FULL</v>
       </c>
       <c r="B87" t="str">
-        <v>Giường</v>
+        <v>Quạt</v>
       </c>
       <c r="C87" t="str">
-        <v>Giường gỗ 1m6</v>
+        <v>Quạt đứng</v>
       </c>
       <c r="D87" t="str">
-        <v>Phòng ngủ 2</v>
+        <v>Phòng ngủ 1</v>
       </c>
       <c r="E87" t="str">
         <v>GOOD</v>
@@ -6531,13 +6531,13 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>HD-MTX-27-RENO-WH-FULL</v>
+        <v>HD-MTX-19-RENO-WH-BASIC-HO</v>
       </c>
       <c r="B88" t="str">
-        <v>Quạt</v>
+        <v>Điều hòa</v>
       </c>
       <c r="C88" t="str">
-        <v>Quạt trần</v>
+        <v>Máy 1.5HP</v>
       </c>
       <c r="D88" t="str">
         <v>Phòng khách</v>
@@ -6549,18 +6549,18 @@
         <v>1</v>
       </c>
       <c r="G88" t="str">
-        <v/>
+        <v>NT cơ bản</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>HD-MTX-27-RENO-WH-FULL</v>
+        <v>HD-MTX-19-RENO-WH-BASIC-HO</v>
       </c>
       <c r="B89" t="str">
-        <v>Quạt</v>
+        <v>Giường</v>
       </c>
       <c r="C89" t="str">
-        <v>Quạt đứng</v>
+        <v>Giường gỗ 1m6</v>
       </c>
       <c r="D89" t="str">
         <v>Phòng ngủ 1</v>
@@ -6577,16 +6577,16 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>HD-MTX-30-RENO-WH-HO-BUY</v>
+        <v>HD-MTX-19-RENO-WH-BASIC-HO</v>
       </c>
       <c r="B90" t="str">
-        <v>Điều hòa</v>
+        <v>Giường</v>
       </c>
       <c r="C90" t="str">
-        <v>Máy 1.5HP</v>
+        <v>Giường gỗ 1m2</v>
       </c>
       <c r="D90" t="str">
-        <v>Phòng khách</v>
+        <v>Phòng ngủ 2</v>
       </c>
       <c r="E90" t="str">
         <v>GOOD</v>
@@ -6595,21 +6595,21 @@
         <v>1</v>
       </c>
       <c r="G90" t="str">
-        <v>NT cơ bản</v>
+        <v/>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>HD-MTX-30-RENO-WH-HO-BUY</v>
+        <v>HD-MTX-19-RENO-WH-BASIC-HO</v>
       </c>
       <c r="B91" t="str">
-        <v>Giường</v>
+        <v>Quạt</v>
       </c>
       <c r="C91" t="str">
-        <v>Giường gỗ 1m6</v>
+        <v>Quạt trần</v>
       </c>
       <c r="D91" t="str">
-        <v>Phòng ngủ</v>
+        <v>Phòng khách</v>
       </c>
       <c r="E91" t="str">
         <v>GOOD</v>
@@ -6623,16 +6623,16 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>HD-MTX-31-RENO-WH-HO-BUY</v>
+        <v>HD-MTX-19-RENO-WH-BASIC-HO</v>
       </c>
       <c r="B92" t="str">
-        <v>Điều hòa</v>
+        <v>Nóng lạnh</v>
       </c>
       <c r="C92" t="str">
-        <v>Máy 1.5HP</v>
+        <v>15L</v>
       </c>
       <c r="D92" t="str">
-        <v>Phòng khách</v>
+        <v>WC tầng 1</v>
       </c>
       <c r="E92" t="str">
         <v>GOOD</v>
@@ -6641,21 +6641,21 @@
         <v>1</v>
       </c>
       <c r="G92" t="str">
-        <v>NT cơ bản</v>
+        <v/>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>HD-MTX-31-RENO-WH-HO-BUY</v>
+        <v>HD-MTX-19-RENO-WH-BASIC-HO</v>
       </c>
       <c r="B93" t="str">
-        <v>Giường</v>
+        <v>Tủ lạnh</v>
       </c>
       <c r="C93" t="str">
-        <v>Giường gỗ 1m6</v>
+        <v>Tủ 150L</v>
       </c>
       <c r="D93" t="str">
-        <v>Phòng ngủ</v>
+        <v>Bếp</v>
       </c>
       <c r="E93" t="str">
         <v>GOOD</v>
@@ -6664,44 +6664,44 @@
         <v>1</v>
       </c>
       <c r="G93" t="str">
-        <v/>
+        <v>NT cơ bản</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>HD-MTX-36-RENO-RM-BASIC-HO</v>
+        <v>HD-MTX-20-RENO-WH-BASIC-HO</v>
       </c>
       <c r="B94" t="str">
-        <v>Giường</v>
+        <v>Điều hòa</v>
       </c>
       <c r="C94" t="str">
-        <v>Giường sắt cũ</v>
+        <v>Máy 1.5HP</v>
       </c>
       <c r="D94" t="str">
-        <v>Tầng 2</v>
+        <v>Phòng khách</v>
       </c>
       <c r="E94" t="str">
         <v>GOOD</v>
       </c>
       <c r="F94">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G94" t="str">
-        <v>TB chủ</v>
+        <v>NT cơ bản</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>HD-MTX-36-RENO-RM-BASIC-HO</v>
+        <v>HD-MTX-20-RENO-WH-BASIC-HO</v>
       </c>
       <c r="B95" t="str">
-        <v>Quạt</v>
+        <v>Giường</v>
       </c>
       <c r="C95" t="str">
-        <v>Quạt trần</v>
+        <v>Giường gỗ 1m6</v>
       </c>
       <c r="D95" t="str">
-        <v>Hành lang</v>
+        <v>Phòng ngủ 1</v>
       </c>
       <c r="E95" t="str">
         <v>GOOD</v>
@@ -6715,53 +6715,53 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>HD-MTX-37-RENO-RM-BASIC-HO</v>
+        <v>HD-MTX-20-RENO-WH-BASIC-HO</v>
       </c>
       <c r="B96" t="str">
         <v>Giường</v>
       </c>
       <c r="C96" t="str">
-        <v>Giường sắt cũ</v>
+        <v>Giường gỗ 1m2</v>
       </c>
       <c r="D96" t="str">
-        <v>Tầng 2</v>
+        <v>Phòng ngủ 2</v>
       </c>
       <c r="E96" t="str">
         <v>GOOD</v>
       </c>
       <c r="F96">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G96" t="str">
-        <v>TB chủ</v>
+        <v/>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>HD-MTX-38-RENO-RM-BASIC-HO</v>
+        <v>HD-MTX-20-RENO-WH-BASIC-HO</v>
       </c>
       <c r="B97" t="str">
         <v>Giường</v>
       </c>
       <c r="C97" t="str">
-        <v>Giường sắt cũ</v>
+        <v>Giường gỗ 1m2</v>
       </c>
       <c r="D97" t="str">
-        <v>Tầng 2</v>
+        <v>Phòng ngủ 3</v>
       </c>
       <c r="E97" t="str">
         <v>GOOD</v>
       </c>
       <c r="F97">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G97" t="str">
-        <v>TB chủ</v>
+        <v/>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>HD-MTX-38-RENO-RM-BASIC-HO</v>
+        <v>HD-MTX-20-RENO-WH-BASIC-HO</v>
       </c>
       <c r="B98" t="str">
         <v>Quạt</v>
@@ -6770,7 +6770,7 @@
         <v>Quạt trần</v>
       </c>
       <c r="D98" t="str">
-        <v>Hành lang</v>
+        <v>Phòng khách</v>
       </c>
       <c r="E98" t="str">
         <v>GOOD</v>
@@ -6784,39 +6784,39 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>HD-MTX-39-RENO-RM-BASIC-HO</v>
+        <v>HD-MTX-20-RENO-WH-BASIC-HO</v>
       </c>
       <c r="B99" t="str">
-        <v>Giường</v>
+        <v>Nóng lạnh</v>
       </c>
       <c r="C99" t="str">
-        <v>Giường sắt cũ</v>
+        <v>15L</v>
       </c>
       <c r="D99" t="str">
-        <v>Tầng 2</v>
+        <v>WC tầng 1</v>
       </c>
       <c r="E99" t="str">
         <v>GOOD</v>
       </c>
       <c r="F99">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G99" t="str">
-        <v>TB chủ</v>
+        <v/>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>HD-MTX-44-RENO-RM-FULL</v>
+        <v>HD-MTX-20-RENO-WH-BASIC-HO</v>
       </c>
       <c r="B100" t="str">
-        <v>Máy giặt</v>
+        <v>Tủ lạnh</v>
       </c>
       <c r="C100" t="str">
-        <v>Máy cũ chung</v>
+        <v>Tủ 150L</v>
       </c>
       <c r="D100" t="str">
-        <v>Sân phơi</v>
+        <v>Bếp</v>
       </c>
       <c r="E100" t="str">
         <v>GOOD</v>
@@ -6825,21 +6825,21 @@
         <v>1</v>
       </c>
       <c r="G100" t="str">
-        <v>TB dùng chung</v>
+        <v>NT cơ bản</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>HD-MTX-44-RENO-RM-FULL</v>
+        <v>HD-MTX-21-RENO-WH-BASIC-HO</v>
       </c>
       <c r="B101" t="str">
-        <v>Tủ lạnh</v>
+        <v>Điều hòa</v>
       </c>
       <c r="C101" t="str">
-        <v>Tủ cũ tầng 1</v>
+        <v>Máy 1.5HP</v>
       </c>
       <c r="D101" t="str">
-        <v>Bếp chung</v>
+        <v>Phòng khách</v>
       </c>
       <c r="E101" t="str">
         <v>GOOD</v>
@@ -6848,21 +6848,21 @@
         <v>1</v>
       </c>
       <c r="G101" t="str">
-        <v/>
+        <v>NT cơ bản</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>HD-MTX-45-RENO-RM-FULL</v>
+        <v>HD-MTX-21-RENO-WH-BASIC-HO</v>
       </c>
       <c r="B102" t="str">
-        <v>Máy giặt</v>
+        <v>Giường</v>
       </c>
       <c r="C102" t="str">
-        <v>Máy cũ chung</v>
+        <v>Giường gỗ 1m6</v>
       </c>
       <c r="D102" t="str">
-        <v>Sân phơi</v>
+        <v>Phòng ngủ 1</v>
       </c>
       <c r="E102" t="str">
         <v>GOOD</v>
@@ -6871,21 +6871,21 @@
         <v>1</v>
       </c>
       <c r="G102" t="str">
-        <v>TB dùng chung</v>
+        <v/>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>HD-MTX-45-RENO-RM-FULL</v>
+        <v>HD-MTX-21-RENO-WH-BASIC-HO</v>
       </c>
       <c r="B103" t="str">
-        <v>Tủ lạnh</v>
+        <v>Quạt</v>
       </c>
       <c r="C103" t="str">
-        <v>Tủ cũ tầng 1</v>
+        <v>Quạt trần</v>
       </c>
       <c r="D103" t="str">
-        <v>Bếp chung</v>
+        <v>Phòng khách</v>
       </c>
       <c r="E103" t="str">
         <v>GOOD</v>
@@ -6899,16 +6899,16 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>HD-MTX-46-RENO-RM-FULL</v>
+        <v>HD-MTX-21-RENO-WH-BASIC-HO</v>
       </c>
       <c r="B104" t="str">
-        <v>Máy giặt</v>
+        <v>Nóng lạnh</v>
       </c>
       <c r="C104" t="str">
-        <v>Máy cũ chung</v>
+        <v>15L</v>
       </c>
       <c r="D104" t="str">
-        <v>Sân phơi</v>
+        <v>WC tầng 1</v>
       </c>
       <c r="E104" t="str">
         <v>GOOD</v>
@@ -6917,21 +6917,21 @@
         <v>1</v>
       </c>
       <c r="G104" t="str">
-        <v>TB dùng chung</v>
+        <v/>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>HD-MTX-46-RENO-RM-FULL</v>
+        <v>HD-MTX-25-RENO-WH-FULL</v>
       </c>
       <c r="B105" t="str">
-        <v>Tủ lạnh</v>
+        <v>Điều hòa</v>
       </c>
       <c r="C105" t="str">
-        <v>Tủ cũ tầng 1</v>
+        <v>1.5HP Inverter</v>
       </c>
       <c r="D105" t="str">
-        <v>Bếp chung</v>
+        <v>Phòng khách</v>
       </c>
       <c r="E105" t="str">
         <v>GOOD</v>
@@ -6945,16 +6945,16 @@
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>HD-MTX-47-RENO-RM-FULL</v>
+        <v>HD-MTX-25-RENO-WH-FULL</v>
       </c>
       <c r="B106" t="str">
-        <v>Máy giặt</v>
+        <v>Điều hòa</v>
       </c>
       <c r="C106" t="str">
-        <v>Máy cũ chung</v>
+        <v>1HP Inverter</v>
       </c>
       <c r="D106" t="str">
-        <v>Sân phơi</v>
+        <v>Phòng ngủ 1</v>
       </c>
       <c r="E106" t="str">
         <v>GOOD</v>
@@ -6963,21 +6963,21 @@
         <v>1</v>
       </c>
       <c r="G106" t="str">
-        <v>TB dùng chung</v>
+        <v/>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>HD-MTX-47-RENO-RM-FULL</v>
+        <v>HD-MTX-25-RENO-WH-FULL</v>
       </c>
       <c r="B107" t="str">
-        <v>Tủ lạnh</v>
+        <v>Điều hòa</v>
       </c>
       <c r="C107" t="str">
-        <v>Tủ cũ tầng 1</v>
+        <v>1HP</v>
       </c>
       <c r="D107" t="str">
-        <v>Bếp chung</v>
+        <v>Phòng ngủ 2</v>
       </c>
       <c r="E107" t="str">
         <v>GOOD</v>
@@ -6991,39 +6991,39 @@
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>HD-MTX-48-RENO-RM-HO-BUY</v>
+        <v>HD-MTX-25-RENO-WH-FULL</v>
       </c>
       <c r="B108" t="str">
-        <v>Giường</v>
+        <v>Tủ lạnh</v>
       </c>
       <c r="C108" t="str">
-        <v>Giường sắt cũ</v>
+        <v>Inverter 200L</v>
       </c>
       <c r="D108" t="str">
-        <v>Tầng 2</v>
+        <v>Bếp</v>
       </c>
       <c r="E108" t="str">
         <v>GOOD</v>
       </c>
       <c r="F108">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G108" t="str">
-        <v>TB chủ</v>
+        <v/>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>HD-MTX-48-RENO-RM-HO-BUY</v>
+        <v>HD-MTX-25-RENO-WH-FULL</v>
       </c>
       <c r="B109" t="str">
-        <v>Quạt</v>
+        <v>Máy giặt</v>
       </c>
       <c r="C109" t="str">
-        <v>Quạt trần</v>
+        <v>Cửa trước 8kg</v>
       </c>
       <c r="D109" t="str">
-        <v>Hành lang</v>
+        <v>Sân sau</v>
       </c>
       <c r="E109" t="str">
         <v>GOOD</v>
@@ -7037,76 +7037,2767 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>HD-MTX-49-RENO-RM-HO-BUY</v>
+        <v>HD-MTX-25-RENO-WH-FULL</v>
       </c>
       <c r="B110" t="str">
-        <v>Giường</v>
+        <v>Nóng lạnh</v>
       </c>
       <c r="C110" t="str">
-        <v>Giường sắt cũ</v>
+        <v>15L</v>
       </c>
       <c r="D110" t="str">
-        <v>Tầng 2</v>
+        <v>WC tầng 1</v>
       </c>
       <c r="E110" t="str">
         <v>GOOD</v>
       </c>
       <c r="F110">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G110" t="str">
-        <v>TB chủ</v>
+        <v/>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>HD-MTX-50-RENO-RM-HO-BUY</v>
+        <v>HD-MTX-25-RENO-WH-FULL</v>
       </c>
       <c r="B111" t="str">
-        <v>Giường</v>
+        <v>Nóng lạnh</v>
       </c>
       <c r="C111" t="str">
-        <v>Giường sắt cũ</v>
+        <v>15L</v>
       </c>
       <c r="D111" t="str">
-        <v>Tầng 2</v>
+        <v>WC tầng 2</v>
       </c>
       <c r="E111" t="str">
         <v>GOOD</v>
       </c>
       <c r="F111">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G111" t="str">
-        <v>TB chủ</v>
+        <v/>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
+        <v>HD-MTX-25-RENO-WH-FULL</v>
+      </c>
+      <c r="B112" t="str">
+        <v>Giường</v>
+      </c>
+      <c r="C112" t="str">
+        <v>Giường gỗ 1m6</v>
+      </c>
+      <c r="D112" t="str">
+        <v>Phòng ngủ 1</v>
+      </c>
+      <c r="E112" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F112">
+        <v>1</v>
+      </c>
+      <c r="G112" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="str">
+        <v>HD-MTX-25-RENO-WH-FULL</v>
+      </c>
+      <c r="B113" t="str">
+        <v>Giường</v>
+      </c>
+      <c r="C113" t="str">
+        <v>Giường gỗ 1m6</v>
+      </c>
+      <c r="D113" t="str">
+        <v>Phòng ngủ 2</v>
+      </c>
+      <c r="E113" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F113">
+        <v>1</v>
+      </c>
+      <c r="G113" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="str">
+        <v>HD-MTX-25-RENO-WH-FULL</v>
+      </c>
+      <c r="B114" t="str">
+        <v>Quạt</v>
+      </c>
+      <c r="C114" t="str">
+        <v>Quạt trần</v>
+      </c>
+      <c r="D114" t="str">
+        <v>Phòng khách</v>
+      </c>
+      <c r="E114" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F114">
+        <v>1</v>
+      </c>
+      <c r="G114" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="str">
+        <v>HD-MTX-25-RENO-WH-FULL</v>
+      </c>
+      <c r="B115" t="str">
+        <v>Quạt</v>
+      </c>
+      <c r="C115" t="str">
+        <v>Quạt đứng</v>
+      </c>
+      <c r="D115" t="str">
+        <v>Phòng ngủ 1</v>
+      </c>
+      <c r="E115" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F115">
+        <v>1</v>
+      </c>
+      <c r="G115" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="str">
+        <v>HD-MTX-25-RENO-WH-FULL</v>
+      </c>
+      <c r="B116" t="str">
+        <v>Quạt</v>
+      </c>
+      <c r="C116" t="str">
+        <v>Quạt đứng</v>
+      </c>
+      <c r="D116" t="str">
+        <v>Phòng ngủ 2</v>
+      </c>
+      <c r="E116" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F116">
+        <v>1</v>
+      </c>
+      <c r="G116" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="str">
+        <v>HD-MTX-26-RENO-WH-FULL</v>
+      </c>
+      <c r="B117" t="str">
+        <v>Điều hòa</v>
+      </c>
+      <c r="C117" t="str">
+        <v>1.5HP Inverter</v>
+      </c>
+      <c r="D117" t="str">
+        <v>Phòng khách</v>
+      </c>
+      <c r="E117" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F117">
+        <v>1</v>
+      </c>
+      <c r="G117" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="str">
+        <v>HD-MTX-26-RENO-WH-FULL</v>
+      </c>
+      <c r="B118" t="str">
+        <v>Điều hòa</v>
+      </c>
+      <c r="C118" t="str">
+        <v>1HP Inverter</v>
+      </c>
+      <c r="D118" t="str">
+        <v>Phòng ngủ 1</v>
+      </c>
+      <c r="E118" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F118">
+        <v>1</v>
+      </c>
+      <c r="G118" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="str">
+        <v>HD-MTX-26-RENO-WH-FULL</v>
+      </c>
+      <c r="B119" t="str">
+        <v>Điều hòa</v>
+      </c>
+      <c r="C119" t="str">
+        <v>1HP</v>
+      </c>
+      <c r="D119" t="str">
+        <v>Phòng ngủ 2</v>
+      </c>
+      <c r="E119" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F119">
+        <v>1</v>
+      </c>
+      <c r="G119" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="str">
+        <v>HD-MTX-26-RENO-WH-FULL</v>
+      </c>
+      <c r="B120" t="str">
+        <v>Điều hòa</v>
+      </c>
+      <c r="C120" t="str">
+        <v>1HP</v>
+      </c>
+      <c r="D120" t="str">
+        <v>Phòng ngủ 3</v>
+      </c>
+      <c r="E120" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F120">
+        <v>1</v>
+      </c>
+      <c r="G120" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="str">
+        <v>HD-MTX-26-RENO-WH-FULL</v>
+      </c>
+      <c r="B121" t="str">
+        <v>Tủ lạnh</v>
+      </c>
+      <c r="C121" t="str">
+        <v>Inverter 200L</v>
+      </c>
+      <c r="D121" t="str">
+        <v>Bếp</v>
+      </c>
+      <c r="E121" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F121">
+        <v>1</v>
+      </c>
+      <c r="G121" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="str">
+        <v>HD-MTX-26-RENO-WH-FULL</v>
+      </c>
+      <c r="B122" t="str">
+        <v>Máy giặt</v>
+      </c>
+      <c r="C122" t="str">
+        <v>Cửa trước 8kg</v>
+      </c>
+      <c r="D122" t="str">
+        <v>Sân sau</v>
+      </c>
+      <c r="E122" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F122">
+        <v>1</v>
+      </c>
+      <c r="G122" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="str">
+        <v>HD-MTX-26-RENO-WH-FULL</v>
+      </c>
+      <c r="B123" t="str">
+        <v>Nóng lạnh</v>
+      </c>
+      <c r="C123" t="str">
+        <v>15L</v>
+      </c>
+      <c r="D123" t="str">
+        <v>WC tầng 1</v>
+      </c>
+      <c r="E123" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F123">
+        <v>1</v>
+      </c>
+      <c r="G123" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="str">
+        <v>HD-MTX-26-RENO-WH-FULL</v>
+      </c>
+      <c r="B124" t="str">
+        <v>Giường</v>
+      </c>
+      <c r="C124" t="str">
+        <v>Giường gỗ 1m6</v>
+      </c>
+      <c r="D124" t="str">
+        <v>Phòng ngủ 1</v>
+      </c>
+      <c r="E124" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F124">
+        <v>1</v>
+      </c>
+      <c r="G124" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="str">
+        <v>HD-MTX-26-RENO-WH-FULL</v>
+      </c>
+      <c r="B125" t="str">
+        <v>Giường</v>
+      </c>
+      <c r="C125" t="str">
+        <v>Giường gỗ 1m6</v>
+      </c>
+      <c r="D125" t="str">
+        <v>Phòng ngủ 2</v>
+      </c>
+      <c r="E125" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F125">
+        <v>1</v>
+      </c>
+      <c r="G125" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="str">
+        <v>HD-MTX-26-RENO-WH-FULL</v>
+      </c>
+      <c r="B126" t="str">
+        <v>Giường</v>
+      </c>
+      <c r="C126" t="str">
+        <v>Giường gỗ 1m6</v>
+      </c>
+      <c r="D126" t="str">
+        <v>Phòng ngủ 3</v>
+      </c>
+      <c r="E126" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F126">
+        <v>1</v>
+      </c>
+      <c r="G126" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="str">
+        <v>HD-MTX-26-RENO-WH-FULL</v>
+      </c>
+      <c r="B127" t="str">
+        <v>Quạt</v>
+      </c>
+      <c r="C127" t="str">
+        <v>Quạt trần</v>
+      </c>
+      <c r="D127" t="str">
+        <v>Phòng khách</v>
+      </c>
+      <c r="E127" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F127">
+        <v>1</v>
+      </c>
+      <c r="G127" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="str">
+        <v>HD-MTX-26-RENO-WH-FULL</v>
+      </c>
+      <c r="B128" t="str">
+        <v>Quạt</v>
+      </c>
+      <c r="C128" t="str">
+        <v>Quạt đứng</v>
+      </c>
+      <c r="D128" t="str">
+        <v>Phòng ngủ 1</v>
+      </c>
+      <c r="E128" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F128">
+        <v>1</v>
+      </c>
+      <c r="G128" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="str">
+        <v>HD-MTX-26-RENO-WH-FULL</v>
+      </c>
+      <c r="B129" t="str">
+        <v>Quạt</v>
+      </c>
+      <c r="C129" t="str">
+        <v>Quạt đứng</v>
+      </c>
+      <c r="D129" t="str">
+        <v>Phòng ngủ 2</v>
+      </c>
+      <c r="E129" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F129">
+        <v>1</v>
+      </c>
+      <c r="G129" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="str">
+        <v>HD-MTX-26-RENO-WH-FULL</v>
+      </c>
+      <c r="B130" t="str">
+        <v>Quạt</v>
+      </c>
+      <c r="C130" t="str">
+        <v>Quạt đứng</v>
+      </c>
+      <c r="D130" t="str">
+        <v>Phòng ngủ 3</v>
+      </c>
+      <c r="E130" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F130">
+        <v>1</v>
+      </c>
+      <c r="G130" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="str">
+        <v>HD-MTX-27-RENO-WH-FULL</v>
+      </c>
+      <c r="B131" t="str">
+        <v>Điều hòa</v>
+      </c>
+      <c r="C131" t="str">
+        <v>1.5HP Inverter</v>
+      </c>
+      <c r="D131" t="str">
+        <v>Phòng khách</v>
+      </c>
+      <c r="E131" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F131">
+        <v>1</v>
+      </c>
+      <c r="G131" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="str">
+        <v>HD-MTX-27-RENO-WH-FULL</v>
+      </c>
+      <c r="B132" t="str">
+        <v>Điều hòa</v>
+      </c>
+      <c r="C132" t="str">
+        <v>1HP Inverter</v>
+      </c>
+      <c r="D132" t="str">
+        <v>Phòng ngủ 1</v>
+      </c>
+      <c r="E132" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F132">
+        <v>1</v>
+      </c>
+      <c r="G132" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="str">
+        <v>HD-MTX-27-RENO-WH-FULL</v>
+      </c>
+      <c r="B133" t="str">
+        <v>Tủ lạnh</v>
+      </c>
+      <c r="C133" t="str">
+        <v>Inverter 200L</v>
+      </c>
+      <c r="D133" t="str">
+        <v>Bếp</v>
+      </c>
+      <c r="E133" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F133">
+        <v>1</v>
+      </c>
+      <c r="G133" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="str">
+        <v>HD-MTX-27-RENO-WH-FULL</v>
+      </c>
+      <c r="B134" t="str">
+        <v>Máy giặt</v>
+      </c>
+      <c r="C134" t="str">
+        <v>Cửa trước 8kg</v>
+      </c>
+      <c r="D134" t="str">
+        <v>Sân sau</v>
+      </c>
+      <c r="E134" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F134">
+        <v>1</v>
+      </c>
+      <c r="G134" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="str">
+        <v>HD-MTX-27-RENO-WH-FULL</v>
+      </c>
+      <c r="B135" t="str">
+        <v>Nóng lạnh</v>
+      </c>
+      <c r="C135" t="str">
+        <v>15L</v>
+      </c>
+      <c r="D135" t="str">
+        <v>WC tầng 1</v>
+      </c>
+      <c r="E135" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F135">
+        <v>1</v>
+      </c>
+      <c r="G135" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="str">
+        <v>HD-MTX-27-RENO-WH-FULL</v>
+      </c>
+      <c r="B136" t="str">
+        <v>Nóng lạnh</v>
+      </c>
+      <c r="C136" t="str">
+        <v>15L</v>
+      </c>
+      <c r="D136" t="str">
+        <v>WC tầng 2</v>
+      </c>
+      <c r="E136" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F136">
+        <v>1</v>
+      </c>
+      <c r="G136" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="str">
+        <v>HD-MTX-27-RENO-WH-FULL</v>
+      </c>
+      <c r="B137" t="str">
+        <v>Giường</v>
+      </c>
+      <c r="C137" t="str">
+        <v>Giường gỗ 1m6</v>
+      </c>
+      <c r="D137" t="str">
+        <v>Phòng ngủ 1</v>
+      </c>
+      <c r="E137" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F137">
+        <v>1</v>
+      </c>
+      <c r="G137" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="str">
+        <v>HD-MTX-27-RENO-WH-FULL</v>
+      </c>
+      <c r="B138" t="str">
+        <v>Quạt</v>
+      </c>
+      <c r="C138" t="str">
+        <v>Quạt trần</v>
+      </c>
+      <c r="D138" t="str">
+        <v>Phòng khách</v>
+      </c>
+      <c r="E138" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F138">
+        <v>1</v>
+      </c>
+      <c r="G138" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="str">
+        <v>HD-MTX-27-RENO-WH-FULL</v>
+      </c>
+      <c r="B139" t="str">
+        <v>Quạt</v>
+      </c>
+      <c r="C139" t="str">
+        <v>Quạt đứng</v>
+      </c>
+      <c r="D139" t="str">
+        <v>Phòng ngủ 1</v>
+      </c>
+      <c r="E139" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F139">
+        <v>1</v>
+      </c>
+      <c r="G139" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="str">
+        <v>HD-MTX-30-RENO-WH-HO-BUY</v>
+      </c>
+      <c r="B140" t="str">
+        <v>Điều hòa</v>
+      </c>
+      <c r="C140" t="str">
+        <v>Máy 1.5HP</v>
+      </c>
+      <c r="D140" t="str">
+        <v>Phòng khách</v>
+      </c>
+      <c r="E140" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F140">
+        <v>1</v>
+      </c>
+      <c r="G140" t="str">
+        <v>NT cơ bản</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="str">
+        <v>HD-MTX-30-RENO-WH-HO-BUY</v>
+      </c>
+      <c r="B141" t="str">
+        <v>Giường</v>
+      </c>
+      <c r="C141" t="str">
+        <v>Giường gỗ 1m6</v>
+      </c>
+      <c r="D141" t="str">
+        <v>Phòng ngủ 1</v>
+      </c>
+      <c r="E141" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F141">
+        <v>1</v>
+      </c>
+      <c r="G141" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="str">
+        <v>HD-MTX-30-RENO-WH-HO-BUY</v>
+      </c>
+      <c r="B142" t="str">
+        <v>Quạt</v>
+      </c>
+      <c r="C142" t="str">
+        <v>Quạt trần</v>
+      </c>
+      <c r="D142" t="str">
+        <v>Phòng khách</v>
+      </c>
+      <c r="E142" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F142">
+        <v>1</v>
+      </c>
+      <c r="G142" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="str">
+        <v>HD-MTX-30-RENO-WH-HO-BUY</v>
+      </c>
+      <c r="B143" t="str">
+        <v>Nóng lạnh</v>
+      </c>
+      <c r="C143" t="str">
+        <v>15L</v>
+      </c>
+      <c r="D143" t="str">
+        <v>WC tầng 1</v>
+      </c>
+      <c r="E143" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F143">
+        <v>1</v>
+      </c>
+      <c r="G143" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="str">
+        <v>HD-MTX-30-RENO-WH-HO-BUY</v>
+      </c>
+      <c r="B144" t="str">
+        <v>Tủ lạnh</v>
+      </c>
+      <c r="C144" t="str">
+        <v>Tủ 150L</v>
+      </c>
+      <c r="D144" t="str">
+        <v>Bếp</v>
+      </c>
+      <c r="E144" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F144">
+        <v>1</v>
+      </c>
+      <c r="G144" t="str">
+        <v>NT cơ bản</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="str">
+        <v>HD-MTX-31-RENO-WH-HO-BUY</v>
+      </c>
+      <c r="B145" t="str">
+        <v>Điều hòa</v>
+      </c>
+      <c r="C145" t="str">
+        <v>Máy 1.5HP</v>
+      </c>
+      <c r="D145" t="str">
+        <v>Phòng khách</v>
+      </c>
+      <c r="E145" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F145">
+        <v>1</v>
+      </c>
+      <c r="G145" t="str">
+        <v>NT cơ bản</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="str">
+        <v>HD-MTX-31-RENO-WH-HO-BUY</v>
+      </c>
+      <c r="B146" t="str">
+        <v>Giường</v>
+      </c>
+      <c r="C146" t="str">
+        <v>Giường gỗ 1m6</v>
+      </c>
+      <c r="D146" t="str">
+        <v>Phòng ngủ 1</v>
+      </c>
+      <c r="E146" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F146">
+        <v>1</v>
+      </c>
+      <c r="G146" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="str">
+        <v>HD-MTX-31-RENO-WH-HO-BUY</v>
+      </c>
+      <c r="B147" t="str">
+        <v>Giường</v>
+      </c>
+      <c r="C147" t="str">
+        <v>Giường gỗ 1m2</v>
+      </c>
+      <c r="D147" t="str">
+        <v>Phòng ngủ 2</v>
+      </c>
+      <c r="E147" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F147">
+        <v>1</v>
+      </c>
+      <c r="G147" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="str">
+        <v>HD-MTX-31-RENO-WH-HO-BUY</v>
+      </c>
+      <c r="B148" t="str">
+        <v>Quạt</v>
+      </c>
+      <c r="C148" t="str">
+        <v>Quạt trần</v>
+      </c>
+      <c r="D148" t="str">
+        <v>Phòng khách</v>
+      </c>
+      <c r="E148" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F148">
+        <v>1</v>
+      </c>
+      <c r="G148" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="str">
+        <v>HD-MTX-31-RENO-WH-HO-BUY</v>
+      </c>
+      <c r="B149" t="str">
+        <v>Nóng lạnh</v>
+      </c>
+      <c r="C149" t="str">
+        <v>15L</v>
+      </c>
+      <c r="D149" t="str">
+        <v>WC tầng 1</v>
+      </c>
+      <c r="E149" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F149">
+        <v>1</v>
+      </c>
+      <c r="G149" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="str">
+        <v>HD-MTX-31-RENO-WH-HO-BUY</v>
+      </c>
+      <c r="B150" t="str">
+        <v>Tủ lạnh</v>
+      </c>
+      <c r="C150" t="str">
+        <v>Tủ 150L</v>
+      </c>
+      <c r="D150" t="str">
+        <v>Bếp</v>
+      </c>
+      <c r="E150" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F150">
+        <v>1</v>
+      </c>
+      <c r="G150" t="str">
+        <v>NT cơ bản</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="str">
+        <v>HD-MTX-36-RENO-RM-BASIC-HO</v>
+      </c>
+      <c r="B151" t="str">
+        <v>Giường</v>
+      </c>
+      <c r="C151" t="str">
+        <v>Giường sắt cũ</v>
+      </c>
+      <c r="D151" t="str">
+        <v>Phòng 101</v>
+      </c>
+      <c r="E151" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F151">
+        <v>1</v>
+      </c>
+      <c r="G151" t="str">
+        <v>TB chủ</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="str">
+        <v>HD-MTX-36-RENO-RM-BASIC-HO</v>
+      </c>
+      <c r="B152" t="str">
+        <v>Giường</v>
+      </c>
+      <c r="C152" t="str">
+        <v>Giường sắt cũ</v>
+      </c>
+      <c r="D152" t="str">
+        <v>Phòng 102</v>
+      </c>
+      <c r="E152" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F152">
+        <v>1</v>
+      </c>
+      <c r="G152" t="str">
+        <v>TB chủ</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="str">
+        <v>HD-MTX-36-RENO-RM-BASIC-HO</v>
+      </c>
+      <c r="B153" t="str">
+        <v>Giường</v>
+      </c>
+      <c r="C153" t="str">
+        <v>Giường sắt cũ</v>
+      </c>
+      <c r="D153" t="str">
+        <v>Phòng 103</v>
+      </c>
+      <c r="E153" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F153">
+        <v>1</v>
+      </c>
+      <c r="G153" t="str">
+        <v>TB chủ</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="str">
+        <v>HD-MTX-36-RENO-RM-BASIC-HO</v>
+      </c>
+      <c r="B154" t="str">
+        <v>Quạt</v>
+      </c>
+      <c r="C154" t="str">
+        <v>Quạt trần</v>
+      </c>
+      <c r="D154" t="str">
+        <v>Hành lang</v>
+      </c>
+      <c r="E154" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F154">
+        <v>1</v>
+      </c>
+      <c r="G154" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="str">
+        <v>HD-MTX-36-RENO-RM-BASIC-HO</v>
+      </c>
+      <c r="B155" t="str">
+        <v>Nóng lạnh</v>
+      </c>
+      <c r="C155" t="str">
+        <v>Máy cũ</v>
+      </c>
+      <c r="D155" t="str">
+        <v>WC chung</v>
+      </c>
+      <c r="E155" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F155">
+        <v>1</v>
+      </c>
+      <c r="G155" t="str">
+        <v>Dùng chung</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="str">
+        <v>HD-MTX-37-RENO-RM-BASIC-HO</v>
+      </c>
+      <c r="B156" t="str">
+        <v>Giường</v>
+      </c>
+      <c r="C156" t="str">
+        <v>Giường sắt cũ</v>
+      </c>
+      <c r="D156" t="str">
+        <v>Phòng 101</v>
+      </c>
+      <c r="E156" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F156">
+        <v>1</v>
+      </c>
+      <c r="G156" t="str">
+        <v>TB chủ</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="str">
+        <v>HD-MTX-37-RENO-RM-BASIC-HO</v>
+      </c>
+      <c r="B157" t="str">
+        <v>Giường</v>
+      </c>
+      <c r="C157" t="str">
+        <v>Giường sắt cũ</v>
+      </c>
+      <c r="D157" t="str">
+        <v>Phòng 102</v>
+      </c>
+      <c r="E157" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F157">
+        <v>1</v>
+      </c>
+      <c r="G157" t="str">
+        <v>TB chủ</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="str">
+        <v>HD-MTX-37-RENO-RM-BASIC-HO</v>
+      </c>
+      <c r="B158" t="str">
+        <v>Giường</v>
+      </c>
+      <c r="C158" t="str">
+        <v>Giường sắt cũ</v>
+      </c>
+      <c r="D158" t="str">
+        <v>Phòng 103</v>
+      </c>
+      <c r="E158" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F158">
+        <v>1</v>
+      </c>
+      <c r="G158" t="str">
+        <v>TB chủ</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="str">
+        <v>HD-MTX-37-RENO-RM-BASIC-HO</v>
+      </c>
+      <c r="B159" t="str">
+        <v>Quạt</v>
+      </c>
+      <c r="C159" t="str">
+        <v>Quạt trần</v>
+      </c>
+      <c r="D159" t="str">
+        <v>Hành lang</v>
+      </c>
+      <c r="E159" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F159">
+        <v>1</v>
+      </c>
+      <c r="G159" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="str">
+        <v>HD-MTX-37-RENO-RM-BASIC-HO</v>
+      </c>
+      <c r="B160" t="str">
+        <v>Nóng lạnh</v>
+      </c>
+      <c r="C160" t="str">
+        <v>Máy cũ</v>
+      </c>
+      <c r="D160" t="str">
+        <v>WC chung</v>
+      </c>
+      <c r="E160" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F160">
+        <v>1</v>
+      </c>
+      <c r="G160" t="str">
+        <v>Dùng chung</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="str">
+        <v>HD-MTX-38-RENO-RM-BASIC-HO</v>
+      </c>
+      <c r="B161" t="str">
+        <v>Giường</v>
+      </c>
+      <c r="C161" t="str">
+        <v>Giường sắt cũ</v>
+      </c>
+      <c r="D161" t="str">
+        <v>Phòng 101</v>
+      </c>
+      <c r="E161" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F161">
+        <v>1</v>
+      </c>
+      <c r="G161" t="str">
+        <v>TB chủ</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="str">
+        <v>HD-MTX-38-RENO-RM-BASIC-HO</v>
+      </c>
+      <c r="B162" t="str">
+        <v>Giường</v>
+      </c>
+      <c r="C162" t="str">
+        <v>Giường sắt cũ</v>
+      </c>
+      <c r="D162" t="str">
+        <v>Phòng 102</v>
+      </c>
+      <c r="E162" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F162">
+        <v>1</v>
+      </c>
+      <c r="G162" t="str">
+        <v>TB chủ</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="str">
+        <v>HD-MTX-38-RENO-RM-BASIC-HO</v>
+      </c>
+      <c r="B163" t="str">
+        <v>Giường</v>
+      </c>
+      <c r="C163" t="str">
+        <v>Giường sắt cũ</v>
+      </c>
+      <c r="D163" t="str">
+        <v>Phòng 103</v>
+      </c>
+      <c r="E163" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F163">
+        <v>1</v>
+      </c>
+      <c r="G163" t="str">
+        <v>TB chủ</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="str">
+        <v>HD-MTX-38-RENO-RM-BASIC-HO</v>
+      </c>
+      <c r="B164" t="str">
+        <v>Quạt</v>
+      </c>
+      <c r="C164" t="str">
+        <v>Quạt trần</v>
+      </c>
+      <c r="D164" t="str">
+        <v>Hành lang</v>
+      </c>
+      <c r="E164" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F164">
+        <v>1</v>
+      </c>
+      <c r="G164" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="str">
+        <v>HD-MTX-38-RENO-RM-BASIC-HO</v>
+      </c>
+      <c r="B165" t="str">
+        <v>Nóng lạnh</v>
+      </c>
+      <c r="C165" t="str">
+        <v>Máy cũ</v>
+      </c>
+      <c r="D165" t="str">
+        <v>WC chung</v>
+      </c>
+      <c r="E165" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F165">
+        <v>1</v>
+      </c>
+      <c r="G165" t="str">
+        <v>Dùng chung</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="str">
+        <v>HD-MTX-39-RENO-RM-BASIC-HO</v>
+      </c>
+      <c r="B166" t="str">
+        <v>Giường</v>
+      </c>
+      <c r="C166" t="str">
+        <v>Giường sắt cũ</v>
+      </c>
+      <c r="D166" t="str">
+        <v>Phòng 101</v>
+      </c>
+      <c r="E166" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F166">
+        <v>1</v>
+      </c>
+      <c r="G166" t="str">
+        <v>TB chủ</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="str">
+        <v>HD-MTX-39-RENO-RM-BASIC-HO</v>
+      </c>
+      <c r="B167" t="str">
+        <v>Giường</v>
+      </c>
+      <c r="C167" t="str">
+        <v>Giường sắt cũ</v>
+      </c>
+      <c r="D167" t="str">
+        <v>Phòng 102</v>
+      </c>
+      <c r="E167" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F167">
+        <v>1</v>
+      </c>
+      <c r="G167" t="str">
+        <v>TB chủ</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="str">
+        <v>HD-MTX-39-RENO-RM-BASIC-HO</v>
+      </c>
+      <c r="B168" t="str">
+        <v>Giường</v>
+      </c>
+      <c r="C168" t="str">
+        <v>Giường sắt cũ</v>
+      </c>
+      <c r="D168" t="str">
+        <v>Phòng 103</v>
+      </c>
+      <c r="E168" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F168">
+        <v>1</v>
+      </c>
+      <c r="G168" t="str">
+        <v>TB chủ</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="str">
+        <v>HD-MTX-39-RENO-RM-BASIC-HO</v>
+      </c>
+      <c r="B169" t="str">
+        <v>Quạt</v>
+      </c>
+      <c r="C169" t="str">
+        <v>Quạt trần</v>
+      </c>
+      <c r="D169" t="str">
+        <v>Hành lang</v>
+      </c>
+      <c r="E169" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F169">
+        <v>1</v>
+      </c>
+      <c r="G169" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="str">
+        <v>HD-MTX-39-RENO-RM-BASIC-HO</v>
+      </c>
+      <c r="B170" t="str">
+        <v>Nóng lạnh</v>
+      </c>
+      <c r="C170" t="str">
+        <v>Máy cũ</v>
+      </c>
+      <c r="D170" t="str">
+        <v>WC chung</v>
+      </c>
+      <c r="E170" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F170">
+        <v>1</v>
+      </c>
+      <c r="G170" t="str">
+        <v>Dùng chung</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="str">
+        <v>HD-MTX-44-RENO-RM-FULL</v>
+      </c>
+      <c r="B171" t="str">
+        <v>Máy giặt</v>
+      </c>
+      <c r="C171" t="str">
+        <v>Máy cũ chung</v>
+      </c>
+      <c r="D171" t="str">
+        <v>Sân phơi</v>
+      </c>
+      <c r="E171" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F171">
+        <v>1</v>
+      </c>
+      <c r="G171" t="str">
+        <v>TB dùng chung</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="str">
+        <v>HD-MTX-44-RENO-RM-FULL</v>
+      </c>
+      <c r="B172" t="str">
+        <v>Tủ lạnh</v>
+      </c>
+      <c r="C172" t="str">
+        <v>Tủ cũ tầng 1</v>
+      </c>
+      <c r="D172" t="str">
+        <v>Bếp chung</v>
+      </c>
+      <c r="E172" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F172">
+        <v>1</v>
+      </c>
+      <c r="G172" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="str">
+        <v>HD-MTX-44-RENO-RM-FULL</v>
+      </c>
+      <c r="B173" t="str">
+        <v>Nóng lạnh</v>
+      </c>
+      <c r="C173" t="str">
+        <v>Máy cũ</v>
+      </c>
+      <c r="D173" t="str">
+        <v>WC chung</v>
+      </c>
+      <c r="E173" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F173">
+        <v>1</v>
+      </c>
+      <c r="G173" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="str">
+        <v>HD-MTX-44-RENO-RM-FULL</v>
+      </c>
+      <c r="B174" t="str">
+        <v>Giường</v>
+      </c>
+      <c r="C174" t="str">
+        <v>Giường gỗ 1m6</v>
+      </c>
+      <c r="D174" t="str">
+        <v>Phòng 101</v>
+      </c>
+      <c r="E174" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F174">
+        <v>1</v>
+      </c>
+      <c r="G174" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="str">
+        <v>HD-MTX-44-RENO-RM-FULL</v>
+      </c>
+      <c r="B175" t="str">
+        <v>Quạt</v>
+      </c>
+      <c r="C175" t="str">
+        <v>Quạt đứng</v>
+      </c>
+      <c r="D175" t="str">
+        <v>Phòng 101</v>
+      </c>
+      <c r="E175" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F175">
+        <v>1</v>
+      </c>
+      <c r="G175" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="str">
+        <v>HD-MTX-44-RENO-RM-FULL</v>
+      </c>
+      <c r="B176" t="str">
+        <v>Giường</v>
+      </c>
+      <c r="C176" t="str">
+        <v>Giường gỗ 1m6</v>
+      </c>
+      <c r="D176" t="str">
+        <v>Phòng 102</v>
+      </c>
+      <c r="E176" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F176">
+        <v>1</v>
+      </c>
+      <c r="G176" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="str">
+        <v>HD-MTX-44-RENO-RM-FULL</v>
+      </c>
+      <c r="B177" t="str">
+        <v>Quạt</v>
+      </c>
+      <c r="C177" t="str">
+        <v>Quạt đứng</v>
+      </c>
+      <c r="D177" t="str">
+        <v>Phòng 102</v>
+      </c>
+      <c r="E177" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F177">
+        <v>1</v>
+      </c>
+      <c r="G177" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="str">
+        <v>HD-MTX-44-RENO-RM-FULL</v>
+      </c>
+      <c r="B178" t="str">
+        <v>Giường</v>
+      </c>
+      <c r="C178" t="str">
+        <v>Giường gỗ 1m6</v>
+      </c>
+      <c r="D178" t="str">
+        <v>Phòng 103</v>
+      </c>
+      <c r="E178" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F178">
+        <v>1</v>
+      </c>
+      <c r="G178" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="str">
+        <v>HD-MTX-44-RENO-RM-FULL</v>
+      </c>
+      <c r="B179" t="str">
+        <v>Quạt</v>
+      </c>
+      <c r="C179" t="str">
+        <v>Quạt đứng</v>
+      </c>
+      <c r="D179" t="str">
+        <v>Phòng 103</v>
+      </c>
+      <c r="E179" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F179">
+        <v>1</v>
+      </c>
+      <c r="G179" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="str">
+        <v>HD-MTX-44-RENO-RM-FULL</v>
+      </c>
+      <c r="B180" t="str">
+        <v>Giường</v>
+      </c>
+      <c r="C180" t="str">
+        <v>Giường gỗ 1m6</v>
+      </c>
+      <c r="D180" t="str">
+        <v>Phòng 104</v>
+      </c>
+      <c r="E180" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F180">
+        <v>1</v>
+      </c>
+      <c r="G180" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="str">
+        <v>HD-MTX-44-RENO-RM-FULL</v>
+      </c>
+      <c r="B181" t="str">
+        <v>Quạt</v>
+      </c>
+      <c r="C181" t="str">
+        <v>Quạt đứng</v>
+      </c>
+      <c r="D181" t="str">
+        <v>Phòng 104</v>
+      </c>
+      <c r="E181" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F181">
+        <v>1</v>
+      </c>
+      <c r="G181" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="str">
+        <v>HD-MTX-45-RENO-RM-FULL</v>
+      </c>
+      <c r="B182" t="str">
+        <v>Máy giặt</v>
+      </c>
+      <c r="C182" t="str">
+        <v>Máy cũ chung</v>
+      </c>
+      <c r="D182" t="str">
+        <v>Sân phơi</v>
+      </c>
+      <c r="E182" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F182">
+        <v>1</v>
+      </c>
+      <c r="G182" t="str">
+        <v>TB dùng chung</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="str">
+        <v>HD-MTX-45-RENO-RM-FULL</v>
+      </c>
+      <c r="B183" t="str">
+        <v>Tủ lạnh</v>
+      </c>
+      <c r="C183" t="str">
+        <v>Tủ cũ tầng 1</v>
+      </c>
+      <c r="D183" t="str">
+        <v>Bếp chung</v>
+      </c>
+      <c r="E183" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F183">
+        <v>1</v>
+      </c>
+      <c r="G183" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="str">
+        <v>HD-MTX-45-RENO-RM-FULL</v>
+      </c>
+      <c r="B184" t="str">
+        <v>Nóng lạnh</v>
+      </c>
+      <c r="C184" t="str">
+        <v>Máy cũ</v>
+      </c>
+      <c r="D184" t="str">
+        <v>WC chung</v>
+      </c>
+      <c r="E184" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F184">
+        <v>1</v>
+      </c>
+      <c r="G184" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="str">
+        <v>HD-MTX-45-RENO-RM-FULL</v>
+      </c>
+      <c r="B185" t="str">
+        <v>Giường</v>
+      </c>
+      <c r="C185" t="str">
+        <v>Giường gỗ 1m6</v>
+      </c>
+      <c r="D185" t="str">
+        <v>Phòng 101</v>
+      </c>
+      <c r="E185" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F185">
+        <v>1</v>
+      </c>
+      <c r="G185" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="str">
+        <v>HD-MTX-45-RENO-RM-FULL</v>
+      </c>
+      <c r="B186" t="str">
+        <v>Quạt</v>
+      </c>
+      <c r="C186" t="str">
+        <v>Quạt đứng</v>
+      </c>
+      <c r="D186" t="str">
+        <v>Phòng 101</v>
+      </c>
+      <c r="E186" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F186">
+        <v>1</v>
+      </c>
+      <c r="G186" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="str">
+        <v>HD-MTX-45-RENO-RM-FULL</v>
+      </c>
+      <c r="B187" t="str">
+        <v>Giường</v>
+      </c>
+      <c r="C187" t="str">
+        <v>Giường gỗ 1m6</v>
+      </c>
+      <c r="D187" t="str">
+        <v>Phòng 102</v>
+      </c>
+      <c r="E187" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F187">
+        <v>1</v>
+      </c>
+      <c r="G187" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="str">
+        <v>HD-MTX-45-RENO-RM-FULL</v>
+      </c>
+      <c r="B188" t="str">
+        <v>Quạt</v>
+      </c>
+      <c r="C188" t="str">
+        <v>Quạt đứng</v>
+      </c>
+      <c r="D188" t="str">
+        <v>Phòng 102</v>
+      </c>
+      <c r="E188" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F188">
+        <v>1</v>
+      </c>
+      <c r="G188" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="str">
+        <v>HD-MTX-45-RENO-RM-FULL</v>
+      </c>
+      <c r="B189" t="str">
+        <v>Giường</v>
+      </c>
+      <c r="C189" t="str">
+        <v>Giường gỗ 1m6</v>
+      </c>
+      <c r="D189" t="str">
+        <v>Phòng 103</v>
+      </c>
+      <c r="E189" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F189">
+        <v>1</v>
+      </c>
+      <c r="G189" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="str">
+        <v>HD-MTX-45-RENO-RM-FULL</v>
+      </c>
+      <c r="B190" t="str">
+        <v>Quạt</v>
+      </c>
+      <c r="C190" t="str">
+        <v>Quạt đứng</v>
+      </c>
+      <c r="D190" t="str">
+        <v>Phòng 103</v>
+      </c>
+      <c r="E190" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F190">
+        <v>1</v>
+      </c>
+      <c r="G190" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="str">
+        <v>HD-MTX-45-RENO-RM-FULL</v>
+      </c>
+      <c r="B191" t="str">
+        <v>Giường</v>
+      </c>
+      <c r="C191" t="str">
+        <v>Giường gỗ 1m6</v>
+      </c>
+      <c r="D191" t="str">
+        <v>Phòng 104</v>
+      </c>
+      <c r="E191" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F191">
+        <v>1</v>
+      </c>
+      <c r="G191" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="str">
+        <v>HD-MTX-45-RENO-RM-FULL</v>
+      </c>
+      <c r="B192" t="str">
+        <v>Quạt</v>
+      </c>
+      <c r="C192" t="str">
+        <v>Quạt đứng</v>
+      </c>
+      <c r="D192" t="str">
+        <v>Phòng 104</v>
+      </c>
+      <c r="E192" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F192">
+        <v>1</v>
+      </c>
+      <c r="G192" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="str">
+        <v>HD-MTX-46-RENO-RM-FULL</v>
+      </c>
+      <c r="B193" t="str">
+        <v>Máy giặt</v>
+      </c>
+      <c r="C193" t="str">
+        <v>Máy cũ chung</v>
+      </c>
+      <c r="D193" t="str">
+        <v>Sân phơi</v>
+      </c>
+      <c r="E193" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F193">
+        <v>1</v>
+      </c>
+      <c r="G193" t="str">
+        <v>TB dùng chung</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="str">
+        <v>HD-MTX-46-RENO-RM-FULL</v>
+      </c>
+      <c r="B194" t="str">
+        <v>Tủ lạnh</v>
+      </c>
+      <c r="C194" t="str">
+        <v>Tủ cũ tầng 1</v>
+      </c>
+      <c r="D194" t="str">
+        <v>Bếp chung</v>
+      </c>
+      <c r="E194" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F194">
+        <v>1</v>
+      </c>
+      <c r="G194" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="str">
+        <v>HD-MTX-46-RENO-RM-FULL</v>
+      </c>
+      <c r="B195" t="str">
+        <v>Nóng lạnh</v>
+      </c>
+      <c r="C195" t="str">
+        <v>Máy cũ</v>
+      </c>
+      <c r="D195" t="str">
+        <v>WC chung</v>
+      </c>
+      <c r="E195" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F195">
+        <v>1</v>
+      </c>
+      <c r="G195" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="str">
+        <v>HD-MTX-46-RENO-RM-FULL</v>
+      </c>
+      <c r="B196" t="str">
+        <v>Giường</v>
+      </c>
+      <c r="C196" t="str">
+        <v>Giường gỗ 1m6</v>
+      </c>
+      <c r="D196" t="str">
+        <v>Phòng 101</v>
+      </c>
+      <c r="E196" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F196">
+        <v>1</v>
+      </c>
+      <c r="G196" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="str">
+        <v>HD-MTX-46-RENO-RM-FULL</v>
+      </c>
+      <c r="B197" t="str">
+        <v>Quạt</v>
+      </c>
+      <c r="C197" t="str">
+        <v>Quạt đứng</v>
+      </c>
+      <c r="D197" t="str">
+        <v>Phòng 101</v>
+      </c>
+      <c r="E197" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F197">
+        <v>1</v>
+      </c>
+      <c r="G197" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="str">
+        <v>HD-MTX-46-RENO-RM-FULL</v>
+      </c>
+      <c r="B198" t="str">
+        <v>Giường</v>
+      </c>
+      <c r="C198" t="str">
+        <v>Giường gỗ 1m6</v>
+      </c>
+      <c r="D198" t="str">
+        <v>Phòng 102</v>
+      </c>
+      <c r="E198" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F198">
+        <v>1</v>
+      </c>
+      <c r="G198" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="str">
+        <v>HD-MTX-46-RENO-RM-FULL</v>
+      </c>
+      <c r="B199" t="str">
+        <v>Quạt</v>
+      </c>
+      <c r="C199" t="str">
+        <v>Quạt đứng</v>
+      </c>
+      <c r="D199" t="str">
+        <v>Phòng 102</v>
+      </c>
+      <c r="E199" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F199">
+        <v>1</v>
+      </c>
+      <c r="G199" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="str">
+        <v>HD-MTX-46-RENO-RM-FULL</v>
+      </c>
+      <c r="B200" t="str">
+        <v>Giường</v>
+      </c>
+      <c r="C200" t="str">
+        <v>Giường gỗ 1m6</v>
+      </c>
+      <c r="D200" t="str">
+        <v>Phòng 103</v>
+      </c>
+      <c r="E200" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F200">
+        <v>1</v>
+      </c>
+      <c r="G200" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="str">
+        <v>HD-MTX-46-RENO-RM-FULL</v>
+      </c>
+      <c r="B201" t="str">
+        <v>Quạt</v>
+      </c>
+      <c r="C201" t="str">
+        <v>Quạt đứng</v>
+      </c>
+      <c r="D201" t="str">
+        <v>Phòng 103</v>
+      </c>
+      <c r="E201" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F201">
+        <v>1</v>
+      </c>
+      <c r="G201" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="str">
+        <v>HD-MTX-46-RENO-RM-FULL</v>
+      </c>
+      <c r="B202" t="str">
+        <v>Giường</v>
+      </c>
+      <c r="C202" t="str">
+        <v>Giường gỗ 1m6</v>
+      </c>
+      <c r="D202" t="str">
+        <v>Phòng 104</v>
+      </c>
+      <c r="E202" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F202">
+        <v>1</v>
+      </c>
+      <c r="G202" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="str">
+        <v>HD-MTX-46-RENO-RM-FULL</v>
+      </c>
+      <c r="B203" t="str">
+        <v>Quạt</v>
+      </c>
+      <c r="C203" t="str">
+        <v>Quạt đứng</v>
+      </c>
+      <c r="D203" t="str">
+        <v>Phòng 104</v>
+      </c>
+      <c r="E203" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F203">
+        <v>1</v>
+      </c>
+      <c r="G203" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="str">
+        <v>HD-MTX-47-RENO-RM-FULL</v>
+      </c>
+      <c r="B204" t="str">
+        <v>Máy giặt</v>
+      </c>
+      <c r="C204" t="str">
+        <v>Máy cũ chung</v>
+      </c>
+      <c r="D204" t="str">
+        <v>Sân phơi</v>
+      </c>
+      <c r="E204" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F204">
+        <v>1</v>
+      </c>
+      <c r="G204" t="str">
+        <v>TB dùng chung</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="str">
+        <v>HD-MTX-47-RENO-RM-FULL</v>
+      </c>
+      <c r="B205" t="str">
+        <v>Tủ lạnh</v>
+      </c>
+      <c r="C205" t="str">
+        <v>Tủ cũ tầng 1</v>
+      </c>
+      <c r="D205" t="str">
+        <v>Bếp chung</v>
+      </c>
+      <c r="E205" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F205">
+        <v>1</v>
+      </c>
+      <c r="G205" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="str">
+        <v>HD-MTX-47-RENO-RM-FULL</v>
+      </c>
+      <c r="B206" t="str">
+        <v>Nóng lạnh</v>
+      </c>
+      <c r="C206" t="str">
+        <v>Máy cũ</v>
+      </c>
+      <c r="D206" t="str">
+        <v>WC chung</v>
+      </c>
+      <c r="E206" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F206">
+        <v>1</v>
+      </c>
+      <c r="G206" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="str">
+        <v>HD-MTX-47-RENO-RM-FULL</v>
+      </c>
+      <c r="B207" t="str">
+        <v>Giường</v>
+      </c>
+      <c r="C207" t="str">
+        <v>Giường gỗ 1m6</v>
+      </c>
+      <c r="D207" t="str">
+        <v>Phòng 101</v>
+      </c>
+      <c r="E207" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F207">
+        <v>1</v>
+      </c>
+      <c r="G207" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="str">
+        <v>HD-MTX-47-RENO-RM-FULL</v>
+      </c>
+      <c r="B208" t="str">
+        <v>Quạt</v>
+      </c>
+      <c r="C208" t="str">
+        <v>Quạt đứng</v>
+      </c>
+      <c r="D208" t="str">
+        <v>Phòng 101</v>
+      </c>
+      <c r="E208" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F208">
+        <v>1</v>
+      </c>
+      <c r="G208" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="str">
+        <v>HD-MTX-47-RENO-RM-FULL</v>
+      </c>
+      <c r="B209" t="str">
+        <v>Giường</v>
+      </c>
+      <c r="C209" t="str">
+        <v>Giường gỗ 1m6</v>
+      </c>
+      <c r="D209" t="str">
+        <v>Phòng 102</v>
+      </c>
+      <c r="E209" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F209">
+        <v>1</v>
+      </c>
+      <c r="G209" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="str">
+        <v>HD-MTX-47-RENO-RM-FULL</v>
+      </c>
+      <c r="B210" t="str">
+        <v>Quạt</v>
+      </c>
+      <c r="C210" t="str">
+        <v>Quạt đứng</v>
+      </c>
+      <c r="D210" t="str">
+        <v>Phòng 102</v>
+      </c>
+      <c r="E210" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F210">
+        <v>1</v>
+      </c>
+      <c r="G210" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="str">
+        <v>HD-MTX-47-RENO-RM-FULL</v>
+      </c>
+      <c r="B211" t="str">
+        <v>Giường</v>
+      </c>
+      <c r="C211" t="str">
+        <v>Giường gỗ 1m6</v>
+      </c>
+      <c r="D211" t="str">
+        <v>Phòng 103</v>
+      </c>
+      <c r="E211" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F211">
+        <v>1</v>
+      </c>
+      <c r="G211" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="str">
+        <v>HD-MTX-47-RENO-RM-FULL</v>
+      </c>
+      <c r="B212" t="str">
+        <v>Quạt</v>
+      </c>
+      <c r="C212" t="str">
+        <v>Quạt đứng</v>
+      </c>
+      <c r="D212" t="str">
+        <v>Phòng 103</v>
+      </c>
+      <c r="E212" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F212">
+        <v>1</v>
+      </c>
+      <c r="G212" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="str">
+        <v>HD-MTX-47-RENO-RM-FULL</v>
+      </c>
+      <c r="B213" t="str">
+        <v>Giường</v>
+      </c>
+      <c r="C213" t="str">
+        <v>Giường gỗ 1m6</v>
+      </c>
+      <c r="D213" t="str">
+        <v>Phòng 104</v>
+      </c>
+      <c r="E213" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F213">
+        <v>1</v>
+      </c>
+      <c r="G213" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="str">
+        <v>HD-MTX-47-RENO-RM-FULL</v>
+      </c>
+      <c r="B214" t="str">
+        <v>Quạt</v>
+      </c>
+      <c r="C214" t="str">
+        <v>Quạt đứng</v>
+      </c>
+      <c r="D214" t="str">
+        <v>Phòng 104</v>
+      </c>
+      <c r="E214" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F214">
+        <v>1</v>
+      </c>
+      <c r="G214" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="str">
+        <v>HD-MTX-48-RENO-RM-HO-BUY</v>
+      </c>
+      <c r="B215" t="str">
+        <v>Giường</v>
+      </c>
+      <c r="C215" t="str">
+        <v>Giường sắt cũ</v>
+      </c>
+      <c r="D215" t="str">
+        <v>Phòng 101</v>
+      </c>
+      <c r="E215" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F215">
+        <v>1</v>
+      </c>
+      <c r="G215" t="str">
+        <v>TB chủ</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="str">
+        <v>HD-MTX-48-RENO-RM-HO-BUY</v>
+      </c>
+      <c r="B216" t="str">
+        <v>Giường</v>
+      </c>
+      <c r="C216" t="str">
+        <v>Giường sắt cũ</v>
+      </c>
+      <c r="D216" t="str">
+        <v>Phòng 102</v>
+      </c>
+      <c r="E216" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F216">
+        <v>1</v>
+      </c>
+      <c r="G216" t="str">
+        <v>TB chủ</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="str">
+        <v>HD-MTX-48-RENO-RM-HO-BUY</v>
+      </c>
+      <c r="B217" t="str">
+        <v>Giường</v>
+      </c>
+      <c r="C217" t="str">
+        <v>Giường sắt cũ</v>
+      </c>
+      <c r="D217" t="str">
+        <v>Phòng 103</v>
+      </c>
+      <c r="E217" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F217">
+        <v>1</v>
+      </c>
+      <c r="G217" t="str">
+        <v>TB chủ</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="str">
+        <v>HD-MTX-48-RENO-RM-HO-BUY</v>
+      </c>
+      <c r="B218" t="str">
+        <v>Quạt</v>
+      </c>
+      <c r="C218" t="str">
+        <v>Quạt trần</v>
+      </c>
+      <c r="D218" t="str">
+        <v>Hành lang</v>
+      </c>
+      <c r="E218" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F218">
+        <v>1</v>
+      </c>
+      <c r="G218" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="str">
+        <v>HD-MTX-48-RENO-RM-HO-BUY</v>
+      </c>
+      <c r="B219" t="str">
+        <v>Nóng lạnh</v>
+      </c>
+      <c r="C219" t="str">
+        <v>Máy cũ</v>
+      </c>
+      <c r="D219" t="str">
+        <v>WC chung</v>
+      </c>
+      <c r="E219" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F219">
+        <v>1</v>
+      </c>
+      <c r="G219" t="str">
+        <v>Dùng chung</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="str">
+        <v>HD-MTX-49-RENO-RM-HO-BUY</v>
+      </c>
+      <c r="B220" t="str">
+        <v>Giường</v>
+      </c>
+      <c r="C220" t="str">
+        <v>Giường sắt cũ</v>
+      </c>
+      <c r="D220" t="str">
+        <v>Phòng 101</v>
+      </c>
+      <c r="E220" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F220">
+        <v>1</v>
+      </c>
+      <c r="G220" t="str">
+        <v>TB chủ</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="str">
+        <v>HD-MTX-49-RENO-RM-HO-BUY</v>
+      </c>
+      <c r="B221" t="str">
+        <v>Giường</v>
+      </c>
+      <c r="C221" t="str">
+        <v>Giường sắt cũ</v>
+      </c>
+      <c r="D221" t="str">
+        <v>Phòng 102</v>
+      </c>
+      <c r="E221" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F221">
+        <v>1</v>
+      </c>
+      <c r="G221" t="str">
+        <v>TB chủ</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="str">
+        <v>HD-MTX-49-RENO-RM-HO-BUY</v>
+      </c>
+      <c r="B222" t="str">
+        <v>Giường</v>
+      </c>
+      <c r="C222" t="str">
+        <v>Giường sắt cũ</v>
+      </c>
+      <c r="D222" t="str">
+        <v>Phòng 103</v>
+      </c>
+      <c r="E222" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F222">
+        <v>1</v>
+      </c>
+      <c r="G222" t="str">
+        <v>TB chủ</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="str">
+        <v>HD-MTX-49-RENO-RM-HO-BUY</v>
+      </c>
+      <c r="B223" t="str">
+        <v>Quạt</v>
+      </c>
+      <c r="C223" t="str">
+        <v>Quạt trần</v>
+      </c>
+      <c r="D223" t="str">
+        <v>Hành lang</v>
+      </c>
+      <c r="E223" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F223">
+        <v>1</v>
+      </c>
+      <c r="G223" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="str">
+        <v>HD-MTX-49-RENO-RM-HO-BUY</v>
+      </c>
+      <c r="B224" t="str">
+        <v>Nóng lạnh</v>
+      </c>
+      <c r="C224" t="str">
+        <v>Máy cũ</v>
+      </c>
+      <c r="D224" t="str">
+        <v>WC chung</v>
+      </c>
+      <c r="E224" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F224">
+        <v>1</v>
+      </c>
+      <c r="G224" t="str">
+        <v>Dùng chung</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="str">
         <v>HD-MTX-50-RENO-RM-HO-BUY</v>
       </c>
-      <c r="B112" t="str">
+      <c r="B225" t="str">
+        <v>Giường</v>
+      </c>
+      <c r="C225" t="str">
+        <v>Giường sắt cũ</v>
+      </c>
+      <c r="D225" t="str">
+        <v>Phòng 101</v>
+      </c>
+      <c r="E225" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F225">
+        <v>1</v>
+      </c>
+      <c r="G225" t="str">
+        <v>TB chủ</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="str">
+        <v>HD-MTX-50-RENO-RM-HO-BUY</v>
+      </c>
+      <c r="B226" t="str">
+        <v>Giường</v>
+      </c>
+      <c r="C226" t="str">
+        <v>Giường sắt cũ</v>
+      </c>
+      <c r="D226" t="str">
+        <v>Phòng 102</v>
+      </c>
+      <c r="E226" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F226">
+        <v>1</v>
+      </c>
+      <c r="G226" t="str">
+        <v>TB chủ</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="str">
+        <v>HD-MTX-50-RENO-RM-HO-BUY</v>
+      </c>
+      <c r="B227" t="str">
+        <v>Giường</v>
+      </c>
+      <c r="C227" t="str">
+        <v>Giường sắt cũ</v>
+      </c>
+      <c r="D227" t="str">
+        <v>Phòng 103</v>
+      </c>
+      <c r="E227" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F227">
+        <v>1</v>
+      </c>
+      <c r="G227" t="str">
+        <v>TB chủ</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="str">
+        <v>HD-MTX-50-RENO-RM-HO-BUY</v>
+      </c>
+      <c r="B228" t="str">
         <v>Quạt</v>
       </c>
-      <c r="C112" t="str">
+      <c r="C228" t="str">
         <v>Quạt trần</v>
       </c>
-      <c r="D112" t="str">
+      <c r="D228" t="str">
         <v>Hành lang</v>
       </c>
-      <c r="E112" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F112">
-        <v>1</v>
-      </c>
-      <c r="G112" t="str">
-        <v/>
+      <c r="E228" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F228">
+        <v>1</v>
+      </c>
+      <c r="G228" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="str">
+        <v>HD-MTX-50-RENO-RM-HO-BUY</v>
+      </c>
+      <c r="B229" t="str">
+        <v>Nóng lạnh</v>
+      </c>
+      <c r="C229" t="str">
+        <v>Máy cũ</v>
+      </c>
+      <c r="D229" t="str">
+        <v>WC chung</v>
+      </c>
+      <c r="E229" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="F229">
+        <v>1</v>
+      </c>
+      <c r="G229" t="str">
+        <v>Dùng chung</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G112"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G229"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/docs/SLMS2026_import_matrix_dot1.xlsx
+++ b/docs/SLMS2026_import_matrix_dot1.xlsx
@@ -4517,7 +4517,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G229"/>
+  <dimension ref="A1:G114"/>
   <cols>
     <col min="1" max="1" width="28.83203125" customWidth="1"/>
     <col min="2" max="2" width="14.83203125" customWidth="1"/>
@@ -4585,7 +4585,7 @@
         <v>Giường gỗ 1m6</v>
       </c>
       <c r="D3" t="str">
-        <v>Phòng ngủ 1</v>
+        <v>Phòng ngủ</v>
       </c>
       <c r="E3" t="str">
         <v>GOOD</v>
@@ -4599,13 +4599,13 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>HD-MTX-06-NORENO-WH-BASIC</v>
+        <v>HD-MTX-07-NORENO-WH-BASIC</v>
       </c>
       <c r="B4" t="str">
-        <v>Quạt</v>
+        <v>Điều hòa</v>
       </c>
       <c r="C4" t="str">
-        <v>Quạt trần</v>
+        <v>Máy 1.5HP</v>
       </c>
       <c r="D4" t="str">
         <v>Phòng khách</v>
@@ -4617,21 +4617,21 @@
         <v>1</v>
       </c>
       <c r="G4" t="str">
-        <v/>
+        <v>NT cơ bản</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>HD-MTX-06-NORENO-WH-BASIC</v>
+        <v>HD-MTX-07-NORENO-WH-BASIC</v>
       </c>
       <c r="B5" t="str">
-        <v>Nóng lạnh</v>
+        <v>Giường</v>
       </c>
       <c r="C5" t="str">
-        <v>15L</v>
+        <v>Giường gỗ 1m6</v>
       </c>
       <c r="D5" t="str">
-        <v>WC tầng 1</v>
+        <v>Phòng ngủ</v>
       </c>
       <c r="E5" t="str">
         <v>GOOD</v>
@@ -4645,16 +4645,16 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>HD-MTX-06-NORENO-WH-BASIC</v>
+        <v>HD-MTX-08-NORENO-WH-BASIC</v>
       </c>
       <c r="B6" t="str">
-        <v>Tủ lạnh</v>
+        <v>Điều hòa</v>
       </c>
       <c r="C6" t="str">
-        <v>Tủ 150L</v>
+        <v>Máy 1.5HP</v>
       </c>
       <c r="D6" t="str">
-        <v>Bếp</v>
+        <v>Phòng khách</v>
       </c>
       <c r="E6" t="str">
         <v>GOOD</v>
@@ -4668,16 +4668,16 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>HD-MTX-07-NORENO-WH-BASIC</v>
+        <v>HD-MTX-08-NORENO-WH-BASIC</v>
       </c>
       <c r="B7" t="str">
-        <v>Điều hòa</v>
+        <v>Giường</v>
       </c>
       <c r="C7" t="str">
-        <v>Máy 1.5HP</v>
+        <v>Giường gỗ 1m6</v>
       </c>
       <c r="D7" t="str">
-        <v>Phòng khách</v>
+        <v>Phòng ngủ</v>
       </c>
       <c r="E7" t="str">
         <v>GOOD</v>
@@ -4686,21 +4686,21 @@
         <v>1</v>
       </c>
       <c r="G7" t="str">
-        <v>NT cơ bản</v>
+        <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>HD-MTX-07-NORENO-WH-BASIC</v>
+        <v>HD-MTX-09-NORENO-WH-BASIC</v>
       </c>
       <c r="B8" t="str">
-        <v>Giường</v>
+        <v>Điều hòa</v>
       </c>
       <c r="C8" t="str">
-        <v>Giường gỗ 1m6</v>
+        <v>Máy 1.5HP</v>
       </c>
       <c r="D8" t="str">
-        <v>Phòng ngủ 1</v>
+        <v>Phòng khách</v>
       </c>
       <c r="E8" t="str">
         <v>GOOD</v>
@@ -4709,21 +4709,21 @@
         <v>1</v>
       </c>
       <c r="G8" t="str">
-        <v/>
+        <v>NT cơ bản</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>HD-MTX-07-NORENO-WH-BASIC</v>
+        <v>HD-MTX-09-NORENO-WH-BASIC</v>
       </c>
       <c r="B9" t="str">
         <v>Giường</v>
       </c>
       <c r="C9" t="str">
-        <v>Giường gỗ 1m2</v>
+        <v>Giường gỗ 1m6</v>
       </c>
       <c r="D9" t="str">
-        <v>Phòng ngủ 2</v>
+        <v>Phòng ngủ</v>
       </c>
       <c r="E9" t="str">
         <v>GOOD</v>
@@ -4737,13 +4737,13 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>HD-MTX-07-NORENO-WH-BASIC</v>
+        <v>HD-MTX-10-NORENO-WH-BASIC</v>
       </c>
       <c r="B10" t="str">
-        <v>Quạt</v>
+        <v>Điều hòa</v>
       </c>
       <c r="C10" t="str">
-        <v>Quạt trần</v>
+        <v>Máy 1.5HP</v>
       </c>
       <c r="D10" t="str">
         <v>Phòng khách</v>
@@ -4755,21 +4755,21 @@
         <v>1</v>
       </c>
       <c r="G10" t="str">
-        <v/>
+        <v>NT cơ bản</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>HD-MTX-07-NORENO-WH-BASIC</v>
+        <v>HD-MTX-10-NORENO-WH-BASIC</v>
       </c>
       <c r="B11" t="str">
-        <v>Nóng lạnh</v>
+        <v>Giường</v>
       </c>
       <c r="C11" t="str">
-        <v>15L</v>
+        <v>Giường gỗ 1m6</v>
       </c>
       <c r="D11" t="str">
-        <v>WC tầng 1</v>
+        <v>Phòng ngủ</v>
       </c>
       <c r="E11" t="str">
         <v>GOOD</v>
@@ -4783,16 +4783,16 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>HD-MTX-07-NORENO-WH-BASIC</v>
+        <v>HD-MTX-11-NORENO-WH-FULL</v>
       </c>
       <c r="B12" t="str">
-        <v>Tủ lạnh</v>
+        <v>Điều hòa</v>
       </c>
       <c r="C12" t="str">
-        <v>Tủ 150L</v>
+        <v>1.5HP Inverter</v>
       </c>
       <c r="D12" t="str">
-        <v>Bếp</v>
+        <v>Phòng khách</v>
       </c>
       <c r="E12" t="str">
         <v>GOOD</v>
@@ -4801,21 +4801,21 @@
         <v>1</v>
       </c>
       <c r="G12" t="str">
-        <v>NT cơ bản</v>
+        <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>HD-MTX-08-NORENO-WH-BASIC</v>
+        <v>HD-MTX-11-NORENO-WH-FULL</v>
       </c>
       <c r="B13" t="str">
         <v>Điều hòa</v>
       </c>
       <c r="C13" t="str">
-        <v>Máy 1.5HP</v>
+        <v>1HP</v>
       </c>
       <c r="D13" t="str">
-        <v>Phòng khách</v>
+        <v>Phòng ngủ 1</v>
       </c>
       <c r="E13" t="str">
         <v>GOOD</v>
@@ -4824,21 +4824,21 @@
         <v>1</v>
       </c>
       <c r="G13" t="str">
-        <v>NT cơ bản</v>
+        <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>HD-MTX-08-NORENO-WH-BASIC</v>
+        <v>HD-MTX-11-NORENO-WH-FULL</v>
       </c>
       <c r="B14" t="str">
-        <v>Giường</v>
+        <v>Tủ lạnh</v>
       </c>
       <c r="C14" t="str">
-        <v>Giường gỗ 1m6</v>
+        <v>Inverter 200L</v>
       </c>
       <c r="D14" t="str">
-        <v>Phòng ngủ 1</v>
+        <v>Bếp</v>
       </c>
       <c r="E14" t="str">
         <v>GOOD</v>
@@ -4852,16 +4852,16 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>HD-MTX-08-NORENO-WH-BASIC</v>
+        <v>HD-MTX-11-NORENO-WH-FULL</v>
       </c>
       <c r="B15" t="str">
-        <v>Giường</v>
+        <v>Máy giặt</v>
       </c>
       <c r="C15" t="str">
-        <v>Giường gỗ 1m2</v>
+        <v>Cửa trước 8kg</v>
       </c>
       <c r="D15" t="str">
-        <v>Phòng ngủ 2</v>
+        <v>Sân sau</v>
       </c>
       <c r="E15" t="str">
         <v>GOOD</v>
@@ -4875,16 +4875,16 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>HD-MTX-08-NORENO-WH-BASIC</v>
+        <v>HD-MTX-11-NORENO-WH-FULL</v>
       </c>
       <c r="B16" t="str">
-        <v>Giường</v>
+        <v>Nóng lạnh</v>
       </c>
       <c r="C16" t="str">
-        <v>Giường gỗ 1m2</v>
+        <v>15L</v>
       </c>
       <c r="D16" t="str">
-        <v>Phòng ngủ 3</v>
+        <v>WC tầng 1</v>
       </c>
       <c r="E16" t="str">
         <v>GOOD</v>
@@ -4898,16 +4898,16 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>HD-MTX-08-NORENO-WH-BASIC</v>
+        <v>HD-MTX-11-NORENO-WH-FULL</v>
       </c>
       <c r="B17" t="str">
-        <v>Quạt</v>
+        <v>Giường</v>
       </c>
       <c r="C17" t="str">
-        <v>Quạt trần</v>
+        <v>Giường gỗ 1m6</v>
       </c>
       <c r="D17" t="str">
-        <v>Phòng khách</v>
+        <v>Phòng ngủ 1</v>
       </c>
       <c r="E17" t="str">
         <v>GOOD</v>
@@ -4921,16 +4921,16 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>HD-MTX-08-NORENO-WH-BASIC</v>
+        <v>HD-MTX-11-NORENO-WH-FULL</v>
       </c>
       <c r="B18" t="str">
-        <v>Nóng lạnh</v>
+        <v>Giường</v>
       </c>
       <c r="C18" t="str">
-        <v>15L</v>
+        <v>Giường gỗ 1m6</v>
       </c>
       <c r="D18" t="str">
-        <v>WC tầng 1</v>
+        <v>Phòng ngủ 2</v>
       </c>
       <c r="E18" t="str">
         <v>GOOD</v>
@@ -4944,16 +4944,16 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>HD-MTX-08-NORENO-WH-BASIC</v>
+        <v>HD-MTX-11-NORENO-WH-FULL</v>
       </c>
       <c r="B19" t="str">
-        <v>Tủ lạnh</v>
+        <v>Quạt</v>
       </c>
       <c r="C19" t="str">
-        <v>Tủ 150L</v>
+        <v>Quạt trần</v>
       </c>
       <c r="D19" t="str">
-        <v>Bếp</v>
+        <v>Phòng khách</v>
       </c>
       <c r="E19" t="str">
         <v>GOOD</v>
@@ -4962,21 +4962,21 @@
         <v>1</v>
       </c>
       <c r="G19" t="str">
-        <v>NT cơ bản</v>
+        <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>HD-MTX-09-NORENO-WH-BASIC</v>
+        <v>HD-MTX-11-NORENO-WH-FULL</v>
       </c>
       <c r="B20" t="str">
-        <v>Điều hòa</v>
+        <v>Quạt</v>
       </c>
       <c r="C20" t="str">
-        <v>Máy 1.5HP</v>
+        <v>Quạt đứng</v>
       </c>
       <c r="D20" t="str">
-        <v>Phòng khách</v>
+        <v>Phòng ngủ 1</v>
       </c>
       <c r="E20" t="str">
         <v>GOOD</v>
@@ -4985,21 +4985,21 @@
         <v>1</v>
       </c>
       <c r="G20" t="str">
-        <v>NT cơ bản</v>
+        <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>HD-MTX-09-NORENO-WH-BASIC</v>
+        <v>HD-MTX-12-NORENO-WH-FULL</v>
       </c>
       <c r="B21" t="str">
-        <v>Giường</v>
+        <v>Điều hòa</v>
       </c>
       <c r="C21" t="str">
-        <v>Giường gỗ 1m6</v>
+        <v>1.5HP Inverter</v>
       </c>
       <c r="D21" t="str">
-        <v>Phòng ngủ 1</v>
+        <v>Phòng khách</v>
       </c>
       <c r="E21" t="str">
         <v>GOOD</v>
@@ -5013,16 +5013,16 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>HD-MTX-09-NORENO-WH-BASIC</v>
+        <v>HD-MTX-12-NORENO-WH-FULL</v>
       </c>
       <c r="B22" t="str">
-        <v>Quạt</v>
+        <v>Điều hòa</v>
       </c>
       <c r="C22" t="str">
-        <v>Quạt trần</v>
+        <v>1HP</v>
       </c>
       <c r="D22" t="str">
-        <v>Phòng khách</v>
+        <v>Phòng ngủ 1</v>
       </c>
       <c r="E22" t="str">
         <v>GOOD</v>
@@ -5036,16 +5036,16 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>HD-MTX-09-NORENO-WH-BASIC</v>
+        <v>HD-MTX-12-NORENO-WH-FULL</v>
       </c>
       <c r="B23" t="str">
-        <v>Nóng lạnh</v>
+        <v>Tủ lạnh</v>
       </c>
       <c r="C23" t="str">
-        <v>15L</v>
+        <v>Inverter 200L</v>
       </c>
       <c r="D23" t="str">
-        <v>WC tầng 1</v>
+        <v>Bếp</v>
       </c>
       <c r="E23" t="str">
         <v>GOOD</v>
@@ -5059,16 +5059,16 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>HD-MTX-10-NORENO-WH-BASIC</v>
+        <v>HD-MTX-12-NORENO-WH-FULL</v>
       </c>
       <c r="B24" t="str">
-        <v>Điều hòa</v>
+        <v>Máy giặt</v>
       </c>
       <c r="C24" t="str">
-        <v>Máy 1.5HP</v>
+        <v>Cửa trước 8kg</v>
       </c>
       <c r="D24" t="str">
-        <v>Phòng khách</v>
+        <v>Sân sau</v>
       </c>
       <c r="E24" t="str">
         <v>GOOD</v>
@@ -5077,21 +5077,21 @@
         <v>1</v>
       </c>
       <c r="G24" t="str">
-        <v>NT cơ bản</v>
+        <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>HD-MTX-10-NORENO-WH-BASIC</v>
+        <v>HD-MTX-12-NORENO-WH-FULL</v>
       </c>
       <c r="B25" t="str">
-        <v>Giường</v>
+        <v>Nóng lạnh</v>
       </c>
       <c r="C25" t="str">
-        <v>Giường gỗ 1m6</v>
+        <v>15L</v>
       </c>
       <c r="D25" t="str">
-        <v>Phòng ngủ 1</v>
+        <v>WC tầng 1</v>
       </c>
       <c r="E25" t="str">
         <v>GOOD</v>
@@ -5105,16 +5105,16 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>HD-MTX-10-NORENO-WH-BASIC</v>
+        <v>HD-MTX-12-NORENO-WH-FULL</v>
       </c>
       <c r="B26" t="str">
         <v>Giường</v>
       </c>
       <c r="C26" t="str">
-        <v>Giường gỗ 1m2</v>
+        <v>Giường gỗ 1m6</v>
       </c>
       <c r="D26" t="str">
-        <v>Phòng ngủ 2</v>
+        <v>Phòng ngủ 1</v>
       </c>
       <c r="E26" t="str">
         <v>GOOD</v>
@@ -5128,16 +5128,16 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>HD-MTX-10-NORENO-WH-BASIC</v>
+        <v>HD-MTX-12-NORENO-WH-FULL</v>
       </c>
       <c r="B27" t="str">
-        <v>Quạt</v>
+        <v>Giường</v>
       </c>
       <c r="C27" t="str">
-        <v>Quạt trần</v>
+        <v>Giường gỗ 1m6</v>
       </c>
       <c r="D27" t="str">
-        <v>Phòng khách</v>
+        <v>Phòng ngủ 2</v>
       </c>
       <c r="E27" t="str">
         <v>GOOD</v>
@@ -5151,16 +5151,16 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>HD-MTX-10-NORENO-WH-BASIC</v>
+        <v>HD-MTX-12-NORENO-WH-FULL</v>
       </c>
       <c r="B28" t="str">
-        <v>Nóng lạnh</v>
+        <v>Quạt</v>
       </c>
       <c r="C28" t="str">
-        <v>15L</v>
+        <v>Quạt trần</v>
       </c>
       <c r="D28" t="str">
-        <v>WC tầng 1</v>
+        <v>Phòng khách</v>
       </c>
       <c r="E28" t="str">
         <v>GOOD</v>
@@ -5174,16 +5174,16 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>HD-MTX-10-NORENO-WH-BASIC</v>
+        <v>HD-MTX-12-NORENO-WH-FULL</v>
       </c>
       <c r="B29" t="str">
-        <v>Tủ lạnh</v>
+        <v>Quạt</v>
       </c>
       <c r="C29" t="str">
-        <v>Tủ 150L</v>
+        <v>Quạt đứng</v>
       </c>
       <c r="D29" t="str">
-        <v>Bếp</v>
+        <v>Phòng ngủ 1</v>
       </c>
       <c r="E29" t="str">
         <v>GOOD</v>
@@ -5192,12 +5192,12 @@
         <v>1</v>
       </c>
       <c r="G29" t="str">
-        <v>NT cơ bản</v>
+        <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>HD-MTX-11-NORENO-WH-FULL</v>
+        <v>HD-MTX-13-NORENO-WH-FULL</v>
       </c>
       <c r="B30" t="str">
         <v>Điều hòa</v>
@@ -5220,13 +5220,13 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>HD-MTX-11-NORENO-WH-FULL</v>
+        <v>HD-MTX-13-NORENO-WH-FULL</v>
       </c>
       <c r="B31" t="str">
         <v>Điều hòa</v>
       </c>
       <c r="C31" t="str">
-        <v>1HP Inverter</v>
+        <v>1HP</v>
       </c>
       <c r="D31" t="str">
         <v>Phòng ngủ 1</v>
@@ -5243,16 +5243,16 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>HD-MTX-11-NORENO-WH-FULL</v>
+        <v>HD-MTX-13-NORENO-WH-FULL</v>
       </c>
       <c r="B32" t="str">
-        <v>Điều hòa</v>
+        <v>Tủ lạnh</v>
       </c>
       <c r="C32" t="str">
-        <v>1HP</v>
+        <v>Inverter 200L</v>
       </c>
       <c r="D32" t="str">
-        <v>Phòng ngủ 2</v>
+        <v>Bếp</v>
       </c>
       <c r="E32" t="str">
         <v>GOOD</v>
@@ -5266,16 +5266,16 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>HD-MTX-11-NORENO-WH-FULL</v>
+        <v>HD-MTX-13-NORENO-WH-FULL</v>
       </c>
       <c r="B33" t="str">
-        <v>Điều hòa</v>
+        <v>Máy giặt</v>
       </c>
       <c r="C33" t="str">
-        <v>1HP</v>
+        <v>Cửa trước 8kg</v>
       </c>
       <c r="D33" t="str">
-        <v>Phòng ngủ 3</v>
+        <v>Sân sau</v>
       </c>
       <c r="E33" t="str">
         <v>GOOD</v>
@@ -5289,16 +5289,16 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>HD-MTX-11-NORENO-WH-FULL</v>
+        <v>HD-MTX-13-NORENO-WH-FULL</v>
       </c>
       <c r="B34" t="str">
-        <v>Tủ lạnh</v>
+        <v>Nóng lạnh</v>
       </c>
       <c r="C34" t="str">
-        <v>Inverter 200L</v>
+        <v>15L</v>
       </c>
       <c r="D34" t="str">
-        <v>Bếp</v>
+        <v>WC tầng 1</v>
       </c>
       <c r="E34" t="str">
         <v>GOOD</v>
@@ -5312,16 +5312,16 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>HD-MTX-11-NORENO-WH-FULL</v>
+        <v>HD-MTX-13-NORENO-WH-FULL</v>
       </c>
       <c r="B35" t="str">
-        <v>Máy giặt</v>
+        <v>Giường</v>
       </c>
       <c r="C35" t="str">
-        <v>Cửa trước 8kg</v>
+        <v>Giường gỗ 1m6</v>
       </c>
       <c r="D35" t="str">
-        <v>Sân sau</v>
+        <v>Phòng ngủ 1</v>
       </c>
       <c r="E35" t="str">
         <v>GOOD</v>
@@ -5335,16 +5335,16 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>HD-MTX-11-NORENO-WH-FULL</v>
+        <v>HD-MTX-13-NORENO-WH-FULL</v>
       </c>
       <c r="B36" t="str">
-        <v>Nóng lạnh</v>
+        <v>Giường</v>
       </c>
       <c r="C36" t="str">
-        <v>15L</v>
+        <v>Giường gỗ 1m6</v>
       </c>
       <c r="D36" t="str">
-        <v>WC tầng 1</v>
+        <v>Phòng ngủ 2</v>
       </c>
       <c r="E36" t="str">
         <v>GOOD</v>
@@ -5358,16 +5358,16 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>HD-MTX-11-NORENO-WH-FULL</v>
+        <v>HD-MTX-13-NORENO-WH-FULL</v>
       </c>
       <c r="B37" t="str">
-        <v>Nóng lạnh</v>
+        <v>Quạt</v>
       </c>
       <c r="C37" t="str">
-        <v>15L</v>
+        <v>Quạt trần</v>
       </c>
       <c r="D37" t="str">
-        <v>WC tầng 2</v>
+        <v>Phòng khách</v>
       </c>
       <c r="E37" t="str">
         <v>GOOD</v>
@@ -5381,13 +5381,13 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>HD-MTX-11-NORENO-WH-FULL</v>
+        <v>HD-MTX-13-NORENO-WH-FULL</v>
       </c>
       <c r="B38" t="str">
-        <v>Giường</v>
+        <v>Quạt</v>
       </c>
       <c r="C38" t="str">
-        <v>Giường gỗ 1m6</v>
+        <v>Quạt đứng</v>
       </c>
       <c r="D38" t="str">
         <v>Phòng ngủ 1</v>
@@ -5404,16 +5404,16 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>HD-MTX-11-NORENO-WH-FULL</v>
+        <v>HD-MTX-14-NORENO-WH-FULL</v>
       </c>
       <c r="B39" t="str">
-        <v>Giường</v>
+        <v>Điều hòa</v>
       </c>
       <c r="C39" t="str">
-        <v>Giường gỗ 1m6</v>
+        <v>1.5HP Inverter</v>
       </c>
       <c r="D39" t="str">
-        <v>Phòng ngủ 2</v>
+        <v>Phòng khách</v>
       </c>
       <c r="E39" t="str">
         <v>GOOD</v>
@@ -5427,16 +5427,16 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>HD-MTX-11-NORENO-WH-FULL</v>
+        <v>HD-MTX-14-NORENO-WH-FULL</v>
       </c>
       <c r="B40" t="str">
-        <v>Giường</v>
+        <v>Điều hòa</v>
       </c>
       <c r="C40" t="str">
-        <v>Giường gỗ 1m6</v>
+        <v>1HP</v>
       </c>
       <c r="D40" t="str">
-        <v>Phòng ngủ 3</v>
+        <v>Phòng ngủ 1</v>
       </c>
       <c r="E40" t="str">
         <v>GOOD</v>
@@ -5450,16 +5450,16 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>HD-MTX-11-NORENO-WH-FULL</v>
+        <v>HD-MTX-14-NORENO-WH-FULL</v>
       </c>
       <c r="B41" t="str">
-        <v>Quạt</v>
+        <v>Tủ lạnh</v>
       </c>
       <c r="C41" t="str">
-        <v>Quạt trần</v>
+        <v>Inverter 200L</v>
       </c>
       <c r="D41" t="str">
-        <v>Phòng khách</v>
+        <v>Bếp</v>
       </c>
       <c r="E41" t="str">
         <v>GOOD</v>
@@ -5473,16 +5473,16 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>HD-MTX-11-NORENO-WH-FULL</v>
+        <v>HD-MTX-14-NORENO-WH-FULL</v>
       </c>
       <c r="B42" t="str">
-        <v>Quạt</v>
+        <v>Máy giặt</v>
       </c>
       <c r="C42" t="str">
-        <v>Quạt đứng</v>
+        <v>Cửa trước 8kg</v>
       </c>
       <c r="D42" t="str">
-        <v>Phòng ngủ 1</v>
+        <v>Sân sau</v>
       </c>
       <c r="E42" t="str">
         <v>GOOD</v>
@@ -5496,16 +5496,16 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>HD-MTX-11-NORENO-WH-FULL</v>
+        <v>HD-MTX-14-NORENO-WH-FULL</v>
       </c>
       <c r="B43" t="str">
-        <v>Quạt</v>
+        <v>Nóng lạnh</v>
       </c>
       <c r="C43" t="str">
-        <v>Quạt đứng</v>
+        <v>15L</v>
       </c>
       <c r="D43" t="str">
-        <v>Phòng ngủ 2</v>
+        <v>WC tầng 1</v>
       </c>
       <c r="E43" t="str">
         <v>GOOD</v>
@@ -5519,16 +5519,16 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>HD-MTX-11-NORENO-WH-FULL</v>
+        <v>HD-MTX-14-NORENO-WH-FULL</v>
       </c>
       <c r="B44" t="str">
-        <v>Quạt</v>
+        <v>Giường</v>
       </c>
       <c r="C44" t="str">
-        <v>Quạt đứng</v>
+        <v>Giường gỗ 1m6</v>
       </c>
       <c r="D44" t="str">
-        <v>Phòng ngủ 3</v>
+        <v>Phòng ngủ 1</v>
       </c>
       <c r="E44" t="str">
         <v>GOOD</v>
@@ -5542,16 +5542,16 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>HD-MTX-12-NORENO-WH-FULL</v>
+        <v>HD-MTX-14-NORENO-WH-FULL</v>
       </c>
       <c r="B45" t="str">
-        <v>Điều hòa</v>
+        <v>Giường</v>
       </c>
       <c r="C45" t="str">
-        <v>1.5HP Inverter</v>
+        <v>Giường gỗ 1m6</v>
       </c>
       <c r="D45" t="str">
-        <v>Phòng khách</v>
+        <v>Phòng ngủ 2</v>
       </c>
       <c r="E45" t="str">
         <v>GOOD</v>
@@ -5565,16 +5565,16 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>HD-MTX-12-NORENO-WH-FULL</v>
+        <v>HD-MTX-14-NORENO-WH-FULL</v>
       </c>
       <c r="B46" t="str">
-        <v>Điều hòa</v>
+        <v>Quạt</v>
       </c>
       <c r="C46" t="str">
-        <v>1HP Inverter</v>
+        <v>Quạt trần</v>
       </c>
       <c r="D46" t="str">
-        <v>Phòng ngủ 1</v>
+        <v>Phòng khách</v>
       </c>
       <c r="E46" t="str">
         <v>GOOD</v>
@@ -5588,16 +5588,16 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>HD-MTX-12-NORENO-WH-FULL</v>
+        <v>HD-MTX-14-NORENO-WH-FULL</v>
       </c>
       <c r="B47" t="str">
-        <v>Tủ lạnh</v>
+        <v>Quạt</v>
       </c>
       <c r="C47" t="str">
-        <v>Inverter 200L</v>
+        <v>Quạt đứng</v>
       </c>
       <c r="D47" t="str">
-        <v>Bếp</v>
+        <v>Phòng ngủ 1</v>
       </c>
       <c r="E47" t="str">
         <v>GOOD</v>
@@ -5611,16 +5611,16 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>HD-MTX-12-NORENO-WH-FULL</v>
+        <v>HD-MTX-15-NORENO-WH-FULL</v>
       </c>
       <c r="B48" t="str">
-        <v>Máy giặt</v>
+        <v>Điều hòa</v>
       </c>
       <c r="C48" t="str">
-        <v>Cửa trước 8kg</v>
+        <v>1.5HP Inverter</v>
       </c>
       <c r="D48" t="str">
-        <v>Sân sau</v>
+        <v>Phòng khách</v>
       </c>
       <c r="E48" t="str">
         <v>GOOD</v>
@@ -5634,16 +5634,16 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>HD-MTX-12-NORENO-WH-FULL</v>
+        <v>HD-MTX-15-NORENO-WH-FULL</v>
       </c>
       <c r="B49" t="str">
-        <v>Nóng lạnh</v>
+        <v>Điều hòa</v>
       </c>
       <c r="C49" t="str">
-        <v>15L</v>
+        <v>1HP</v>
       </c>
       <c r="D49" t="str">
-        <v>WC tầng 1</v>
+        <v>Phòng ngủ 1</v>
       </c>
       <c r="E49" t="str">
         <v>GOOD</v>
@@ -5657,16 +5657,16 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>HD-MTX-12-NORENO-WH-FULL</v>
+        <v>HD-MTX-15-NORENO-WH-FULL</v>
       </c>
       <c r="B50" t="str">
-        <v>Giường</v>
+        <v>Tủ lạnh</v>
       </c>
       <c r="C50" t="str">
-        <v>Giường gỗ 1m6</v>
+        <v>Inverter 200L</v>
       </c>
       <c r="D50" t="str">
-        <v>Phòng ngủ 1</v>
+        <v>Bếp</v>
       </c>
       <c r="E50" t="str">
         <v>GOOD</v>
@@ -5680,16 +5680,16 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>HD-MTX-12-NORENO-WH-FULL</v>
+        <v>HD-MTX-15-NORENO-WH-FULL</v>
       </c>
       <c r="B51" t="str">
-        <v>Quạt</v>
+        <v>Máy giặt</v>
       </c>
       <c r="C51" t="str">
-        <v>Quạt trần</v>
+        <v>Cửa trước 8kg</v>
       </c>
       <c r="D51" t="str">
-        <v>Phòng khách</v>
+        <v>Sân sau</v>
       </c>
       <c r="E51" t="str">
         <v>GOOD</v>
@@ -5703,16 +5703,16 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>HD-MTX-12-NORENO-WH-FULL</v>
+        <v>HD-MTX-15-NORENO-WH-FULL</v>
       </c>
       <c r="B52" t="str">
-        <v>Quạt</v>
+        <v>Nóng lạnh</v>
       </c>
       <c r="C52" t="str">
-        <v>Quạt đứng</v>
+        <v>15L</v>
       </c>
       <c r="D52" t="str">
-        <v>Phòng ngủ 1</v>
+        <v>WC tầng 1</v>
       </c>
       <c r="E52" t="str">
         <v>GOOD</v>
@@ -5726,16 +5726,16 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>HD-MTX-13-NORENO-WH-FULL</v>
+        <v>HD-MTX-15-NORENO-WH-FULL</v>
       </c>
       <c r="B53" t="str">
-        <v>Điều hòa</v>
+        <v>Giường</v>
       </c>
       <c r="C53" t="str">
-        <v>1.5HP Inverter</v>
+        <v>Giường gỗ 1m6</v>
       </c>
       <c r="D53" t="str">
-        <v>Phòng khách</v>
+        <v>Phòng ngủ 1</v>
       </c>
       <c r="E53" t="str">
         <v>GOOD</v>
@@ -5749,16 +5749,16 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>HD-MTX-13-NORENO-WH-FULL</v>
+        <v>HD-MTX-15-NORENO-WH-FULL</v>
       </c>
       <c r="B54" t="str">
-        <v>Điều hòa</v>
+        <v>Giường</v>
       </c>
       <c r="C54" t="str">
-        <v>1HP Inverter</v>
+        <v>Giường gỗ 1m6</v>
       </c>
       <c r="D54" t="str">
-        <v>Phòng ngủ 1</v>
+        <v>Phòng ngủ 2</v>
       </c>
       <c r="E54" t="str">
         <v>GOOD</v>
@@ -5772,16 +5772,16 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>HD-MTX-13-NORENO-WH-FULL</v>
+        <v>HD-MTX-15-NORENO-WH-FULL</v>
       </c>
       <c r="B55" t="str">
-        <v>Điều hòa</v>
+        <v>Quạt</v>
       </c>
       <c r="C55" t="str">
-        <v>1HP</v>
+        <v>Quạt trần</v>
       </c>
       <c r="D55" t="str">
-        <v>Phòng ngủ 2</v>
+        <v>Phòng khách</v>
       </c>
       <c r="E55" t="str">
         <v>GOOD</v>
@@ -5795,16 +5795,16 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>HD-MTX-13-NORENO-WH-FULL</v>
+        <v>HD-MTX-15-NORENO-WH-FULL</v>
       </c>
       <c r="B56" t="str">
-        <v>Tủ lạnh</v>
+        <v>Quạt</v>
       </c>
       <c r="C56" t="str">
-        <v>Inverter 200L</v>
+        <v>Quạt đứng</v>
       </c>
       <c r="D56" t="str">
-        <v>Bếp</v>
+        <v>Phòng ngủ 1</v>
       </c>
       <c r="E56" t="str">
         <v>GOOD</v>
@@ -5818,16 +5818,16 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>HD-MTX-13-NORENO-WH-FULL</v>
+        <v>HD-MTX-19-RENO-WH-BASIC-HO</v>
       </c>
       <c r="B57" t="str">
-        <v>Máy giặt</v>
+        <v>Điều hòa</v>
       </c>
       <c r="C57" t="str">
-        <v>Cửa trước 8kg</v>
+        <v>Máy 1.5HP</v>
       </c>
       <c r="D57" t="str">
-        <v>Sân sau</v>
+        <v>Phòng khách</v>
       </c>
       <c r="E57" t="str">
         <v>GOOD</v>
@@ -5836,21 +5836,21 @@
         <v>1</v>
       </c>
       <c r="G57" t="str">
-        <v/>
+        <v>NT cơ bản</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>HD-MTX-13-NORENO-WH-FULL</v>
+        <v>HD-MTX-19-RENO-WH-BASIC-HO</v>
       </c>
       <c r="B58" t="str">
-        <v>Nóng lạnh</v>
+        <v>Giường</v>
       </c>
       <c r="C58" t="str">
-        <v>15L</v>
+        <v>Giường gỗ 1m6</v>
       </c>
       <c r="D58" t="str">
-        <v>WC tầng 1</v>
+        <v>Phòng ngủ</v>
       </c>
       <c r="E58" t="str">
         <v>GOOD</v>
@@ -5864,16 +5864,16 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>HD-MTX-13-NORENO-WH-FULL</v>
+        <v>HD-MTX-20-RENO-WH-BASIC-HO</v>
       </c>
       <c r="B59" t="str">
-        <v>Nóng lạnh</v>
+        <v>Điều hòa</v>
       </c>
       <c r="C59" t="str">
-        <v>15L</v>
+        <v>Máy 1.5HP</v>
       </c>
       <c r="D59" t="str">
-        <v>WC tầng 2</v>
+        <v>Phòng khách</v>
       </c>
       <c r="E59" t="str">
         <v>GOOD</v>
@@ -5882,12 +5882,12 @@
         <v>1</v>
       </c>
       <c r="G59" t="str">
-        <v/>
+        <v>NT cơ bản</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>HD-MTX-13-NORENO-WH-FULL</v>
+        <v>HD-MTX-20-RENO-WH-BASIC-HO</v>
       </c>
       <c r="B60" t="str">
         <v>Giường</v>
@@ -5896,7 +5896,7 @@
         <v>Giường gỗ 1m6</v>
       </c>
       <c r="D60" t="str">
-        <v>Phòng ngủ 1</v>
+        <v>Phòng ngủ</v>
       </c>
       <c r="E60" t="str">
         <v>GOOD</v>
@@ -5910,16 +5910,16 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>HD-MTX-13-NORENO-WH-FULL</v>
+        <v>HD-MTX-21-RENO-WH-BASIC-HO</v>
       </c>
       <c r="B61" t="str">
-        <v>Giường</v>
+        <v>Điều hòa</v>
       </c>
       <c r="C61" t="str">
-        <v>Giường gỗ 1m6</v>
+        <v>Máy 1.5HP</v>
       </c>
       <c r="D61" t="str">
-        <v>Phòng ngủ 2</v>
+        <v>Phòng khách</v>
       </c>
       <c r="E61" t="str">
         <v>GOOD</v>
@@ -5928,21 +5928,21 @@
         <v>1</v>
       </c>
       <c r="G61" t="str">
-        <v/>
+        <v>NT cơ bản</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>HD-MTX-13-NORENO-WH-FULL</v>
+        <v>HD-MTX-21-RENO-WH-BASIC-HO</v>
       </c>
       <c r="B62" t="str">
-        <v>Quạt</v>
+        <v>Giường</v>
       </c>
       <c r="C62" t="str">
-        <v>Quạt trần</v>
+        <v>Giường gỗ 1m6</v>
       </c>
       <c r="D62" t="str">
-        <v>Phòng khách</v>
+        <v>Phòng ngủ</v>
       </c>
       <c r="E62" t="str">
         <v>GOOD</v>
@@ -5956,16 +5956,16 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>HD-MTX-13-NORENO-WH-FULL</v>
+        <v>HD-MTX-25-RENO-WH-FULL</v>
       </c>
       <c r="B63" t="str">
-        <v>Quạt</v>
+        <v>Điều hòa</v>
       </c>
       <c r="C63" t="str">
-        <v>Quạt đứng</v>
+        <v>1.5HP Inverter</v>
       </c>
       <c r="D63" t="str">
-        <v>Phòng ngủ 1</v>
+        <v>Phòng khách</v>
       </c>
       <c r="E63" t="str">
         <v>GOOD</v>
@@ -5979,16 +5979,16 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>HD-MTX-13-NORENO-WH-FULL</v>
+        <v>HD-MTX-25-RENO-WH-FULL</v>
       </c>
       <c r="B64" t="str">
-        <v>Quạt</v>
+        <v>Điều hòa</v>
       </c>
       <c r="C64" t="str">
-        <v>Quạt đứng</v>
+        <v>1HP</v>
       </c>
       <c r="D64" t="str">
-        <v>Phòng ngủ 2</v>
+        <v>Phòng ngủ 1</v>
       </c>
       <c r="E64" t="str">
         <v>GOOD</v>
@@ -6002,16 +6002,16 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>HD-MTX-14-NORENO-WH-FULL</v>
+        <v>HD-MTX-25-RENO-WH-FULL</v>
       </c>
       <c r="B65" t="str">
-        <v>Điều hòa</v>
+        <v>Tủ lạnh</v>
       </c>
       <c r="C65" t="str">
-        <v>1.5HP Inverter</v>
+        <v>Inverter 200L</v>
       </c>
       <c r="D65" t="str">
-        <v>Phòng khách</v>
+        <v>Bếp</v>
       </c>
       <c r="E65" t="str">
         <v>GOOD</v>
@@ -6025,16 +6025,16 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>HD-MTX-14-NORENO-WH-FULL</v>
+        <v>HD-MTX-25-RENO-WH-FULL</v>
       </c>
       <c r="B66" t="str">
-        <v>Điều hòa</v>
+        <v>Máy giặt</v>
       </c>
       <c r="C66" t="str">
-        <v>1HP Inverter</v>
+        <v>Cửa trước 8kg</v>
       </c>
       <c r="D66" t="str">
-        <v>Phòng ngủ 1</v>
+        <v>Sân sau</v>
       </c>
       <c r="E66" t="str">
         <v>GOOD</v>
@@ -6048,16 +6048,16 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>HD-MTX-14-NORENO-WH-FULL</v>
+        <v>HD-MTX-25-RENO-WH-FULL</v>
       </c>
       <c r="B67" t="str">
-        <v>Điều hòa</v>
+        <v>Nóng lạnh</v>
       </c>
       <c r="C67" t="str">
-        <v>1HP</v>
+        <v>15L</v>
       </c>
       <c r="D67" t="str">
-        <v>Phòng ngủ 2</v>
+        <v>WC tầng 1</v>
       </c>
       <c r="E67" t="str">
         <v>GOOD</v>
@@ -6071,16 +6071,16 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>HD-MTX-14-NORENO-WH-FULL</v>
+        <v>HD-MTX-25-RENO-WH-FULL</v>
       </c>
       <c r="B68" t="str">
-        <v>Điều hòa</v>
+        <v>Giường</v>
       </c>
       <c r="C68" t="str">
-        <v>1HP</v>
+        <v>Giường gỗ 1m6</v>
       </c>
       <c r="D68" t="str">
-        <v>Phòng ngủ 3</v>
+        <v>Phòng ngủ 1</v>
       </c>
       <c r="E68" t="str">
         <v>GOOD</v>
@@ -6094,16 +6094,16 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>HD-MTX-14-NORENO-WH-FULL</v>
+        <v>HD-MTX-25-RENO-WH-FULL</v>
       </c>
       <c r="B69" t="str">
-        <v>Tủ lạnh</v>
+        <v>Giường</v>
       </c>
       <c r="C69" t="str">
-        <v>Inverter 200L</v>
+        <v>Giường gỗ 1m6</v>
       </c>
       <c r="D69" t="str">
-        <v>Bếp</v>
+        <v>Phòng ngủ 2</v>
       </c>
       <c r="E69" t="str">
         <v>GOOD</v>
@@ -6117,16 +6117,16 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>HD-MTX-14-NORENO-WH-FULL</v>
+        <v>HD-MTX-25-RENO-WH-FULL</v>
       </c>
       <c r="B70" t="str">
-        <v>Máy giặt</v>
+        <v>Quạt</v>
       </c>
       <c r="C70" t="str">
-        <v>Cửa trước 8kg</v>
+        <v>Quạt trần</v>
       </c>
       <c r="D70" t="str">
-        <v>Sân sau</v>
+        <v>Phòng khách</v>
       </c>
       <c r="E70" t="str">
         <v>GOOD</v>
@@ -6140,16 +6140,16 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>HD-MTX-14-NORENO-WH-FULL</v>
+        <v>HD-MTX-25-RENO-WH-FULL</v>
       </c>
       <c r="B71" t="str">
-        <v>Nóng lạnh</v>
+        <v>Quạt</v>
       </c>
       <c r="C71" t="str">
-        <v>15L</v>
+        <v>Quạt đứng</v>
       </c>
       <c r="D71" t="str">
-        <v>WC tầng 1</v>
+        <v>Phòng ngủ 1</v>
       </c>
       <c r="E71" t="str">
         <v>GOOD</v>
@@ -6163,16 +6163,16 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>HD-MTX-14-NORENO-WH-FULL</v>
+        <v>HD-MTX-26-RENO-WH-FULL</v>
       </c>
       <c r="B72" t="str">
-        <v>Giường</v>
+        <v>Điều hòa</v>
       </c>
       <c r="C72" t="str">
-        <v>Giường gỗ 1m6</v>
+        <v>1.5HP Inverter</v>
       </c>
       <c r="D72" t="str">
-        <v>Phòng ngủ 1</v>
+        <v>Phòng khách</v>
       </c>
       <c r="E72" t="str">
         <v>GOOD</v>
@@ -6186,16 +6186,16 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>HD-MTX-14-NORENO-WH-FULL</v>
+        <v>HD-MTX-26-RENO-WH-FULL</v>
       </c>
       <c r="B73" t="str">
-        <v>Giường</v>
+        <v>Điều hòa</v>
       </c>
       <c r="C73" t="str">
-        <v>Giường gỗ 1m6</v>
+        <v>1HP</v>
       </c>
       <c r="D73" t="str">
-        <v>Phòng ngủ 2</v>
+        <v>Phòng ngủ 1</v>
       </c>
       <c r="E73" t="str">
         <v>GOOD</v>
@@ -6209,16 +6209,16 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>HD-MTX-14-NORENO-WH-FULL</v>
+        <v>HD-MTX-26-RENO-WH-FULL</v>
       </c>
       <c r="B74" t="str">
-        <v>Giường</v>
+        <v>Tủ lạnh</v>
       </c>
       <c r="C74" t="str">
-        <v>Giường gỗ 1m6</v>
+        <v>Inverter 200L</v>
       </c>
       <c r="D74" t="str">
-        <v>Phòng ngủ 3</v>
+        <v>Bếp</v>
       </c>
       <c r="E74" t="str">
         <v>GOOD</v>
@@ -6232,16 +6232,16 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>HD-MTX-14-NORENO-WH-FULL</v>
+        <v>HD-MTX-26-RENO-WH-FULL</v>
       </c>
       <c r="B75" t="str">
-        <v>Quạt</v>
+        <v>Máy giặt</v>
       </c>
       <c r="C75" t="str">
-        <v>Quạt trần</v>
+        <v>Cửa trước 8kg</v>
       </c>
       <c r="D75" t="str">
-        <v>Phòng khách</v>
+        <v>Sân sau</v>
       </c>
       <c r="E75" t="str">
         <v>GOOD</v>
@@ -6255,16 +6255,16 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>HD-MTX-14-NORENO-WH-FULL</v>
+        <v>HD-MTX-26-RENO-WH-FULL</v>
       </c>
       <c r="B76" t="str">
-        <v>Quạt</v>
+        <v>Nóng lạnh</v>
       </c>
       <c r="C76" t="str">
-        <v>Quạt đứng</v>
+        <v>15L</v>
       </c>
       <c r="D76" t="str">
-        <v>Phòng ngủ 1</v>
+        <v>WC tầng 1</v>
       </c>
       <c r="E76" t="str">
         <v>GOOD</v>
@@ -6278,16 +6278,16 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>HD-MTX-14-NORENO-WH-FULL</v>
+        <v>HD-MTX-26-RENO-WH-FULL</v>
       </c>
       <c r="B77" t="str">
-        <v>Quạt</v>
+        <v>Giường</v>
       </c>
       <c r="C77" t="str">
-        <v>Quạt đứng</v>
+        <v>Giường gỗ 1m6</v>
       </c>
       <c r="D77" t="str">
-        <v>Phòng ngủ 2</v>
+        <v>Phòng ngủ 1</v>
       </c>
       <c r="E77" t="str">
         <v>GOOD</v>
@@ -6301,16 +6301,16 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>HD-MTX-14-NORENO-WH-FULL</v>
+        <v>HD-MTX-26-RENO-WH-FULL</v>
       </c>
       <c r="B78" t="str">
-        <v>Quạt</v>
+        <v>Giường</v>
       </c>
       <c r="C78" t="str">
-        <v>Quạt đứng</v>
+        <v>Giường gỗ 1m6</v>
       </c>
       <c r="D78" t="str">
-        <v>Phòng ngủ 3</v>
+        <v>Phòng ngủ 2</v>
       </c>
       <c r="E78" t="str">
         <v>GOOD</v>
@@ -6324,13 +6324,13 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>HD-MTX-15-NORENO-WH-FULL</v>
+        <v>HD-MTX-26-RENO-WH-FULL</v>
       </c>
       <c r="B79" t="str">
-        <v>Điều hòa</v>
+        <v>Quạt</v>
       </c>
       <c r="C79" t="str">
-        <v>1.5HP Inverter</v>
+        <v>Quạt trần</v>
       </c>
       <c r="D79" t="str">
         <v>Phòng khách</v>
@@ -6347,13 +6347,13 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>HD-MTX-15-NORENO-WH-FULL</v>
+        <v>HD-MTX-26-RENO-WH-FULL</v>
       </c>
       <c r="B80" t="str">
-        <v>Điều hòa</v>
+        <v>Quạt</v>
       </c>
       <c r="C80" t="str">
-        <v>1HP Inverter</v>
+        <v>Quạt đứng</v>
       </c>
       <c r="D80" t="str">
         <v>Phòng ngủ 1</v>
@@ -6370,16 +6370,16 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>HD-MTX-15-NORENO-WH-FULL</v>
+        <v>HD-MTX-27-RENO-WH-FULL</v>
       </c>
       <c r="B81" t="str">
-        <v>Tủ lạnh</v>
+        <v>Điều hòa</v>
       </c>
       <c r="C81" t="str">
-        <v>Inverter 200L</v>
+        <v>1.5HP Inverter</v>
       </c>
       <c r="D81" t="str">
-        <v>Bếp</v>
+        <v>Phòng khách</v>
       </c>
       <c r="E81" t="str">
         <v>GOOD</v>
@@ -6393,16 +6393,16 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>HD-MTX-15-NORENO-WH-FULL</v>
+        <v>HD-MTX-27-RENO-WH-FULL</v>
       </c>
       <c r="B82" t="str">
-        <v>Máy giặt</v>
+        <v>Điều hòa</v>
       </c>
       <c r="C82" t="str">
-        <v>Cửa trước 8kg</v>
+        <v>1HP</v>
       </c>
       <c r="D82" t="str">
-        <v>Sân sau</v>
+        <v>Phòng ngủ 1</v>
       </c>
       <c r="E82" t="str">
         <v>GOOD</v>
@@ -6416,16 +6416,16 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>HD-MTX-15-NORENO-WH-FULL</v>
+        <v>HD-MTX-27-RENO-WH-FULL</v>
       </c>
       <c r="B83" t="str">
-        <v>Nóng lạnh</v>
+        <v>Tủ lạnh</v>
       </c>
       <c r="C83" t="str">
-        <v>15L</v>
+        <v>Inverter 200L</v>
       </c>
       <c r="D83" t="str">
-        <v>WC tầng 1</v>
+        <v>Bếp</v>
       </c>
       <c r="E83" t="str">
         <v>GOOD</v>
@@ -6439,16 +6439,16 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>HD-MTX-15-NORENO-WH-FULL</v>
+        <v>HD-MTX-27-RENO-WH-FULL</v>
       </c>
       <c r="B84" t="str">
-        <v>Nóng lạnh</v>
+        <v>Máy giặt</v>
       </c>
       <c r="C84" t="str">
-        <v>15L</v>
+        <v>Cửa trước 8kg</v>
       </c>
       <c r="D84" t="str">
-        <v>WC tầng 2</v>
+        <v>Sân sau</v>
       </c>
       <c r="E84" t="str">
         <v>GOOD</v>
@@ -6462,16 +6462,16 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>HD-MTX-15-NORENO-WH-FULL</v>
+        <v>HD-MTX-27-RENO-WH-FULL</v>
       </c>
       <c r="B85" t="str">
-        <v>Giường</v>
+        <v>Nóng lạnh</v>
       </c>
       <c r="C85" t="str">
-        <v>Giường gỗ 1m6</v>
+        <v>15L</v>
       </c>
       <c r="D85" t="str">
-        <v>Phòng ngủ 1</v>
+        <v>WC tầng 1</v>
       </c>
       <c r="E85" t="str">
         <v>GOOD</v>
@@ -6485,16 +6485,16 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>HD-MTX-15-NORENO-WH-FULL</v>
+        <v>HD-MTX-27-RENO-WH-FULL</v>
       </c>
       <c r="B86" t="str">
-        <v>Quạt</v>
+        <v>Giường</v>
       </c>
       <c r="C86" t="str">
-        <v>Quạt trần</v>
+        <v>Giường gỗ 1m6</v>
       </c>
       <c r="D86" t="str">
-        <v>Phòng khách</v>
+        <v>Phòng ngủ 1</v>
       </c>
       <c r="E86" t="str">
         <v>GOOD</v>
@@ -6508,16 +6508,16 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>HD-MTX-15-NORENO-WH-FULL</v>
+        <v>HD-MTX-27-RENO-WH-FULL</v>
       </c>
       <c r="B87" t="str">
-        <v>Quạt</v>
+        <v>Giường</v>
       </c>
       <c r="C87" t="str">
-        <v>Quạt đứng</v>
+        <v>Giường gỗ 1m6</v>
       </c>
       <c r="D87" t="str">
-        <v>Phòng ngủ 1</v>
+        <v>Phòng ngủ 2</v>
       </c>
       <c r="E87" t="str">
         <v>GOOD</v>
@@ -6531,13 +6531,13 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>HD-MTX-19-RENO-WH-BASIC-HO</v>
+        <v>HD-MTX-27-RENO-WH-FULL</v>
       </c>
       <c r="B88" t="str">
-        <v>Điều hòa</v>
+        <v>Quạt</v>
       </c>
       <c r="C88" t="str">
-        <v>Máy 1.5HP</v>
+        <v>Quạt trần</v>
       </c>
       <c r="D88" t="str">
         <v>Phòng khách</v>
@@ -6549,18 +6549,18 @@
         <v>1</v>
       </c>
       <c r="G88" t="str">
-        <v>NT cơ bản</v>
+        <v/>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>HD-MTX-19-RENO-WH-BASIC-HO</v>
+        <v>HD-MTX-27-RENO-WH-FULL</v>
       </c>
       <c r="B89" t="str">
-        <v>Giường</v>
+        <v>Quạt</v>
       </c>
       <c r="C89" t="str">
-        <v>Giường gỗ 1m6</v>
+        <v>Quạt đứng</v>
       </c>
       <c r="D89" t="str">
         <v>Phòng ngủ 1</v>
@@ -6577,16 +6577,16 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>HD-MTX-19-RENO-WH-BASIC-HO</v>
+        <v>HD-MTX-28-RENO-WH-HO-NOBUY</v>
       </c>
       <c r="B90" t="str">
-        <v>Giường</v>
+        <v>Máy giặt</v>
       </c>
       <c r="C90" t="str">
-        <v>Giường gỗ 1m2</v>
+        <v>Máy cũ</v>
       </c>
       <c r="D90" t="str">
-        <v>Phòng ngủ 2</v>
+        <v>Sân sau</v>
       </c>
       <c r="E90" t="str">
         <v>GOOD</v>
@@ -6595,21 +6595,21 @@
         <v>1</v>
       </c>
       <c r="G90" t="str">
-        <v/>
+        <v>TB chủ — không NT</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>HD-MTX-19-RENO-WH-BASIC-HO</v>
+        <v>HD-MTX-29-RENO-WH-HO-NOBUY</v>
       </c>
       <c r="B91" t="str">
-        <v>Quạt</v>
+        <v>Máy giặt</v>
       </c>
       <c r="C91" t="str">
-        <v>Quạt trần</v>
+        <v>Máy cũ</v>
       </c>
       <c r="D91" t="str">
-        <v>Phòng khách</v>
+        <v>Sân sau</v>
       </c>
       <c r="E91" t="str">
         <v>GOOD</v>
@@ -6618,21 +6618,21 @@
         <v>1</v>
       </c>
       <c r="G91" t="str">
-        <v/>
+        <v>TB chủ — không NT</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>HD-MTX-19-RENO-WH-BASIC-HO</v>
+        <v>HD-MTX-30-RENO-WH-HO-BUY</v>
       </c>
       <c r="B92" t="str">
-        <v>Nóng lạnh</v>
+        <v>Điều hòa</v>
       </c>
       <c r="C92" t="str">
-        <v>15L</v>
+        <v>Máy 1.5HP</v>
       </c>
       <c r="D92" t="str">
-        <v>WC tầng 1</v>
+        <v>Phòng khách</v>
       </c>
       <c r="E92" t="str">
         <v>GOOD</v>
@@ -6641,21 +6641,21 @@
         <v>1</v>
       </c>
       <c r="G92" t="str">
-        <v/>
+        <v>NT cơ bản</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>HD-MTX-19-RENO-WH-BASIC-HO</v>
+        <v>HD-MTX-30-RENO-WH-HO-BUY</v>
       </c>
       <c r="B93" t="str">
-        <v>Tủ lạnh</v>
+        <v>Giường</v>
       </c>
       <c r="C93" t="str">
-        <v>Tủ 150L</v>
+        <v>Giường gỗ 1m6</v>
       </c>
       <c r="D93" t="str">
-        <v>Bếp</v>
+        <v>Phòng ngủ</v>
       </c>
       <c r="E93" t="str">
         <v>GOOD</v>
@@ -6664,12 +6664,12 @@
         <v>1</v>
       </c>
       <c r="G93" t="str">
-        <v>NT cơ bản</v>
+        <v/>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>HD-MTX-20-RENO-WH-BASIC-HO</v>
+        <v>HD-MTX-31-RENO-WH-HO-BUY</v>
       </c>
       <c r="B94" t="str">
         <v>Điều hòa</v>
@@ -6692,7 +6692,7 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>HD-MTX-20-RENO-WH-BASIC-HO</v>
+        <v>HD-MTX-31-RENO-WH-HO-BUY</v>
       </c>
       <c r="B95" t="str">
         <v>Giường</v>
@@ -6701,7 +6701,7 @@
         <v>Giường gỗ 1m6</v>
       </c>
       <c r="D95" t="str">
-        <v>Phòng ngủ 1</v>
+        <v>Phòng ngủ</v>
       </c>
       <c r="E95" t="str">
         <v>GOOD</v>
@@ -6715,39 +6715,39 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>HD-MTX-20-RENO-WH-BASIC-HO</v>
+        <v>HD-MTX-36-RENO-RM-BASIC-HO</v>
       </c>
       <c r="B96" t="str">
         <v>Giường</v>
       </c>
       <c r="C96" t="str">
-        <v>Giường gỗ 1m2</v>
+        <v>Giường sắt cũ</v>
       </c>
       <c r="D96" t="str">
-        <v>Phòng ngủ 2</v>
+        <v>Tầng 2</v>
       </c>
       <c r="E96" t="str">
         <v>GOOD</v>
       </c>
       <c r="F96">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G96" t="str">
-        <v/>
+        <v>TB chủ</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>HD-MTX-20-RENO-WH-BASIC-HO</v>
+        <v>HD-MTX-36-RENO-RM-BASIC-HO</v>
       </c>
       <c r="B97" t="str">
-        <v>Giường</v>
+        <v>Quạt</v>
       </c>
       <c r="C97" t="str">
-        <v>Giường gỗ 1m2</v>
+        <v>Quạt trần</v>
       </c>
       <c r="D97" t="str">
-        <v>Phòng ngủ 3</v>
+        <v>Hành lang</v>
       </c>
       <c r="E97" t="str">
         <v>GOOD</v>
@@ -6761,62 +6761,62 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>HD-MTX-20-RENO-WH-BASIC-HO</v>
+        <v>HD-MTX-37-RENO-RM-BASIC-HO</v>
       </c>
       <c r="B98" t="str">
-        <v>Quạt</v>
+        <v>Giường</v>
       </c>
       <c r="C98" t="str">
-        <v>Quạt trần</v>
+        <v>Giường sắt cũ</v>
       </c>
       <c r="D98" t="str">
-        <v>Phòng khách</v>
+        <v>Tầng 2</v>
       </c>
       <c r="E98" t="str">
         <v>GOOD</v>
       </c>
       <c r="F98">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G98" t="str">
-        <v/>
+        <v>TB chủ</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>HD-MTX-20-RENO-WH-BASIC-HO</v>
+        <v>HD-MTX-38-RENO-RM-BASIC-HO</v>
       </c>
       <c r="B99" t="str">
-        <v>Nóng lạnh</v>
+        <v>Giường</v>
       </c>
       <c r="C99" t="str">
-        <v>15L</v>
+        <v>Giường sắt cũ</v>
       </c>
       <c r="D99" t="str">
-        <v>WC tầng 1</v>
+        <v>Tầng 2</v>
       </c>
       <c r="E99" t="str">
         <v>GOOD</v>
       </c>
       <c r="F99">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G99" t="str">
-        <v/>
+        <v>TB chủ</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>HD-MTX-20-RENO-WH-BASIC-HO</v>
+        <v>HD-MTX-38-RENO-RM-BASIC-HO</v>
       </c>
       <c r="B100" t="str">
-        <v>Tủ lạnh</v>
+        <v>Quạt</v>
       </c>
       <c r="C100" t="str">
-        <v>Tủ 150L</v>
+        <v>Quạt trần</v>
       </c>
       <c r="D100" t="str">
-        <v>Bếp</v>
+        <v>Hành lang</v>
       </c>
       <c r="E100" t="str">
         <v>GOOD</v>
@@ -6825,44 +6825,44 @@
         <v>1</v>
       </c>
       <c r="G100" t="str">
-        <v>NT cơ bản</v>
+        <v/>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>HD-MTX-21-RENO-WH-BASIC-HO</v>
+        <v>HD-MTX-39-RENO-RM-BASIC-HO</v>
       </c>
       <c r="B101" t="str">
-        <v>Điều hòa</v>
+        <v>Giường</v>
       </c>
       <c r="C101" t="str">
-        <v>Máy 1.5HP</v>
+        <v>Giường sắt cũ</v>
       </c>
       <c r="D101" t="str">
-        <v>Phòng khách</v>
+        <v>Tầng 2</v>
       </c>
       <c r="E101" t="str">
         <v>GOOD</v>
       </c>
       <c r="F101">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G101" t="str">
-        <v>NT cơ bản</v>
+        <v>TB chủ</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>HD-MTX-21-RENO-WH-BASIC-HO</v>
+        <v>HD-MTX-44-RENO-RM-FULL</v>
       </c>
       <c r="B102" t="str">
-        <v>Giường</v>
+        <v>Máy giặt</v>
       </c>
       <c r="C102" t="str">
-        <v>Giường gỗ 1m6</v>
+        <v>Máy cũ chung</v>
       </c>
       <c r="D102" t="str">
-        <v>Phòng ngủ 1</v>
+        <v>Sân phơi</v>
       </c>
       <c r="E102" t="str">
         <v>GOOD</v>
@@ -6871,21 +6871,21 @@
         <v>1</v>
       </c>
       <c r="G102" t="str">
-        <v/>
+        <v>TB dùng chung</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>HD-MTX-21-RENO-WH-BASIC-HO</v>
+        <v>HD-MTX-44-RENO-RM-FULL</v>
       </c>
       <c r="B103" t="str">
-        <v>Quạt</v>
+        <v>Tủ lạnh</v>
       </c>
       <c r="C103" t="str">
-        <v>Quạt trần</v>
+        <v>Tủ cũ tầng 1</v>
       </c>
       <c r="D103" t="str">
-        <v>Phòng khách</v>
+        <v>Bếp chung</v>
       </c>
       <c r="E103" t="str">
         <v>GOOD</v>
@@ -6899,16 +6899,16 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>HD-MTX-21-RENO-WH-BASIC-HO</v>
+        <v>HD-MTX-45-RENO-RM-FULL</v>
       </c>
       <c r="B104" t="str">
-        <v>Nóng lạnh</v>
+        <v>Máy giặt</v>
       </c>
       <c r="C104" t="str">
-        <v>15L</v>
+        <v>Máy cũ chung</v>
       </c>
       <c r="D104" t="str">
-        <v>WC tầng 1</v>
+        <v>Sân phơi</v>
       </c>
       <c r="E104" t="str">
         <v>GOOD</v>
@@ -6917,21 +6917,21 @@
         <v>1</v>
       </c>
       <c r="G104" t="str">
-        <v/>
+        <v>TB dùng chung</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>HD-MTX-25-RENO-WH-FULL</v>
+        <v>HD-MTX-45-RENO-RM-FULL</v>
       </c>
       <c r="B105" t="str">
-        <v>Điều hòa</v>
+        <v>Tủ lạnh</v>
       </c>
       <c r="C105" t="str">
-        <v>1.5HP Inverter</v>
+        <v>Tủ cũ tầng 1</v>
       </c>
       <c r="D105" t="str">
-        <v>Phòng khách</v>
+        <v>Bếp chung</v>
       </c>
       <c r="E105" t="str">
         <v>GOOD</v>
@@ -6945,16 +6945,16 @@
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>HD-MTX-25-RENO-WH-FULL</v>
+        <v>HD-MTX-46-RENO-RM-FULL</v>
       </c>
       <c r="B106" t="str">
-        <v>Điều hòa</v>
+        <v>Máy giặt</v>
       </c>
       <c r="C106" t="str">
-        <v>1HP Inverter</v>
+        <v>Máy cũ chung</v>
       </c>
       <c r="D106" t="str">
-        <v>Phòng ngủ 1</v>
+        <v>Sân phơi</v>
       </c>
       <c r="E106" t="str">
         <v>GOOD</v>
@@ -6963,21 +6963,21 @@
         <v>1</v>
       </c>
       <c r="G106" t="str">
-        <v/>
+        <v>TB dùng chung</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>HD-MTX-25-RENO-WH-FULL</v>
+        <v>HD-MTX-46-RENO-RM-FULL</v>
       </c>
       <c r="B107" t="str">
-        <v>Điều hòa</v>
+        <v>Tủ lạnh</v>
       </c>
       <c r="C107" t="str">
-        <v>1HP</v>
+        <v>Tủ cũ tầng 1</v>
       </c>
       <c r="D107" t="str">
-        <v>Phòng ngủ 2</v>
+        <v>Bếp chung</v>
       </c>
       <c r="E107" t="str">
         <v>GOOD</v>
@@ -6991,16 +6991,16 @@
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>HD-MTX-25-RENO-WH-FULL</v>
+        <v>HD-MTX-47-RENO-RM-FULL</v>
       </c>
       <c r="B108" t="str">
-        <v>Tủ lạnh</v>
+        <v>Máy giặt</v>
       </c>
       <c r="C108" t="str">
-        <v>Inverter 200L</v>
+        <v>Máy cũ chung</v>
       </c>
       <c r="D108" t="str">
-        <v>Bếp</v>
+        <v>Sân phơi</v>
       </c>
       <c r="E108" t="str">
         <v>GOOD</v>
@@ -7009,21 +7009,21 @@
         <v>1</v>
       </c>
       <c r="G108" t="str">
-        <v/>
+        <v>TB dùng chung</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>HD-MTX-25-RENO-WH-FULL</v>
+        <v>HD-MTX-47-RENO-RM-FULL</v>
       </c>
       <c r="B109" t="str">
-        <v>Máy giặt</v>
+        <v>Tủ lạnh</v>
       </c>
       <c r="C109" t="str">
-        <v>Cửa trước 8kg</v>
+        <v>Tủ cũ tầng 1</v>
       </c>
       <c r="D109" t="str">
-        <v>Sân sau</v>
+        <v>Bếp chung</v>
       </c>
       <c r="E109" t="str">
         <v>GOOD</v>
@@ -7037,39 +7037,39 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>HD-MTX-25-RENO-WH-FULL</v>
+        <v>HD-MTX-48-RENO-RM-HO-BUY</v>
       </c>
       <c r="B110" t="str">
-        <v>Nóng lạnh</v>
+        <v>Giường</v>
       </c>
       <c r="C110" t="str">
-        <v>15L</v>
+        <v>Giường sắt cũ</v>
       </c>
       <c r="D110" t="str">
-        <v>WC tầng 1</v>
+        <v>Tầng 2</v>
       </c>
       <c r="E110" t="str">
         <v>GOOD</v>
       </c>
       <c r="F110">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G110" t="str">
-        <v/>
+        <v>TB chủ</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>HD-MTX-25-RENO-WH-FULL</v>
+        <v>HD-MTX-48-RENO-RM-HO-BUY</v>
       </c>
       <c r="B111" t="str">
-        <v>Nóng lạnh</v>
+        <v>Quạt</v>
       </c>
       <c r="C111" t="str">
-        <v>15L</v>
+        <v>Quạt trần</v>
       </c>
       <c r="D111" t="str">
-        <v>WC tầng 2</v>
+        <v>Hành lang</v>
       </c>
       <c r="E111" t="str">
         <v>GOOD</v>
@@ -7083,53 +7083,53 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>HD-MTX-25-RENO-WH-FULL</v>
+        <v>HD-MTX-49-RENO-RM-HO-BUY</v>
       </c>
       <c r="B112" t="str">
         <v>Giường</v>
       </c>
       <c r="C112" t="str">
-        <v>Giường gỗ 1m6</v>
+        <v>Giường sắt cũ</v>
       </c>
       <c r="D112" t="str">
-        <v>Phòng ngủ 1</v>
+        <v>Tầng 2</v>
       </c>
       <c r="E112" t="str">
         <v>GOOD</v>
       </c>
       <c r="F112">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G112" t="str">
-        <v/>
+        <v>TB chủ</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>HD-MTX-25-RENO-WH-FULL</v>
+        <v>HD-MTX-50-RENO-RM-HO-BUY</v>
       </c>
       <c r="B113" t="str">
         <v>Giường</v>
       </c>
       <c r="C113" t="str">
-        <v>Giường gỗ 1m6</v>
+        <v>Giường sắt cũ</v>
       </c>
       <c r="D113" t="str">
-        <v>Phòng ngủ 2</v>
+        <v>Tầng 2</v>
       </c>
       <c r="E113" t="str">
         <v>GOOD</v>
       </c>
       <c r="F113">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G113" t="str">
-        <v/>
+        <v>TB chủ</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>HD-MTX-25-RENO-WH-FULL</v>
+        <v>HD-MTX-50-RENO-RM-HO-BUY</v>
       </c>
       <c r="B114" t="str">
         <v>Quạt</v>
@@ -7138,7 +7138,7 @@
         <v>Quạt trần</v>
       </c>
       <c r="D114" t="str">
-        <v>Phòng khách</v>
+        <v>Hành lang</v>
       </c>
       <c r="E114" t="str">
         <v>GOOD</v>
@@ -7148,2656 +7148,11 @@
       </c>
       <c r="G114" t="str">
         <v/>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="str">
-        <v>HD-MTX-25-RENO-WH-FULL</v>
-      </c>
-      <c r="B115" t="str">
-        <v>Quạt</v>
-      </c>
-      <c r="C115" t="str">
-        <v>Quạt đứng</v>
-      </c>
-      <c r="D115" t="str">
-        <v>Phòng ngủ 1</v>
-      </c>
-      <c r="E115" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F115">
-        <v>1</v>
-      </c>
-      <c r="G115" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="str">
-        <v>HD-MTX-25-RENO-WH-FULL</v>
-      </c>
-      <c r="B116" t="str">
-        <v>Quạt</v>
-      </c>
-      <c r="C116" t="str">
-        <v>Quạt đứng</v>
-      </c>
-      <c r="D116" t="str">
-        <v>Phòng ngủ 2</v>
-      </c>
-      <c r="E116" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F116">
-        <v>1</v>
-      </c>
-      <c r="G116" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="str">
-        <v>HD-MTX-26-RENO-WH-FULL</v>
-      </c>
-      <c r="B117" t="str">
-        <v>Điều hòa</v>
-      </c>
-      <c r="C117" t="str">
-        <v>1.5HP Inverter</v>
-      </c>
-      <c r="D117" t="str">
-        <v>Phòng khách</v>
-      </c>
-      <c r="E117" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F117">
-        <v>1</v>
-      </c>
-      <c r="G117" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="str">
-        <v>HD-MTX-26-RENO-WH-FULL</v>
-      </c>
-      <c r="B118" t="str">
-        <v>Điều hòa</v>
-      </c>
-      <c r="C118" t="str">
-        <v>1HP Inverter</v>
-      </c>
-      <c r="D118" t="str">
-        <v>Phòng ngủ 1</v>
-      </c>
-      <c r="E118" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F118">
-        <v>1</v>
-      </c>
-      <c r="G118" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="str">
-        <v>HD-MTX-26-RENO-WH-FULL</v>
-      </c>
-      <c r="B119" t="str">
-        <v>Điều hòa</v>
-      </c>
-      <c r="C119" t="str">
-        <v>1HP</v>
-      </c>
-      <c r="D119" t="str">
-        <v>Phòng ngủ 2</v>
-      </c>
-      <c r="E119" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F119">
-        <v>1</v>
-      </c>
-      <c r="G119" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="str">
-        <v>HD-MTX-26-RENO-WH-FULL</v>
-      </c>
-      <c r="B120" t="str">
-        <v>Điều hòa</v>
-      </c>
-      <c r="C120" t="str">
-        <v>1HP</v>
-      </c>
-      <c r="D120" t="str">
-        <v>Phòng ngủ 3</v>
-      </c>
-      <c r="E120" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F120">
-        <v>1</v>
-      </c>
-      <c r="G120" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="str">
-        <v>HD-MTX-26-RENO-WH-FULL</v>
-      </c>
-      <c r="B121" t="str">
-        <v>Tủ lạnh</v>
-      </c>
-      <c r="C121" t="str">
-        <v>Inverter 200L</v>
-      </c>
-      <c r="D121" t="str">
-        <v>Bếp</v>
-      </c>
-      <c r="E121" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F121">
-        <v>1</v>
-      </c>
-      <c r="G121" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="str">
-        <v>HD-MTX-26-RENO-WH-FULL</v>
-      </c>
-      <c r="B122" t="str">
-        <v>Máy giặt</v>
-      </c>
-      <c r="C122" t="str">
-        <v>Cửa trước 8kg</v>
-      </c>
-      <c r="D122" t="str">
-        <v>Sân sau</v>
-      </c>
-      <c r="E122" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F122">
-        <v>1</v>
-      </c>
-      <c r="G122" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="str">
-        <v>HD-MTX-26-RENO-WH-FULL</v>
-      </c>
-      <c r="B123" t="str">
-        <v>Nóng lạnh</v>
-      </c>
-      <c r="C123" t="str">
-        <v>15L</v>
-      </c>
-      <c r="D123" t="str">
-        <v>WC tầng 1</v>
-      </c>
-      <c r="E123" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F123">
-        <v>1</v>
-      </c>
-      <c r="G123" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="str">
-        <v>HD-MTX-26-RENO-WH-FULL</v>
-      </c>
-      <c r="B124" t="str">
-        <v>Giường</v>
-      </c>
-      <c r="C124" t="str">
-        <v>Giường gỗ 1m6</v>
-      </c>
-      <c r="D124" t="str">
-        <v>Phòng ngủ 1</v>
-      </c>
-      <c r="E124" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F124">
-        <v>1</v>
-      </c>
-      <c r="G124" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="str">
-        <v>HD-MTX-26-RENO-WH-FULL</v>
-      </c>
-      <c r="B125" t="str">
-        <v>Giường</v>
-      </c>
-      <c r="C125" t="str">
-        <v>Giường gỗ 1m6</v>
-      </c>
-      <c r="D125" t="str">
-        <v>Phòng ngủ 2</v>
-      </c>
-      <c r="E125" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F125">
-        <v>1</v>
-      </c>
-      <c r="G125" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="str">
-        <v>HD-MTX-26-RENO-WH-FULL</v>
-      </c>
-      <c r="B126" t="str">
-        <v>Giường</v>
-      </c>
-      <c r="C126" t="str">
-        <v>Giường gỗ 1m6</v>
-      </c>
-      <c r="D126" t="str">
-        <v>Phòng ngủ 3</v>
-      </c>
-      <c r="E126" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F126">
-        <v>1</v>
-      </c>
-      <c r="G126" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="str">
-        <v>HD-MTX-26-RENO-WH-FULL</v>
-      </c>
-      <c r="B127" t="str">
-        <v>Quạt</v>
-      </c>
-      <c r="C127" t="str">
-        <v>Quạt trần</v>
-      </c>
-      <c r="D127" t="str">
-        <v>Phòng khách</v>
-      </c>
-      <c r="E127" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F127">
-        <v>1</v>
-      </c>
-      <c r="G127" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="str">
-        <v>HD-MTX-26-RENO-WH-FULL</v>
-      </c>
-      <c r="B128" t="str">
-        <v>Quạt</v>
-      </c>
-      <c r="C128" t="str">
-        <v>Quạt đứng</v>
-      </c>
-      <c r="D128" t="str">
-        <v>Phòng ngủ 1</v>
-      </c>
-      <c r="E128" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F128">
-        <v>1</v>
-      </c>
-      <c r="G128" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="str">
-        <v>HD-MTX-26-RENO-WH-FULL</v>
-      </c>
-      <c r="B129" t="str">
-        <v>Quạt</v>
-      </c>
-      <c r="C129" t="str">
-        <v>Quạt đứng</v>
-      </c>
-      <c r="D129" t="str">
-        <v>Phòng ngủ 2</v>
-      </c>
-      <c r="E129" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F129">
-        <v>1</v>
-      </c>
-      <c r="G129" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="str">
-        <v>HD-MTX-26-RENO-WH-FULL</v>
-      </c>
-      <c r="B130" t="str">
-        <v>Quạt</v>
-      </c>
-      <c r="C130" t="str">
-        <v>Quạt đứng</v>
-      </c>
-      <c r="D130" t="str">
-        <v>Phòng ngủ 3</v>
-      </c>
-      <c r="E130" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F130">
-        <v>1</v>
-      </c>
-      <c r="G130" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="str">
-        <v>HD-MTX-27-RENO-WH-FULL</v>
-      </c>
-      <c r="B131" t="str">
-        <v>Điều hòa</v>
-      </c>
-      <c r="C131" t="str">
-        <v>1.5HP Inverter</v>
-      </c>
-      <c r="D131" t="str">
-        <v>Phòng khách</v>
-      </c>
-      <c r="E131" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F131">
-        <v>1</v>
-      </c>
-      <c r="G131" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="str">
-        <v>HD-MTX-27-RENO-WH-FULL</v>
-      </c>
-      <c r="B132" t="str">
-        <v>Điều hòa</v>
-      </c>
-      <c r="C132" t="str">
-        <v>1HP Inverter</v>
-      </c>
-      <c r="D132" t="str">
-        <v>Phòng ngủ 1</v>
-      </c>
-      <c r="E132" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F132">
-        <v>1</v>
-      </c>
-      <c r="G132" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="str">
-        <v>HD-MTX-27-RENO-WH-FULL</v>
-      </c>
-      <c r="B133" t="str">
-        <v>Tủ lạnh</v>
-      </c>
-      <c r="C133" t="str">
-        <v>Inverter 200L</v>
-      </c>
-      <c r="D133" t="str">
-        <v>Bếp</v>
-      </c>
-      <c r="E133" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F133">
-        <v>1</v>
-      </c>
-      <c r="G133" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="str">
-        <v>HD-MTX-27-RENO-WH-FULL</v>
-      </c>
-      <c r="B134" t="str">
-        <v>Máy giặt</v>
-      </c>
-      <c r="C134" t="str">
-        <v>Cửa trước 8kg</v>
-      </c>
-      <c r="D134" t="str">
-        <v>Sân sau</v>
-      </c>
-      <c r="E134" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F134">
-        <v>1</v>
-      </c>
-      <c r="G134" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="str">
-        <v>HD-MTX-27-RENO-WH-FULL</v>
-      </c>
-      <c r="B135" t="str">
-        <v>Nóng lạnh</v>
-      </c>
-      <c r="C135" t="str">
-        <v>15L</v>
-      </c>
-      <c r="D135" t="str">
-        <v>WC tầng 1</v>
-      </c>
-      <c r="E135" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F135">
-        <v>1</v>
-      </c>
-      <c r="G135" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="str">
-        <v>HD-MTX-27-RENO-WH-FULL</v>
-      </c>
-      <c r="B136" t="str">
-        <v>Nóng lạnh</v>
-      </c>
-      <c r="C136" t="str">
-        <v>15L</v>
-      </c>
-      <c r="D136" t="str">
-        <v>WC tầng 2</v>
-      </c>
-      <c r="E136" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F136">
-        <v>1</v>
-      </c>
-      <c r="G136" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="str">
-        <v>HD-MTX-27-RENO-WH-FULL</v>
-      </c>
-      <c r="B137" t="str">
-        <v>Giường</v>
-      </c>
-      <c r="C137" t="str">
-        <v>Giường gỗ 1m6</v>
-      </c>
-      <c r="D137" t="str">
-        <v>Phòng ngủ 1</v>
-      </c>
-      <c r="E137" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F137">
-        <v>1</v>
-      </c>
-      <c r="G137" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="str">
-        <v>HD-MTX-27-RENO-WH-FULL</v>
-      </c>
-      <c r="B138" t="str">
-        <v>Quạt</v>
-      </c>
-      <c r="C138" t="str">
-        <v>Quạt trần</v>
-      </c>
-      <c r="D138" t="str">
-        <v>Phòng khách</v>
-      </c>
-      <c r="E138" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F138">
-        <v>1</v>
-      </c>
-      <c r="G138" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="str">
-        <v>HD-MTX-27-RENO-WH-FULL</v>
-      </c>
-      <c r="B139" t="str">
-        <v>Quạt</v>
-      </c>
-      <c r="C139" t="str">
-        <v>Quạt đứng</v>
-      </c>
-      <c r="D139" t="str">
-        <v>Phòng ngủ 1</v>
-      </c>
-      <c r="E139" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F139">
-        <v>1</v>
-      </c>
-      <c r="G139" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="str">
-        <v>HD-MTX-30-RENO-WH-HO-BUY</v>
-      </c>
-      <c r="B140" t="str">
-        <v>Điều hòa</v>
-      </c>
-      <c r="C140" t="str">
-        <v>Máy 1.5HP</v>
-      </c>
-      <c r="D140" t="str">
-        <v>Phòng khách</v>
-      </c>
-      <c r="E140" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F140">
-        <v>1</v>
-      </c>
-      <c r="G140" t="str">
-        <v>NT cơ bản</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="str">
-        <v>HD-MTX-30-RENO-WH-HO-BUY</v>
-      </c>
-      <c r="B141" t="str">
-        <v>Giường</v>
-      </c>
-      <c r="C141" t="str">
-        <v>Giường gỗ 1m6</v>
-      </c>
-      <c r="D141" t="str">
-        <v>Phòng ngủ 1</v>
-      </c>
-      <c r="E141" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F141">
-        <v>1</v>
-      </c>
-      <c r="G141" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="str">
-        <v>HD-MTX-30-RENO-WH-HO-BUY</v>
-      </c>
-      <c r="B142" t="str">
-        <v>Quạt</v>
-      </c>
-      <c r="C142" t="str">
-        <v>Quạt trần</v>
-      </c>
-      <c r="D142" t="str">
-        <v>Phòng khách</v>
-      </c>
-      <c r="E142" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F142">
-        <v>1</v>
-      </c>
-      <c r="G142" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="str">
-        <v>HD-MTX-30-RENO-WH-HO-BUY</v>
-      </c>
-      <c r="B143" t="str">
-        <v>Nóng lạnh</v>
-      </c>
-      <c r="C143" t="str">
-        <v>15L</v>
-      </c>
-      <c r="D143" t="str">
-        <v>WC tầng 1</v>
-      </c>
-      <c r="E143" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F143">
-        <v>1</v>
-      </c>
-      <c r="G143" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="str">
-        <v>HD-MTX-30-RENO-WH-HO-BUY</v>
-      </c>
-      <c r="B144" t="str">
-        <v>Tủ lạnh</v>
-      </c>
-      <c r="C144" t="str">
-        <v>Tủ 150L</v>
-      </c>
-      <c r="D144" t="str">
-        <v>Bếp</v>
-      </c>
-      <c r="E144" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F144">
-        <v>1</v>
-      </c>
-      <c r="G144" t="str">
-        <v>NT cơ bản</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="str">
-        <v>HD-MTX-31-RENO-WH-HO-BUY</v>
-      </c>
-      <c r="B145" t="str">
-        <v>Điều hòa</v>
-      </c>
-      <c r="C145" t="str">
-        <v>Máy 1.5HP</v>
-      </c>
-      <c r="D145" t="str">
-        <v>Phòng khách</v>
-      </c>
-      <c r="E145" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F145">
-        <v>1</v>
-      </c>
-      <c r="G145" t="str">
-        <v>NT cơ bản</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="str">
-        <v>HD-MTX-31-RENO-WH-HO-BUY</v>
-      </c>
-      <c r="B146" t="str">
-        <v>Giường</v>
-      </c>
-      <c r="C146" t="str">
-        <v>Giường gỗ 1m6</v>
-      </c>
-      <c r="D146" t="str">
-        <v>Phòng ngủ 1</v>
-      </c>
-      <c r="E146" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F146">
-        <v>1</v>
-      </c>
-      <c r="G146" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="str">
-        <v>HD-MTX-31-RENO-WH-HO-BUY</v>
-      </c>
-      <c r="B147" t="str">
-        <v>Giường</v>
-      </c>
-      <c r="C147" t="str">
-        <v>Giường gỗ 1m2</v>
-      </c>
-      <c r="D147" t="str">
-        <v>Phòng ngủ 2</v>
-      </c>
-      <c r="E147" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F147">
-        <v>1</v>
-      </c>
-      <c r="G147" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="str">
-        <v>HD-MTX-31-RENO-WH-HO-BUY</v>
-      </c>
-      <c r="B148" t="str">
-        <v>Quạt</v>
-      </c>
-      <c r="C148" t="str">
-        <v>Quạt trần</v>
-      </c>
-      <c r="D148" t="str">
-        <v>Phòng khách</v>
-      </c>
-      <c r="E148" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F148">
-        <v>1</v>
-      </c>
-      <c r="G148" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="str">
-        <v>HD-MTX-31-RENO-WH-HO-BUY</v>
-      </c>
-      <c r="B149" t="str">
-        <v>Nóng lạnh</v>
-      </c>
-      <c r="C149" t="str">
-        <v>15L</v>
-      </c>
-      <c r="D149" t="str">
-        <v>WC tầng 1</v>
-      </c>
-      <c r="E149" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F149">
-        <v>1</v>
-      </c>
-      <c r="G149" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="str">
-        <v>HD-MTX-31-RENO-WH-HO-BUY</v>
-      </c>
-      <c r="B150" t="str">
-        <v>Tủ lạnh</v>
-      </c>
-      <c r="C150" t="str">
-        <v>Tủ 150L</v>
-      </c>
-      <c r="D150" t="str">
-        <v>Bếp</v>
-      </c>
-      <c r="E150" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F150">
-        <v>1</v>
-      </c>
-      <c r="G150" t="str">
-        <v>NT cơ bản</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="str">
-        <v>HD-MTX-36-RENO-RM-BASIC-HO</v>
-      </c>
-      <c r="B151" t="str">
-        <v>Giường</v>
-      </c>
-      <c r="C151" t="str">
-        <v>Giường sắt cũ</v>
-      </c>
-      <c r="D151" t="str">
-        <v>Phòng 101</v>
-      </c>
-      <c r="E151" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F151">
-        <v>1</v>
-      </c>
-      <c r="G151" t="str">
-        <v>TB chủ</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="str">
-        <v>HD-MTX-36-RENO-RM-BASIC-HO</v>
-      </c>
-      <c r="B152" t="str">
-        <v>Giường</v>
-      </c>
-      <c r="C152" t="str">
-        <v>Giường sắt cũ</v>
-      </c>
-      <c r="D152" t="str">
-        <v>Phòng 102</v>
-      </c>
-      <c r="E152" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F152">
-        <v>1</v>
-      </c>
-      <c r="G152" t="str">
-        <v>TB chủ</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="str">
-        <v>HD-MTX-36-RENO-RM-BASIC-HO</v>
-      </c>
-      <c r="B153" t="str">
-        <v>Giường</v>
-      </c>
-      <c r="C153" t="str">
-        <v>Giường sắt cũ</v>
-      </c>
-      <c r="D153" t="str">
-        <v>Phòng 103</v>
-      </c>
-      <c r="E153" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F153">
-        <v>1</v>
-      </c>
-      <c r="G153" t="str">
-        <v>TB chủ</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="str">
-        <v>HD-MTX-36-RENO-RM-BASIC-HO</v>
-      </c>
-      <c r="B154" t="str">
-        <v>Quạt</v>
-      </c>
-      <c r="C154" t="str">
-        <v>Quạt trần</v>
-      </c>
-      <c r="D154" t="str">
-        <v>Hành lang</v>
-      </c>
-      <c r="E154" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F154">
-        <v>1</v>
-      </c>
-      <c r="G154" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="str">
-        <v>HD-MTX-36-RENO-RM-BASIC-HO</v>
-      </c>
-      <c r="B155" t="str">
-        <v>Nóng lạnh</v>
-      </c>
-      <c r="C155" t="str">
-        <v>Máy cũ</v>
-      </c>
-      <c r="D155" t="str">
-        <v>WC chung</v>
-      </c>
-      <c r="E155" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F155">
-        <v>1</v>
-      </c>
-      <c r="G155" t="str">
-        <v>Dùng chung</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="str">
-        <v>HD-MTX-37-RENO-RM-BASIC-HO</v>
-      </c>
-      <c r="B156" t="str">
-        <v>Giường</v>
-      </c>
-      <c r="C156" t="str">
-        <v>Giường sắt cũ</v>
-      </c>
-      <c r="D156" t="str">
-        <v>Phòng 101</v>
-      </c>
-      <c r="E156" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F156">
-        <v>1</v>
-      </c>
-      <c r="G156" t="str">
-        <v>TB chủ</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="str">
-        <v>HD-MTX-37-RENO-RM-BASIC-HO</v>
-      </c>
-      <c r="B157" t="str">
-        <v>Giường</v>
-      </c>
-      <c r="C157" t="str">
-        <v>Giường sắt cũ</v>
-      </c>
-      <c r="D157" t="str">
-        <v>Phòng 102</v>
-      </c>
-      <c r="E157" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F157">
-        <v>1</v>
-      </c>
-      <c r="G157" t="str">
-        <v>TB chủ</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="str">
-        <v>HD-MTX-37-RENO-RM-BASIC-HO</v>
-      </c>
-      <c r="B158" t="str">
-        <v>Giường</v>
-      </c>
-      <c r="C158" t="str">
-        <v>Giường sắt cũ</v>
-      </c>
-      <c r="D158" t="str">
-        <v>Phòng 103</v>
-      </c>
-      <c r="E158" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F158">
-        <v>1</v>
-      </c>
-      <c r="G158" t="str">
-        <v>TB chủ</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="str">
-        <v>HD-MTX-37-RENO-RM-BASIC-HO</v>
-      </c>
-      <c r="B159" t="str">
-        <v>Quạt</v>
-      </c>
-      <c r="C159" t="str">
-        <v>Quạt trần</v>
-      </c>
-      <c r="D159" t="str">
-        <v>Hành lang</v>
-      </c>
-      <c r="E159" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F159">
-        <v>1</v>
-      </c>
-      <c r="G159" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="str">
-        <v>HD-MTX-37-RENO-RM-BASIC-HO</v>
-      </c>
-      <c r="B160" t="str">
-        <v>Nóng lạnh</v>
-      </c>
-      <c r="C160" t="str">
-        <v>Máy cũ</v>
-      </c>
-      <c r="D160" t="str">
-        <v>WC chung</v>
-      </c>
-      <c r="E160" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F160">
-        <v>1</v>
-      </c>
-      <c r="G160" t="str">
-        <v>Dùng chung</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="str">
-        <v>HD-MTX-38-RENO-RM-BASIC-HO</v>
-      </c>
-      <c r="B161" t="str">
-        <v>Giường</v>
-      </c>
-      <c r="C161" t="str">
-        <v>Giường sắt cũ</v>
-      </c>
-      <c r="D161" t="str">
-        <v>Phòng 101</v>
-      </c>
-      <c r="E161" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F161">
-        <v>1</v>
-      </c>
-      <c r="G161" t="str">
-        <v>TB chủ</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="str">
-        <v>HD-MTX-38-RENO-RM-BASIC-HO</v>
-      </c>
-      <c r="B162" t="str">
-        <v>Giường</v>
-      </c>
-      <c r="C162" t="str">
-        <v>Giường sắt cũ</v>
-      </c>
-      <c r="D162" t="str">
-        <v>Phòng 102</v>
-      </c>
-      <c r="E162" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F162">
-        <v>1</v>
-      </c>
-      <c r="G162" t="str">
-        <v>TB chủ</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="str">
-        <v>HD-MTX-38-RENO-RM-BASIC-HO</v>
-      </c>
-      <c r="B163" t="str">
-        <v>Giường</v>
-      </c>
-      <c r="C163" t="str">
-        <v>Giường sắt cũ</v>
-      </c>
-      <c r="D163" t="str">
-        <v>Phòng 103</v>
-      </c>
-      <c r="E163" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F163">
-        <v>1</v>
-      </c>
-      <c r="G163" t="str">
-        <v>TB chủ</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="str">
-        <v>HD-MTX-38-RENO-RM-BASIC-HO</v>
-      </c>
-      <c r="B164" t="str">
-        <v>Quạt</v>
-      </c>
-      <c r="C164" t="str">
-        <v>Quạt trần</v>
-      </c>
-      <c r="D164" t="str">
-        <v>Hành lang</v>
-      </c>
-      <c r="E164" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F164">
-        <v>1</v>
-      </c>
-      <c r="G164" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="str">
-        <v>HD-MTX-38-RENO-RM-BASIC-HO</v>
-      </c>
-      <c r="B165" t="str">
-        <v>Nóng lạnh</v>
-      </c>
-      <c r="C165" t="str">
-        <v>Máy cũ</v>
-      </c>
-      <c r="D165" t="str">
-        <v>WC chung</v>
-      </c>
-      <c r="E165" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F165">
-        <v>1</v>
-      </c>
-      <c r="G165" t="str">
-        <v>Dùng chung</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="str">
-        <v>HD-MTX-39-RENO-RM-BASIC-HO</v>
-      </c>
-      <c r="B166" t="str">
-        <v>Giường</v>
-      </c>
-      <c r="C166" t="str">
-        <v>Giường sắt cũ</v>
-      </c>
-      <c r="D166" t="str">
-        <v>Phòng 101</v>
-      </c>
-      <c r="E166" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F166">
-        <v>1</v>
-      </c>
-      <c r="G166" t="str">
-        <v>TB chủ</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="str">
-        <v>HD-MTX-39-RENO-RM-BASIC-HO</v>
-      </c>
-      <c r="B167" t="str">
-        <v>Giường</v>
-      </c>
-      <c r="C167" t="str">
-        <v>Giường sắt cũ</v>
-      </c>
-      <c r="D167" t="str">
-        <v>Phòng 102</v>
-      </c>
-      <c r="E167" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F167">
-        <v>1</v>
-      </c>
-      <c r="G167" t="str">
-        <v>TB chủ</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="str">
-        <v>HD-MTX-39-RENO-RM-BASIC-HO</v>
-      </c>
-      <c r="B168" t="str">
-        <v>Giường</v>
-      </c>
-      <c r="C168" t="str">
-        <v>Giường sắt cũ</v>
-      </c>
-      <c r="D168" t="str">
-        <v>Phòng 103</v>
-      </c>
-      <c r="E168" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F168">
-        <v>1</v>
-      </c>
-      <c r="G168" t="str">
-        <v>TB chủ</v>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="str">
-        <v>HD-MTX-39-RENO-RM-BASIC-HO</v>
-      </c>
-      <c r="B169" t="str">
-        <v>Quạt</v>
-      </c>
-      <c r="C169" t="str">
-        <v>Quạt trần</v>
-      </c>
-      <c r="D169" t="str">
-        <v>Hành lang</v>
-      </c>
-      <c r="E169" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F169">
-        <v>1</v>
-      </c>
-      <c r="G169" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="str">
-        <v>HD-MTX-39-RENO-RM-BASIC-HO</v>
-      </c>
-      <c r="B170" t="str">
-        <v>Nóng lạnh</v>
-      </c>
-      <c r="C170" t="str">
-        <v>Máy cũ</v>
-      </c>
-      <c r="D170" t="str">
-        <v>WC chung</v>
-      </c>
-      <c r="E170" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F170">
-        <v>1</v>
-      </c>
-      <c r="G170" t="str">
-        <v>Dùng chung</v>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="str">
-        <v>HD-MTX-44-RENO-RM-FULL</v>
-      </c>
-      <c r="B171" t="str">
-        <v>Máy giặt</v>
-      </c>
-      <c r="C171" t="str">
-        <v>Máy cũ chung</v>
-      </c>
-      <c r="D171" t="str">
-        <v>Sân phơi</v>
-      </c>
-      <c r="E171" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F171">
-        <v>1</v>
-      </c>
-      <c r="G171" t="str">
-        <v>TB dùng chung</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="str">
-        <v>HD-MTX-44-RENO-RM-FULL</v>
-      </c>
-      <c r="B172" t="str">
-        <v>Tủ lạnh</v>
-      </c>
-      <c r="C172" t="str">
-        <v>Tủ cũ tầng 1</v>
-      </c>
-      <c r="D172" t="str">
-        <v>Bếp chung</v>
-      </c>
-      <c r="E172" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F172">
-        <v>1</v>
-      </c>
-      <c r="G172" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="str">
-        <v>HD-MTX-44-RENO-RM-FULL</v>
-      </c>
-      <c r="B173" t="str">
-        <v>Nóng lạnh</v>
-      </c>
-      <c r="C173" t="str">
-        <v>Máy cũ</v>
-      </c>
-      <c r="D173" t="str">
-        <v>WC chung</v>
-      </c>
-      <c r="E173" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F173">
-        <v>1</v>
-      </c>
-      <c r="G173" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="str">
-        <v>HD-MTX-44-RENO-RM-FULL</v>
-      </c>
-      <c r="B174" t="str">
-        <v>Giường</v>
-      </c>
-      <c r="C174" t="str">
-        <v>Giường gỗ 1m6</v>
-      </c>
-      <c r="D174" t="str">
-        <v>Phòng 101</v>
-      </c>
-      <c r="E174" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F174">
-        <v>1</v>
-      </c>
-      <c r="G174" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="str">
-        <v>HD-MTX-44-RENO-RM-FULL</v>
-      </c>
-      <c r="B175" t="str">
-        <v>Quạt</v>
-      </c>
-      <c r="C175" t="str">
-        <v>Quạt đứng</v>
-      </c>
-      <c r="D175" t="str">
-        <v>Phòng 101</v>
-      </c>
-      <c r="E175" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F175">
-        <v>1</v>
-      </c>
-      <c r="G175" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="str">
-        <v>HD-MTX-44-RENO-RM-FULL</v>
-      </c>
-      <c r="B176" t="str">
-        <v>Giường</v>
-      </c>
-      <c r="C176" t="str">
-        <v>Giường gỗ 1m6</v>
-      </c>
-      <c r="D176" t="str">
-        <v>Phòng 102</v>
-      </c>
-      <c r="E176" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F176">
-        <v>1</v>
-      </c>
-      <c r="G176" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="str">
-        <v>HD-MTX-44-RENO-RM-FULL</v>
-      </c>
-      <c r="B177" t="str">
-        <v>Quạt</v>
-      </c>
-      <c r="C177" t="str">
-        <v>Quạt đứng</v>
-      </c>
-      <c r="D177" t="str">
-        <v>Phòng 102</v>
-      </c>
-      <c r="E177" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F177">
-        <v>1</v>
-      </c>
-      <c r="G177" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="str">
-        <v>HD-MTX-44-RENO-RM-FULL</v>
-      </c>
-      <c r="B178" t="str">
-        <v>Giường</v>
-      </c>
-      <c r="C178" t="str">
-        <v>Giường gỗ 1m6</v>
-      </c>
-      <c r="D178" t="str">
-        <v>Phòng 103</v>
-      </c>
-      <c r="E178" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F178">
-        <v>1</v>
-      </c>
-      <c r="G178" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="str">
-        <v>HD-MTX-44-RENO-RM-FULL</v>
-      </c>
-      <c r="B179" t="str">
-        <v>Quạt</v>
-      </c>
-      <c r="C179" t="str">
-        <v>Quạt đứng</v>
-      </c>
-      <c r="D179" t="str">
-        <v>Phòng 103</v>
-      </c>
-      <c r="E179" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F179">
-        <v>1</v>
-      </c>
-      <c r="G179" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="str">
-        <v>HD-MTX-44-RENO-RM-FULL</v>
-      </c>
-      <c r="B180" t="str">
-        <v>Giường</v>
-      </c>
-      <c r="C180" t="str">
-        <v>Giường gỗ 1m6</v>
-      </c>
-      <c r="D180" t="str">
-        <v>Phòng 104</v>
-      </c>
-      <c r="E180" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F180">
-        <v>1</v>
-      </c>
-      <c r="G180" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="str">
-        <v>HD-MTX-44-RENO-RM-FULL</v>
-      </c>
-      <c r="B181" t="str">
-        <v>Quạt</v>
-      </c>
-      <c r="C181" t="str">
-        <v>Quạt đứng</v>
-      </c>
-      <c r="D181" t="str">
-        <v>Phòng 104</v>
-      </c>
-      <c r="E181" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F181">
-        <v>1</v>
-      </c>
-      <c r="G181" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="str">
-        <v>HD-MTX-45-RENO-RM-FULL</v>
-      </c>
-      <c r="B182" t="str">
-        <v>Máy giặt</v>
-      </c>
-      <c r="C182" t="str">
-        <v>Máy cũ chung</v>
-      </c>
-      <c r="D182" t="str">
-        <v>Sân phơi</v>
-      </c>
-      <c r="E182" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F182">
-        <v>1</v>
-      </c>
-      <c r="G182" t="str">
-        <v>TB dùng chung</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="str">
-        <v>HD-MTX-45-RENO-RM-FULL</v>
-      </c>
-      <c r="B183" t="str">
-        <v>Tủ lạnh</v>
-      </c>
-      <c r="C183" t="str">
-        <v>Tủ cũ tầng 1</v>
-      </c>
-      <c r="D183" t="str">
-        <v>Bếp chung</v>
-      </c>
-      <c r="E183" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F183">
-        <v>1</v>
-      </c>
-      <c r="G183" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="str">
-        <v>HD-MTX-45-RENO-RM-FULL</v>
-      </c>
-      <c r="B184" t="str">
-        <v>Nóng lạnh</v>
-      </c>
-      <c r="C184" t="str">
-        <v>Máy cũ</v>
-      </c>
-      <c r="D184" t="str">
-        <v>WC chung</v>
-      </c>
-      <c r="E184" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F184">
-        <v>1</v>
-      </c>
-      <c r="G184" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="str">
-        <v>HD-MTX-45-RENO-RM-FULL</v>
-      </c>
-      <c r="B185" t="str">
-        <v>Giường</v>
-      </c>
-      <c r="C185" t="str">
-        <v>Giường gỗ 1m6</v>
-      </c>
-      <c r="D185" t="str">
-        <v>Phòng 101</v>
-      </c>
-      <c r="E185" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F185">
-        <v>1</v>
-      </c>
-      <c r="G185" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="str">
-        <v>HD-MTX-45-RENO-RM-FULL</v>
-      </c>
-      <c r="B186" t="str">
-        <v>Quạt</v>
-      </c>
-      <c r="C186" t="str">
-        <v>Quạt đứng</v>
-      </c>
-      <c r="D186" t="str">
-        <v>Phòng 101</v>
-      </c>
-      <c r="E186" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F186">
-        <v>1</v>
-      </c>
-      <c r="G186" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="str">
-        <v>HD-MTX-45-RENO-RM-FULL</v>
-      </c>
-      <c r="B187" t="str">
-        <v>Giường</v>
-      </c>
-      <c r="C187" t="str">
-        <v>Giường gỗ 1m6</v>
-      </c>
-      <c r="D187" t="str">
-        <v>Phòng 102</v>
-      </c>
-      <c r="E187" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F187">
-        <v>1</v>
-      </c>
-      <c r="G187" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="str">
-        <v>HD-MTX-45-RENO-RM-FULL</v>
-      </c>
-      <c r="B188" t="str">
-        <v>Quạt</v>
-      </c>
-      <c r="C188" t="str">
-        <v>Quạt đứng</v>
-      </c>
-      <c r="D188" t="str">
-        <v>Phòng 102</v>
-      </c>
-      <c r="E188" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F188">
-        <v>1</v>
-      </c>
-      <c r="G188" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="str">
-        <v>HD-MTX-45-RENO-RM-FULL</v>
-      </c>
-      <c r="B189" t="str">
-        <v>Giường</v>
-      </c>
-      <c r="C189" t="str">
-        <v>Giường gỗ 1m6</v>
-      </c>
-      <c r="D189" t="str">
-        <v>Phòng 103</v>
-      </c>
-      <c r="E189" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F189">
-        <v>1</v>
-      </c>
-      <c r="G189" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="str">
-        <v>HD-MTX-45-RENO-RM-FULL</v>
-      </c>
-      <c r="B190" t="str">
-        <v>Quạt</v>
-      </c>
-      <c r="C190" t="str">
-        <v>Quạt đứng</v>
-      </c>
-      <c r="D190" t="str">
-        <v>Phòng 103</v>
-      </c>
-      <c r="E190" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F190">
-        <v>1</v>
-      </c>
-      <c r="G190" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="str">
-        <v>HD-MTX-45-RENO-RM-FULL</v>
-      </c>
-      <c r="B191" t="str">
-        <v>Giường</v>
-      </c>
-      <c r="C191" t="str">
-        <v>Giường gỗ 1m6</v>
-      </c>
-      <c r="D191" t="str">
-        <v>Phòng 104</v>
-      </c>
-      <c r="E191" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F191">
-        <v>1</v>
-      </c>
-      <c r="G191" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="str">
-        <v>HD-MTX-45-RENO-RM-FULL</v>
-      </c>
-      <c r="B192" t="str">
-        <v>Quạt</v>
-      </c>
-      <c r="C192" t="str">
-        <v>Quạt đứng</v>
-      </c>
-      <c r="D192" t="str">
-        <v>Phòng 104</v>
-      </c>
-      <c r="E192" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F192">
-        <v>1</v>
-      </c>
-      <c r="G192" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="str">
-        <v>HD-MTX-46-RENO-RM-FULL</v>
-      </c>
-      <c r="B193" t="str">
-        <v>Máy giặt</v>
-      </c>
-      <c r="C193" t="str">
-        <v>Máy cũ chung</v>
-      </c>
-      <c r="D193" t="str">
-        <v>Sân phơi</v>
-      </c>
-      <c r="E193" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F193">
-        <v>1</v>
-      </c>
-      <c r="G193" t="str">
-        <v>TB dùng chung</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="str">
-        <v>HD-MTX-46-RENO-RM-FULL</v>
-      </c>
-      <c r="B194" t="str">
-        <v>Tủ lạnh</v>
-      </c>
-      <c r="C194" t="str">
-        <v>Tủ cũ tầng 1</v>
-      </c>
-      <c r="D194" t="str">
-        <v>Bếp chung</v>
-      </c>
-      <c r="E194" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F194">
-        <v>1</v>
-      </c>
-      <c r="G194" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="str">
-        <v>HD-MTX-46-RENO-RM-FULL</v>
-      </c>
-      <c r="B195" t="str">
-        <v>Nóng lạnh</v>
-      </c>
-      <c r="C195" t="str">
-        <v>Máy cũ</v>
-      </c>
-      <c r="D195" t="str">
-        <v>WC chung</v>
-      </c>
-      <c r="E195" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F195">
-        <v>1</v>
-      </c>
-      <c r="G195" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="str">
-        <v>HD-MTX-46-RENO-RM-FULL</v>
-      </c>
-      <c r="B196" t="str">
-        <v>Giường</v>
-      </c>
-      <c r="C196" t="str">
-        <v>Giường gỗ 1m6</v>
-      </c>
-      <c r="D196" t="str">
-        <v>Phòng 101</v>
-      </c>
-      <c r="E196" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F196">
-        <v>1</v>
-      </c>
-      <c r="G196" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="str">
-        <v>HD-MTX-46-RENO-RM-FULL</v>
-      </c>
-      <c r="B197" t="str">
-        <v>Quạt</v>
-      </c>
-      <c r="C197" t="str">
-        <v>Quạt đứng</v>
-      </c>
-      <c r="D197" t="str">
-        <v>Phòng 101</v>
-      </c>
-      <c r="E197" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F197">
-        <v>1</v>
-      </c>
-      <c r="G197" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="str">
-        <v>HD-MTX-46-RENO-RM-FULL</v>
-      </c>
-      <c r="B198" t="str">
-        <v>Giường</v>
-      </c>
-      <c r="C198" t="str">
-        <v>Giường gỗ 1m6</v>
-      </c>
-      <c r="D198" t="str">
-        <v>Phòng 102</v>
-      </c>
-      <c r="E198" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F198">
-        <v>1</v>
-      </c>
-      <c r="G198" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="str">
-        <v>HD-MTX-46-RENO-RM-FULL</v>
-      </c>
-      <c r="B199" t="str">
-        <v>Quạt</v>
-      </c>
-      <c r="C199" t="str">
-        <v>Quạt đứng</v>
-      </c>
-      <c r="D199" t="str">
-        <v>Phòng 102</v>
-      </c>
-      <c r="E199" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F199">
-        <v>1</v>
-      </c>
-      <c r="G199" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="str">
-        <v>HD-MTX-46-RENO-RM-FULL</v>
-      </c>
-      <c r="B200" t="str">
-        <v>Giường</v>
-      </c>
-      <c r="C200" t="str">
-        <v>Giường gỗ 1m6</v>
-      </c>
-      <c r="D200" t="str">
-        <v>Phòng 103</v>
-      </c>
-      <c r="E200" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F200">
-        <v>1</v>
-      </c>
-      <c r="G200" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="str">
-        <v>HD-MTX-46-RENO-RM-FULL</v>
-      </c>
-      <c r="B201" t="str">
-        <v>Quạt</v>
-      </c>
-      <c r="C201" t="str">
-        <v>Quạt đứng</v>
-      </c>
-      <c r="D201" t="str">
-        <v>Phòng 103</v>
-      </c>
-      <c r="E201" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F201">
-        <v>1</v>
-      </c>
-      <c r="G201" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" t="str">
-        <v>HD-MTX-46-RENO-RM-FULL</v>
-      </c>
-      <c r="B202" t="str">
-        <v>Giường</v>
-      </c>
-      <c r="C202" t="str">
-        <v>Giường gỗ 1m6</v>
-      </c>
-      <c r="D202" t="str">
-        <v>Phòng 104</v>
-      </c>
-      <c r="E202" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F202">
-        <v>1</v>
-      </c>
-      <c r="G202" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="str">
-        <v>HD-MTX-46-RENO-RM-FULL</v>
-      </c>
-      <c r="B203" t="str">
-        <v>Quạt</v>
-      </c>
-      <c r="C203" t="str">
-        <v>Quạt đứng</v>
-      </c>
-      <c r="D203" t="str">
-        <v>Phòng 104</v>
-      </c>
-      <c r="E203" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F203">
-        <v>1</v>
-      </c>
-      <c r="G203" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" t="str">
-        <v>HD-MTX-47-RENO-RM-FULL</v>
-      </c>
-      <c r="B204" t="str">
-        <v>Máy giặt</v>
-      </c>
-      <c r="C204" t="str">
-        <v>Máy cũ chung</v>
-      </c>
-      <c r="D204" t="str">
-        <v>Sân phơi</v>
-      </c>
-      <c r="E204" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F204">
-        <v>1</v>
-      </c>
-      <c r="G204" t="str">
-        <v>TB dùng chung</v>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" t="str">
-        <v>HD-MTX-47-RENO-RM-FULL</v>
-      </c>
-      <c r="B205" t="str">
-        <v>Tủ lạnh</v>
-      </c>
-      <c r="C205" t="str">
-        <v>Tủ cũ tầng 1</v>
-      </c>
-      <c r="D205" t="str">
-        <v>Bếp chung</v>
-      </c>
-      <c r="E205" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F205">
-        <v>1</v>
-      </c>
-      <c r="G205" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" t="str">
-        <v>HD-MTX-47-RENO-RM-FULL</v>
-      </c>
-      <c r="B206" t="str">
-        <v>Nóng lạnh</v>
-      </c>
-      <c r="C206" t="str">
-        <v>Máy cũ</v>
-      </c>
-      <c r="D206" t="str">
-        <v>WC chung</v>
-      </c>
-      <c r="E206" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F206">
-        <v>1</v>
-      </c>
-      <c r="G206" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" t="str">
-        <v>HD-MTX-47-RENO-RM-FULL</v>
-      </c>
-      <c r="B207" t="str">
-        <v>Giường</v>
-      </c>
-      <c r="C207" t="str">
-        <v>Giường gỗ 1m6</v>
-      </c>
-      <c r="D207" t="str">
-        <v>Phòng 101</v>
-      </c>
-      <c r="E207" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F207">
-        <v>1</v>
-      </c>
-      <c r="G207" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" t="str">
-        <v>HD-MTX-47-RENO-RM-FULL</v>
-      </c>
-      <c r="B208" t="str">
-        <v>Quạt</v>
-      </c>
-      <c r="C208" t="str">
-        <v>Quạt đứng</v>
-      </c>
-      <c r="D208" t="str">
-        <v>Phòng 101</v>
-      </c>
-      <c r="E208" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F208">
-        <v>1</v>
-      </c>
-      <c r="G208" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" t="str">
-        <v>HD-MTX-47-RENO-RM-FULL</v>
-      </c>
-      <c r="B209" t="str">
-        <v>Giường</v>
-      </c>
-      <c r="C209" t="str">
-        <v>Giường gỗ 1m6</v>
-      </c>
-      <c r="D209" t="str">
-        <v>Phòng 102</v>
-      </c>
-      <c r="E209" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F209">
-        <v>1</v>
-      </c>
-      <c r="G209" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" t="str">
-        <v>HD-MTX-47-RENO-RM-FULL</v>
-      </c>
-      <c r="B210" t="str">
-        <v>Quạt</v>
-      </c>
-      <c r="C210" t="str">
-        <v>Quạt đứng</v>
-      </c>
-      <c r="D210" t="str">
-        <v>Phòng 102</v>
-      </c>
-      <c r="E210" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F210">
-        <v>1</v>
-      </c>
-      <c r="G210" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" t="str">
-        <v>HD-MTX-47-RENO-RM-FULL</v>
-      </c>
-      <c r="B211" t="str">
-        <v>Giường</v>
-      </c>
-      <c r="C211" t="str">
-        <v>Giường gỗ 1m6</v>
-      </c>
-      <c r="D211" t="str">
-        <v>Phòng 103</v>
-      </c>
-      <c r="E211" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F211">
-        <v>1</v>
-      </c>
-      <c r="G211" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" t="str">
-        <v>HD-MTX-47-RENO-RM-FULL</v>
-      </c>
-      <c r="B212" t="str">
-        <v>Quạt</v>
-      </c>
-      <c r="C212" t="str">
-        <v>Quạt đứng</v>
-      </c>
-      <c r="D212" t="str">
-        <v>Phòng 103</v>
-      </c>
-      <c r="E212" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F212">
-        <v>1</v>
-      </c>
-      <c r="G212" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" t="str">
-        <v>HD-MTX-47-RENO-RM-FULL</v>
-      </c>
-      <c r="B213" t="str">
-        <v>Giường</v>
-      </c>
-      <c r="C213" t="str">
-        <v>Giường gỗ 1m6</v>
-      </c>
-      <c r="D213" t="str">
-        <v>Phòng 104</v>
-      </c>
-      <c r="E213" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F213">
-        <v>1</v>
-      </c>
-      <c r="G213" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" t="str">
-        <v>HD-MTX-47-RENO-RM-FULL</v>
-      </c>
-      <c r="B214" t="str">
-        <v>Quạt</v>
-      </c>
-      <c r="C214" t="str">
-        <v>Quạt đứng</v>
-      </c>
-      <c r="D214" t="str">
-        <v>Phòng 104</v>
-      </c>
-      <c r="E214" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F214">
-        <v>1</v>
-      </c>
-      <c r="G214" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" t="str">
-        <v>HD-MTX-48-RENO-RM-HO-BUY</v>
-      </c>
-      <c r="B215" t="str">
-        <v>Giường</v>
-      </c>
-      <c r="C215" t="str">
-        <v>Giường sắt cũ</v>
-      </c>
-      <c r="D215" t="str">
-        <v>Phòng 101</v>
-      </c>
-      <c r="E215" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F215">
-        <v>1</v>
-      </c>
-      <c r="G215" t="str">
-        <v>TB chủ</v>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" t="str">
-        <v>HD-MTX-48-RENO-RM-HO-BUY</v>
-      </c>
-      <c r="B216" t="str">
-        <v>Giường</v>
-      </c>
-      <c r="C216" t="str">
-        <v>Giường sắt cũ</v>
-      </c>
-      <c r="D216" t="str">
-        <v>Phòng 102</v>
-      </c>
-      <c r="E216" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F216">
-        <v>1</v>
-      </c>
-      <c r="G216" t="str">
-        <v>TB chủ</v>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" t="str">
-        <v>HD-MTX-48-RENO-RM-HO-BUY</v>
-      </c>
-      <c r="B217" t="str">
-        <v>Giường</v>
-      </c>
-      <c r="C217" t="str">
-        <v>Giường sắt cũ</v>
-      </c>
-      <c r="D217" t="str">
-        <v>Phòng 103</v>
-      </c>
-      <c r="E217" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F217">
-        <v>1</v>
-      </c>
-      <c r="G217" t="str">
-        <v>TB chủ</v>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" t="str">
-        <v>HD-MTX-48-RENO-RM-HO-BUY</v>
-      </c>
-      <c r="B218" t="str">
-        <v>Quạt</v>
-      </c>
-      <c r="C218" t="str">
-        <v>Quạt trần</v>
-      </c>
-      <c r="D218" t="str">
-        <v>Hành lang</v>
-      </c>
-      <c r="E218" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F218">
-        <v>1</v>
-      </c>
-      <c r="G218" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" t="str">
-        <v>HD-MTX-48-RENO-RM-HO-BUY</v>
-      </c>
-      <c r="B219" t="str">
-        <v>Nóng lạnh</v>
-      </c>
-      <c r="C219" t="str">
-        <v>Máy cũ</v>
-      </c>
-      <c r="D219" t="str">
-        <v>WC chung</v>
-      </c>
-      <c r="E219" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F219">
-        <v>1</v>
-      </c>
-      <c r="G219" t="str">
-        <v>Dùng chung</v>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" t="str">
-        <v>HD-MTX-49-RENO-RM-HO-BUY</v>
-      </c>
-      <c r="B220" t="str">
-        <v>Giường</v>
-      </c>
-      <c r="C220" t="str">
-        <v>Giường sắt cũ</v>
-      </c>
-      <c r="D220" t="str">
-        <v>Phòng 101</v>
-      </c>
-      <c r="E220" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F220">
-        <v>1</v>
-      </c>
-      <c r="G220" t="str">
-        <v>TB chủ</v>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" t="str">
-        <v>HD-MTX-49-RENO-RM-HO-BUY</v>
-      </c>
-      <c r="B221" t="str">
-        <v>Giường</v>
-      </c>
-      <c r="C221" t="str">
-        <v>Giường sắt cũ</v>
-      </c>
-      <c r="D221" t="str">
-        <v>Phòng 102</v>
-      </c>
-      <c r="E221" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F221">
-        <v>1</v>
-      </c>
-      <c r="G221" t="str">
-        <v>TB chủ</v>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" t="str">
-        <v>HD-MTX-49-RENO-RM-HO-BUY</v>
-      </c>
-      <c r="B222" t="str">
-        <v>Giường</v>
-      </c>
-      <c r="C222" t="str">
-        <v>Giường sắt cũ</v>
-      </c>
-      <c r="D222" t="str">
-        <v>Phòng 103</v>
-      </c>
-      <c r="E222" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F222">
-        <v>1</v>
-      </c>
-      <c r="G222" t="str">
-        <v>TB chủ</v>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" t="str">
-        <v>HD-MTX-49-RENO-RM-HO-BUY</v>
-      </c>
-      <c r="B223" t="str">
-        <v>Quạt</v>
-      </c>
-      <c r="C223" t="str">
-        <v>Quạt trần</v>
-      </c>
-      <c r="D223" t="str">
-        <v>Hành lang</v>
-      </c>
-      <c r="E223" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F223">
-        <v>1</v>
-      </c>
-      <c r="G223" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" t="str">
-        <v>HD-MTX-49-RENO-RM-HO-BUY</v>
-      </c>
-      <c r="B224" t="str">
-        <v>Nóng lạnh</v>
-      </c>
-      <c r="C224" t="str">
-        <v>Máy cũ</v>
-      </c>
-      <c r="D224" t="str">
-        <v>WC chung</v>
-      </c>
-      <c r="E224" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F224">
-        <v>1</v>
-      </c>
-      <c r="G224" t="str">
-        <v>Dùng chung</v>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" t="str">
-        <v>HD-MTX-50-RENO-RM-HO-BUY</v>
-      </c>
-      <c r="B225" t="str">
-        <v>Giường</v>
-      </c>
-      <c r="C225" t="str">
-        <v>Giường sắt cũ</v>
-      </c>
-      <c r="D225" t="str">
-        <v>Phòng 101</v>
-      </c>
-      <c r="E225" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F225">
-        <v>1</v>
-      </c>
-      <c r="G225" t="str">
-        <v>TB chủ</v>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" t="str">
-        <v>HD-MTX-50-RENO-RM-HO-BUY</v>
-      </c>
-      <c r="B226" t="str">
-        <v>Giường</v>
-      </c>
-      <c r="C226" t="str">
-        <v>Giường sắt cũ</v>
-      </c>
-      <c r="D226" t="str">
-        <v>Phòng 102</v>
-      </c>
-      <c r="E226" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F226">
-        <v>1</v>
-      </c>
-      <c r="G226" t="str">
-        <v>TB chủ</v>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" t="str">
-        <v>HD-MTX-50-RENO-RM-HO-BUY</v>
-      </c>
-      <c r="B227" t="str">
-        <v>Giường</v>
-      </c>
-      <c r="C227" t="str">
-        <v>Giường sắt cũ</v>
-      </c>
-      <c r="D227" t="str">
-        <v>Phòng 103</v>
-      </c>
-      <c r="E227" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F227">
-        <v>1</v>
-      </c>
-      <c r="G227" t="str">
-        <v>TB chủ</v>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" t="str">
-        <v>HD-MTX-50-RENO-RM-HO-BUY</v>
-      </c>
-      <c r="B228" t="str">
-        <v>Quạt</v>
-      </c>
-      <c r="C228" t="str">
-        <v>Quạt trần</v>
-      </c>
-      <c r="D228" t="str">
-        <v>Hành lang</v>
-      </c>
-      <c r="E228" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F228">
-        <v>1</v>
-      </c>
-      <c r="G228" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" t="str">
-        <v>HD-MTX-50-RENO-RM-HO-BUY</v>
-      </c>
-      <c r="B229" t="str">
-        <v>Nóng lạnh</v>
-      </c>
-      <c r="C229" t="str">
-        <v>Máy cũ</v>
-      </c>
-      <c r="D229" t="str">
-        <v>WC chung</v>
-      </c>
-      <c r="E229" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F229">
-        <v>1</v>
-      </c>
-      <c r="G229" t="str">
-        <v>Dùng chung</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G229"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G114"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/docs/SLMS2026_import_matrix_dot1.xlsx
+++ b/docs/SLMS2026_import_matrix_dot1.xlsx
@@ -403,12 +403,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:A9"/>
   <cols>
-    <col min="1" max="1" width="110.83203125" customWidth="1"/>
+    <col min="1" max="1" width="41.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>Hướng dẫn — Ma trận onboarding 50 căn (đợt 1)</v>
+        <v>Hướng dẫn — 50 căn onboarding (đợt 1)</v>
       </c>
     </row>
     <row r="2">
@@ -418,37 +418,37 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>File cover 50 HĐ: nguyên căn (full / cơ bản / không NT) + theo phòng (cơ bản / không NT / full).</v>
+        <v>40 NGUYEN_CAN (#1–#40) + 10 THEO_PHONG (#41–#50, mỗi căn ≥3 phòng).</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Sheet "0. Ma_Tran_Onboarding": tra cứu STT.</v>
+        <v>NT khai thác CHỈ tính TB mua mới ở file đợt 2 — đồ chủ bàn giao không tính.</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>API: POST /api/v1/import/lease-excel?dryRun=</v>
+        <v>Sheet "0. Ma_Tran_Onboarding": tra cứu STT / mức NT (FULL, BASIC, NONE).</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v/>
+        <v>API: POST /api/v1/import/lease-excel?dryRun=</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>NORENO (15 HĐ): sau đợt 1 tự gửi Host — KHÔNG import file đợt 2.</v>
+        <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>RENO (35 HĐ): sau đợt 1 ở UNDER_RENOVATION — cần file đợt 2.</v>
+        <v>Tất cả 50 căn là RENO: sau đợt 1 ở UNDER_RENOVATION — bắt buộc import đợt 2.</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Zone: chỉ quận đã seed (Q1, Q3, BT, GV, PN, Cầu Giấy).</v>
+        <v>Quận/Huyện chỉ gồm: Quận 1, Quận 3, Bình Thạnh, Gò Vấp, Phú Nhuận (Zone seeder).</v>
       </c>
     </row>
   </sheetData>
@@ -460,17 +460,18 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I56"/>
+  <dimension ref="A1:J60"/>
   <cols>
-    <col min="1" max="1" width="5.83203125" customWidth="1"/>
-    <col min="2" max="2" width="36.83203125" customWidth="1"/>
-    <col min="3" max="3" width="12.83203125" customWidth="1"/>
-    <col min="4" max="4" width="14.83203125" customWidth="1"/>
-    <col min="5" max="5" width="16.83203125" customWidth="1"/>
-    <col min="6" max="6" width="12.83203125" customWidth="1"/>
-    <col min="7" max="7" width="10.83203125" customWidth="1"/>
-    <col min="8" max="8" width="10.83203125" customWidth="1"/>
-    <col min="9" max="9" width="60.83203125" customWidth="1"/>
+    <col min="1" max="1" width="16.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="16.83203125" customWidth="1"/>
+    <col min="4" max="4" width="16.83203125" customWidth="1"/>
+    <col min="5" max="5" width="26.83203125" customWidth="1"/>
+    <col min="6" max="6" width="18.83203125" customWidth="1"/>
+    <col min="7" max="7" width="16.83203125" customWidth="1"/>
+    <col min="8" max="8" width="16.83203125" customWidth="1"/>
+    <col min="9" max="9" width="16.83203125" customWidth="1"/>
+    <col min="10" max="10" width="16.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -484,21 +485,24 @@
         <v>RENO/NORENO</v>
       </c>
       <c r="D1" t="str">
+        <v>Hình thức đ2</v>
+      </c>
+      <c r="E1" t="str">
+        <v>NT khai thác (mua mới)</v>
+      </c>
+      <c r="F1" t="str">
         <v>TB bàn giao đ1</v>
       </c>
-      <c r="E1" t="str">
-        <v>Hình thức đ2</v>
-      </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>Cải tạo đ2</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>TB mua đ2</v>
       </c>
-      <c r="H1" t="str">
+      <c r="I1" t="str">
         <v>File đợt 2</v>
       </c>
-      <c r="I1" t="str">
+      <c r="J1" t="str">
         <v>Diễn giải</v>
       </c>
     </row>
@@ -507,28 +511,31 @@
         <v>1</v>
       </c>
       <c r="B2" t="str">
-        <v>HD-MTX-01-NORENO-WH-NONE</v>
+        <v>HD-MTX-01-RENO-WH-FULL</v>
       </c>
       <c r="C2" t="str">
-        <v>NORENO</v>
+        <v>RENO</v>
       </c>
       <c r="D2" t="str">
-        <v>Không</v>
+        <v>NGUYEN_CAN</v>
       </c>
       <c r="E2" t="str">
-        <v>—</v>
+        <v>FULL</v>
       </c>
       <c r="F2" t="str">
-        <v>—</v>
+        <v>Có (không tính NT)</v>
       </c>
       <c r="G2" t="str">
-        <v>—</v>
+        <v>Có (≥1 dòng)</v>
       </c>
       <c r="H2" t="str">
-        <v>Không</v>
+        <v>Có (khớp NT)</v>
       </c>
       <c r="I2" t="str">
-        <v>#1 NORENO | nguyên căn | không nội thất | TB bàn giao: Không</v>
+        <v>Có</v>
+      </c>
+      <c r="J2" t="str">
+        <v>#1 RENO | NGUYEN_CAN | NT mua mới: FULL | TB bàn giao: không tính NT</v>
       </c>
     </row>
     <row r="3">
@@ -536,28 +543,31 @@
         <v>2</v>
       </c>
       <c r="B3" t="str">
-        <v>HD-MTX-02-NORENO-WH-NONE</v>
+        <v>HD-MTX-02-RENO-WH-FULL</v>
       </c>
       <c r="C3" t="str">
-        <v>NORENO</v>
+        <v>RENO</v>
       </c>
       <c r="D3" t="str">
-        <v>Không</v>
+        <v>NGUYEN_CAN</v>
       </c>
       <c r="E3" t="str">
-        <v>—</v>
+        <v>FULL</v>
       </c>
       <c r="F3" t="str">
-        <v>—</v>
+        <v>Có (không tính NT)</v>
       </c>
       <c r="G3" t="str">
-        <v>—</v>
+        <v>Có (≥1 dòng)</v>
       </c>
       <c r="H3" t="str">
-        <v>Không</v>
+        <v>Có (khớp NT)</v>
       </c>
       <c r="I3" t="str">
-        <v>#2 NORENO | nguyên căn | không nội thất | TB bàn giao: Không</v>
+        <v>Có</v>
+      </c>
+      <c r="J3" t="str">
+        <v>#2 RENO | NGUYEN_CAN | NT mua mới: FULL | TB bàn giao: không tính NT</v>
       </c>
     </row>
     <row r="4">
@@ -565,28 +575,31 @@
         <v>3</v>
       </c>
       <c r="B4" t="str">
-        <v>HD-MTX-03-NORENO-WH-NONE</v>
+        <v>HD-MTX-03-RENO-WH-FULL</v>
       </c>
       <c r="C4" t="str">
-        <v>NORENO</v>
+        <v>RENO</v>
       </c>
       <c r="D4" t="str">
+        <v>NGUYEN_CAN</v>
+      </c>
+      <c r="E4" t="str">
+        <v>FULL</v>
+      </c>
+      <c r="F4" t="str">
         <v>Không</v>
       </c>
-      <c r="E4" t="str">
-        <v>—</v>
-      </c>
-      <c r="F4" t="str">
-        <v>—</v>
-      </c>
       <c r="G4" t="str">
-        <v>—</v>
+        <v>Có (≥1 dòng)</v>
       </c>
       <c r="H4" t="str">
-        <v>Không</v>
+        <v>Có (khớp NT)</v>
       </c>
       <c r="I4" t="str">
-        <v>#3 NORENO | nguyên căn | không nội thất | TB bàn giao: Không</v>
+        <v>Có</v>
+      </c>
+      <c r="J4" t="str">
+        <v>#3 RENO | NGUYEN_CAN | NT mua mới: FULL | TB bàn giao: không tính NT</v>
       </c>
     </row>
     <row r="5">
@@ -594,28 +607,31 @@
         <v>4</v>
       </c>
       <c r="B5" t="str">
-        <v>HD-MTX-04-NORENO-WH-NONE</v>
+        <v>HD-MTX-04-RENO-WH-FULL</v>
       </c>
       <c r="C5" t="str">
-        <v>NORENO</v>
+        <v>RENO</v>
       </c>
       <c r="D5" t="str">
-        <v>Không</v>
+        <v>NGUYEN_CAN</v>
       </c>
       <c r="E5" t="str">
-        <v>—</v>
+        <v>FULL</v>
       </c>
       <c r="F5" t="str">
-        <v>—</v>
+        <v>Có (không tính NT)</v>
       </c>
       <c r="G5" t="str">
-        <v>—</v>
+        <v>Có (≥1 dòng)</v>
       </c>
       <c r="H5" t="str">
-        <v>Không</v>
+        <v>Có (khớp NT)</v>
       </c>
       <c r="I5" t="str">
-        <v>#4 NORENO | nguyên căn | không nội thất | TB bàn giao: Không</v>
+        <v>Có</v>
+      </c>
+      <c r="J5" t="str">
+        <v>#4 RENO | NGUYEN_CAN | NT mua mới: FULL | TB bàn giao: không tính NT</v>
       </c>
     </row>
     <row r="6">
@@ -623,28 +639,31 @@
         <v>5</v>
       </c>
       <c r="B6" t="str">
-        <v>HD-MTX-05-NORENO-WH-NONE</v>
+        <v>HD-MTX-05-RENO-WH-FULL</v>
       </c>
       <c r="C6" t="str">
-        <v>NORENO</v>
+        <v>RENO</v>
       </c>
       <c r="D6" t="str">
-        <v>Không</v>
+        <v>NGUYEN_CAN</v>
       </c>
       <c r="E6" t="str">
-        <v>—</v>
+        <v>FULL</v>
       </c>
       <c r="F6" t="str">
-        <v>—</v>
+        <v>Có (không tính NT)</v>
       </c>
       <c r="G6" t="str">
-        <v>—</v>
+        <v>Có (≥1 dòng)</v>
       </c>
       <c r="H6" t="str">
-        <v>Không</v>
+        <v>Có (khớp NT)</v>
       </c>
       <c r="I6" t="str">
-        <v>#5 NORENO | nguyên căn | không nội thất | TB bàn giao: Không</v>
+        <v>Có</v>
+      </c>
+      <c r="J6" t="str">
+        <v>#5 RENO | NGUYEN_CAN | NT mua mới: FULL | TB bàn giao: không tính NT</v>
       </c>
     </row>
     <row r="7">
@@ -652,28 +671,31 @@
         <v>6</v>
       </c>
       <c r="B7" t="str">
-        <v>HD-MTX-06-NORENO-WH-BASIC</v>
+        <v>HD-MTX-06-RENO-WH-FULL</v>
       </c>
       <c r="C7" t="str">
-        <v>NORENO</v>
+        <v>RENO</v>
       </c>
       <c r="D7" t="str">
+        <v>NGUYEN_CAN</v>
+      </c>
+      <c r="E7" t="str">
+        <v>FULL</v>
+      </c>
+      <c r="F7" t="str">
+        <v>Không</v>
+      </c>
+      <c r="G7" t="str">
+        <v>Có (≥1 dòng)</v>
+      </c>
+      <c r="H7" t="str">
+        <v>Có (khớp NT)</v>
+      </c>
+      <c r="I7" t="str">
         <v>Có</v>
       </c>
-      <c r="E7" t="str">
-        <v>—</v>
-      </c>
-      <c r="F7" t="str">
-        <v>—</v>
-      </c>
-      <c r="G7" t="str">
-        <v>—</v>
-      </c>
-      <c r="H7" t="str">
-        <v>Không</v>
-      </c>
-      <c r="I7" t="str">
-        <v>#6 NORENO | nguyên căn | nội thất cơ bản | TB bàn giao: Có</v>
+      <c r="J7" t="str">
+        <v>#6 RENO | NGUYEN_CAN | NT mua mới: FULL | TB bàn giao: không tính NT</v>
       </c>
     </row>
     <row r="8">
@@ -681,28 +703,31 @@
         <v>7</v>
       </c>
       <c r="B8" t="str">
-        <v>HD-MTX-07-NORENO-WH-BASIC</v>
+        <v>HD-MTX-07-RENO-WH-FULL</v>
       </c>
       <c r="C8" t="str">
-        <v>NORENO</v>
+        <v>RENO</v>
       </c>
       <c r="D8" t="str">
+        <v>NGUYEN_CAN</v>
+      </c>
+      <c r="E8" t="str">
+        <v>FULL</v>
+      </c>
+      <c r="F8" t="str">
+        <v>Có (không tính NT)</v>
+      </c>
+      <c r="G8" t="str">
+        <v>Có (≥1 dòng)</v>
+      </c>
+      <c r="H8" t="str">
+        <v>Có (khớp NT)</v>
+      </c>
+      <c r="I8" t="str">
         <v>Có</v>
       </c>
-      <c r="E8" t="str">
-        <v>—</v>
-      </c>
-      <c r="F8" t="str">
-        <v>—</v>
-      </c>
-      <c r="G8" t="str">
-        <v>—</v>
-      </c>
-      <c r="H8" t="str">
-        <v>Không</v>
-      </c>
-      <c r="I8" t="str">
-        <v>#7 NORENO | nguyên căn | nội thất cơ bản | TB bàn giao: Có</v>
+      <c r="J8" t="str">
+        <v>#7 RENO | NGUYEN_CAN | NT mua mới: FULL | TB bàn giao: không tính NT</v>
       </c>
     </row>
     <row r="9">
@@ -710,28 +735,31 @@
         <v>8</v>
       </c>
       <c r="B9" t="str">
-        <v>HD-MTX-08-NORENO-WH-BASIC</v>
+        <v>HD-MTX-08-RENO-WH-FULL</v>
       </c>
       <c r="C9" t="str">
-        <v>NORENO</v>
+        <v>RENO</v>
       </c>
       <c r="D9" t="str">
+        <v>NGUYEN_CAN</v>
+      </c>
+      <c r="E9" t="str">
+        <v>FULL</v>
+      </c>
+      <c r="F9" t="str">
+        <v>Có (không tính NT)</v>
+      </c>
+      <c r="G9" t="str">
+        <v>Có (≥1 dòng)</v>
+      </c>
+      <c r="H9" t="str">
+        <v>Có (khớp NT)</v>
+      </c>
+      <c r="I9" t="str">
         <v>Có</v>
       </c>
-      <c r="E9" t="str">
-        <v>—</v>
-      </c>
-      <c r="F9" t="str">
-        <v>—</v>
-      </c>
-      <c r="G9" t="str">
-        <v>—</v>
-      </c>
-      <c r="H9" t="str">
-        <v>Không</v>
-      </c>
-      <c r="I9" t="str">
-        <v>#8 NORENO | nguyên căn | nội thất cơ bản | TB bàn giao: Có</v>
+      <c r="J9" t="str">
+        <v>#8 RENO | NGUYEN_CAN | NT mua mới: FULL | TB bàn giao: không tính NT</v>
       </c>
     </row>
     <row r="10">
@@ -739,28 +767,31 @@
         <v>9</v>
       </c>
       <c r="B10" t="str">
-        <v>HD-MTX-09-NORENO-WH-BASIC</v>
+        <v>HD-MTX-09-RENO-WH-FULL</v>
       </c>
       <c r="C10" t="str">
-        <v>NORENO</v>
+        <v>RENO</v>
       </c>
       <c r="D10" t="str">
+        <v>NGUYEN_CAN</v>
+      </c>
+      <c r="E10" t="str">
+        <v>FULL</v>
+      </c>
+      <c r="F10" t="str">
+        <v>Không</v>
+      </c>
+      <c r="G10" t="str">
+        <v>Có (≥1 dòng)</v>
+      </c>
+      <c r="H10" t="str">
+        <v>Có (khớp NT)</v>
+      </c>
+      <c r="I10" t="str">
         <v>Có</v>
       </c>
-      <c r="E10" t="str">
-        <v>—</v>
-      </c>
-      <c r="F10" t="str">
-        <v>—</v>
-      </c>
-      <c r="G10" t="str">
-        <v>—</v>
-      </c>
-      <c r="H10" t="str">
-        <v>Không</v>
-      </c>
-      <c r="I10" t="str">
-        <v>#9 NORENO | nguyên căn | nội thất cơ bản | TB bàn giao: Có</v>
+      <c r="J10" t="str">
+        <v>#9 RENO | NGUYEN_CAN | NT mua mới: FULL | TB bàn giao: không tính NT</v>
       </c>
     </row>
     <row r="11">
@@ -768,28 +799,31 @@
         <v>10</v>
       </c>
       <c r="B11" t="str">
-        <v>HD-MTX-10-NORENO-WH-BASIC</v>
+        <v>HD-MTX-10-RENO-WH-FULL</v>
       </c>
       <c r="C11" t="str">
-        <v>NORENO</v>
+        <v>RENO</v>
       </c>
       <c r="D11" t="str">
+        <v>NGUYEN_CAN</v>
+      </c>
+      <c r="E11" t="str">
+        <v>FULL</v>
+      </c>
+      <c r="F11" t="str">
+        <v>Có (không tính NT)</v>
+      </c>
+      <c r="G11" t="str">
+        <v>Có (≥1 dòng)</v>
+      </c>
+      <c r="H11" t="str">
+        <v>Có (khớp NT)</v>
+      </c>
+      <c r="I11" t="str">
         <v>Có</v>
       </c>
-      <c r="E11" t="str">
-        <v>—</v>
-      </c>
-      <c r="F11" t="str">
-        <v>—</v>
-      </c>
-      <c r="G11" t="str">
-        <v>—</v>
-      </c>
-      <c r="H11" t="str">
-        <v>Không</v>
-      </c>
-      <c r="I11" t="str">
-        <v>#10 NORENO | nguyên căn | nội thất cơ bản | TB bàn giao: Có</v>
+      <c r="J11" t="str">
+        <v>#10 RENO | NGUYEN_CAN | NT mua mới: FULL | TB bàn giao: không tính NT</v>
       </c>
     </row>
     <row r="12">
@@ -797,28 +831,31 @@
         <v>11</v>
       </c>
       <c r="B12" t="str">
-        <v>HD-MTX-11-NORENO-WH-FULL</v>
+        <v>HD-MTX-11-RENO-WH-FULL</v>
       </c>
       <c r="C12" t="str">
-        <v>NORENO</v>
+        <v>RENO</v>
       </c>
       <c r="D12" t="str">
+        <v>NGUYEN_CAN</v>
+      </c>
+      <c r="E12" t="str">
+        <v>FULL</v>
+      </c>
+      <c r="F12" t="str">
+        <v>Có (không tính NT)</v>
+      </c>
+      <c r="G12" t="str">
+        <v>Có (≥1 dòng)</v>
+      </c>
+      <c r="H12" t="str">
+        <v>Có (khớp NT)</v>
+      </c>
+      <c r="I12" t="str">
         <v>Có</v>
       </c>
-      <c r="E12" t="str">
-        <v>—</v>
-      </c>
-      <c r="F12" t="str">
-        <v>—</v>
-      </c>
-      <c r="G12" t="str">
-        <v>—</v>
-      </c>
-      <c r="H12" t="str">
-        <v>Không</v>
-      </c>
-      <c r="I12" t="str">
-        <v>#11 NORENO | nguyên căn | full nội thất | TB bàn giao: Có</v>
+      <c r="J12" t="str">
+        <v>#11 RENO | NGUYEN_CAN | NT mua mới: FULL | TB bàn giao: không tính NT</v>
       </c>
     </row>
     <row r="13">
@@ -826,28 +863,31 @@
         <v>12</v>
       </c>
       <c r="B13" t="str">
-        <v>HD-MTX-12-NORENO-WH-FULL</v>
+        <v>HD-MTX-12-RENO-WH-FULL</v>
       </c>
       <c r="C13" t="str">
-        <v>NORENO</v>
+        <v>RENO</v>
       </c>
       <c r="D13" t="str">
+        <v>NGUYEN_CAN</v>
+      </c>
+      <c r="E13" t="str">
+        <v>FULL</v>
+      </c>
+      <c r="F13" t="str">
+        <v>Không</v>
+      </c>
+      <c r="G13" t="str">
+        <v>Có (≥1 dòng)</v>
+      </c>
+      <c r="H13" t="str">
+        <v>Có (khớp NT)</v>
+      </c>
+      <c r="I13" t="str">
         <v>Có</v>
       </c>
-      <c r="E13" t="str">
-        <v>—</v>
-      </c>
-      <c r="F13" t="str">
-        <v>—</v>
-      </c>
-      <c r="G13" t="str">
-        <v>—</v>
-      </c>
-      <c r="H13" t="str">
-        <v>Không</v>
-      </c>
-      <c r="I13" t="str">
-        <v>#12 NORENO | nguyên căn | full nội thất | TB bàn giao: Có</v>
+      <c r="J13" t="str">
+        <v>#12 RENO | NGUYEN_CAN | NT mua mới: FULL | TB bàn giao: không tính NT</v>
       </c>
     </row>
     <row r="14">
@@ -855,28 +895,31 @@
         <v>13</v>
       </c>
       <c r="B14" t="str">
-        <v>HD-MTX-13-NORENO-WH-FULL</v>
+        <v>HD-MTX-13-RENO-WH-FULL</v>
       </c>
       <c r="C14" t="str">
-        <v>NORENO</v>
+        <v>RENO</v>
       </c>
       <c r="D14" t="str">
+        <v>NGUYEN_CAN</v>
+      </c>
+      <c r="E14" t="str">
+        <v>FULL</v>
+      </c>
+      <c r="F14" t="str">
+        <v>Có (không tính NT)</v>
+      </c>
+      <c r="G14" t="str">
+        <v>Có (≥1 dòng)</v>
+      </c>
+      <c r="H14" t="str">
+        <v>Có (khớp NT)</v>
+      </c>
+      <c r="I14" t="str">
         <v>Có</v>
       </c>
-      <c r="E14" t="str">
-        <v>—</v>
-      </c>
-      <c r="F14" t="str">
-        <v>—</v>
-      </c>
-      <c r="G14" t="str">
-        <v>—</v>
-      </c>
-      <c r="H14" t="str">
-        <v>Không</v>
-      </c>
-      <c r="I14" t="str">
-        <v>#13 NORENO | nguyên căn | full nội thất | TB bàn giao: Có</v>
+      <c r="J14" t="str">
+        <v>#13 RENO | NGUYEN_CAN | NT mua mới: FULL | TB bàn giao: không tính NT</v>
       </c>
     </row>
     <row r="15">
@@ -884,28 +927,31 @@
         <v>14</v>
       </c>
       <c r="B15" t="str">
-        <v>HD-MTX-14-NORENO-WH-FULL</v>
+        <v>HD-MTX-14-RENO-WH-FULL</v>
       </c>
       <c r="C15" t="str">
-        <v>NORENO</v>
+        <v>RENO</v>
       </c>
       <c r="D15" t="str">
+        <v>NGUYEN_CAN</v>
+      </c>
+      <c r="E15" t="str">
+        <v>FULL</v>
+      </c>
+      <c r="F15" t="str">
+        <v>Có (không tính NT)</v>
+      </c>
+      <c r="G15" t="str">
+        <v>Có (≥1 dòng)</v>
+      </c>
+      <c r="H15" t="str">
+        <v>Có (khớp NT)</v>
+      </c>
+      <c r="I15" t="str">
         <v>Có</v>
       </c>
-      <c r="E15" t="str">
-        <v>—</v>
-      </c>
-      <c r="F15" t="str">
-        <v>—</v>
-      </c>
-      <c r="G15" t="str">
-        <v>—</v>
-      </c>
-      <c r="H15" t="str">
-        <v>Không</v>
-      </c>
-      <c r="I15" t="str">
-        <v>#14 NORENO | nguyên căn | full nội thất | TB bàn giao: Có</v>
+      <c r="J15" t="str">
+        <v>#14 RENO | NGUYEN_CAN | NT mua mới: FULL | TB bàn giao: không tính NT</v>
       </c>
     </row>
     <row r="16">
@@ -913,28 +959,31 @@
         <v>15</v>
       </c>
       <c r="B16" t="str">
-        <v>HD-MTX-15-NORENO-WH-FULL</v>
+        <v>HD-MTX-15-RENO-WH-BASIC</v>
       </c>
       <c r="C16" t="str">
-        <v>NORENO</v>
+        <v>RENO</v>
       </c>
       <c r="D16" t="str">
+        <v>NGUYEN_CAN</v>
+      </c>
+      <c r="E16" t="str">
+        <v>BASIC</v>
+      </c>
+      <c r="F16" t="str">
+        <v>Không</v>
+      </c>
+      <c r="G16" t="str">
+        <v>Có (≥1 dòng)</v>
+      </c>
+      <c r="H16" t="str">
+        <v>Có (khớp NT)</v>
+      </c>
+      <c r="I16" t="str">
         <v>Có</v>
       </c>
-      <c r="E16" t="str">
-        <v>—</v>
-      </c>
-      <c r="F16" t="str">
-        <v>—</v>
-      </c>
-      <c r="G16" t="str">
-        <v>—</v>
-      </c>
-      <c r="H16" t="str">
-        <v>Không</v>
-      </c>
-      <c r="I16" t="str">
-        <v>#15 NORENO | nguyên căn | full nội thất | TB bàn giao: Có</v>
+      <c r="J16" t="str">
+        <v>#15 RENO | NGUYEN_CAN | NT mua mới: BASIC | TB bàn giao: không tính NT</v>
       </c>
     </row>
     <row r="17">
@@ -942,28 +991,31 @@
         <v>16</v>
       </c>
       <c r="B17" t="str">
-        <v>HD-MTX-16-RENO-WH-NONE</v>
+        <v>HD-MTX-16-RENO-WH-BASIC</v>
       </c>
       <c r="C17" t="str">
         <v>RENO</v>
       </c>
       <c r="D17" t="str">
-        <v>Không</v>
+        <v>NGUYEN_CAN</v>
       </c>
       <c r="E17" t="str">
-        <v>NGUYEN_CAN</v>
+        <v>BASIC</v>
       </c>
       <c r="F17" t="str">
+        <v>Có (không tính NT)</v>
+      </c>
+      <c r="G17" t="str">
         <v>Có (≥1 dòng)</v>
       </c>
-      <c r="G17" t="str">
-        <v>Không</v>
-      </c>
       <c r="H17" t="str">
+        <v>Có (khớp NT)</v>
+      </c>
+      <c r="I17" t="str">
         <v>Có</v>
       </c>
-      <c r="I17" t="str">
-        <v>#16 RENO | nguyên căn | không nội thất | TB bàn giao: Không</v>
+      <c r="J17" t="str">
+        <v>#16 RENO | NGUYEN_CAN | NT mua mới: BASIC | TB bàn giao: không tính NT</v>
       </c>
     </row>
     <row r="18">
@@ -971,28 +1023,31 @@
         <v>17</v>
       </c>
       <c r="B18" t="str">
-        <v>HD-MTX-17-RENO-WH-NONE</v>
+        <v>HD-MTX-17-RENO-WH-BASIC</v>
       </c>
       <c r="C18" t="str">
         <v>RENO</v>
       </c>
       <c r="D18" t="str">
-        <v>Không</v>
+        <v>NGUYEN_CAN</v>
       </c>
       <c r="E18" t="str">
-        <v>NGUYEN_CAN</v>
+        <v>BASIC</v>
       </c>
       <c r="F18" t="str">
+        <v>Có (không tính NT)</v>
+      </c>
+      <c r="G18" t="str">
         <v>Có (≥1 dòng)</v>
       </c>
-      <c r="G18" t="str">
-        <v>Không</v>
-      </c>
       <c r="H18" t="str">
+        <v>Có (khớp NT)</v>
+      </c>
+      <c r="I18" t="str">
         <v>Có</v>
       </c>
-      <c r="I18" t="str">
-        <v>#17 RENO | nguyên căn | không nội thất | TB bàn giao: Không</v>
+      <c r="J18" t="str">
+        <v>#17 RENO | NGUYEN_CAN | NT mua mới: BASIC | TB bàn giao: không tính NT</v>
       </c>
     </row>
     <row r="19">
@@ -1000,28 +1055,31 @@
         <v>18</v>
       </c>
       <c r="B19" t="str">
-        <v>HD-MTX-18-RENO-WH-NONE</v>
+        <v>HD-MTX-18-RENO-WH-BASIC</v>
       </c>
       <c r="C19" t="str">
         <v>RENO</v>
       </c>
       <c r="D19" t="str">
+        <v>NGUYEN_CAN</v>
+      </c>
+      <c r="E19" t="str">
+        <v>BASIC</v>
+      </c>
+      <c r="F19" t="str">
         <v>Không</v>
       </c>
-      <c r="E19" t="str">
-        <v>NGUYEN_CAN</v>
-      </c>
-      <c r="F19" t="str">
+      <c r="G19" t="str">
         <v>Có (≥1 dòng)</v>
       </c>
-      <c r="G19" t="str">
-        <v>Không</v>
-      </c>
       <c r="H19" t="str">
+        <v>Có (khớp NT)</v>
+      </c>
+      <c r="I19" t="str">
         <v>Có</v>
       </c>
-      <c r="I19" t="str">
-        <v>#18 RENO | nguyên căn | không nội thất | TB bàn giao: Không</v>
+      <c r="J19" t="str">
+        <v>#18 RENO | NGUYEN_CAN | NT mua mới: BASIC | TB bàn giao: không tính NT</v>
       </c>
     </row>
     <row r="20">
@@ -1029,28 +1087,31 @@
         <v>19</v>
       </c>
       <c r="B20" t="str">
-        <v>HD-MTX-19-RENO-WH-BASIC-HO</v>
+        <v>HD-MTX-19-RENO-WH-BASIC</v>
       </c>
       <c r="C20" t="str">
         <v>RENO</v>
       </c>
       <c r="D20" t="str">
+        <v>NGUYEN_CAN</v>
+      </c>
+      <c r="E20" t="str">
+        <v>BASIC</v>
+      </c>
+      <c r="F20" t="str">
+        <v>Có (không tính NT)</v>
+      </c>
+      <c r="G20" t="str">
+        <v>Có (≥1 dòng)</v>
+      </c>
+      <c r="H20" t="str">
+        <v>Có (khớp NT)</v>
+      </c>
+      <c r="I20" t="str">
         <v>Có</v>
       </c>
-      <c r="E20" t="str">
-        <v>NGUYEN_CAN</v>
-      </c>
-      <c r="F20" t="str">
-        <v>Có (≥1 dòng)</v>
-      </c>
-      <c r="G20" t="str">
-        <v>Không</v>
-      </c>
-      <c r="H20" t="str">
-        <v>Có</v>
-      </c>
-      <c r="I20" t="str">
-        <v>#19 RENO | nguyên căn | nội thất cơ bản | TB bàn giao: Có</v>
+      <c r="J20" t="str">
+        <v>#19 RENO | NGUYEN_CAN | NT mua mới: BASIC | TB bàn giao: không tính NT</v>
       </c>
     </row>
     <row r="21">
@@ -1058,28 +1119,31 @@
         <v>20</v>
       </c>
       <c r="B21" t="str">
-        <v>HD-MTX-20-RENO-WH-BASIC-HO</v>
+        <v>HD-MTX-20-RENO-WH-BASIC</v>
       </c>
       <c r="C21" t="str">
         <v>RENO</v>
       </c>
       <c r="D21" t="str">
+        <v>NGUYEN_CAN</v>
+      </c>
+      <c r="E21" t="str">
+        <v>BASIC</v>
+      </c>
+      <c r="F21" t="str">
+        <v>Có (không tính NT)</v>
+      </c>
+      <c r="G21" t="str">
+        <v>Có (≥1 dòng)</v>
+      </c>
+      <c r="H21" t="str">
+        <v>Có (khớp NT)</v>
+      </c>
+      <c r="I21" t="str">
         <v>Có</v>
       </c>
-      <c r="E21" t="str">
-        <v>NGUYEN_CAN</v>
-      </c>
-      <c r="F21" t="str">
-        <v>Có (≥1 dòng)</v>
-      </c>
-      <c r="G21" t="str">
-        <v>Không</v>
-      </c>
-      <c r="H21" t="str">
-        <v>Có</v>
-      </c>
-      <c r="I21" t="str">
-        <v>#20 RENO | nguyên căn | nội thất cơ bản | TB bàn giao: Có</v>
+      <c r="J21" t="str">
+        <v>#20 RENO | NGUYEN_CAN | NT mua mới: BASIC | TB bàn giao: không tính NT</v>
       </c>
     </row>
     <row r="22">
@@ -1087,28 +1151,31 @@
         <v>21</v>
       </c>
       <c r="B22" t="str">
-        <v>HD-MTX-21-RENO-WH-BASIC-HO</v>
+        <v>HD-MTX-21-RENO-WH-BASIC</v>
       </c>
       <c r="C22" t="str">
         <v>RENO</v>
       </c>
       <c r="D22" t="str">
+        <v>NGUYEN_CAN</v>
+      </c>
+      <c r="E22" t="str">
+        <v>BASIC</v>
+      </c>
+      <c r="F22" t="str">
+        <v>Không</v>
+      </c>
+      <c r="G22" t="str">
+        <v>Có (≥1 dòng)</v>
+      </c>
+      <c r="H22" t="str">
+        <v>Có (khớp NT)</v>
+      </c>
+      <c r="I22" t="str">
         <v>Có</v>
       </c>
-      <c r="E22" t="str">
-        <v>NGUYEN_CAN</v>
-      </c>
-      <c r="F22" t="str">
-        <v>Có (≥1 dòng)</v>
-      </c>
-      <c r="G22" t="str">
-        <v>Không</v>
-      </c>
-      <c r="H22" t="str">
-        <v>Có</v>
-      </c>
-      <c r="I22" t="str">
-        <v>#21 RENO | nguyên căn | nội thất cơ bản | TB bàn giao: Có</v>
+      <c r="J22" t="str">
+        <v>#21 RENO | NGUYEN_CAN | NT mua mới: BASIC | TB bàn giao: không tính NT</v>
       </c>
     </row>
     <row r="23">
@@ -1116,28 +1183,31 @@
         <v>22</v>
       </c>
       <c r="B23" t="str">
-        <v>HD-MTX-22-RENO-WH-BASIC-BUY</v>
+        <v>HD-MTX-22-RENO-WH-BASIC</v>
       </c>
       <c r="C23" t="str">
         <v>RENO</v>
       </c>
       <c r="D23" t="str">
-        <v>Không</v>
+        <v>NGUYEN_CAN</v>
       </c>
       <c r="E23" t="str">
-        <v>NGUYEN_CAN</v>
+        <v>BASIC</v>
       </c>
       <c r="F23" t="str">
+        <v>Có (không tính NT)</v>
+      </c>
+      <c r="G23" t="str">
         <v>Có (≥1 dòng)</v>
       </c>
-      <c r="G23" t="str">
+      <c r="H23" t="str">
+        <v>Có (khớp NT)</v>
+      </c>
+      <c r="I23" t="str">
         <v>Có</v>
       </c>
-      <c r="H23" t="str">
-        <v>Có</v>
-      </c>
-      <c r="I23" t="str">
-        <v>#22 RENO | nguyên căn | nội thất cơ bản | TB bàn giao: Không</v>
+      <c r="J23" t="str">
+        <v>#22 RENO | NGUYEN_CAN | NT mua mới: BASIC | TB bàn giao: không tính NT</v>
       </c>
     </row>
     <row r="24">
@@ -1145,28 +1215,31 @@
         <v>23</v>
       </c>
       <c r="B24" t="str">
-        <v>HD-MTX-23-RENO-WH-BASIC-BUY</v>
+        <v>HD-MTX-23-RENO-WH-BASIC</v>
       </c>
       <c r="C24" t="str">
         <v>RENO</v>
       </c>
       <c r="D24" t="str">
-        <v>Không</v>
+        <v>NGUYEN_CAN</v>
       </c>
       <c r="E24" t="str">
-        <v>NGUYEN_CAN</v>
+        <v>BASIC</v>
       </c>
       <c r="F24" t="str">
+        <v>Có (không tính NT)</v>
+      </c>
+      <c r="G24" t="str">
         <v>Có (≥1 dòng)</v>
       </c>
-      <c r="G24" t="str">
+      <c r="H24" t="str">
+        <v>Có (khớp NT)</v>
+      </c>
+      <c r="I24" t="str">
         <v>Có</v>
       </c>
-      <c r="H24" t="str">
-        <v>Có</v>
-      </c>
-      <c r="I24" t="str">
-        <v>#23 RENO | nguyên căn | nội thất cơ bản | TB bàn giao: Không</v>
+      <c r="J24" t="str">
+        <v>#23 RENO | NGUYEN_CAN | NT mua mới: BASIC | TB bàn giao: không tính NT</v>
       </c>
     </row>
     <row r="25">
@@ -1174,28 +1247,31 @@
         <v>24</v>
       </c>
       <c r="B25" t="str">
-        <v>HD-MTX-24-RENO-WH-BASIC-BUY</v>
+        <v>HD-MTX-24-RENO-WH-BASIC</v>
       </c>
       <c r="C25" t="str">
         <v>RENO</v>
       </c>
       <c r="D25" t="str">
+        <v>NGUYEN_CAN</v>
+      </c>
+      <c r="E25" t="str">
+        <v>BASIC</v>
+      </c>
+      <c r="F25" t="str">
         <v>Không</v>
       </c>
-      <c r="E25" t="str">
-        <v>NGUYEN_CAN</v>
-      </c>
-      <c r="F25" t="str">
+      <c r="G25" t="str">
         <v>Có (≥1 dòng)</v>
       </c>
-      <c r="G25" t="str">
+      <c r="H25" t="str">
+        <v>Có (khớp NT)</v>
+      </c>
+      <c r="I25" t="str">
         <v>Có</v>
       </c>
-      <c r="H25" t="str">
-        <v>Có</v>
-      </c>
-      <c r="I25" t="str">
-        <v>#24 RENO | nguyên căn | nội thất cơ bản | TB bàn giao: Không</v>
+      <c r="J25" t="str">
+        <v>#24 RENO | NGUYEN_CAN | NT mua mới: BASIC | TB bàn giao: không tính NT</v>
       </c>
     </row>
     <row r="26">
@@ -1203,28 +1279,31 @@
         <v>25</v>
       </c>
       <c r="B26" t="str">
-        <v>HD-MTX-25-RENO-WH-FULL</v>
+        <v>HD-MTX-25-RENO-WH-BASIC</v>
       </c>
       <c r="C26" t="str">
         <v>RENO</v>
       </c>
       <c r="D26" t="str">
+        <v>NGUYEN_CAN</v>
+      </c>
+      <c r="E26" t="str">
+        <v>BASIC</v>
+      </c>
+      <c r="F26" t="str">
+        <v>Có (không tính NT)</v>
+      </c>
+      <c r="G26" t="str">
+        <v>Có (≥1 dòng)</v>
+      </c>
+      <c r="H26" t="str">
+        <v>Có (khớp NT)</v>
+      </c>
+      <c r="I26" t="str">
         <v>Có</v>
       </c>
-      <c r="E26" t="str">
-        <v>NGUYEN_CAN</v>
-      </c>
-      <c r="F26" t="str">
-        <v>Có (≥1 dòng)</v>
-      </c>
-      <c r="G26" t="str">
-        <v>Có</v>
-      </c>
-      <c r="H26" t="str">
-        <v>Có</v>
-      </c>
-      <c r="I26" t="str">
-        <v>#25 RENO | nguyên căn | full nội thất | TB bàn giao: Có</v>
+      <c r="J26" t="str">
+        <v>#25 RENO | NGUYEN_CAN | NT mua mới: BASIC | TB bàn giao: không tính NT</v>
       </c>
     </row>
     <row r="27">
@@ -1232,28 +1311,31 @@
         <v>26</v>
       </c>
       <c r="B27" t="str">
-        <v>HD-MTX-26-RENO-WH-FULL</v>
+        <v>HD-MTX-26-RENO-WH-BASIC</v>
       </c>
       <c r="C27" t="str">
         <v>RENO</v>
       </c>
       <c r="D27" t="str">
+        <v>NGUYEN_CAN</v>
+      </c>
+      <c r="E27" t="str">
+        <v>BASIC</v>
+      </c>
+      <c r="F27" t="str">
+        <v>Có (không tính NT)</v>
+      </c>
+      <c r="G27" t="str">
+        <v>Có (≥1 dòng)</v>
+      </c>
+      <c r="H27" t="str">
+        <v>Có (khớp NT)</v>
+      </c>
+      <c r="I27" t="str">
         <v>Có</v>
       </c>
-      <c r="E27" t="str">
-        <v>NGUYEN_CAN</v>
-      </c>
-      <c r="F27" t="str">
-        <v>Có (≥1 dòng)</v>
-      </c>
-      <c r="G27" t="str">
-        <v>Có</v>
-      </c>
-      <c r="H27" t="str">
-        <v>Có</v>
-      </c>
-      <c r="I27" t="str">
-        <v>#26 RENO | nguyên căn | full nội thất | TB bàn giao: Có</v>
+      <c r="J27" t="str">
+        <v>#26 RENO | NGUYEN_CAN | NT mua mới: BASIC | TB bàn giao: không tính NT</v>
       </c>
     </row>
     <row r="28">
@@ -1261,28 +1343,31 @@
         <v>27</v>
       </c>
       <c r="B28" t="str">
-        <v>HD-MTX-27-RENO-WH-FULL</v>
+        <v>HD-MTX-27-RENO-WH-BASIC</v>
       </c>
       <c r="C28" t="str">
         <v>RENO</v>
       </c>
       <c r="D28" t="str">
+        <v>NGUYEN_CAN</v>
+      </c>
+      <c r="E28" t="str">
+        <v>BASIC</v>
+      </c>
+      <c r="F28" t="str">
+        <v>Không</v>
+      </c>
+      <c r="G28" t="str">
+        <v>Có (≥1 dòng)</v>
+      </c>
+      <c r="H28" t="str">
+        <v>Có (khớp NT)</v>
+      </c>
+      <c r="I28" t="str">
         <v>Có</v>
       </c>
-      <c r="E28" t="str">
-        <v>NGUYEN_CAN</v>
-      </c>
-      <c r="F28" t="str">
-        <v>Có (≥1 dòng)</v>
-      </c>
-      <c r="G28" t="str">
-        <v>Có</v>
-      </c>
-      <c r="H28" t="str">
-        <v>Có</v>
-      </c>
-      <c r="I28" t="str">
-        <v>#27 RENO | nguyên căn | full nội thất | TB bàn giao: Có</v>
+      <c r="J28" t="str">
+        <v>#27 RENO | NGUYEN_CAN | NT mua mới: BASIC | TB bàn giao: không tính NT</v>
       </c>
     </row>
     <row r="29">
@@ -1290,28 +1375,31 @@
         <v>28</v>
       </c>
       <c r="B29" t="str">
-        <v>HD-MTX-28-RENO-WH-HO-NOBUY</v>
+        <v>HD-MTX-28-RENO-WH-NONE</v>
       </c>
       <c r="C29" t="str">
         <v>RENO</v>
       </c>
       <c r="D29" t="str">
+        <v>NGUYEN_CAN</v>
+      </c>
+      <c r="E29" t="str">
+        <v>NONE</v>
+      </c>
+      <c r="F29" t="str">
+        <v>Có (không tính NT)</v>
+      </c>
+      <c r="G29" t="str">
+        <v>Có (≥1 dòng)</v>
+      </c>
+      <c r="H29" t="str">
+        <v>Không</v>
+      </c>
+      <c r="I29" t="str">
         <v>Có</v>
       </c>
-      <c r="E29" t="str">
-        <v>NGUYEN_CAN</v>
-      </c>
-      <c r="F29" t="str">
-        <v>Có (≥1 dòng)</v>
-      </c>
-      <c r="G29" t="str">
-        <v>Không</v>
-      </c>
-      <c r="H29" t="str">
-        <v>Có</v>
-      </c>
-      <c r="I29" t="str">
-        <v>#28 RENO | nguyên căn | không nội thất | TB bàn giao: Có</v>
+      <c r="J29" t="str">
+        <v>#28 RENO | NGUYEN_CAN | NT mua mới: NONE | TB bàn giao: không tính NT</v>
       </c>
     </row>
     <row r="30">
@@ -1319,28 +1407,31 @@
         <v>29</v>
       </c>
       <c r="B30" t="str">
-        <v>HD-MTX-29-RENO-WH-HO-NOBUY</v>
+        <v>HD-MTX-29-RENO-WH-NONE</v>
       </c>
       <c r="C30" t="str">
         <v>RENO</v>
       </c>
       <c r="D30" t="str">
+        <v>NGUYEN_CAN</v>
+      </c>
+      <c r="E30" t="str">
+        <v>NONE</v>
+      </c>
+      <c r="F30" t="str">
+        <v>Có (không tính NT)</v>
+      </c>
+      <c r="G30" t="str">
+        <v>Có (≥1 dòng)</v>
+      </c>
+      <c r="H30" t="str">
+        <v>Không</v>
+      </c>
+      <c r="I30" t="str">
         <v>Có</v>
       </c>
-      <c r="E30" t="str">
-        <v>NGUYEN_CAN</v>
-      </c>
-      <c r="F30" t="str">
-        <v>Có (≥1 dòng)</v>
-      </c>
-      <c r="G30" t="str">
-        <v>Không</v>
-      </c>
-      <c r="H30" t="str">
-        <v>Có</v>
-      </c>
-      <c r="I30" t="str">
-        <v>#29 RENO | nguyên căn | không nội thất | TB bàn giao: Có</v>
+      <c r="J30" t="str">
+        <v>#29 RENO | NGUYEN_CAN | NT mua mới: NONE | TB bàn giao: không tính NT</v>
       </c>
     </row>
     <row r="31">
@@ -1348,28 +1439,31 @@
         <v>30</v>
       </c>
       <c r="B31" t="str">
-        <v>HD-MTX-30-RENO-WH-HO-BUY</v>
+        <v>HD-MTX-30-RENO-WH-NONE</v>
       </c>
       <c r="C31" t="str">
         <v>RENO</v>
       </c>
       <c r="D31" t="str">
+        <v>NGUYEN_CAN</v>
+      </c>
+      <c r="E31" t="str">
+        <v>NONE</v>
+      </c>
+      <c r="F31" t="str">
+        <v>Không</v>
+      </c>
+      <c r="G31" t="str">
+        <v>Có (≥1 dòng)</v>
+      </c>
+      <c r="H31" t="str">
+        <v>Không</v>
+      </c>
+      <c r="I31" t="str">
         <v>Có</v>
       </c>
-      <c r="E31" t="str">
-        <v>NGUYEN_CAN</v>
-      </c>
-      <c r="F31" t="str">
-        <v>Có (≥1 dòng)</v>
-      </c>
-      <c r="G31" t="str">
-        <v>Có</v>
-      </c>
-      <c r="H31" t="str">
-        <v>Có</v>
-      </c>
-      <c r="I31" t="str">
-        <v>#30 RENO | nguyên căn | nội thất cơ bản | TB bàn giao: Có</v>
+      <c r="J31" t="str">
+        <v>#30 RENO | NGUYEN_CAN | NT mua mới: NONE | TB bàn giao: không tính NT</v>
       </c>
     </row>
     <row r="32">
@@ -1377,28 +1471,31 @@
         <v>31</v>
       </c>
       <c r="B32" t="str">
-        <v>HD-MTX-31-RENO-WH-HO-BUY</v>
+        <v>HD-MTX-31-RENO-WH-NONE</v>
       </c>
       <c r="C32" t="str">
         <v>RENO</v>
       </c>
       <c r="D32" t="str">
+        <v>NGUYEN_CAN</v>
+      </c>
+      <c r="E32" t="str">
+        <v>NONE</v>
+      </c>
+      <c r="F32" t="str">
+        <v>Có (không tính NT)</v>
+      </c>
+      <c r="G32" t="str">
+        <v>Có (≥1 dòng)</v>
+      </c>
+      <c r="H32" t="str">
+        <v>Không</v>
+      </c>
+      <c r="I32" t="str">
         <v>Có</v>
       </c>
-      <c r="E32" t="str">
-        <v>NGUYEN_CAN</v>
-      </c>
-      <c r="F32" t="str">
-        <v>Có (≥1 dòng)</v>
-      </c>
-      <c r="G32" t="str">
-        <v>Có</v>
-      </c>
-      <c r="H32" t="str">
-        <v>Có</v>
-      </c>
-      <c r="I32" t="str">
-        <v>#31 RENO | nguyên căn | nội thất cơ bản | TB bàn giao: Có</v>
+      <c r="J32" t="str">
+        <v>#31 RENO | NGUYEN_CAN | NT mua mới: NONE | TB bàn giao: không tính NT</v>
       </c>
     </row>
     <row r="33">
@@ -1406,28 +1503,31 @@
         <v>32</v>
       </c>
       <c r="B33" t="str">
-        <v>HD-MTX-32-RENO-RM-NONE</v>
+        <v>HD-MTX-32-RENO-WH-NONE</v>
       </c>
       <c r="C33" t="str">
         <v>RENO</v>
       </c>
       <c r="D33" t="str">
+        <v>NGUYEN_CAN</v>
+      </c>
+      <c r="E33" t="str">
+        <v>NONE</v>
+      </c>
+      <c r="F33" t="str">
+        <v>Có (không tính NT)</v>
+      </c>
+      <c r="G33" t="str">
+        <v>Có (≥1 dòng)</v>
+      </c>
+      <c r="H33" t="str">
         <v>Không</v>
       </c>
-      <c r="E33" t="str">
-        <v>THEO_PHONG (3)</v>
-      </c>
-      <c r="F33" t="str">
-        <v>Có (≥1 dòng)</v>
-      </c>
-      <c r="G33" t="str">
-        <v>Không</v>
-      </c>
-      <c r="H33" t="str">
+      <c r="I33" t="str">
         <v>Có</v>
       </c>
-      <c r="I33" t="str">
-        <v>#32 RENO | theo phòng (3p) | không nội thất | TB bàn giao: Không</v>
+      <c r="J33" t="str">
+        <v>#32 RENO | NGUYEN_CAN | NT mua mới: NONE | TB bàn giao: không tính NT</v>
       </c>
     </row>
     <row r="34">
@@ -1435,28 +1535,31 @@
         <v>33</v>
       </c>
       <c r="B34" t="str">
-        <v>HD-MTX-33-RENO-RM-NONE</v>
+        <v>HD-MTX-33-RENO-WH-NONE</v>
       </c>
       <c r="C34" t="str">
         <v>RENO</v>
       </c>
       <c r="D34" t="str">
+        <v>NGUYEN_CAN</v>
+      </c>
+      <c r="E34" t="str">
+        <v>NONE</v>
+      </c>
+      <c r="F34" t="str">
         <v>Không</v>
       </c>
-      <c r="E34" t="str">
-        <v>THEO_PHONG (3)</v>
-      </c>
-      <c r="F34" t="str">
+      <c r="G34" t="str">
         <v>Có (≥1 dòng)</v>
       </c>
-      <c r="G34" t="str">
+      <c r="H34" t="str">
         <v>Không</v>
       </c>
-      <c r="H34" t="str">
+      <c r="I34" t="str">
         <v>Có</v>
       </c>
-      <c r="I34" t="str">
-        <v>#33 RENO | theo phòng (3p) | không nội thất | TB bàn giao: Không</v>
+      <c r="J34" t="str">
+        <v>#33 RENO | NGUYEN_CAN | NT mua mới: NONE | TB bàn giao: không tính NT</v>
       </c>
     </row>
     <row r="35">
@@ -1464,28 +1567,31 @@
         <v>34</v>
       </c>
       <c r="B35" t="str">
-        <v>HD-MTX-34-RENO-RM-NONE</v>
+        <v>HD-MTX-34-RENO-WH-NONE</v>
       </c>
       <c r="C35" t="str">
         <v>RENO</v>
       </c>
       <c r="D35" t="str">
+        <v>NGUYEN_CAN</v>
+      </c>
+      <c r="E35" t="str">
+        <v>NONE</v>
+      </c>
+      <c r="F35" t="str">
+        <v>Có (không tính NT)</v>
+      </c>
+      <c r="G35" t="str">
+        <v>Có (≥1 dòng)</v>
+      </c>
+      <c r="H35" t="str">
         <v>Không</v>
       </c>
-      <c r="E35" t="str">
-        <v>THEO_PHONG (3)</v>
-      </c>
-      <c r="F35" t="str">
-        <v>Có (≥1 dòng)</v>
-      </c>
-      <c r="G35" t="str">
-        <v>Không</v>
-      </c>
-      <c r="H35" t="str">
+      <c r="I35" t="str">
         <v>Có</v>
       </c>
-      <c r="I35" t="str">
-        <v>#34 RENO | theo phòng (3p) | không nội thất | TB bàn giao: Không</v>
+      <c r="J35" t="str">
+        <v>#34 RENO | NGUYEN_CAN | NT mua mới: NONE | TB bàn giao: không tính NT</v>
       </c>
     </row>
     <row r="36">
@@ -1493,28 +1599,31 @@
         <v>35</v>
       </c>
       <c r="B36" t="str">
-        <v>HD-MTX-35-RENO-RM-NONE</v>
+        <v>HD-MTX-35-RENO-WH-NONE</v>
       </c>
       <c r="C36" t="str">
         <v>RENO</v>
       </c>
       <c r="D36" t="str">
+        <v>NGUYEN_CAN</v>
+      </c>
+      <c r="E36" t="str">
+        <v>NONE</v>
+      </c>
+      <c r="F36" t="str">
+        <v>Có (không tính NT)</v>
+      </c>
+      <c r="G36" t="str">
+        <v>Có (≥1 dòng)</v>
+      </c>
+      <c r="H36" t="str">
         <v>Không</v>
       </c>
-      <c r="E36" t="str">
-        <v>THEO_PHONG (3)</v>
-      </c>
-      <c r="F36" t="str">
-        <v>Có (≥1 dòng)</v>
-      </c>
-      <c r="G36" t="str">
-        <v>Không</v>
-      </c>
-      <c r="H36" t="str">
+      <c r="I36" t="str">
         <v>Có</v>
       </c>
-      <c r="I36" t="str">
-        <v>#35 RENO | theo phòng (3p) | không nội thất | TB bàn giao: Không</v>
+      <c r="J36" t="str">
+        <v>#35 RENO | NGUYEN_CAN | NT mua mới: NONE | TB bàn giao: không tính NT</v>
       </c>
     </row>
     <row r="37">
@@ -1522,28 +1631,31 @@
         <v>36</v>
       </c>
       <c r="B37" t="str">
-        <v>HD-MTX-36-RENO-RM-BASIC-HO</v>
+        <v>HD-MTX-36-RENO-WH-NONE</v>
       </c>
       <c r="C37" t="str">
         <v>RENO</v>
       </c>
       <c r="D37" t="str">
+        <v>NGUYEN_CAN</v>
+      </c>
+      <c r="E37" t="str">
+        <v>NONE</v>
+      </c>
+      <c r="F37" t="str">
+        <v>Không</v>
+      </c>
+      <c r="G37" t="str">
+        <v>Có (≥1 dòng)</v>
+      </c>
+      <c r="H37" t="str">
+        <v>Không</v>
+      </c>
+      <c r="I37" t="str">
         <v>Có</v>
       </c>
-      <c r="E37" t="str">
-        <v>THEO_PHONG (3)</v>
-      </c>
-      <c r="F37" t="str">
-        <v>Có (≥1 dòng)</v>
-      </c>
-      <c r="G37" t="str">
-        <v>Không</v>
-      </c>
-      <c r="H37" t="str">
-        <v>Có</v>
-      </c>
-      <c r="I37" t="str">
-        <v>#36 RENO | theo phòng (3p) | nội thất cơ bản | TB bàn giao: Có</v>
+      <c r="J37" t="str">
+        <v>#36 RENO | NGUYEN_CAN | NT mua mới: NONE | TB bàn giao: không tính NT</v>
       </c>
     </row>
     <row r="38">
@@ -1551,28 +1663,31 @@
         <v>37</v>
       </c>
       <c r="B38" t="str">
-        <v>HD-MTX-37-RENO-RM-BASIC-HO</v>
+        <v>HD-MTX-37-RENO-WH-NONE</v>
       </c>
       <c r="C38" t="str">
         <v>RENO</v>
       </c>
       <c r="D38" t="str">
+        <v>NGUYEN_CAN</v>
+      </c>
+      <c r="E38" t="str">
+        <v>NONE</v>
+      </c>
+      <c r="F38" t="str">
+        <v>Có (không tính NT)</v>
+      </c>
+      <c r="G38" t="str">
+        <v>Có (≥1 dòng)</v>
+      </c>
+      <c r="H38" t="str">
+        <v>Không</v>
+      </c>
+      <c r="I38" t="str">
         <v>Có</v>
       </c>
-      <c r="E38" t="str">
-        <v>THEO_PHONG (3)</v>
-      </c>
-      <c r="F38" t="str">
-        <v>Có (≥1 dòng)</v>
-      </c>
-      <c r="G38" t="str">
-        <v>Không</v>
-      </c>
-      <c r="H38" t="str">
-        <v>Có</v>
-      </c>
-      <c r="I38" t="str">
-        <v>#37 RENO | theo phòng (3p) | nội thất cơ bản | TB bàn giao: Có</v>
+      <c r="J38" t="str">
+        <v>#37 RENO | NGUYEN_CAN | NT mua mới: NONE | TB bàn giao: không tính NT</v>
       </c>
     </row>
     <row r="39">
@@ -1580,28 +1695,31 @@
         <v>38</v>
       </c>
       <c r="B39" t="str">
-        <v>HD-MTX-38-RENO-RM-BASIC-HO</v>
+        <v>HD-MTX-38-RENO-WH-NONE</v>
       </c>
       <c r="C39" t="str">
         <v>RENO</v>
       </c>
       <c r="D39" t="str">
+        <v>NGUYEN_CAN</v>
+      </c>
+      <c r="E39" t="str">
+        <v>NONE</v>
+      </c>
+      <c r="F39" t="str">
+        <v>Có (không tính NT)</v>
+      </c>
+      <c r="G39" t="str">
+        <v>Có (≥1 dòng)</v>
+      </c>
+      <c r="H39" t="str">
+        <v>Không</v>
+      </c>
+      <c r="I39" t="str">
         <v>Có</v>
       </c>
-      <c r="E39" t="str">
-        <v>THEO_PHONG (3)</v>
-      </c>
-      <c r="F39" t="str">
-        <v>Có (≥1 dòng)</v>
-      </c>
-      <c r="G39" t="str">
-        <v>Không</v>
-      </c>
-      <c r="H39" t="str">
-        <v>Có</v>
-      </c>
-      <c r="I39" t="str">
-        <v>#38 RENO | theo phòng (3p) | nội thất cơ bản | TB bàn giao: Có</v>
+      <c r="J39" t="str">
+        <v>#38 RENO | NGUYEN_CAN | NT mua mới: NONE | TB bàn giao: không tính NT</v>
       </c>
     </row>
     <row r="40">
@@ -1609,28 +1727,31 @@
         <v>39</v>
       </c>
       <c r="B40" t="str">
-        <v>HD-MTX-39-RENO-RM-BASIC-HO</v>
+        <v>HD-MTX-39-RENO-WH-NONE</v>
       </c>
       <c r="C40" t="str">
         <v>RENO</v>
       </c>
       <c r="D40" t="str">
+        <v>NGUYEN_CAN</v>
+      </c>
+      <c r="E40" t="str">
+        <v>NONE</v>
+      </c>
+      <c r="F40" t="str">
+        <v>Không</v>
+      </c>
+      <c r="G40" t="str">
+        <v>Có (≥1 dòng)</v>
+      </c>
+      <c r="H40" t="str">
+        <v>Không</v>
+      </c>
+      <c r="I40" t="str">
         <v>Có</v>
       </c>
-      <c r="E40" t="str">
-        <v>THEO_PHONG (3)</v>
-      </c>
-      <c r="F40" t="str">
-        <v>Có (≥1 dòng)</v>
-      </c>
-      <c r="G40" t="str">
-        <v>Không</v>
-      </c>
-      <c r="H40" t="str">
-        <v>Có</v>
-      </c>
-      <c r="I40" t="str">
-        <v>#39 RENO | theo phòng (3p) | nội thất cơ bản | TB bàn giao: Có</v>
+      <c r="J40" t="str">
+        <v>#39 RENO | NGUYEN_CAN | NT mua mới: NONE | TB bàn giao: không tính NT</v>
       </c>
     </row>
     <row r="41">
@@ -1638,28 +1759,31 @@
         <v>40</v>
       </c>
       <c r="B41" t="str">
-        <v>HD-MTX-40-RENO-RM-BASIC-BUY</v>
+        <v>HD-MTX-40-RENO-WH-NONE</v>
       </c>
       <c r="C41" t="str">
         <v>RENO</v>
       </c>
       <c r="D41" t="str">
+        <v>NGUYEN_CAN</v>
+      </c>
+      <c r="E41" t="str">
+        <v>NONE</v>
+      </c>
+      <c r="F41" t="str">
+        <v>Có (không tính NT)</v>
+      </c>
+      <c r="G41" t="str">
+        <v>Có (≥1 dòng)</v>
+      </c>
+      <c r="H41" t="str">
         <v>Không</v>
       </c>
-      <c r="E41" t="str">
-        <v>THEO_PHONG (3)</v>
-      </c>
-      <c r="F41" t="str">
-        <v>Có (≥1 dòng)</v>
-      </c>
-      <c r="G41" t="str">
+      <c r="I41" t="str">
         <v>Có</v>
       </c>
-      <c r="H41" t="str">
-        <v>Có</v>
-      </c>
-      <c r="I41" t="str">
-        <v>#40 RENO | theo phòng (3p) | nội thất cơ bản | TB bàn giao: Không</v>
+      <c r="J41" t="str">
+        <v>#40 RENO | NGUYEN_CAN | NT mua mới: NONE | TB bàn giao: không tính NT</v>
       </c>
     </row>
     <row r="42">
@@ -1667,28 +1791,31 @@
         <v>41</v>
       </c>
       <c r="B42" t="str">
-        <v>HD-MTX-41-RENO-RM-BASIC-BUY</v>
+        <v>HD-MTX-41-RENO-RM-FULL</v>
       </c>
       <c r="C42" t="str">
         <v>RENO</v>
       </c>
       <c r="D42" t="str">
-        <v>Không</v>
+        <v>THEO_PHONG (3)</v>
       </c>
       <c r="E42" t="str">
-        <v>THEO_PHONG (4)</v>
+        <v>FULL</v>
       </c>
       <c r="F42" t="str">
+        <v>Có (không tính NT)</v>
+      </c>
+      <c r="G42" t="str">
         <v>Có (≥1 dòng)</v>
       </c>
-      <c r="G42" t="str">
+      <c r="H42" t="str">
+        <v>Có (khớp NT)</v>
+      </c>
+      <c r="I42" t="str">
         <v>Có</v>
       </c>
-      <c r="H42" t="str">
-        <v>Có</v>
-      </c>
-      <c r="I42" t="str">
-        <v>#41 RENO | theo phòng (4p) | nội thất cơ bản | TB bàn giao: Không</v>
+      <c r="J42" t="str">
+        <v>#41 RENO | THEO_PHONG (3 phòng) | NT mua mới: FULL | TB bàn giao: không tính NT</v>
       </c>
     </row>
     <row r="43">
@@ -1696,28 +1823,31 @@
         <v>42</v>
       </c>
       <c r="B43" t="str">
-        <v>HD-MTX-42-RENO-RM-BASIC-BUY</v>
+        <v>HD-MTX-42-RENO-RM-FULL</v>
       </c>
       <c r="C43" t="str">
         <v>RENO</v>
       </c>
       <c r="D43" t="str">
+        <v>THEO_PHONG (4)</v>
+      </c>
+      <c r="E43" t="str">
+        <v>FULL</v>
+      </c>
+      <c r="F43" t="str">
         <v>Không</v>
       </c>
-      <c r="E43" t="str">
-        <v>THEO_PHONG (3)</v>
-      </c>
-      <c r="F43" t="str">
+      <c r="G43" t="str">
         <v>Có (≥1 dòng)</v>
       </c>
-      <c r="G43" t="str">
+      <c r="H43" t="str">
+        <v>Có (khớp NT)</v>
+      </c>
+      <c r="I43" t="str">
         <v>Có</v>
       </c>
-      <c r="H43" t="str">
-        <v>Có</v>
-      </c>
-      <c r="I43" t="str">
-        <v>#42 RENO | theo phòng (3p) | nội thất cơ bản | TB bàn giao: Không</v>
+      <c r="J43" t="str">
+        <v>#42 RENO | THEO_PHONG (4 phòng) | NT mua mới: FULL | TB bàn giao: không tính NT</v>
       </c>
     </row>
     <row r="44">
@@ -1725,28 +1855,31 @@
         <v>43</v>
       </c>
       <c r="B44" t="str">
-        <v>HD-MTX-43-RENO-RM-BASIC-BUY</v>
+        <v>HD-MTX-43-RENO-RM-FULL</v>
       </c>
       <c r="C44" t="str">
         <v>RENO</v>
       </c>
       <c r="D44" t="str">
-        <v>Không</v>
+        <v>THEO_PHONG (5)</v>
       </c>
       <c r="E44" t="str">
-        <v>THEO_PHONG (4)</v>
+        <v>FULL</v>
       </c>
       <c r="F44" t="str">
+        <v>Có (không tính NT)</v>
+      </c>
+      <c r="G44" t="str">
         <v>Có (≥1 dòng)</v>
       </c>
-      <c r="G44" t="str">
+      <c r="H44" t="str">
+        <v>Có (khớp NT)</v>
+      </c>
+      <c r="I44" t="str">
         <v>Có</v>
       </c>
-      <c r="H44" t="str">
-        <v>Có</v>
-      </c>
-      <c r="I44" t="str">
-        <v>#43 RENO | theo phòng (4p) | nội thất cơ bản | TB bàn giao: Không</v>
+      <c r="J44" t="str">
+        <v>#43 RENO | THEO_PHONG (5 phòng) | NT mua mới: FULL | TB bàn giao: không tính NT</v>
       </c>
     </row>
     <row r="45">
@@ -1760,22 +1893,25 @@
         <v>RENO</v>
       </c>
       <c r="D45" t="str">
+        <v>THEO_PHONG (3)</v>
+      </c>
+      <c r="E45" t="str">
+        <v>FULL</v>
+      </c>
+      <c r="F45" t="str">
+        <v>Có (không tính NT)</v>
+      </c>
+      <c r="G45" t="str">
+        <v>Có (≥1 dòng)</v>
+      </c>
+      <c r="H45" t="str">
+        <v>Có (khớp NT)</v>
+      </c>
+      <c r="I45" t="str">
         <v>Có</v>
       </c>
-      <c r="E45" t="str">
-        <v>THEO_PHONG (4)</v>
-      </c>
-      <c r="F45" t="str">
-        <v>Có (≥1 dòng)</v>
-      </c>
-      <c r="G45" t="str">
-        <v>Có</v>
-      </c>
-      <c r="H45" t="str">
-        <v>Có</v>
-      </c>
-      <c r="I45" t="str">
-        <v>#44 RENO | theo phòng (4p) | full nội thất | TB bàn giao: Có</v>
+      <c r="J45" t="str">
+        <v>#44 RENO | THEO_PHONG (3 phòng) | NT mua mới: FULL | TB bàn giao: không tính NT</v>
       </c>
     </row>
     <row r="46">
@@ -1783,28 +1919,31 @@
         <v>45</v>
       </c>
       <c r="B46" t="str">
-        <v>HD-MTX-45-RENO-RM-FULL</v>
+        <v>HD-MTX-45-RENO-RM-BASIC</v>
       </c>
       <c r="C46" t="str">
         <v>RENO</v>
       </c>
       <c r="D46" t="str">
+        <v>THEO_PHONG (3)</v>
+      </c>
+      <c r="E46" t="str">
+        <v>BASIC</v>
+      </c>
+      <c r="F46" t="str">
+        <v>Không</v>
+      </c>
+      <c r="G46" t="str">
+        <v>Có (≥1 dòng)</v>
+      </c>
+      <c r="H46" t="str">
+        <v>Có (khớp NT)</v>
+      </c>
+      <c r="I46" t="str">
         <v>Có</v>
       </c>
-      <c r="E46" t="str">
-        <v>THEO_PHONG (4)</v>
-      </c>
-      <c r="F46" t="str">
-        <v>Có (≥1 dòng)</v>
-      </c>
-      <c r="G46" t="str">
-        <v>Có</v>
-      </c>
-      <c r="H46" t="str">
-        <v>Có</v>
-      </c>
-      <c r="I46" t="str">
-        <v>#45 RENO | theo phòng (4p) | full nội thất | TB bàn giao: Có</v>
+      <c r="J46" t="str">
+        <v>#45 RENO | THEO_PHONG (3 phòng) | NT mua mới: BASIC | TB bàn giao: không tính NT</v>
       </c>
     </row>
     <row r="47">
@@ -1812,28 +1951,31 @@
         <v>46</v>
       </c>
       <c r="B47" t="str">
-        <v>HD-MTX-46-RENO-RM-FULL</v>
+        <v>HD-MTX-46-RENO-RM-BASIC</v>
       </c>
       <c r="C47" t="str">
         <v>RENO</v>
       </c>
       <c r="D47" t="str">
+        <v>THEO_PHONG (4)</v>
+      </c>
+      <c r="E47" t="str">
+        <v>BASIC</v>
+      </c>
+      <c r="F47" t="str">
+        <v>Có (không tính NT)</v>
+      </c>
+      <c r="G47" t="str">
+        <v>Có (≥1 dòng)</v>
+      </c>
+      <c r="H47" t="str">
+        <v>Có (khớp NT)</v>
+      </c>
+      <c r="I47" t="str">
         <v>Có</v>
       </c>
-      <c r="E47" t="str">
-        <v>THEO_PHONG (4)</v>
-      </c>
-      <c r="F47" t="str">
-        <v>Có (≥1 dòng)</v>
-      </c>
-      <c r="G47" t="str">
-        <v>Có</v>
-      </c>
-      <c r="H47" t="str">
-        <v>Có</v>
-      </c>
-      <c r="I47" t="str">
-        <v>#46 RENO | theo phòng (4p) | full nội thất | TB bàn giao: Có</v>
+      <c r="J47" t="str">
+        <v>#46 RENO | THEO_PHONG (4 phòng) | NT mua mới: BASIC | TB bàn giao: không tính NT</v>
       </c>
     </row>
     <row r="48">
@@ -1841,28 +1983,31 @@
         <v>47</v>
       </c>
       <c r="B48" t="str">
-        <v>HD-MTX-47-RENO-RM-FULL</v>
+        <v>HD-MTX-47-RENO-RM-BASIC</v>
       </c>
       <c r="C48" t="str">
         <v>RENO</v>
       </c>
       <c r="D48" t="str">
+        <v>THEO_PHONG (5)</v>
+      </c>
+      <c r="E48" t="str">
+        <v>BASIC</v>
+      </c>
+      <c r="F48" t="str">
+        <v>Có (không tính NT)</v>
+      </c>
+      <c r="G48" t="str">
+        <v>Có (≥1 dòng)</v>
+      </c>
+      <c r="H48" t="str">
+        <v>Có (khớp NT)</v>
+      </c>
+      <c r="I48" t="str">
         <v>Có</v>
       </c>
-      <c r="E48" t="str">
-        <v>THEO_PHONG (4)</v>
-      </c>
-      <c r="F48" t="str">
-        <v>Có (≥1 dòng)</v>
-      </c>
-      <c r="G48" t="str">
-        <v>Có</v>
-      </c>
-      <c r="H48" t="str">
-        <v>Có</v>
-      </c>
-      <c r="I48" t="str">
-        <v>#47 RENO | theo phòng (4p) | full nội thất | TB bàn giao: Có</v>
+      <c r="J48" t="str">
+        <v>#47 RENO | THEO_PHONG (5 phòng) | NT mua mới: BASIC | TB bàn giao: không tính NT</v>
       </c>
     </row>
     <row r="49">
@@ -1870,28 +2015,31 @@
         <v>48</v>
       </c>
       <c r="B49" t="str">
-        <v>HD-MTX-48-RENO-RM-HO-BUY</v>
+        <v>HD-MTX-48-RENO-RM-BASIC</v>
       </c>
       <c r="C49" t="str">
         <v>RENO</v>
       </c>
       <c r="D49" t="str">
+        <v>THEO_PHONG (6)</v>
+      </c>
+      <c r="E49" t="str">
+        <v>BASIC</v>
+      </c>
+      <c r="F49" t="str">
+        <v>Không</v>
+      </c>
+      <c r="G49" t="str">
+        <v>Có (≥1 dòng)</v>
+      </c>
+      <c r="H49" t="str">
+        <v>Có (khớp NT)</v>
+      </c>
+      <c r="I49" t="str">
         <v>Có</v>
       </c>
-      <c r="E49" t="str">
-        <v>THEO_PHONG (3)</v>
-      </c>
-      <c r="F49" t="str">
-        <v>Có (≥1 dòng)</v>
-      </c>
-      <c r="G49" t="str">
-        <v>Có</v>
-      </c>
-      <c r="H49" t="str">
-        <v>Có</v>
-      </c>
-      <c r="I49" t="str">
-        <v>#48 RENO | theo phòng (3p) | nội thất cơ bản | TB bàn giao: Có</v>
+      <c r="J49" t="str">
+        <v>#48 RENO | THEO_PHONG (6 phòng) | NT mua mới: BASIC | TB bàn giao: không tính NT</v>
       </c>
     </row>
     <row r="50">
@@ -1899,28 +2047,31 @@
         <v>49</v>
       </c>
       <c r="B50" t="str">
-        <v>HD-MTX-49-RENO-RM-HO-BUY</v>
+        <v>HD-MTX-49-RENO-RM-NONE</v>
       </c>
       <c r="C50" t="str">
         <v>RENO</v>
       </c>
       <c r="D50" t="str">
+        <v>THEO_PHONG (3)</v>
+      </c>
+      <c r="E50" t="str">
+        <v>NONE</v>
+      </c>
+      <c r="F50" t="str">
+        <v>Có (không tính NT)</v>
+      </c>
+      <c r="G50" t="str">
+        <v>Có (≥1 dòng)</v>
+      </c>
+      <c r="H50" t="str">
+        <v>Không</v>
+      </c>
+      <c r="I50" t="str">
         <v>Có</v>
       </c>
-      <c r="E50" t="str">
-        <v>THEO_PHONG (3)</v>
-      </c>
-      <c r="F50" t="str">
-        <v>Có (≥1 dòng)</v>
-      </c>
-      <c r="G50" t="str">
-        <v>Có</v>
-      </c>
-      <c r="H50" t="str">
-        <v>Có</v>
-      </c>
-      <c r="I50" t="str">
-        <v>#49 RENO | theo phòng (3p) | nội thất cơ bản | TB bàn giao: Có</v>
+      <c r="J50" t="str">
+        <v>#49 RENO | THEO_PHONG (3 phòng) | NT mua mới: NONE | TB bàn giao: không tính NT</v>
       </c>
     </row>
     <row r="51">
@@ -1928,63 +2079,91 @@
         <v>50</v>
       </c>
       <c r="B51" t="str">
-        <v>HD-MTX-50-RENO-RM-HO-BUY</v>
+        <v>HD-MTX-50-RENO-RM-NONE</v>
       </c>
       <c r="C51" t="str">
         <v>RENO</v>
       </c>
       <c r="D51" t="str">
+        <v>THEO_PHONG (4)</v>
+      </c>
+      <c r="E51" t="str">
+        <v>NONE</v>
+      </c>
+      <c r="F51" t="str">
+        <v>Có (không tính NT)</v>
+      </c>
+      <c r="G51" t="str">
+        <v>Có (≥1 dòng)</v>
+      </c>
+      <c r="H51" t="str">
+        <v>Không</v>
+      </c>
+      <c r="I51" t="str">
         <v>Có</v>
       </c>
-      <c r="E51" t="str">
-        <v>THEO_PHONG (3)</v>
-      </c>
-      <c r="F51" t="str">
-        <v>Có (≥1 dòng)</v>
-      </c>
-      <c r="G51" t="str">
-        <v>Có</v>
-      </c>
-      <c r="H51" t="str">
-        <v>Có</v>
-      </c>
-      <c r="I51" t="str">
-        <v>#50 RENO | theo phòng (3p) | nội thất cơ bản | TB bàn giao: Có</v>
+      <c r="J51" t="str">
+        <v>#50 RENO | THEO_PHONG (4 phòng) | NT mua mới: NONE | TB bàn giao: không tính NT</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v/>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Tổng: 50 HĐ onboarding (nguyên căn full/cơ bản/không NT + theo phòng cơ bản/không NT).</v>
+        <v>Tổng: 50 HĐ — 40 NGUYEN_CAN (#1–#40) + 10 THEO_PHONG (#41–#50, mỗi căn ≥3 phòng).</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>NORENO: import đợt 1 xong → tự gửi Host. RENO: cần import đợt 2.</v>
+        <v>#1–#14 FULL | #15–#27 BASIC | #28–#40 NONE — nguyên căn.</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Zone chỉ gồm quận trong ZoneDataSeeder: Q1, Q3, Bình Thạnh, Gò Vấp, Phú Nhuận, Cầu Giấy.</v>
+        <v>#41–#44 FULL | #45–#48 BASIC | #49–#50 NONE — theo phòng.</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Catalog thiết bị / hạng mục cải tạo: MasterDataSeeder.</v>
+        <v>NT khai thác CHỈ tính TB mua mới đợt 2. Đồ chủ bàn giao đợt 1 không tính.</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>FULL nguyên căn: ĐH + quạt + giường + tủ lạnh + máy giặt + nóng lạnh + bàn ăn + tủ quần áo + bếp từ.</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>FULL theo phòng: mỗi phòng giường + quạt + ĐH + nóng lạnh; thêm tủ lạnh + máy giặt khu vực chung.</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>BASIC: giường + quạt (nguyên căn theo khu vực / theo phòng từng phòng).</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>NONE: không dòng TB mua mới. Tất cả 50 căn đều RENO — import đợt 2 sau đợt 1.</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I56"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J60"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B20"/>
   <cols>
-    <col min="1" max="1" width="28.83203125" customWidth="1"/>
-    <col min="2" max="2" width="40.83203125" customWidth="1"/>
+    <col min="1" max="1" width="26.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2021,71 +2200,132 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Giường</v>
+        <v>Bàn ăn</v>
       </c>
       <c r="B5" t="str">
-        <v>Giường ngủ các loại</v>
+        <v>Bàn ăn và ghế</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Nóng lạnh</v>
+        <v>Giường</v>
       </c>
       <c r="B6" t="str">
-        <v>Máy nước nóng</v>
+        <v>Giường ngủ các loại</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Quạt</v>
+        <v>Tủ quần áo</v>
       </c>
       <c r="B7" t="str">
-        <v>Quạt điện / quạt trần</v>
+        <v>Tủ đựng quần áo</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>Bếp từ</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Bếp từ / bếp gas</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Mã khu vực</v>
+        <v>Nóng lạnh</v>
       </c>
       <c r="B9" t="str">
-        <v>Mô tả</v>
+        <v>Máy nước nóng</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>LIVING_ROOM</v>
+        <v>Quạt</v>
       </c>
       <c r="B10" t="str">
-        <v>Phòng khách</v>
+        <v>Quạt điện / quạt trần</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>KITCHEN</v>
+        <v>Khác</v>
       </c>
       <c r="B11" t="str">
-        <v>Nhà bếp</v>
+        <v>Thiết bị khác</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>BATHROOM</v>
-      </c>
-      <c r="B12" t="str">
-        <v>Phòng tắm / WC</v>
+        <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
+        <v>Mã khu vực</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Mô tả</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>LIVING_ROOM</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Phòng khách</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>BEDROOM</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Phòng ngủ</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>KITCHEN</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Nhà bếp</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>BATHROOM</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Phòng tắm / WC</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
         <v>BALCONY</v>
       </c>
-      <c r="B13" t="str">
+      <c r="B18" t="str">
         <v>Ban công</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>GARAGE</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Gara / sân</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>OTHER</v>
+      </c>
+      <c r="B20" t="str">
+        <v>Khu vực khác</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B13"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B20"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2094,21 +2334,21 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:O51"/>
   <cols>
-    <col min="1" max="1" width="13.83203125" customWidth="1"/>
-    <col min="2" max="2" width="13.83203125" customWidth="1"/>
-    <col min="3" max="3" width="18.83203125" customWidth="1"/>
-    <col min="4" max="4" width="12.83203125" customWidth="1"/>
-    <col min="5" max="5" width="16.83203125" customWidth="1"/>
-    <col min="6" max="6" width="16.83203125" customWidth="1"/>
-    <col min="7" max="7" width="15.83203125" customWidth="1"/>
-    <col min="8" max="8" width="16.83203125" customWidth="1"/>
-    <col min="9" max="9" width="14.83203125" customWidth="1"/>
-    <col min="10" max="10" width="15.83203125" customWidth="1"/>
-    <col min="11" max="11" width="13.83203125" customWidth="1"/>
-    <col min="12" max="12" width="16.83203125" customWidth="1"/>
-    <col min="13" max="13" width="14.83203125" customWidth="1"/>
-    <col min="14" max="14" width="15.83203125" customWidth="1"/>
-    <col min="15" max="15" width="16.83203125" customWidth="1"/>
+    <col min="1" max="1" width="16.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="20.83203125" customWidth="1"/>
+    <col min="4" max="4" width="16.83203125" customWidth="1"/>
+    <col min="5" max="5" width="18.83203125" customWidth="1"/>
+    <col min="6" max="6" width="18.83203125" customWidth="1"/>
+    <col min="7" max="7" width="17.83203125" customWidth="1"/>
+    <col min="8" max="8" width="18.83203125" customWidth="1"/>
+    <col min="9" max="9" width="16.83203125" customWidth="1"/>
+    <col min="10" max="10" width="17.83203125" customWidth="1"/>
+    <col min="11" max="11" width="16.83203125" customWidth="1"/>
+    <col min="12" max="12" width="18.83203125" customWidth="1"/>
+    <col min="13" max="13" width="16.83203125" customWidth="1"/>
+    <col min="14" max="14" width="17.83203125" customWidth="1"/>
+    <col min="15" max="15" width="18.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2160,13 +2400,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>HD-MTX-01-NORENO-WH-NONE</v>
+        <v>HD-MTX-01-RENO-WH-FULL</v>
       </c>
       <c r="B2" t="str">
-        <v>MTX#01 NGUYEN_CAN NONE</v>
+        <v>MTX#01 NGUYEN_CAN full NT</v>
       </c>
       <c r="C2" t="str">
-        <v>1 Ma Trận Quận 1</v>
+        <v>11 Nguyễn Huệ</v>
       </c>
       <c r="D2" t="str">
         <v>Quận 1</v>
@@ -2175,45 +2415,45 @@
         <v>TP. Hồ Chí Minh</v>
       </c>
       <c r="F2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="G2">
-        <v>17.6</v>
+        <v>12.2</v>
       </c>
       <c r="H2">
-        <v>5.9</v>
+        <v>8.7</v>
       </c>
       <c r="I2">
         <v>2</v>
       </c>
       <c r="J2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K2" t="str">
-        <v>Nguyễn Văn A</v>
+        <v>Nguyễn Văn An</v>
       </c>
       <c r="L2">
-        <v>233000000</v>
+        <v>187500000</v>
       </c>
       <c r="M2" t="str">
         <v>2026-03-01</v>
       </c>
       <c r="N2" t="str">
-        <v>2028-04-01</v>
+        <v>2028-03-31</v>
       </c>
       <c r="O2" t="str">
-        <v>Ma trận #1 — NORENO | nguyên căn | không nội thất | TB bàn giao: Không | không đợt 2</v>
+        <v>MTX#01 NGUYEN_CAN full NT — RENO. NT khai thác = TB mua mới đợt 2 (FULL). Đồ chủ bàn giao (nếu có) chỉ ghi nhận, không tính NT.</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>HD-MTX-02-NORENO-WH-NONE</v>
+        <v>HD-MTX-02-RENO-WH-FULL</v>
       </c>
       <c r="B3" t="str">
-        <v>MTX#02 NGUYEN_CAN NONE</v>
+        <v>MTX#02 NGUYEN_CAN full NT</v>
       </c>
       <c r="C3" t="str">
-        <v>2 Ma Trận Quận 3</v>
+        <v>12 Nam Kỳ Khởi Nghĩa</v>
       </c>
       <c r="D3" t="str">
         <v>Quận 3</v>
@@ -2222,45 +2462,45 @@
         <v>TP. Hồ Chí Minh</v>
       </c>
       <c r="F3">
-        <v>123</v>
+        <v>97</v>
       </c>
       <c r="G3">
-        <v>19.5</v>
+        <v>11.7</v>
       </c>
       <c r="H3">
-        <v>6.3</v>
+        <v>8.3</v>
       </c>
       <c r="I3">
         <v>1</v>
       </c>
       <c r="J3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K3" t="str">
-        <v>Trần Thị B</v>
+        <v>Trần Thị Bình</v>
       </c>
       <c r="L3">
-        <v>266000000</v>
+        <v>190000000</v>
       </c>
       <c r="M3" t="str">
         <v>2026-04-01</v>
       </c>
       <c r="N3" t="str">
-        <v>2028-06-01</v>
+        <v>2028-04-30</v>
       </c>
       <c r="O3" t="str">
-        <v>Ma trận #2 — NORENO | nguyên căn | không nội thất | TB bàn giao: Không | không đợt 2</v>
+        <v>MTX#02 NGUYEN_CAN full NT — RENO. NT khai thác = TB mua mới đợt 2 (FULL). Đồ chủ bàn giao (nếu có) chỉ ghi nhận, không tính NT.</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>HD-MTX-03-NORENO-WH-NONE</v>
+        <v>HD-MTX-03-RENO-WH-FULL</v>
       </c>
       <c r="B4" t="str">
-        <v>MTX#03 NGUYEN_CAN NONE</v>
+        <v>MTX#03 NGUYEN_CAN full NT</v>
       </c>
       <c r="C4" t="str">
-        <v>3 Ma Trận Bình Thạnh</v>
+        <v>13 Điện Biên Phủ</v>
       </c>
       <c r="D4" t="str">
         <v>Bình Thạnh</v>
@@ -2269,45 +2509,45 @@
         <v>TP. Hồ Chí Minh</v>
       </c>
       <c r="F4">
-        <v>97</v>
+        <v>112</v>
       </c>
       <c r="G4">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="H4">
-        <v>6.7</v>
+        <v>9</v>
       </c>
       <c r="I4">
         <v>2</v>
       </c>
       <c r="J4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K4" t="str">
-        <v>Lê Văn C</v>
+        <v>Lê Văn Cường</v>
       </c>
       <c r="L4">
-        <v>224000000</v>
+        <v>192500000</v>
       </c>
       <c r="M4" t="str">
         <v>2026-05-01</v>
       </c>
       <c r="N4" t="str">
-        <v>2028-08-01</v>
+        <v>2028-05-31</v>
       </c>
       <c r="O4" t="str">
-        <v>Ma trận #3 — NORENO | nguyên căn | không nội thất | TB bàn giao: Không | không đợt 2</v>
+        <v>MTX#03 NGUYEN_CAN full NT — RENO. NT khai thác = TB mua mới đợt 2 (FULL). Đồ chủ bàn giao (nếu có) chỉ ghi nhận, không tính NT.</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>HD-MTX-04-NORENO-WH-NONE</v>
+        <v>HD-MTX-04-RENO-WH-FULL</v>
       </c>
       <c r="B5" t="str">
-        <v>MTX#04 NGUYEN_CAN NONE</v>
+        <v>MTX#04 NGUYEN_CAN full NT</v>
       </c>
       <c r="C5" t="str">
-        <v>4 Ma Trận Gò Vấp</v>
+        <v>14 Lê Đức Thọ</v>
       </c>
       <c r="D5" t="str">
         <v>Gò Vấp</v>
@@ -2316,13 +2556,13 @@
         <v>TP. Hồ Chí Minh</v>
       </c>
       <c r="F5">
-        <v>116</v>
+        <v>103</v>
       </c>
       <c r="G5">
-        <v>16.3</v>
+        <v>12</v>
       </c>
       <c r="H5">
-        <v>7.1</v>
+        <v>8.6</v>
       </c>
       <c r="I5">
         <v>1</v>
@@ -2331,30 +2571,30 @@
         <v>3</v>
       </c>
       <c r="K5" t="str">
-        <v>Phạm Thị D</v>
+        <v>Phạm Thị Dung</v>
       </c>
       <c r="L5">
-        <v>257000000</v>
+        <v>195000000</v>
       </c>
       <c r="M5" t="str">
         <v>2026-06-01</v>
       </c>
       <c r="N5" t="str">
-        <v>2028-10-01</v>
+        <v>2028-06-30</v>
       </c>
       <c r="O5" t="str">
-        <v>Ma trận #4 — NORENO | nguyên căn | không nội thất | TB bàn giao: Không | không đợt 2</v>
+        <v>MTX#04 NGUYEN_CAN full NT — RENO. NT khai thác = TB mua mới đợt 2 (FULL). Đồ chủ bàn giao (nếu có) chỉ ghi nhận, không tính NT.</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>HD-MTX-05-NORENO-WH-NONE</v>
+        <v>HD-MTX-05-RENO-WH-FULL</v>
       </c>
       <c r="B6" t="str">
-        <v>MTX#05 NGUYEN_CAN NONE</v>
+        <v>MTX#05 NGUYEN_CAN full NT</v>
       </c>
       <c r="C6" t="str">
-        <v>5 Ma Trận Phú Nhuận</v>
+        <v>15 Hoàng Văn Thụ</v>
       </c>
       <c r="D6" t="str">
         <v>Phú Nhuận</v>
@@ -2363,13 +2603,13 @@
         <v>TP. Hồ Chí Minh</v>
       </c>
       <c r="F6">
-        <v>135</v>
+        <v>103</v>
       </c>
       <c r="G6">
-        <v>24.5</v>
+        <v>12</v>
       </c>
       <c r="H6">
-        <v>5.5</v>
+        <v>8.6</v>
       </c>
       <c r="I6">
         <v>2</v>
@@ -2378,233 +2618,233 @@
         <v>4</v>
       </c>
       <c r="K6" t="str">
-        <v>Hoàng Văn E</v>
+        <v>Hoàng Văn Em</v>
       </c>
       <c r="L6">
-        <v>290000000</v>
+        <v>197500000</v>
       </c>
       <c r="M6" t="str">
         <v>2026-07-01</v>
       </c>
       <c r="N6" t="str">
-        <v>2028-12-01</v>
+        <v>2028-07-31</v>
       </c>
       <c r="O6" t="str">
-        <v>Ma trận #5 — NORENO | nguyên căn | không nội thất | TB bàn giao: Không | không đợt 2</v>
+        <v>MTX#05 NGUYEN_CAN full NT — RENO. NT khai thác = TB mua mới đợt 2 (FULL). Đồ chủ bàn giao (nếu có) chỉ ghi nhận, không tính NT.</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>HD-MTX-06-NORENO-WH-BASIC</v>
+        <v>HD-MTX-06-RENO-WH-FULL</v>
       </c>
       <c r="B7" t="str">
-        <v>MTX#06 NGUYEN_CAN BASIC</v>
+        <v>MTX#06 NGUYEN_CAN full NT</v>
       </c>
       <c r="C7" t="str">
-        <v>6 Ma Trận Cầu Giấy</v>
+        <v>16 Nguyễn Huệ</v>
       </c>
       <c r="D7" t="str">
-        <v>Cầu Giấy</v>
+        <v>Quận 1</v>
       </c>
       <c r="E7" t="str">
-        <v>Hà Nội</v>
+        <v>TP. Hồ Chí Minh</v>
       </c>
       <c r="F7">
-        <v>109</v>
+        <v>94</v>
       </c>
       <c r="G7">
-        <v>18.5</v>
+        <v>11.5</v>
       </c>
       <c r="H7">
-        <v>5.9</v>
+        <v>8.2</v>
       </c>
       <c r="I7">
         <v>1</v>
       </c>
       <c r="J7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K7" t="str">
-        <v>Võ Thị F</v>
+        <v>Võ Thị Phương</v>
       </c>
       <c r="L7">
-        <v>248000000</v>
+        <v>200000000</v>
       </c>
       <c r="M7" t="str">
         <v>2026-08-01</v>
       </c>
       <c r="N7" t="str">
-        <v>2029-02-01</v>
+        <v>2028-08-31</v>
       </c>
       <c r="O7" t="str">
-        <v>Ma trận #6 — NORENO | nguyên căn | nội thất cơ bản | TB bàn giao: Có | không đợt 2</v>
+        <v>MTX#06 NGUYEN_CAN full NT — RENO. NT khai thác = TB mua mới đợt 2 (FULL). Đồ chủ bàn giao (nếu có) chỉ ghi nhận, không tính NT.</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>HD-MTX-07-NORENO-WH-BASIC</v>
+        <v>HD-MTX-07-RENO-WH-FULL</v>
       </c>
       <c r="B8" t="str">
-        <v>MTX#07 NGUYEN_CAN BASIC</v>
+        <v>MTX#07 NGUYEN_CAN full NT</v>
       </c>
       <c r="C8" t="str">
-        <v>7 Ma Trận Quận 1</v>
+        <v>17 Lý Chính Thắng</v>
       </c>
       <c r="D8" t="str">
-        <v>Quận 1</v>
+        <v>Quận 3</v>
       </c>
       <c r="E8" t="str">
         <v>TP. Hồ Chí Minh</v>
       </c>
       <c r="F8">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="G8">
-        <v>15.9</v>
+        <v>12.4</v>
       </c>
       <c r="H8">
-        <v>6.3</v>
+        <v>8.8</v>
       </c>
       <c r="I8">
         <v>2</v>
       </c>
       <c r="J8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K8" t="str">
-        <v>Đặng Văn G</v>
+        <v>Đặng Văn Giang</v>
       </c>
       <c r="L8">
-        <v>281000000</v>
+        <v>202500000</v>
       </c>
       <c r="M8" t="str">
         <v>2026-09-01</v>
       </c>
       <c r="N8" t="str">
-        <v>2029-04-01</v>
+        <v>2028-09-30</v>
       </c>
       <c r="O8" t="str">
-        <v>Ma trận #7 — NORENO | nguyên căn | nội thất cơ bản | TB bàn giao: Có | không đợt 2</v>
+        <v>MTX#07 NGUYEN_CAN full NT — RENO. NT khai thác = TB mua mới đợt 2 (FULL). Đồ chủ bàn giao (nếu có) chỉ ghi nhận, không tính NT.</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>HD-MTX-08-NORENO-WH-BASIC</v>
+        <v>HD-MTX-08-RENO-WH-FULL</v>
       </c>
       <c r="B9" t="str">
-        <v>MTX#08 NGUYEN_CAN BASIC</v>
+        <v>MTX#08 NGUYEN_CAN full NT</v>
       </c>
       <c r="C9" t="str">
-        <v>8 Ma Trận Quận 3</v>
+        <v>18 Nơ Trang Long</v>
       </c>
       <c r="D9" t="str">
-        <v>Quận 3</v>
+        <v>Bình Thạnh</v>
       </c>
       <c r="E9" t="str">
         <v>TP. Hồ Chí Minh</v>
       </c>
       <c r="F9">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="G9">
-        <v>17.8</v>
+        <v>11.8</v>
       </c>
       <c r="H9">
-        <v>6.7</v>
+        <v>8.5</v>
       </c>
       <c r="I9">
         <v>1</v>
       </c>
       <c r="J9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K9" t="str">
-        <v>Bùi Thị H</v>
+        <v>Bùi Thị Hoa</v>
       </c>
       <c r="L9">
-        <v>250000000</v>
+        <v>205000000</v>
       </c>
       <c r="M9" t="str">
         <v>2026-10-01</v>
       </c>
       <c r="N9" t="str">
-        <v>2029-06-01</v>
+        <v>2028-10-31</v>
       </c>
       <c r="O9" t="str">
-        <v>Ma trận #8 — NORENO | nguyên căn | nội thất cơ bản | TB bàn giao: Có | không đợt 2</v>
+        <v>MTX#08 NGUYEN_CAN full NT — RENO. NT khai thác = TB mua mới đợt 2 (FULL). Đồ chủ bàn giao (nếu có) chỉ ghi nhận, không tính NT.</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>HD-MTX-09-NORENO-WH-BASIC</v>
+        <v>HD-MTX-09-RENO-WH-FULL</v>
       </c>
       <c r="B10" t="str">
-        <v>MTX#09 NGUYEN_CAN BASIC</v>
+        <v>MTX#09 NGUYEN_CAN full NT</v>
       </c>
       <c r="C10" t="str">
-        <v>9 Ma Trận Bình Thạnh</v>
+        <v>19 Quang Trung</v>
       </c>
       <c r="D10" t="str">
-        <v>Bình Thạnh</v>
+        <v>Gò Vấp</v>
       </c>
       <c r="E10" t="str">
         <v>TP. Hồ Chí Minh</v>
       </c>
       <c r="F10">
-        <v>93</v>
+        <v>115</v>
       </c>
       <c r="G10">
-        <v>13.1</v>
+        <v>12.7</v>
       </c>
       <c r="H10">
-        <v>7.1</v>
+        <v>9.1</v>
       </c>
       <c r="I10">
         <v>2</v>
       </c>
       <c r="J10">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K10" t="str">
-        <v>Ngô Văn I</v>
+        <v>Ngô Văn Ích</v>
       </c>
       <c r="L10">
-        <v>208000000</v>
+        <v>207500000</v>
       </c>
       <c r="M10" t="str">
-        <v>2026-03-01</v>
+        <v>2026-11-01</v>
       </c>
       <c r="N10" t="str">
-        <v>2028-12-01</v>
+        <v>2028-11-30</v>
       </c>
       <c r="O10" t="str">
-        <v>Ma trận #9 — NORENO | nguyên căn | nội thất cơ bản | TB bàn giao: Có | không đợt 2</v>
+        <v>MTX#09 NGUYEN_CAN full NT — RENO. NT khai thác = TB mua mới đợt 2 (FULL). Đồ chủ bàn giao (nếu có) chỉ ghi nhận, không tính NT.</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>HD-MTX-10-NORENO-WH-BASIC</v>
+        <v>HD-MTX-10-RENO-WH-FULL</v>
       </c>
       <c r="B11" t="str">
-        <v>MTX#10 NGUYEN_CAN BASIC</v>
+        <v>MTX#10 NGUYEN_CAN full NT</v>
       </c>
       <c r="C11" t="str">
-        <v>10 Ma Trận Gò Vấp</v>
+        <v>20 Phan Xích Long</v>
       </c>
       <c r="D11" t="str">
-        <v>Gò Vấp</v>
+        <v>Phú Nhuận</v>
       </c>
       <c r="E11" t="str">
         <v>TP. Hồ Chí Minh</v>
       </c>
       <c r="F11">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="G11">
-        <v>20.4</v>
+        <v>11.3</v>
       </c>
       <c r="H11">
-        <v>5.5</v>
+        <v>8.1</v>
       </c>
       <c r="I11">
         <v>1</v>
@@ -2613,45 +2853,45 @@
         <v>3</v>
       </c>
       <c r="K11" t="str">
-        <v>Dương Thị K</v>
+        <v>Dương Thị Kim</v>
       </c>
       <c r="L11">
-        <v>241000000</v>
+        <v>210000000</v>
       </c>
       <c r="M11" t="str">
-        <v>2026-04-01</v>
+        <v>2026-12-01</v>
       </c>
       <c r="N11" t="str">
-        <v>2029-02-01</v>
+        <v>2028-12-31</v>
       </c>
       <c r="O11" t="str">
-        <v>Ma trận #10 — NORENO | nguyên căn | nội thất cơ bản | TB bàn giao: Có | không đợt 2</v>
+        <v>MTX#10 NGUYEN_CAN full NT — RENO. NT khai thác = TB mua mới đợt 2 (FULL). Đồ chủ bàn giao (nếu có) chỉ ghi nhận, không tính NT.</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>HD-MTX-11-NORENO-WH-FULL</v>
+        <v>HD-MTX-11-RENO-WH-FULL</v>
       </c>
       <c r="B12" t="str">
-        <v>MTX#11 NGUYEN_CAN FULL</v>
+        <v>MTX#11 NGUYEN_CAN full NT</v>
       </c>
       <c r="C12" t="str">
-        <v>11 Ma Trận Phú Nhuận</v>
+        <v>21 Nguyễn Huệ</v>
       </c>
       <c r="D12" t="str">
-        <v>Phú Nhuận</v>
+        <v>Quận 1</v>
       </c>
       <c r="E12" t="str">
         <v>TP. Hồ Chí Minh</v>
       </c>
       <c r="F12">
-        <v>131</v>
+        <v>106</v>
       </c>
       <c r="G12">
-        <v>22.2</v>
+        <v>12.2</v>
       </c>
       <c r="H12">
-        <v>5.9</v>
+        <v>8.7</v>
       </c>
       <c r="I12">
         <v>2</v>
@@ -2660,327 +2900,327 @@
         <v>4</v>
       </c>
       <c r="K12" t="str">
-        <v>Lý Văn L</v>
+        <v>Lý Văn Long</v>
       </c>
       <c r="L12">
-        <v>274000000</v>
+        <v>212500000</v>
       </c>
       <c r="M12" t="str">
-        <v>2026-05-01</v>
+        <v>2026-03-01</v>
       </c>
       <c r="N12" t="str">
-        <v>2029-04-01</v>
+        <v>2028-03-31</v>
       </c>
       <c r="O12" t="str">
-        <v>Ma trận #11 — NORENO | nguyên căn | full nội thất | TB bàn giao: Có | không đợt 2</v>
+        <v>MTX#11 NGUYEN_CAN full NT — RENO. NT khai thác = TB mua mới đợt 2 (FULL). Đồ chủ bàn giao (nếu có) chỉ ghi nhận, không tính NT.</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>HD-MTX-12-NORENO-WH-FULL</v>
+        <v>HD-MTX-12-RENO-WH-FULL</v>
       </c>
       <c r="B13" t="str">
-        <v>MTX#12 NGUYEN_CAN FULL</v>
+        <v>MTX#12 NGUYEN_CAN full NT</v>
       </c>
       <c r="C13" t="str">
-        <v>12 Ma Trận Cầu Giấy</v>
+        <v>22 Cách Mạng Tháng 8</v>
       </c>
       <c r="D13" t="str">
-        <v>Cầu Giấy</v>
+        <v>Quận 3</v>
       </c>
       <c r="E13" t="str">
-        <v>Hà Nội</v>
+        <v>TP. Hồ Chí Minh</v>
       </c>
       <c r="F13">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="G13">
-        <v>16.7</v>
+        <v>11.7</v>
       </c>
       <c r="H13">
-        <v>6.3</v>
+        <v>8.3</v>
       </c>
       <c r="I13">
         <v>1</v>
       </c>
       <c r="J13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K13" t="str">
-        <v>Mai Thị M</v>
+        <v>Mai Thị My</v>
       </c>
       <c r="L13">
-        <v>232000000</v>
+        <v>215000000</v>
       </c>
       <c r="M13" t="str">
-        <v>2026-06-01</v>
+        <v>2026-04-01</v>
       </c>
       <c r="N13" t="str">
-        <v>2028-06-01</v>
+        <v>2028-04-30</v>
       </c>
       <c r="O13" t="str">
-        <v>Ma trận #12 — NORENO | nguyên căn | full nội thất | TB bàn giao: Có | không đợt 2</v>
+        <v>MTX#12 NGUYEN_CAN full NT — RENO. NT khai thác = TB mua mới đợt 2 (FULL). Đồ chủ bàn giao (nếu có) chỉ ghi nhận, không tính NT.</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>HD-MTX-13-NORENO-WH-FULL</v>
+        <v>HD-MTX-13-RENO-WH-FULL</v>
       </c>
       <c r="B14" t="str">
-        <v>MTX#13 NGUYEN_CAN FULL</v>
+        <v>MTX#13 NGUYEN_CAN full NT</v>
       </c>
       <c r="C14" t="str">
-        <v>13 Ma Trận Quận 1</v>
+        <v>23 Phan Văn Trị</v>
       </c>
       <c r="D14" t="str">
-        <v>Quận 1</v>
+        <v>Bình Thạnh</v>
       </c>
       <c r="E14" t="str">
         <v>TP. Hồ Chí Minh</v>
       </c>
       <c r="F14">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="G14">
-        <v>18.5</v>
+        <v>12.5</v>
       </c>
       <c r="H14">
-        <v>6.7</v>
+        <v>9</v>
       </c>
       <c r="I14">
         <v>2</v>
       </c>
       <c r="J14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K14" t="str">
-        <v>Phan Văn N</v>
+        <v>Phan Văn Nam</v>
       </c>
       <c r="L14">
-        <v>265000000</v>
+        <v>217500000</v>
       </c>
       <c r="M14" t="str">
-        <v>2026-07-01</v>
+        <v>2026-05-01</v>
       </c>
       <c r="N14" t="str">
-        <v>2028-08-01</v>
+        <v>2028-05-31</v>
       </c>
       <c r="O14" t="str">
-        <v>Ma trận #13 — NORENO | nguyên căn | full nội thất | TB bàn giao: Có | không đợt 2</v>
+        <v>MTX#13 NGUYEN_CAN full NT — RENO. NT khai thác = TB mua mới đợt 2 (FULL). Đồ chủ bàn giao (nếu có) chỉ ghi nhận, không tính NT.</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>HD-MTX-14-NORENO-WH-FULL</v>
+        <v>HD-MTX-14-RENO-WH-FULL</v>
       </c>
       <c r="B15" t="str">
-        <v>MTX#14 NGUYEN_CAN FULL</v>
+        <v>MTX#14 NGUYEN_CAN full NT</v>
       </c>
       <c r="C15" t="str">
-        <v>14 Ma Trận Quận 3</v>
+        <v>24 Phạm Văn Chiêu</v>
       </c>
       <c r="D15" t="str">
-        <v>Quận 3</v>
+        <v>Gò Vấp</v>
       </c>
       <c r="E15" t="str">
         <v>TP. Hồ Chí Minh</v>
       </c>
       <c r="F15">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="G15">
-        <v>16.2</v>
+        <v>12</v>
       </c>
       <c r="H15">
-        <v>7.1</v>
+        <v>8.6</v>
       </c>
       <c r="I15">
         <v>1</v>
       </c>
       <c r="J15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K15" t="str">
-        <v>Trịnh Thị O</v>
+        <v>Trịnh Thị Oanh</v>
       </c>
       <c r="L15">
-        <v>298000000</v>
+        <v>220000000</v>
       </c>
       <c r="M15" t="str">
-        <v>2026-08-01</v>
+        <v>2026-06-01</v>
       </c>
       <c r="N15" t="str">
-        <v>2028-10-01</v>
+        <v>2028-06-30</v>
       </c>
       <c r="O15" t="str">
-        <v>Ma trận #14 — NORENO | nguyên căn | full nội thất | TB bàn giao: Có | không đợt 2</v>
+        <v>MTX#14 NGUYEN_CAN full NT — RENO. NT khai thác = TB mua mới đợt 2 (FULL). Đồ chủ bàn giao (nếu có) chỉ ghi nhận, không tính NT.</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>HD-MTX-15-NORENO-WH-FULL</v>
+        <v>HD-MTX-15-RENO-WH-BASIC</v>
       </c>
       <c r="B16" t="str">
-        <v>MTX#15 NGUYEN_CAN FULL</v>
+        <v>MTX#15 NGUYEN_CAN NT cơ bản</v>
       </c>
       <c r="C16" t="str">
-        <v>15 Ma Trận Bình Thạnh</v>
+        <v>25 Nguyễn Văn Trỗi</v>
       </c>
       <c r="D16" t="str">
-        <v>Bình Thạnh</v>
+        <v>Phú Nhuận</v>
       </c>
       <c r="E16" t="str">
         <v>TP. Hồ Chí Minh</v>
       </c>
       <c r="F16">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G16">
-        <v>16.2</v>
+        <v>11.3</v>
       </c>
       <c r="H16">
-        <v>5.5</v>
+        <v>8.1</v>
       </c>
       <c r="I16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J16">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K16" t="str">
-        <v>Huỳnh Văn P</v>
+        <v>Vũ Văn Phát</v>
       </c>
       <c r="L16">
-        <v>256000000</v>
+        <v>207500000</v>
       </c>
       <c r="M16" t="str">
-        <v>2026-09-01</v>
+        <v>2026-07-01</v>
       </c>
       <c r="N16" t="str">
-        <v>2028-12-01</v>
+        <v>2028-07-31</v>
       </c>
       <c r="O16" t="str">
-        <v>Ma trận #15 — NORENO | nguyên căn | full nội thất | TB bàn giao: Có | không đợt 2</v>
+        <v>MTX#15 NGUYEN_CAN NT cơ bản — RENO. NT khai thác = TB mua mới đợt 2 (BASIC). Đồ chủ bàn giao (nếu có) chỉ ghi nhận, không tính NT.</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>HD-MTX-16-RENO-WH-NONE</v>
+        <v>HD-MTX-16-RENO-WH-BASIC</v>
       </c>
       <c r="B17" t="str">
-        <v>MTX#16 NGUYEN_CAN NONE</v>
+        <v>MTX#16 NGUYEN_CAN NT cơ bản</v>
       </c>
       <c r="C17" t="str">
-        <v>16 Ma Trận Gò Vấp</v>
+        <v>26 Nguyễn Huệ</v>
       </c>
       <c r="D17" t="str">
-        <v>Gò Vấp</v>
+        <v>Quận 1</v>
       </c>
       <c r="E17" t="str">
         <v>TP. Hồ Chí Minh</v>
       </c>
       <c r="F17">
-        <v>108</v>
+        <v>82</v>
       </c>
       <c r="G17">
-        <v>18.3</v>
+        <v>10.7</v>
       </c>
       <c r="H17">
-        <v>5.9</v>
+        <v>7.7</v>
       </c>
       <c r="I17">
         <v>1</v>
       </c>
       <c r="J17">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K17" t="str">
-        <v>Nguyễn Văn A</v>
+        <v>Cao Thị Quyên</v>
       </c>
       <c r="L17">
-        <v>225000000</v>
+        <v>210000000</v>
       </c>
       <c r="M17" t="str">
-        <v>2026-10-01</v>
+        <v>2026-08-01</v>
       </c>
       <c r="N17" t="str">
-        <v>2029-02-01</v>
+        <v>2028-08-31</v>
       </c>
       <c r="O17" t="str">
-        <v>Ma trận #16 — RENO | nguyên căn | không nội thất | TB bàn giao: Không | TB mua đ2: Không</v>
+        <v>MTX#16 NGUYEN_CAN NT cơ bản — RENO. NT khai thác = TB mua mới đợt 2 (BASIC). Đồ chủ bàn giao (nếu có) chỉ ghi nhận, không tính NT.</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>HD-MTX-17-RENO-WH-NONE</v>
+        <v>HD-MTX-17-RENO-WH-BASIC</v>
       </c>
       <c r="B18" t="str">
-        <v>MTX#17 NGUYEN_CAN NONE</v>
+        <v>MTX#17 NGUYEN_CAN NT cơ bản</v>
       </c>
       <c r="C18" t="str">
-        <v>17 Ma Trận Phú Nhuận</v>
+        <v>27 Võ Văn Tần</v>
       </c>
       <c r="D18" t="str">
-        <v>Phú Nhuận</v>
+        <v>Quận 3</v>
       </c>
       <c r="E18" t="str">
         <v>TP. Hồ Chí Minh</v>
       </c>
       <c r="F18">
-        <v>127</v>
+        <v>97</v>
       </c>
       <c r="G18">
-        <v>20.2</v>
+        <v>11.7</v>
       </c>
       <c r="H18">
-        <v>6.3</v>
+        <v>8.3</v>
       </c>
       <c r="I18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J18">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K18" t="str">
-        <v>Trần Thị B</v>
+        <v>Lương Văn Rạng</v>
       </c>
       <c r="L18">
-        <v>258000000</v>
+        <v>212500000</v>
       </c>
       <c r="M18" t="str">
-        <v>2026-03-01</v>
+        <v>2026-09-01</v>
       </c>
       <c r="N18" t="str">
-        <v>2028-08-01</v>
+        <v>2028-09-30</v>
       </c>
       <c r="O18" t="str">
-        <v>Ma trận #17 — RENO | nguyên căn | không nội thất | TB bàn giao: Không | TB mua đ2: Không</v>
+        <v>MTX#17 NGUYEN_CAN NT cơ bản — RENO. NT khai thác = TB mua mới đợt 2 (BASIC). Đồ chủ bàn giao (nếu có) chỉ ghi nhận, không tính NT.</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>HD-MTX-18-RENO-WH-NONE</v>
+        <v>HD-MTX-18-RENO-WH-BASIC</v>
       </c>
       <c r="B19" t="str">
-        <v>MTX#18 NGUYEN_CAN NONE</v>
+        <v>MTX#18 NGUYEN_CAN NT cơ bản</v>
       </c>
       <c r="C19" t="str">
-        <v>18 Ma Trận Cầu Giấy</v>
+        <v>28 Xô Viết Nghệ Tĩnh</v>
       </c>
       <c r="D19" t="str">
-        <v>Cầu Giấy</v>
+        <v>Bình Thạnh</v>
       </c>
       <c r="E19" t="str">
-        <v>Hà Nội</v>
+        <v>TP. Hồ Chí Minh</v>
       </c>
       <c r="F19">
-        <v>101</v>
+        <v>88</v>
       </c>
       <c r="G19">
-        <v>15.1</v>
+        <v>11.1</v>
       </c>
       <c r="H19">
-        <v>6.7</v>
+        <v>7.9</v>
       </c>
       <c r="I19">
         <v>1</v>
@@ -2989,280 +3229,280 @@
         <v>2</v>
       </c>
       <c r="K19" t="str">
-        <v>Lê Văn C</v>
+        <v>Tô Thị Sen</v>
       </c>
       <c r="L19">
-        <v>216000000</v>
+        <v>215000000</v>
       </c>
       <c r="M19" t="str">
-        <v>2026-04-01</v>
+        <v>2026-10-01</v>
       </c>
       <c r="N19" t="str">
-        <v>2028-10-01</v>
+        <v>2028-10-31</v>
       </c>
       <c r="O19" t="str">
-        <v>Ma trận #18 — RENO | nguyên căn | không nội thất | TB bàn giao: Không | TB mua đ2: Không</v>
+        <v>MTX#18 NGUYEN_CAN NT cơ bản — RENO. NT khai thác = TB mua mới đợt 2 (BASIC). Đồ chủ bàn giao (nếu có) chỉ ghi nhận, không tính NT.</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>HD-MTX-19-RENO-WH-BASIC-HO</v>
+        <v>HD-MTX-19-RENO-WH-BASIC</v>
       </c>
       <c r="B20" t="str">
-        <v>MTX#19 NGUYEN_CAN BASIC</v>
+        <v>MTX#19 NGUYEN_CAN NT cơ bản</v>
       </c>
       <c r="C20" t="str">
-        <v>19 Ma Trận Quận 1</v>
+        <v>29 Nguyễn Oanh</v>
       </c>
       <c r="D20" t="str">
-        <v>Quận 1</v>
+        <v>Gò Vấp</v>
       </c>
       <c r="E20" t="str">
         <v>TP. Hồ Chí Minh</v>
       </c>
       <c r="F20">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="G20">
-        <v>16.9</v>
+        <v>12</v>
       </c>
       <c r="H20">
-        <v>7.1</v>
+        <v>8.6</v>
       </c>
       <c r="I20">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J20">
         <v>3</v>
       </c>
       <c r="K20" t="str">
-        <v>Phạm Thị D</v>
+        <v>Huỳnh Văn Tâm</v>
       </c>
       <c r="L20">
-        <v>249000000</v>
+        <v>217500000</v>
       </c>
       <c r="M20" t="str">
-        <v>2026-05-01</v>
+        <v>2026-11-01</v>
       </c>
       <c r="N20" t="str">
-        <v>2028-12-01</v>
+        <v>2028-11-30</v>
       </c>
       <c r="O20" t="str">
-        <v>Ma trận #19 — RENO | nguyên căn | nội thất cơ bản | TB bàn giao: Có | TB mua đ2: Không</v>
+        <v>MTX#19 NGUYEN_CAN NT cơ bản — RENO. NT khai thác = TB mua mới đợt 2 (BASIC). Đồ chủ bàn giao (nếu có) chỉ ghi nhận, không tính NT.</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>HD-MTX-20-RENO-WH-BASIC-HO</v>
+        <v>HD-MTX-20-RENO-WH-BASIC</v>
       </c>
       <c r="B21" t="str">
-        <v>MTX#20 NGUYEN_CAN BASIC</v>
+        <v>MTX#20 NGUYEN_CAN NT cơ bản</v>
       </c>
       <c r="C21" t="str">
-        <v>20 Ma Trận Quận 3</v>
+        <v>30 Trường Sa</v>
       </c>
       <c r="D21" t="str">
-        <v>Quận 3</v>
+        <v>Phú Nhuận</v>
       </c>
       <c r="E21" t="str">
         <v>TP. Hồ Chí Minh</v>
       </c>
       <c r="F21">
-        <v>139</v>
+        <v>79</v>
       </c>
       <c r="G21">
-        <v>25.3</v>
+        <v>10.5</v>
       </c>
       <c r="H21">
-        <v>5.5</v>
+        <v>7.5</v>
       </c>
       <c r="I21">
         <v>1</v>
       </c>
       <c r="J21">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K21" t="str">
-        <v>Hoàng Văn E</v>
+        <v>Đỗ Thị Uyên</v>
       </c>
       <c r="L21">
-        <v>282000000</v>
+        <v>220000000</v>
       </c>
       <c r="M21" t="str">
-        <v>2026-06-01</v>
+        <v>2026-12-01</v>
       </c>
       <c r="N21" t="str">
-        <v>2029-02-01</v>
+        <v>2028-12-31</v>
       </c>
       <c r="O21" t="str">
-        <v>Ma trận #20 — RENO | nguyên căn | nội thất cơ bản | TB bàn giao: Có | TB mua đ2: Không</v>
+        <v>MTX#20 NGUYEN_CAN NT cơ bản — RENO. NT khai thác = TB mua mới đợt 2 (BASIC). Đồ chủ bàn giao (nếu có) chỉ ghi nhận, không tính NT.</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>HD-MTX-21-RENO-WH-BASIC-HO</v>
+        <v>HD-MTX-21-RENO-WH-BASIC</v>
       </c>
       <c r="B22" t="str">
-        <v>MTX#21 NGUYEN_CAN BASIC</v>
+        <v>MTX#21 NGUYEN_CAN NT cơ bản</v>
       </c>
       <c r="C22" t="str">
-        <v>21 Ma Trận Bình Thạnh</v>
+        <v>31 Nguyễn Huệ</v>
       </c>
       <c r="D22" t="str">
-        <v>Bình Thạnh</v>
+        <v>Quận 1</v>
       </c>
       <c r="E22" t="str">
         <v>TP. Hồ Chí Minh</v>
       </c>
       <c r="F22">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="G22">
-        <v>14.4</v>
+        <v>11.5</v>
       </c>
       <c r="H22">
-        <v>5.9</v>
+        <v>8.2</v>
       </c>
       <c r="I22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J22">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K22" t="str">
-        <v>Võ Thị F</v>
+        <v>Hồ Văn Vinh</v>
       </c>
       <c r="L22">
-        <v>240000000</v>
+        <v>222500000</v>
       </c>
       <c r="M22" t="str">
-        <v>2026-07-01</v>
+        <v>2026-03-01</v>
       </c>
       <c r="N22" t="str">
-        <v>2029-04-01</v>
+        <v>2028-03-31</v>
       </c>
       <c r="O22" t="str">
-        <v>Ma trận #21 — RENO | nguyên căn | nội thất cơ bản | TB bàn giao: Có | TB mua đ2: Không</v>
+        <v>MTX#21 NGUYEN_CAN NT cơ bản — RENO. NT khai thác = TB mua mới đợt 2 (BASIC). Đồ chủ bàn giao (nếu có) chỉ ghi nhận, không tính NT.</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>HD-MTX-22-RENO-WH-BASIC-BUY</v>
+        <v>HD-MTX-22-RENO-WH-BASIC</v>
       </c>
       <c r="B23" t="str">
-        <v>MTX#22 NGUYEN_CAN BASIC</v>
+        <v>MTX#22 NGUYEN_CAN NT cơ bản</v>
       </c>
       <c r="C23" t="str">
-        <v>22 Ma Trận Gò Vấp</v>
+        <v>32 Nam Kỳ Khởi Nghĩa</v>
       </c>
       <c r="D23" t="str">
-        <v>Gò Vấp</v>
+        <v>Quận 3</v>
       </c>
       <c r="E23" t="str">
         <v>TP. Hồ Chí Minh</v>
       </c>
       <c r="F23">
-        <v>104</v>
+        <v>85</v>
       </c>
       <c r="G23">
-        <v>16.5</v>
+        <v>10.9</v>
       </c>
       <c r="H23">
-        <v>6.3</v>
+        <v>7.8</v>
       </c>
       <c r="I23">
         <v>1</v>
       </c>
       <c r="J23">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K23" t="str">
-        <v>Đặng Văn G</v>
+        <v>Đinh Thị Xuân</v>
       </c>
       <c r="L23">
-        <v>273000000</v>
+        <v>225000000</v>
       </c>
       <c r="M23" t="str">
-        <v>2026-08-01</v>
+        <v>2026-04-01</v>
       </c>
       <c r="N23" t="str">
-        <v>2029-06-01</v>
+        <v>2028-04-30</v>
       </c>
       <c r="O23" t="str">
-        <v>Ma trận #22 — RENO | nguyên căn | nội thất cơ bản | TB bàn giao: Không | TB mua đ2: Có</v>
+        <v>MTX#22 NGUYEN_CAN NT cơ bản — RENO. NT khai thác = TB mua mới đợt 2 (BASIC). Đồ chủ bàn giao (nếu có) chỉ ghi nhận, không tính NT.</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>HD-MTX-23-RENO-WH-BASIC-BUY</v>
+        <v>HD-MTX-23-RENO-WH-BASIC</v>
       </c>
       <c r="B24" t="str">
-        <v>MTX#23 NGUYEN_CAN BASIC</v>
+        <v>MTX#23 NGUYEN_CAN NT cơ bản</v>
       </c>
       <c r="C24" t="str">
-        <v>23 Ma Trận Phú Nhuận</v>
+        <v>33 Điện Biên Phủ</v>
       </c>
       <c r="D24" t="str">
-        <v>Phú Nhuận</v>
+        <v>Bình Thạnh</v>
       </c>
       <c r="E24" t="str">
         <v>TP. Hồ Chí Minh</v>
       </c>
       <c r="F24">
-        <v>123</v>
+        <v>100</v>
       </c>
       <c r="G24">
-        <v>18.4</v>
+        <v>11.8</v>
       </c>
       <c r="H24">
-        <v>6.7</v>
+        <v>8.5</v>
       </c>
       <c r="I24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J24">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K24" t="str">
-        <v>Bùi Thị H</v>
+        <v>Lại Văn Yên</v>
       </c>
       <c r="L24">
-        <v>306000000</v>
+        <v>227500000</v>
       </c>
       <c r="M24" t="str">
-        <v>2026-09-01</v>
+        <v>2026-05-01</v>
       </c>
       <c r="N24" t="str">
-        <v>2029-08-01</v>
+        <v>2028-05-31</v>
       </c>
       <c r="O24" t="str">
-        <v>Ma trận #23 — RENO | nguyên căn | nội thất cơ bản | TB bàn giao: Không | TB mua đ2: Có</v>
+        <v>MTX#23 NGUYEN_CAN NT cơ bản — RENO. NT khai thác = TB mua mới đợt 2 (BASIC). Đồ chủ bàn giao (nếu có) chỉ ghi nhận, không tính NT.</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>HD-MTX-24-RENO-WH-BASIC-BUY</v>
+        <v>HD-MTX-24-RENO-WH-BASIC</v>
       </c>
       <c r="B25" t="str">
-        <v>MTX#24 NGUYEN_CAN BASIC</v>
+        <v>MTX#24 NGUYEN_CAN NT cơ bản</v>
       </c>
       <c r="C25" t="str">
-        <v>24 Ma Trận Cầu Giấy</v>
+        <v>34 Lê Đức Thọ</v>
       </c>
       <c r="D25" t="str">
-        <v>Cầu Giấy</v>
+        <v>Gò Vấp</v>
       </c>
       <c r="E25" t="str">
-        <v>Hà Nội</v>
+        <v>TP. Hồ Chí Minh</v>
       </c>
       <c r="F25">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="G25">
-        <v>13.7</v>
+        <v>11.3</v>
       </c>
       <c r="H25">
-        <v>7.1</v>
+        <v>8.1</v>
       </c>
       <c r="I25">
         <v>1</v>
@@ -3271,280 +3511,280 @@
         <v>2</v>
       </c>
       <c r="K25" t="str">
-        <v>Ngô Văn I</v>
+        <v>Tạ Thị Ánh</v>
       </c>
       <c r="L25">
-        <v>200000000</v>
+        <v>230000000</v>
       </c>
       <c r="M25" t="str">
-        <v>2026-10-01</v>
+        <v>2026-06-01</v>
       </c>
       <c r="N25" t="str">
-        <v>2028-10-01</v>
+        <v>2028-06-30</v>
       </c>
       <c r="O25" t="str">
-        <v>Ma trận #24 — RENO | nguyên căn | nội thất cơ bản | TB bàn giao: Không | TB mua đ2: Có</v>
+        <v>MTX#24 NGUYEN_CAN NT cơ bản — RENO. NT khai thác = TB mua mới đợt 2 (BASIC). Đồ chủ bàn giao (nếu có) chỉ ghi nhận, không tính NT.</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>HD-MTX-25-RENO-WH-FULL</v>
+        <v>HD-MTX-25-RENO-WH-BASIC</v>
       </c>
       <c r="B26" t="str">
-        <v>MTX#25 NGUYEN_CAN FULL</v>
+        <v>MTX#25 NGUYEN_CAN NT cơ bản</v>
       </c>
       <c r="C26" t="str">
-        <v>25 Ma Trận Quận 1</v>
+        <v>35 Hoàng Văn Thụ</v>
       </c>
       <c r="D26" t="str">
-        <v>Quận 1</v>
+        <v>Phú Nhuận</v>
       </c>
       <c r="E26" t="str">
         <v>TP. Hồ Chí Minh</v>
       </c>
       <c r="F26">
-        <v>116</v>
+        <v>91</v>
       </c>
       <c r="G26">
-        <v>21.1</v>
+        <v>11.3</v>
       </c>
       <c r="H26">
-        <v>5.5</v>
+        <v>8.1</v>
       </c>
       <c r="I26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J26">
         <v>3</v>
       </c>
       <c r="K26" t="str">
-        <v>Dương Thị K</v>
+        <v>Châu Văn Bảo</v>
       </c>
       <c r="L26">
-        <v>233000000</v>
+        <v>232500000</v>
       </c>
       <c r="M26" t="str">
-        <v>2026-03-01</v>
+        <v>2026-07-01</v>
       </c>
       <c r="N26" t="str">
-        <v>2028-04-01</v>
+        <v>2028-07-31</v>
       </c>
       <c r="O26" t="str">
-        <v>Ma trận #25 — RENO | nguyên căn | full nội thất | TB bàn giao: Có | TB mua đ2: Có</v>
+        <v>MTX#25 NGUYEN_CAN NT cơ bản — RENO. NT khai thác = TB mua mới đợt 2 (BASIC). Đồ chủ bàn giao (nếu có) chỉ ghi nhận, không tính NT.</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>HD-MTX-26-RENO-WH-FULL</v>
+        <v>HD-MTX-26-RENO-WH-BASIC</v>
       </c>
       <c r="B27" t="str">
-        <v>MTX#26 NGUYEN_CAN FULL</v>
+        <v>MTX#26 NGUYEN_CAN NT cơ bản</v>
       </c>
       <c r="C27" t="str">
-        <v>26 Ma Trận Quận 3</v>
+        <v>36 Nguyễn Huệ</v>
       </c>
       <c r="D27" t="str">
-        <v>Quận 3</v>
+        <v>Quận 1</v>
       </c>
       <c r="E27" t="str">
         <v>TP. Hồ Chí Minh</v>
       </c>
       <c r="F27">
-        <v>135</v>
+        <v>82</v>
       </c>
       <c r="G27">
-        <v>22.9</v>
+        <v>10.7</v>
       </c>
       <c r="H27">
-        <v>5.9</v>
+        <v>7.7</v>
       </c>
       <c r="I27">
         <v>1</v>
       </c>
       <c r="J27">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K27" t="str">
-        <v>Lý Văn L</v>
+        <v>Kiều Thị Chi</v>
       </c>
       <c r="L27">
-        <v>266000000</v>
+        <v>235000000</v>
       </c>
       <c r="M27" t="str">
-        <v>2026-04-01</v>
+        <v>2026-08-01</v>
       </c>
       <c r="N27" t="str">
-        <v>2028-06-01</v>
+        <v>2028-08-31</v>
       </c>
       <c r="O27" t="str">
-        <v>Ma trận #26 — RENO | nguyên căn | full nội thất | TB bàn giao: Có | TB mua đ2: Có</v>
+        <v>MTX#26 NGUYEN_CAN NT cơ bản — RENO. NT khai thác = TB mua mới đợt 2 (BASIC). Đồ chủ bàn giao (nếu có) chỉ ghi nhận, không tính NT.</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>HD-MTX-27-RENO-WH-FULL</v>
+        <v>HD-MTX-27-RENO-WH-BASIC</v>
       </c>
       <c r="B28" t="str">
-        <v>MTX#27 NGUYEN_CAN FULL</v>
+        <v>MTX#27 NGUYEN_CAN NT cơ bản</v>
       </c>
       <c r="C28" t="str">
-        <v>27 Ma Trận Bình Thạnh</v>
+        <v>37 Lý Chính Thắng</v>
       </c>
       <c r="D28" t="str">
-        <v>Bình Thạnh</v>
+        <v>Quận 3</v>
       </c>
       <c r="E28" t="str">
         <v>TP. Hồ Chí Minh</v>
       </c>
       <c r="F28">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="G28">
-        <v>17.3</v>
+        <v>11.7</v>
       </c>
       <c r="H28">
-        <v>6.3</v>
+        <v>8.3</v>
       </c>
       <c r="I28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J28">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K28" t="str">
-        <v>Mai Thị M</v>
+        <v>Ông Văn Đạt</v>
       </c>
       <c r="L28">
-        <v>224000000</v>
+        <v>237500000</v>
       </c>
       <c r="M28" t="str">
-        <v>2026-05-01</v>
+        <v>2026-09-01</v>
       </c>
       <c r="N28" t="str">
-        <v>2028-08-01</v>
+        <v>2028-09-30</v>
       </c>
       <c r="O28" t="str">
-        <v>Ma trận #27 — RENO | nguyên căn | full nội thất | TB bàn giao: Có | TB mua đ2: Có</v>
+        <v>MTX#27 NGUYEN_CAN NT cơ bản — RENO. NT khai thác = TB mua mới đợt 2 (BASIC). Đồ chủ bàn giao (nếu có) chỉ ghi nhận, không tính NT.</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>HD-MTX-28-RENO-WH-HO-NOBUY</v>
+        <v>HD-MTX-28-RENO-WH-NONE</v>
       </c>
       <c r="B29" t="str">
-        <v>MTX#28 NGUYEN_CAN NONE</v>
+        <v>MTX#28 NGUYEN_CAN không NT</v>
       </c>
       <c r="C29" t="str">
-        <v>28 Ma Trận Gò Vấp</v>
+        <v>38 Nơ Trang Long</v>
       </c>
       <c r="D29" t="str">
-        <v>Gò Vấp</v>
+        <v>Bình Thạnh</v>
       </c>
       <c r="E29" t="str">
         <v>TP. Hồ Chí Minh</v>
       </c>
       <c r="F29">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="G29">
-        <v>14.9</v>
+        <v>11.1</v>
       </c>
       <c r="H29">
-        <v>6.7</v>
+        <v>7.9</v>
       </c>
       <c r="I29">
         <v>1</v>
       </c>
       <c r="J29">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K29" t="str">
-        <v>Phan Văn N</v>
+        <v>Thái Thị Hạnh</v>
       </c>
       <c r="L29">
-        <v>257000000</v>
+        <v>230000000</v>
       </c>
       <c r="M29" t="str">
-        <v>2026-06-01</v>
+        <v>2026-10-01</v>
       </c>
       <c r="N29" t="str">
-        <v>2028-10-01</v>
+        <v>2028-10-31</v>
       </c>
       <c r="O29" t="str">
-        <v>Ma trận #28 — RENO | nguyên căn | không nội thất | TB bàn giao: Có | TB mua đ2: Không</v>
+        <v>MTX#28 NGUYEN_CAN không NT — RENO. NT khai thác = TB mua mới đợt 2 (NONE). Đồ chủ bàn giao (nếu có) chỉ ghi nhận, không tính NT.</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>HD-MTX-29-RENO-WH-HO-NOBUY</v>
+        <v>HD-MTX-29-RENO-WH-NONE</v>
       </c>
       <c r="B30" t="str">
-        <v>MTX#29 NGUYEN_CAN NONE</v>
+        <v>MTX#29 NGUYEN_CAN không NT</v>
       </c>
       <c r="C30" t="str">
-        <v>29 Ma Trận Phú Nhuận</v>
+        <v>39 Quang Trung</v>
       </c>
       <c r="D30" t="str">
-        <v>Phú Nhuận</v>
+        <v>Gò Vấp</v>
       </c>
       <c r="E30" t="str">
         <v>TP. Hồ Chí Minh</v>
       </c>
       <c r="F30">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="G30">
-        <v>16.8</v>
+        <v>12</v>
       </c>
       <c r="H30">
-        <v>7.1</v>
+        <v>8.6</v>
       </c>
       <c r="I30">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J30">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K30" t="str">
-        <v>Trịnh Thị O</v>
+        <v>Từ Văn Khải</v>
       </c>
       <c r="L30">
-        <v>290000000</v>
+        <v>232500000</v>
       </c>
       <c r="M30" t="str">
-        <v>2026-07-01</v>
+        <v>2026-11-01</v>
       </c>
       <c r="N30" t="str">
-        <v>2028-12-01</v>
+        <v>2028-11-30</v>
       </c>
       <c r="O30" t="str">
-        <v>Ma trận #29 — RENO | nguyên căn | không nội thất | TB bàn giao: Có | TB mua đ2: Không</v>
+        <v>MTX#29 NGUYEN_CAN không NT — RENO. NT khai thác = TB mua mới đợt 2 (NONE). Đồ chủ bàn giao (nếu có) chỉ ghi nhận, không tính NT.</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>HD-MTX-30-RENO-WH-HO-BUY</v>
+        <v>HD-MTX-30-RENO-WH-NONE</v>
       </c>
       <c r="B31" t="str">
-        <v>MTX#30 NGUYEN_CAN BASIC</v>
+        <v>MTX#30 NGUYEN_CAN không NT</v>
       </c>
       <c r="C31" t="str">
-        <v>30 Ma Trận Cầu Giấy</v>
+        <v>40 Phan Xích Long</v>
       </c>
       <c r="D31" t="str">
-        <v>Cầu Giấy</v>
+        <v>Phú Nhuận</v>
       </c>
       <c r="E31" t="str">
-        <v>Hà Nội</v>
+        <v>TP. Hồ Chí Minh</v>
       </c>
       <c r="F31">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="G31">
-        <v>16.9</v>
+        <v>10.5</v>
       </c>
       <c r="H31">
-        <v>5.5</v>
+        <v>7.5</v>
       </c>
       <c r="I31">
         <v>1</v>
@@ -3553,30 +3793,30 @@
         <v>2</v>
       </c>
       <c r="K31" t="str">
-        <v>Huỳnh Văn P</v>
+        <v>Lâm Thị Lan</v>
       </c>
       <c r="L31">
-        <v>248000000</v>
+        <v>235000000</v>
       </c>
       <c r="M31" t="str">
-        <v>2026-08-01</v>
+        <v>2026-12-01</v>
       </c>
       <c r="N31" t="str">
-        <v>2029-02-01</v>
+        <v>2028-12-31</v>
       </c>
       <c r="O31" t="str">
-        <v>Ma trận #30 — RENO | nguyên căn | nội thất cơ bản | TB bàn giao: Có | TB mua đ2: Có</v>
+        <v>MTX#30 NGUYEN_CAN không NT — RENO. NT khai thác = TB mua mới đợt 2 (NONE). Đồ chủ bàn giao (nếu có) chỉ ghi nhận, không tính NT.</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>HD-MTX-31-RENO-WH-HO-BUY</v>
+        <v>HD-MTX-31-RENO-WH-NONE</v>
       </c>
       <c r="B32" t="str">
-        <v>MTX#31 NGUYEN_CAN BASIC</v>
+        <v>MTX#31 NGUYEN_CAN không NT</v>
       </c>
       <c r="C32" t="str">
-        <v>31 Ma Trận Quận 1</v>
+        <v>41 Nguyễn Huệ</v>
       </c>
       <c r="D32" t="str">
         <v>Quận 1</v>
@@ -3585,45 +3825,45 @@
         <v>TP. Hồ Chí Minh</v>
       </c>
       <c r="F32">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="G32">
-        <v>19</v>
+        <v>11.5</v>
       </c>
       <c r="H32">
-        <v>5.9</v>
+        <v>8.2</v>
       </c>
       <c r="I32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J32">
         <v>3</v>
       </c>
       <c r="K32" t="str">
-        <v>Nguyễn Văn A</v>
+        <v>Quách Văn Minh</v>
       </c>
       <c r="L32">
-        <v>281000000</v>
+        <v>237500000</v>
       </c>
       <c r="M32" t="str">
-        <v>2026-09-01</v>
+        <v>2026-03-01</v>
       </c>
       <c r="N32" t="str">
-        <v>2029-04-01</v>
+        <v>2028-03-31</v>
       </c>
       <c r="O32" t="str">
-        <v>Ma trận #31 — RENO | nguyên căn | nội thất cơ bản | TB bàn giao: Có | TB mua đ2: Có</v>
+        <v>MTX#31 NGUYEN_CAN không NT — RENO. NT khai thác = TB mua mới đợt 2 (NONE). Đồ chủ bàn giao (nếu có) chỉ ghi nhận, không tính NT.</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>HD-MTX-32-RENO-RM-NONE</v>
+        <v>HD-MTX-32-RENO-WH-NONE</v>
       </c>
       <c r="B33" t="str">
-        <v>MTX#32 THEO_PHONG NONE</v>
+        <v>MTX#32 NGUYEN_CAN không NT</v>
       </c>
       <c r="C33" t="str">
-        <v>32 Ma Trận Quận 3</v>
+        <v>42 Cách Mạng Tháng 8</v>
       </c>
       <c r="D33" t="str">
         <v>Quận 3</v>
@@ -3632,45 +3872,45 @@
         <v>TP. Hồ Chí Minh</v>
       </c>
       <c r="F33">
-        <v>112</v>
+        <v>85</v>
       </c>
       <c r="G33">
-        <v>17.8</v>
+        <v>10.9</v>
       </c>
       <c r="H33">
-        <v>6.3</v>
+        <v>7.8</v>
       </c>
       <c r="I33">
+        <v>1</v>
+      </c>
+      <c r="J33">
         <v>2</v>
       </c>
-      <c r="J33">
-        <v>4</v>
-      </c>
       <c r="K33" t="str">
-        <v>Trần Thị B</v>
+        <v>Hà Thị Nga</v>
       </c>
       <c r="L33">
-        <v>226000000</v>
+        <v>240000000</v>
       </c>
       <c r="M33" t="str">
-        <v>2026-10-01</v>
+        <v>2026-04-01</v>
       </c>
       <c r="N33" t="str">
-        <v>2029-06-01</v>
+        <v>2028-04-30</v>
       </c>
       <c r="O33" t="str">
-        <v>Ma trận #32 — RENO | theo phòng (3p) | không nội thất | TB bàn giao: Không | TB mua đ2: Không</v>
+        <v>MTX#32 NGUYEN_CAN không NT — RENO. NT khai thác = TB mua mới đợt 2 (NONE). Đồ chủ bàn giao (nếu có) chỉ ghi nhận, không tính NT.</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>HD-MTX-33-RENO-RM-NONE</v>
+        <v>HD-MTX-33-RENO-WH-NONE</v>
       </c>
       <c r="B34" t="str">
-        <v>MTX#33 THEO_PHONG NONE</v>
+        <v>MTX#33 NGUYEN_CAN không NT</v>
       </c>
       <c r="C34" t="str">
-        <v>33 Ma Trận Bình Thạnh</v>
+        <v>43 Phan Văn Trị</v>
       </c>
       <c r="D34" t="str">
         <v>Bình Thạnh</v>
@@ -3679,45 +3919,45 @@
         <v>TP. Hồ Chí Minh</v>
       </c>
       <c r="F34">
-        <v>115</v>
+        <v>100</v>
       </c>
       <c r="G34">
-        <v>17.2</v>
+        <v>11.8</v>
       </c>
       <c r="H34">
-        <v>6.7</v>
+        <v>8.5</v>
       </c>
       <c r="I34">
+        <v>1</v>
+      </c>
+      <c r="J34">
         <v>3</v>
       </c>
-      <c r="J34">
-        <v>4</v>
-      </c>
       <c r="K34" t="str">
-        <v>Lê Văn C</v>
+        <v>Trương Văn Phong</v>
       </c>
       <c r="L34">
-        <v>231000000</v>
+        <v>242500000</v>
       </c>
       <c r="M34" t="str">
-        <v>2026-03-01</v>
+        <v>2026-05-01</v>
       </c>
       <c r="N34" t="str">
-        <v>2028-12-01</v>
+        <v>2028-05-31</v>
       </c>
       <c r="O34" t="str">
-        <v>Ma trận #33 — RENO | theo phòng (3p) | không nội thất | TB bàn giao: Không | TB mua đ2: Không</v>
+        <v>MTX#33 NGUYEN_CAN không NT — RENO. NT khai thác = TB mua mới đợt 2 (NONE). Đồ chủ bàn giao (nếu có) chỉ ghi nhận, không tính NT.</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>HD-MTX-34-RENO-RM-NONE</v>
+        <v>HD-MTX-34-RENO-WH-NONE</v>
       </c>
       <c r="B35" t="str">
-        <v>MTX#34 THEO_PHONG NONE</v>
+        <v>MTX#34 NGUYEN_CAN không NT</v>
       </c>
       <c r="C35" t="str">
-        <v>34 Ma Trận Gò Vấp</v>
+        <v>44 Phạm Văn Chiêu</v>
       </c>
       <c r="D35" t="str">
         <v>Gò Vấp</v>
@@ -3726,45 +3966,45 @@
         <v>TP. Hồ Chí Minh</v>
       </c>
       <c r="F35">
-        <v>118</v>
+        <v>91</v>
       </c>
       <c r="G35">
-        <v>16.6</v>
+        <v>11.3</v>
       </c>
       <c r="H35">
-        <v>7.1</v>
+        <v>8.1</v>
       </c>
       <c r="I35">
+        <v>1</v>
+      </c>
+      <c r="J35">
         <v>2</v>
       </c>
-      <c r="J35">
-        <v>4</v>
-      </c>
       <c r="K35" t="str">
-        <v>Phạm Thị D</v>
+        <v>Đoàn Thị Quế</v>
       </c>
       <c r="L35">
-        <v>236000000</v>
+        <v>245000000</v>
       </c>
       <c r="M35" t="str">
-        <v>2026-04-01</v>
+        <v>2026-06-01</v>
       </c>
       <c r="N35" t="str">
-        <v>2029-02-01</v>
+        <v>2028-06-30</v>
       </c>
       <c r="O35" t="str">
-        <v>Ma trận #34 — RENO | theo phòng (3p) | không nội thất | TB bàn giao: Không | TB mua đ2: Không</v>
+        <v>MTX#34 NGUYEN_CAN không NT — RENO. NT khai thác = TB mua mới đợt 2 (NONE). Đồ chủ bàn giao (nếu có) chỉ ghi nhận, không tính NT.</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>HD-MTX-35-RENO-RM-NONE</v>
+        <v>HD-MTX-35-RENO-WH-NONE</v>
       </c>
       <c r="B36" t="str">
-        <v>MTX#35 THEO_PHONG NONE</v>
+        <v>MTX#35 NGUYEN_CAN không NT</v>
       </c>
       <c r="C36" t="str">
-        <v>35 Ma Trận Phú Nhuận</v>
+        <v>45 Nguyễn Văn Trỗi</v>
       </c>
       <c r="D36" t="str">
         <v>Phú Nhuận</v>
@@ -3773,410 +4013,410 @@
         <v>TP. Hồ Chí Minh</v>
       </c>
       <c r="F36">
-        <v>106</v>
+        <v>91</v>
       </c>
       <c r="G36">
-        <v>19.3</v>
+        <v>11.3</v>
       </c>
       <c r="H36">
-        <v>5.5</v>
+        <v>8.1</v>
       </c>
       <c r="I36">
+        <v>1</v>
+      </c>
+      <c r="J36">
         <v>3</v>
       </c>
-      <c r="J36">
-        <v>4</v>
-      </c>
       <c r="K36" t="str">
-        <v>Hoàng Văn E</v>
+        <v>La Văn Sơn</v>
       </c>
       <c r="L36">
-        <v>241000000</v>
+        <v>247500000</v>
       </c>
       <c r="M36" t="str">
-        <v>2026-05-01</v>
+        <v>2026-07-01</v>
       </c>
       <c r="N36" t="str">
-        <v>2029-04-01</v>
+        <v>2028-07-31</v>
       </c>
       <c r="O36" t="str">
-        <v>Ma trận #35 — RENO | theo phòng (3p) | không nội thất | TB bàn giao: Không | TB mua đ2: Không</v>
+        <v>MTX#35 NGUYEN_CAN không NT — RENO. NT khai thác = TB mua mới đợt 2 (NONE). Đồ chủ bàn giao (nếu có) chỉ ghi nhận, không tính NT.</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>HD-MTX-36-RENO-RM-BASIC-HO</v>
+        <v>HD-MTX-36-RENO-WH-NONE</v>
       </c>
       <c r="B37" t="str">
-        <v>MTX#36 THEO_PHONG BASIC</v>
+        <v>MTX#36 NGUYEN_CAN không NT</v>
       </c>
       <c r="C37" t="str">
-        <v>36 Ma Trận Cầu Giấy</v>
+        <v>46 Nguyễn Huệ</v>
       </c>
       <c r="D37" t="str">
-        <v>Cầu Giấy</v>
+        <v>Quận 1</v>
       </c>
       <c r="E37" t="str">
-        <v>Hà Nội</v>
+        <v>TP. Hồ Chí Minh</v>
       </c>
       <c r="F37">
-        <v>109</v>
+        <v>82</v>
       </c>
       <c r="G37">
-        <v>18.5</v>
+        <v>10.7</v>
       </c>
       <c r="H37">
-        <v>5.9</v>
+        <v>7.7</v>
       </c>
       <c r="I37">
+        <v>1</v>
+      </c>
+      <c r="J37">
         <v>2</v>
       </c>
-      <c r="J37">
-        <v>4</v>
-      </c>
       <c r="K37" t="str">
-        <v>Võ Thị F</v>
+        <v>Ung Thị Trang</v>
       </c>
       <c r="L37">
-        <v>216000000</v>
+        <v>250000000</v>
       </c>
       <c r="M37" t="str">
-        <v>2026-06-01</v>
+        <v>2026-08-01</v>
       </c>
       <c r="N37" t="str">
-        <v>2028-06-01</v>
+        <v>2028-08-31</v>
       </c>
       <c r="O37" t="str">
-        <v>Ma trận #36 — RENO | theo phòng (3p) | nội thất cơ bản | TB bàn giao: Có | TB mua đ2: Không</v>
+        <v>MTX#36 NGUYEN_CAN không NT — RENO. NT khai thác = TB mua mới đợt 2 (NONE). Đồ chủ bàn giao (nếu có) chỉ ghi nhận, không tính NT.</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>HD-MTX-37-RENO-RM-BASIC-HO</v>
+        <v>HD-MTX-37-RENO-WH-NONE</v>
       </c>
       <c r="B38" t="str">
-        <v>MTX#37 THEO_PHONG BASIC</v>
+        <v>MTX#37 NGUYEN_CAN không NT</v>
       </c>
       <c r="C38" t="str">
-        <v>37 Ma Trận Quận 1</v>
+        <v>47 Võ Văn Tần</v>
       </c>
       <c r="D38" t="str">
-        <v>Quận 1</v>
+        <v>Quận 3</v>
       </c>
       <c r="E38" t="str">
         <v>TP. Hồ Chí Minh</v>
       </c>
       <c r="F38">
-        <v>112</v>
+        <v>97</v>
       </c>
       <c r="G38">
-        <v>17.8</v>
+        <v>11.7</v>
       </c>
       <c r="H38">
-        <v>6.3</v>
+        <v>8.3</v>
       </c>
       <c r="I38">
+        <v>1</v>
+      </c>
+      <c r="J38">
         <v>3</v>
       </c>
-      <c r="J38">
-        <v>4</v>
-      </c>
       <c r="K38" t="str">
-        <v>Đặng Văn G</v>
+        <v>Vi Văn Út</v>
       </c>
       <c r="L38">
-        <v>221000000</v>
+        <v>252500000</v>
       </c>
       <c r="M38" t="str">
-        <v>2026-07-01</v>
+        <v>2026-09-01</v>
       </c>
       <c r="N38" t="str">
-        <v>2028-08-01</v>
+        <v>2028-09-30</v>
       </c>
       <c r="O38" t="str">
-        <v>Ma trận #37 — RENO | theo phòng (3p) | nội thất cơ bản | TB bàn giao: Có | TB mua đ2: Không</v>
+        <v>MTX#37 NGUYEN_CAN không NT — RENO. NT khai thác = TB mua mới đợt 2 (NONE). Đồ chủ bàn giao (nếu có) chỉ ghi nhận, không tính NT.</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>HD-MTX-38-RENO-RM-BASIC-HO</v>
+        <v>HD-MTX-38-RENO-WH-NONE</v>
       </c>
       <c r="B39" t="str">
-        <v>MTX#38 THEO_PHONG BASIC</v>
+        <v>MTX#38 NGUYEN_CAN không NT</v>
       </c>
       <c r="C39" t="str">
-        <v>38 Ma Trận Quận 3</v>
+        <v>48 Xô Viết Nghệ Tĩnh</v>
       </c>
       <c r="D39" t="str">
-        <v>Quận 3</v>
+        <v>Bình Thạnh</v>
       </c>
       <c r="E39" t="str">
         <v>TP. Hồ Chí Minh</v>
       </c>
       <c r="F39">
-        <v>115</v>
+        <v>88</v>
       </c>
       <c r="G39">
-        <v>17.2</v>
+        <v>11.1</v>
       </c>
       <c r="H39">
-        <v>6.7</v>
+        <v>7.9</v>
       </c>
       <c r="I39">
+        <v>1</v>
+      </c>
+      <c r="J39">
         <v>2</v>
       </c>
-      <c r="J39">
-        <v>4</v>
-      </c>
       <c r="K39" t="str">
-        <v>Bùi Thị H</v>
+        <v>Mạc Thị Vân</v>
       </c>
       <c r="L39">
-        <v>226000000</v>
+        <v>255000000</v>
       </c>
       <c r="M39" t="str">
-        <v>2026-08-01</v>
+        <v>2026-10-01</v>
       </c>
       <c r="N39" t="str">
-        <v>2028-10-01</v>
+        <v>2028-10-31</v>
       </c>
       <c r="O39" t="str">
-        <v>Ma trận #38 — RENO | theo phòng (3p) | nội thất cơ bản | TB bàn giao: Có | TB mua đ2: Không</v>
+        <v>MTX#38 NGUYEN_CAN không NT — RENO. NT khai thác = TB mua mới đợt 2 (NONE). Đồ chủ bàn giao (nếu có) chỉ ghi nhận, không tính NT.</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>HD-MTX-39-RENO-RM-BASIC-HO</v>
+        <v>HD-MTX-39-RENO-WH-NONE</v>
       </c>
       <c r="B40" t="str">
-        <v>MTX#39 THEO_PHONG BASIC</v>
+        <v>MTX#39 NGUYEN_CAN không NT</v>
       </c>
       <c r="C40" t="str">
-        <v>39 Ma Trận Bình Thạnh</v>
+        <v>49 Nguyễn Oanh</v>
       </c>
       <c r="D40" t="str">
-        <v>Bình Thạnh</v>
+        <v>Gò Vấp</v>
       </c>
       <c r="E40" t="str">
         <v>TP. Hồ Chí Minh</v>
       </c>
       <c r="F40">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="G40">
-        <v>16.6</v>
+        <v>12</v>
       </c>
       <c r="H40">
-        <v>7.1</v>
+        <v>8.6</v>
       </c>
       <c r="I40">
+        <v>1</v>
+      </c>
+      <c r="J40">
         <v>3</v>
       </c>
-      <c r="J40">
-        <v>4</v>
-      </c>
       <c r="K40" t="str">
-        <v>Ngô Văn I</v>
+        <v>Chu Văn Xuân</v>
       </c>
       <c r="L40">
-        <v>231000000</v>
+        <v>257500000</v>
       </c>
       <c r="M40" t="str">
-        <v>2026-09-01</v>
+        <v>2026-11-01</v>
       </c>
       <c r="N40" t="str">
-        <v>2028-12-01</v>
+        <v>2028-11-30</v>
       </c>
       <c r="O40" t="str">
-        <v>Ma trận #39 — RENO | theo phòng (3p) | nội thất cơ bản | TB bàn giao: Có | TB mua đ2: Không</v>
+        <v>MTX#39 NGUYEN_CAN không NT — RENO. NT khai thác = TB mua mới đợt 2 (NONE). Đồ chủ bàn giao (nếu có) chỉ ghi nhận, không tính NT.</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>HD-MTX-40-RENO-RM-BASIC-BUY</v>
+        <v>HD-MTX-40-RENO-WH-NONE</v>
       </c>
       <c r="B41" t="str">
-        <v>MTX#40 THEO_PHONG BASIC</v>
+        <v>MTX#40 NGUYEN_CAN không NT</v>
       </c>
       <c r="C41" t="str">
-        <v>40 Ma Trận Gò Vấp</v>
+        <v>50 Trường Sa</v>
       </c>
       <c r="D41" t="str">
-        <v>Gò Vấp</v>
+        <v>Phú Nhuận</v>
       </c>
       <c r="E41" t="str">
         <v>TP. Hồ Chí Minh</v>
       </c>
       <c r="F41">
-        <v>106</v>
+        <v>79</v>
       </c>
       <c r="G41">
-        <v>19.3</v>
+        <v>10.5</v>
       </c>
       <c r="H41">
-        <v>5.5</v>
+        <v>7.5</v>
       </c>
       <c r="I41">
+        <v>1</v>
+      </c>
+      <c r="J41">
         <v>2</v>
       </c>
-      <c r="J41">
-        <v>4</v>
-      </c>
       <c r="K41" t="str">
-        <v>Dương Thị K</v>
+        <v>Triệu Thị Yến</v>
       </c>
       <c r="L41">
-        <v>236000000</v>
+        <v>260000000</v>
       </c>
       <c r="M41" t="str">
-        <v>2026-10-01</v>
+        <v>2026-12-01</v>
       </c>
       <c r="N41" t="str">
-        <v>2029-02-01</v>
+        <v>2028-12-31</v>
       </c>
       <c r="O41" t="str">
-        <v>Ma trận #40 — RENO | theo phòng (3p) | nội thất cơ bản | TB bàn giao: Không | TB mua đ2: Có</v>
+        <v>MTX#40 NGUYEN_CAN không NT — RENO. NT khai thác = TB mua mới đợt 2 (NONE). Đồ chủ bàn giao (nếu có) chỉ ghi nhận, không tính NT.</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>HD-MTX-41-RENO-RM-BASIC-BUY</v>
+        <v>HD-MTX-41-RENO-RM-FULL</v>
       </c>
       <c r="B42" t="str">
-        <v>MTX#41 THEO_PHONG BASIC</v>
+        <v>MTX#41 THEO_PHONG full NT</v>
       </c>
       <c r="C42" t="str">
-        <v>41 Ma Trận Phú Nhuận</v>
+        <v>51 Nguyễn Huệ</v>
       </c>
       <c r="D42" t="str">
-        <v>Phú Nhuận</v>
+        <v>Quận 1</v>
       </c>
       <c r="E42" t="str">
         <v>TP. Hồ Chí Minh</v>
       </c>
       <c r="F42">
-        <v>121</v>
+        <v>90</v>
       </c>
       <c r="G42">
-        <v>20.5</v>
+        <v>11.2</v>
       </c>
       <c r="H42">
-        <v>5.9</v>
+        <v>8</v>
       </c>
       <c r="I42">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J42">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K42" t="str">
-        <v>Lý Văn L</v>
+        <v>Ông Thị Hòa</v>
       </c>
       <c r="L42">
-        <v>253000000</v>
+        <v>307500000</v>
       </c>
       <c r="M42" t="str">
         <v>2026-03-01</v>
       </c>
       <c r="N42" t="str">
-        <v>2028-08-01</v>
+        <v>2028-03-31</v>
       </c>
       <c r="O42" t="str">
-        <v>Ma trận #41 — RENO | theo phòng (4p) | nội thất cơ bản | TB bàn giao: Không | TB mua đ2: Có</v>
+        <v>MTX#41 THEO_PHONG full NT — RENO. NT khai thác = TB mua mới đợt 2 (FULL). Đồ chủ bàn giao (nếu có) chỉ ghi nhận, không tính NT.</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>HD-MTX-42-RENO-RM-BASIC-BUY</v>
+        <v>HD-MTX-42-RENO-RM-FULL</v>
       </c>
       <c r="B43" t="str">
-        <v>MTX#42 THEO_PHONG BASIC</v>
+        <v>MTX#42 THEO_PHONG full NT</v>
       </c>
       <c r="C43" t="str">
-        <v>42 Ma Trận Cầu Giấy</v>
+        <v>52 Nam Kỳ Khởi Nghĩa</v>
       </c>
       <c r="D43" t="str">
-        <v>Cầu Giấy</v>
+        <v>Quận 3</v>
       </c>
       <c r="E43" t="str">
-        <v>Hà Nội</v>
+        <v>TP. Hồ Chí Minh</v>
       </c>
       <c r="F43">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="G43">
-        <v>17.8</v>
+        <v>12.6</v>
       </c>
       <c r="H43">
-        <v>6.3</v>
+        <v>9</v>
       </c>
       <c r="I43">
         <v>2</v>
       </c>
       <c r="J43">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K43" t="str">
-        <v>Mai Thị M</v>
+        <v>Bạch Văn Khoa</v>
       </c>
       <c r="L43">
-        <v>216000000</v>
+        <v>310000000</v>
       </c>
       <c r="M43" t="str">
         <v>2026-04-01</v>
       </c>
       <c r="N43" t="str">
-        <v>2028-10-01</v>
+        <v>2028-04-30</v>
       </c>
       <c r="O43" t="str">
-        <v>Ma trận #42 — RENO | theo phòng (3p) | nội thất cơ bản | TB bàn giao: Không | TB mua đ2: Có</v>
+        <v>MTX#42 THEO_PHONG full NT — RENO. NT khai thác = TB mua mới đợt 2 (FULL). Đồ chủ bàn giao (nếu có) chỉ ghi nhận, không tính NT.</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>HD-MTX-43-RENO-RM-BASIC-BUY</v>
+        <v>HD-MTX-43-RENO-RM-FULL</v>
       </c>
       <c r="B44" t="str">
-        <v>MTX#43 THEO_PHONG BASIC</v>
+        <v>MTX#43 THEO_PHONG full NT</v>
       </c>
       <c r="C44" t="str">
-        <v>43 Ma Trận Quận 1</v>
+        <v>53 Điện Biên Phủ</v>
       </c>
       <c r="D44" t="str">
-        <v>Quận 1</v>
+        <v>Bình Thạnh</v>
       </c>
       <c r="E44" t="str">
         <v>TP. Hồ Chí Minh</v>
       </c>
       <c r="F44">
-        <v>127</v>
+        <v>138</v>
       </c>
       <c r="G44">
-        <v>19</v>
+        <v>13.9</v>
       </c>
       <c r="H44">
-        <v>6.7</v>
+        <v>9.9</v>
       </c>
       <c r="I44">
         <v>3</v>
       </c>
       <c r="J44">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K44" t="str">
-        <v>Phan Văn N</v>
+        <v>Nhan Thị Linh</v>
       </c>
       <c r="L44">
-        <v>233000000</v>
+        <v>312500000</v>
       </c>
       <c r="M44" t="str">
         <v>2026-05-01</v>
       </c>
       <c r="N44" t="str">
-        <v>2028-12-01</v>
+        <v>2028-05-31</v>
       </c>
       <c r="O44" t="str">
-        <v>Ma trận #43 — RENO | theo phòng (4p) | nội thất cơ bản | TB bàn giao: Không | TB mua đ2: Có</v>
+        <v>MTX#43 THEO_PHONG full NT — RENO. NT khai thác = TB mua mới đợt 2 (FULL). Đồ chủ bàn giao (nếu có) chỉ ghi nhận, không tính NT.</v>
       </c>
     </row>
     <row r="45">
@@ -4184,119 +4424,119 @@
         <v>HD-MTX-44-RENO-RM-FULL</v>
       </c>
       <c r="B45" t="str">
-        <v>MTX#44 THEO_PHONG FULL</v>
+        <v>MTX#44 THEO_PHONG full NT</v>
       </c>
       <c r="C45" t="str">
-        <v>44 Ma Trận Quận 3</v>
+        <v>54 Lê Đức Thọ</v>
       </c>
       <c r="D45" t="str">
-        <v>Quận 3</v>
+        <v>Gò Vấp</v>
       </c>
       <c r="E45" t="str">
         <v>TP. Hồ Chí Minh</v>
       </c>
       <c r="F45">
-        <v>130</v>
+        <v>90</v>
       </c>
       <c r="G45">
-        <v>18.3</v>
+        <v>11.2</v>
       </c>
       <c r="H45">
-        <v>7.1</v>
+        <v>8</v>
       </c>
       <c r="I45">
         <v>2</v>
       </c>
       <c r="J45">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K45" t="str">
-        <v>Trịnh Thị O</v>
+        <v>Tống Văn Mạnh</v>
       </c>
       <c r="L45">
-        <v>238000000</v>
+        <v>315000000</v>
       </c>
       <c r="M45" t="str">
         <v>2026-06-01</v>
       </c>
       <c r="N45" t="str">
-        <v>2029-02-01</v>
+        <v>2028-06-30</v>
       </c>
       <c r="O45" t="str">
-        <v>Ma trận #44 — RENO | theo phòng (4p) | full nội thất | TB bàn giao: Có | TB mua đ2: Có</v>
+        <v>MTX#44 THEO_PHONG full NT — RENO. NT khai thác = TB mua mới đợt 2 (FULL). Đồ chủ bàn giao (nếu có) chỉ ghi nhận, không tính NT.</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>HD-MTX-45-RENO-RM-FULL</v>
+        <v>HD-MTX-45-RENO-RM-BASIC</v>
       </c>
       <c r="B46" t="str">
-        <v>MTX#45 THEO_PHONG FULL</v>
+        <v>MTX#45 THEO_PHONG NT cơ bản</v>
       </c>
       <c r="C46" t="str">
-        <v>45 Ma Trận Bình Thạnh</v>
+        <v>55 Hoàng Văn Thụ</v>
       </c>
       <c r="D46" t="str">
-        <v>Bình Thạnh</v>
+        <v>Phú Nhuận</v>
       </c>
       <c r="E46" t="str">
         <v>TP. Hồ Chí Minh</v>
       </c>
       <c r="F46">
-        <v>118</v>
+        <v>90</v>
       </c>
       <c r="G46">
-        <v>21.5</v>
+        <v>11.2</v>
       </c>
       <c r="H46">
-        <v>5.5</v>
+        <v>8</v>
       </c>
       <c r="I46">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J46">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K46" t="str">
-        <v>Huỳnh Văn P</v>
+        <v>Lục Thị Nhung</v>
       </c>
       <c r="L46">
-        <v>243000000</v>
+        <v>302500000</v>
       </c>
       <c r="M46" t="str">
         <v>2026-07-01</v>
       </c>
       <c r="N46" t="str">
-        <v>2029-04-01</v>
+        <v>2028-07-31</v>
       </c>
       <c r="O46" t="str">
-        <v>Ma trận #45 — RENO | theo phòng (4p) | full nội thất | TB bàn giao: Có | TB mua đ2: Có</v>
+        <v>MTX#45 THEO_PHONG NT cơ bản — RENO. NT khai thác = TB mua mới đợt 2 (BASIC). Đồ chủ bàn giao (nếu có) chỉ ghi nhận, không tính NT.</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>HD-MTX-46-RENO-RM-FULL</v>
+        <v>HD-MTX-46-RENO-RM-BASIC</v>
       </c>
       <c r="B47" t="str">
-        <v>MTX#46 THEO_PHONG FULL</v>
+        <v>MTX#46 THEO_PHONG NT cơ bản</v>
       </c>
       <c r="C47" t="str">
-        <v>46 Ma Trận Gò Vấp</v>
+        <v>56 Nguyễn Huệ</v>
       </c>
       <c r="D47" t="str">
-        <v>Gò Vấp</v>
+        <v>Quận 1</v>
       </c>
       <c r="E47" t="str">
         <v>TP. Hồ Chí Minh</v>
       </c>
       <c r="F47">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="G47">
-        <v>20.5</v>
+        <v>12.6</v>
       </c>
       <c r="H47">
-        <v>5.9</v>
+        <v>9</v>
       </c>
       <c r="I47">
         <v>2</v>
@@ -4305,207 +4545,207 @@
         <v>5</v>
       </c>
       <c r="K47" t="str">
-        <v>Nguyễn Văn A</v>
+        <v>Nghiêm Văn Phúc</v>
       </c>
       <c r="L47">
-        <v>248000000</v>
+        <v>305000000</v>
       </c>
       <c r="M47" t="str">
         <v>2026-08-01</v>
       </c>
       <c r="N47" t="str">
-        <v>2029-06-01</v>
+        <v>2028-08-31</v>
       </c>
       <c r="O47" t="str">
-        <v>Ma trận #46 — RENO | theo phòng (4p) | full nội thất | TB bàn giao: Có | TB mua đ2: Có</v>
+        <v>MTX#46 THEO_PHONG NT cơ bản — RENO. NT khai thác = TB mua mới đợt 2 (BASIC). Đồ chủ bàn giao (nếu có) chỉ ghi nhận, không tính NT.</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>HD-MTX-47-RENO-RM-FULL</v>
+        <v>HD-MTX-47-RENO-RM-BASIC</v>
       </c>
       <c r="B48" t="str">
-        <v>MTX#47 THEO_PHONG FULL</v>
+        <v>MTX#47 THEO_PHONG NT cơ bản</v>
       </c>
       <c r="C48" t="str">
-        <v>47 Ma Trận Phú Nhuận</v>
+        <v>57 Lý Chính Thắng</v>
       </c>
       <c r="D48" t="str">
-        <v>Phú Nhuận</v>
+        <v>Quận 3</v>
       </c>
       <c r="E48" t="str">
         <v>TP. Hồ Chí Minh</v>
       </c>
       <c r="F48">
-        <v>124</v>
+        <v>138</v>
       </c>
       <c r="G48">
-        <v>19.7</v>
+        <v>13.9</v>
       </c>
       <c r="H48">
-        <v>6.3</v>
+        <v>9.9</v>
       </c>
       <c r="I48">
         <v>3</v>
       </c>
       <c r="J48">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K48" t="str">
-        <v>Trần Thị B</v>
+        <v>Âu Thị Quyên</v>
       </c>
       <c r="L48">
-        <v>253000000</v>
+        <v>307500000</v>
       </c>
       <c r="M48" t="str">
         <v>2026-09-01</v>
       </c>
       <c r="N48" t="str">
-        <v>2029-08-01</v>
+        <v>2028-09-30</v>
       </c>
       <c r="O48" t="str">
-        <v>Ma trận #47 — RENO | theo phòng (4p) | full nội thất | TB bàn giao: Có | TB mua đ2: Có</v>
+        <v>MTX#47 THEO_PHONG NT cơ bản — RENO. NT khai thác = TB mua mới đợt 2 (BASIC). Đồ chủ bàn giao (nếu có) chỉ ghi nhận, không tính NT.</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>HD-MTX-48-RENO-RM-HO-BUY</v>
+        <v>HD-MTX-48-RENO-RM-BASIC</v>
       </c>
       <c r="B49" t="str">
-        <v>MTX#48 THEO_PHONG BASIC</v>
+        <v>MTX#48 THEO_PHONG NT cơ bản</v>
       </c>
       <c r="C49" t="str">
-        <v>48 Ma Trận Cầu Giấy</v>
+        <v>58 Nơ Trang Long</v>
       </c>
       <c r="D49" t="str">
-        <v>Cầu Giấy</v>
+        <v>Bình Thạnh</v>
       </c>
       <c r="E49" t="str">
-        <v>Hà Nội</v>
+        <v>TP. Hồ Chí Minh</v>
       </c>
       <c r="F49">
-        <v>115</v>
+        <v>162</v>
       </c>
       <c r="G49">
-        <v>17.2</v>
+        <v>15.1</v>
       </c>
       <c r="H49">
-        <v>6.7</v>
+        <v>10.7</v>
       </c>
       <c r="I49">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J49">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K49" t="str">
-        <v>Lê Văn C</v>
+        <v>Giang Văn Sỹ</v>
       </c>
       <c r="L49">
-        <v>216000000</v>
+        <v>310000000</v>
       </c>
       <c r="M49" t="str">
         <v>2026-10-01</v>
       </c>
       <c r="N49" t="str">
-        <v>2028-10-01</v>
+        <v>2028-10-31</v>
       </c>
       <c r="O49" t="str">
-        <v>Ma trận #48 — RENO | theo phòng (3p) | nội thất cơ bản | TB bàn giao: Có | TB mua đ2: Có</v>
+        <v>MTX#48 THEO_PHONG NT cơ bản — RENO. NT khai thác = TB mua mới đợt 2 (BASIC). Đồ chủ bàn giao (nếu có) chỉ ghi nhận, không tính NT.</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>HD-MTX-49-RENO-RM-HO-BUY</v>
+        <v>HD-MTX-49-RENO-RM-NONE</v>
       </c>
       <c r="B50" t="str">
-        <v>MTX#49 THEO_PHONG BASIC</v>
+        <v>MTX#49 THEO_PHONG không NT</v>
       </c>
       <c r="C50" t="str">
-        <v>49 Ma Trận Quận 1</v>
+        <v>59 Quang Trung</v>
       </c>
       <c r="D50" t="str">
-        <v>Quận 1</v>
+        <v>Gò Vấp</v>
       </c>
       <c r="E50" t="str">
         <v>TP. Hồ Chí Minh</v>
       </c>
       <c r="F50">
-        <v>118</v>
+        <v>90</v>
       </c>
       <c r="G50">
-        <v>16.6</v>
+        <v>11.2</v>
       </c>
       <c r="H50">
-        <v>7.1</v>
+        <v>8</v>
       </c>
       <c r="I50">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J50">
         <v>4</v>
       </c>
       <c r="K50" t="str">
-        <v>Phạm Thị D</v>
+        <v>Thạch Thị Tuyết</v>
       </c>
       <c r="L50">
-        <v>221000000</v>
+        <v>302500000</v>
       </c>
       <c r="M50" t="str">
-        <v>2026-03-01</v>
+        <v>2026-11-01</v>
       </c>
       <c r="N50" t="str">
-        <v>2028-04-01</v>
+        <v>2028-11-30</v>
       </c>
       <c r="O50" t="str">
-        <v>Ma trận #49 — RENO | theo phòng (3p) | nội thất cơ bản | TB bàn giao: Có | TB mua đ2: Có</v>
+        <v>MTX#49 THEO_PHONG không NT — RENO. NT khai thác = TB mua mới đợt 2 (NONE). Đồ chủ bàn giao (nếu có) chỉ ghi nhận, không tính NT.</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>HD-MTX-50-RENO-RM-HO-BUY</v>
+        <v>HD-MTX-50-RENO-RM-NONE</v>
       </c>
       <c r="B51" t="str">
-        <v>MTX#50 THEO_PHONG BASIC</v>
+        <v>MTX#50 THEO_PHONG không NT</v>
       </c>
       <c r="C51" t="str">
-        <v>50 Ma Trận Quận 3</v>
+        <v>60 Phan Xích Long</v>
       </c>
       <c r="D51" t="str">
-        <v>Quận 3</v>
+        <v>Phú Nhuận</v>
       </c>
       <c r="E51" t="str">
         <v>TP. Hồ Chí Minh</v>
       </c>
       <c r="F51">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="G51">
-        <v>19.3</v>
+        <v>12.6</v>
       </c>
       <c r="H51">
-        <v>5.5</v>
+        <v>9</v>
       </c>
       <c r="I51">
         <v>2</v>
       </c>
       <c r="J51">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K51" t="str">
-        <v>Hoàng Văn E</v>
+        <v>Lữ Văn Vũ</v>
       </c>
       <c r="L51">
-        <v>226000000</v>
+        <v>305000000</v>
       </c>
       <c r="M51" t="str">
-        <v>2026-04-01</v>
+        <v>2026-12-01</v>
       </c>
       <c r="N51" t="str">
-        <v>2028-06-01</v>
+        <v>2028-12-31</v>
       </c>
       <c r="O51" t="str">
-        <v>Ma trận #50 — RENO | theo phòng (3p) | nội thất cơ bản | TB bàn giao: Có | TB mua đ2: Có</v>
+        <v>MTX#50 THEO_PHONG không NT — RENO. NT khai thác = TB mua mới đợt 2 (NONE). Đồ chủ bàn giao (nếu có) chỉ ghi nhận, không tính NT.</v>
       </c>
     </row>
   </sheetData>
@@ -4517,15 +4757,15 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G114"/>
+  <dimension ref="A1:G59"/>
   <cols>
-    <col min="1" max="1" width="28.83203125" customWidth="1"/>
-    <col min="2" max="2" width="14.83203125" customWidth="1"/>
+    <col min="1" max="1" width="20.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
     <col min="3" max="3" width="18.83203125" customWidth="1"/>
     <col min="4" max="4" width="16.83203125" customWidth="1"/>
-    <col min="5" max="5" width="16.83203125" customWidth="1"/>
-    <col min="6" max="6" width="10.83203125" customWidth="1"/>
-    <col min="7" max="7" width="18.83203125" customWidth="1"/>
+    <col min="5" max="5" width="23.83203125" customWidth="1"/>
+    <col min="6" max="6" width="16.83203125" customWidth="1"/>
+    <col min="7" max="7" width="16.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4553,13 +4793,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>HD-MTX-06-NORENO-WH-BASIC</v>
+        <v>HD-MTX-01-RENO-WH-FULL</v>
       </c>
       <c r="B2" t="str">
-        <v>Điều hòa</v>
+        <v>Quạt</v>
       </c>
       <c r="C2" t="str">
-        <v>Máy 1.5HP</v>
+        <v>Quạt trần cũ của chủ</v>
       </c>
       <c r="D2" t="str">
         <v>Phòng khách</v>
@@ -4571,18 +4811,18 @@
         <v>1</v>
       </c>
       <c r="G2" t="str">
-        <v>NT cơ bản</v>
+        <v>Đồ chủ gốc — không tính NT khai thác</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>HD-MTX-06-NORENO-WH-BASIC</v>
+        <v>HD-MTX-01-RENO-WH-FULL</v>
       </c>
       <c r="B3" t="str">
         <v>Giường</v>
       </c>
       <c r="C3" t="str">
-        <v>Giường gỗ 1m6</v>
+        <v>Giường sắt cũ</v>
       </c>
       <c r="D3" t="str">
         <v>Phòng ngủ</v>
@@ -4594,18 +4834,18 @@
         <v>1</v>
       </c>
       <c r="G3" t="str">
-        <v/>
+        <v>Đồ chủ gốc — không tính NT khai thác</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>HD-MTX-07-NORENO-WH-BASIC</v>
+        <v>HD-MTX-02-RENO-WH-FULL</v>
       </c>
       <c r="B4" t="str">
-        <v>Điều hòa</v>
+        <v>Quạt</v>
       </c>
       <c r="C4" t="str">
-        <v>Máy 1.5HP</v>
+        <v>Quạt trần cũ của chủ</v>
       </c>
       <c r="D4" t="str">
         <v>Phòng khách</v>
@@ -4617,41 +4857,41 @@
         <v>1</v>
       </c>
       <c r="G4" t="str">
-        <v>NT cơ bản</v>
+        <v>Đồ chủ gốc — không tính NT khai thác</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>HD-MTX-07-NORENO-WH-BASIC</v>
+        <v>HD-MTX-02-RENO-WH-FULL</v>
       </c>
       <c r="B5" t="str">
-        <v>Giường</v>
+        <v>Tủ lạnh</v>
       </c>
       <c r="C5" t="str">
-        <v>Giường gỗ 1m6</v>
+        <v>Tủ 150L cũ</v>
       </c>
       <c r="D5" t="str">
-        <v>Phòng ngủ</v>
+        <v>Bếp</v>
       </c>
       <c r="E5" t="str">
-        <v>GOOD</v>
+        <v>DAMAGED</v>
       </c>
       <c r="F5">
         <v>1</v>
       </c>
       <c r="G5" t="str">
-        <v/>
+        <v>Đồ chủ gốc hỏng — đợt 2 mua mới nếu có NT</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>HD-MTX-08-NORENO-WH-BASIC</v>
+        <v>HD-MTX-04-RENO-WH-FULL</v>
       </c>
       <c r="B6" t="str">
-        <v>Điều hòa</v>
+        <v>Quạt</v>
       </c>
       <c r="C6" t="str">
-        <v>Máy 1.5HP</v>
+        <v>Quạt trần cũ của chủ</v>
       </c>
       <c r="D6" t="str">
         <v>Phòng khách</v>
@@ -4663,41 +4903,41 @@
         <v>1</v>
       </c>
       <c r="G6" t="str">
-        <v>NT cơ bản</v>
+        <v>Đồ chủ gốc — không tính NT khai thác</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>HD-MTX-08-NORENO-WH-BASIC</v>
+        <v>HD-MTX-04-RENO-WH-FULL</v>
       </c>
       <c r="B7" t="str">
-        <v>Giường</v>
+        <v>Tủ lạnh</v>
       </c>
       <c r="C7" t="str">
-        <v>Giường gỗ 1m6</v>
+        <v>Tủ 150L cũ</v>
       </c>
       <c r="D7" t="str">
-        <v>Phòng ngủ</v>
+        <v>Bếp</v>
       </c>
       <c r="E7" t="str">
-        <v>GOOD</v>
+        <v>DAMAGED</v>
       </c>
       <c r="F7">
         <v>1</v>
       </c>
       <c r="G7" t="str">
-        <v/>
+        <v>Đồ chủ gốc hỏng — đợt 2 mua mới nếu có NT</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>HD-MTX-09-NORENO-WH-BASIC</v>
+        <v>HD-MTX-05-RENO-WH-FULL</v>
       </c>
       <c r="B8" t="str">
-        <v>Điều hòa</v>
+        <v>Quạt</v>
       </c>
       <c r="C8" t="str">
-        <v>Máy 1.5HP</v>
+        <v>Quạt trần cũ của chủ</v>
       </c>
       <c r="D8" t="str">
         <v>Phòng khách</v>
@@ -4709,21 +4949,21 @@
         <v>1</v>
       </c>
       <c r="G8" t="str">
-        <v>NT cơ bản</v>
+        <v>Đồ chủ gốc — không tính NT khai thác</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>HD-MTX-09-NORENO-WH-BASIC</v>
+        <v>HD-MTX-07-RENO-WH-FULL</v>
       </c>
       <c r="B9" t="str">
-        <v>Giường</v>
+        <v>Quạt</v>
       </c>
       <c r="C9" t="str">
-        <v>Giường gỗ 1m6</v>
+        <v>Quạt trần cũ của chủ</v>
       </c>
       <c r="D9" t="str">
-        <v>Phòng ngủ</v>
+        <v>Phòng khách</v>
       </c>
       <c r="E9" t="str">
         <v>GOOD</v>
@@ -4732,18 +4972,18 @@
         <v>1</v>
       </c>
       <c r="G9" t="str">
-        <v/>
+        <v>Đồ chủ gốc — không tính NT khai thác</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>HD-MTX-10-NORENO-WH-BASIC</v>
+        <v>HD-MTX-08-RENO-WH-FULL</v>
       </c>
       <c r="B10" t="str">
-        <v>Điều hòa</v>
+        <v>Quạt</v>
       </c>
       <c r="C10" t="str">
-        <v>Máy 1.5HP</v>
+        <v>Quạt trần cũ của chủ</v>
       </c>
       <c r="D10" t="str">
         <v>Phòng khách</v>
@@ -4755,41 +4995,41 @@
         <v>1</v>
       </c>
       <c r="G10" t="str">
-        <v>NT cơ bản</v>
+        <v>Đồ chủ gốc — không tính NT khai thác</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>HD-MTX-10-NORENO-WH-BASIC</v>
+        <v>HD-MTX-08-RENO-WH-FULL</v>
       </c>
       <c r="B11" t="str">
-        <v>Giường</v>
+        <v>Tủ lạnh</v>
       </c>
       <c r="C11" t="str">
-        <v>Giường gỗ 1m6</v>
+        <v>Tủ 150L cũ</v>
       </c>
       <c r="D11" t="str">
-        <v>Phòng ngủ</v>
+        <v>Bếp</v>
       </c>
       <c r="E11" t="str">
-        <v>GOOD</v>
+        <v>DAMAGED</v>
       </c>
       <c r="F11">
         <v>1</v>
       </c>
       <c r="G11" t="str">
-        <v/>
+        <v>Đồ chủ gốc hỏng — đợt 2 mua mới nếu có NT</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>HD-MTX-11-NORENO-WH-FULL</v>
+        <v>HD-MTX-10-RENO-WH-FULL</v>
       </c>
       <c r="B12" t="str">
-        <v>Điều hòa</v>
+        <v>Quạt</v>
       </c>
       <c r="C12" t="str">
-        <v>1.5HP Inverter</v>
+        <v>Quạt trần cũ của chủ</v>
       </c>
       <c r="D12" t="str">
         <v>Phòng khách</v>
@@ -4801,44 +5041,44 @@
         <v>1</v>
       </c>
       <c r="G12" t="str">
-        <v/>
+        <v>Đồ chủ gốc — không tính NT khai thác</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>HD-MTX-11-NORENO-WH-FULL</v>
+        <v>HD-MTX-10-RENO-WH-FULL</v>
       </c>
       <c r="B13" t="str">
-        <v>Điều hòa</v>
+        <v>Tủ lạnh</v>
       </c>
       <c r="C13" t="str">
-        <v>1HP</v>
+        <v>Tủ 150L cũ</v>
       </c>
       <c r="D13" t="str">
-        <v>Phòng ngủ 1</v>
+        <v>Bếp</v>
       </c>
       <c r="E13" t="str">
-        <v>GOOD</v>
+        <v>DAMAGED</v>
       </c>
       <c r="F13">
         <v>1</v>
       </c>
       <c r="G13" t="str">
-        <v/>
+        <v>Đồ chủ gốc hỏng — đợt 2 mua mới nếu có NT</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>HD-MTX-11-NORENO-WH-FULL</v>
+        <v>HD-MTX-11-RENO-WH-FULL</v>
       </c>
       <c r="B14" t="str">
-        <v>Tủ lạnh</v>
+        <v>Quạt</v>
       </c>
       <c r="C14" t="str">
-        <v>Inverter 200L</v>
+        <v>Quạt trần cũ của chủ</v>
       </c>
       <c r="D14" t="str">
-        <v>Bếp</v>
+        <v>Phòng khách</v>
       </c>
       <c r="E14" t="str">
         <v>GOOD</v>
@@ -4847,21 +5087,21 @@
         <v>1</v>
       </c>
       <c r="G14" t="str">
-        <v/>
+        <v>Đồ chủ gốc — không tính NT khai thác</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>HD-MTX-11-NORENO-WH-FULL</v>
+        <v>HD-MTX-11-RENO-WH-FULL</v>
       </c>
       <c r="B15" t="str">
-        <v>Máy giặt</v>
+        <v>Giường</v>
       </c>
       <c r="C15" t="str">
-        <v>Cửa trước 8kg</v>
+        <v>Giường sắt cũ</v>
       </c>
       <c r="D15" t="str">
-        <v>Sân sau</v>
+        <v>Phòng ngủ</v>
       </c>
       <c r="E15" t="str">
         <v>GOOD</v>
@@ -4870,21 +5110,21 @@
         <v>1</v>
       </c>
       <c r="G15" t="str">
-        <v/>
+        <v>Đồ chủ gốc — không tính NT khai thác</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>HD-MTX-11-NORENO-WH-FULL</v>
+        <v>HD-MTX-13-RENO-WH-FULL</v>
       </c>
       <c r="B16" t="str">
-        <v>Nóng lạnh</v>
+        <v>Quạt</v>
       </c>
       <c r="C16" t="str">
-        <v>15L</v>
+        <v>Quạt trần cũ của chủ</v>
       </c>
       <c r="D16" t="str">
-        <v>WC tầng 1</v>
+        <v>Phòng khách</v>
       </c>
       <c r="E16" t="str">
         <v>GOOD</v>
@@ -4893,21 +5133,21 @@
         <v>1</v>
       </c>
       <c r="G16" t="str">
-        <v/>
+        <v>Đồ chủ gốc — không tính NT khai thác</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>HD-MTX-11-NORENO-WH-FULL</v>
+        <v>HD-MTX-14-RENO-WH-FULL</v>
       </c>
       <c r="B17" t="str">
-        <v>Giường</v>
+        <v>Quạt</v>
       </c>
       <c r="C17" t="str">
-        <v>Giường gỗ 1m6</v>
+        <v>Quạt trần cũ của chủ</v>
       </c>
       <c r="D17" t="str">
-        <v>Phòng ngủ 1</v>
+        <v>Phòng khách</v>
       </c>
       <c r="E17" t="str">
         <v>GOOD</v>
@@ -4916,41 +5156,41 @@
         <v>1</v>
       </c>
       <c r="G17" t="str">
-        <v/>
+        <v>Đồ chủ gốc — không tính NT khai thác</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>HD-MTX-11-NORENO-WH-FULL</v>
+        <v>HD-MTX-14-RENO-WH-FULL</v>
       </c>
       <c r="B18" t="str">
-        <v>Giường</v>
+        <v>Tủ lạnh</v>
       </c>
       <c r="C18" t="str">
-        <v>Giường gỗ 1m6</v>
+        <v>Tủ 150L cũ</v>
       </c>
       <c r="D18" t="str">
-        <v>Phòng ngủ 2</v>
+        <v>Bếp</v>
       </c>
       <c r="E18" t="str">
-        <v>GOOD</v>
+        <v>DAMAGED</v>
       </c>
       <c r="F18">
         <v>1</v>
       </c>
       <c r="G18" t="str">
-        <v/>
+        <v>Đồ chủ gốc hỏng — đợt 2 mua mới nếu có NT</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>HD-MTX-11-NORENO-WH-FULL</v>
+        <v>HD-MTX-16-RENO-WH-BASIC</v>
       </c>
       <c r="B19" t="str">
         <v>Quạt</v>
       </c>
       <c r="C19" t="str">
-        <v>Quạt trần</v>
+        <v>Quạt trần cũ của chủ</v>
       </c>
       <c r="D19" t="str">
         <v>Phòng khách</v>
@@ -4962,44 +5202,44 @@
         <v>1</v>
       </c>
       <c r="G19" t="str">
-        <v/>
+        <v>Đồ chủ gốc — không tính NT khai thác</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>HD-MTX-11-NORENO-WH-FULL</v>
+        <v>HD-MTX-16-RENO-WH-BASIC</v>
       </c>
       <c r="B20" t="str">
-        <v>Quạt</v>
+        <v>Tủ lạnh</v>
       </c>
       <c r="C20" t="str">
-        <v>Quạt đứng</v>
+        <v>Tủ 150L cũ</v>
       </c>
       <c r="D20" t="str">
-        <v>Phòng ngủ 1</v>
+        <v>Bếp</v>
       </c>
       <c r="E20" t="str">
-        <v>GOOD</v>
+        <v>DAMAGED</v>
       </c>
       <c r="F20">
         <v>1</v>
       </c>
       <c r="G20" t="str">
-        <v/>
+        <v>Đồ chủ gốc hỏng — đợt 2 mua mới nếu có NT</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>HD-MTX-12-NORENO-WH-FULL</v>
+        <v>HD-MTX-16-RENO-WH-BASIC</v>
       </c>
       <c r="B21" t="str">
-        <v>Điều hòa</v>
+        <v>Giường</v>
       </c>
       <c r="C21" t="str">
-        <v>1.5HP Inverter</v>
+        <v>Giường sắt cũ</v>
       </c>
       <c r="D21" t="str">
-        <v>Phòng khách</v>
+        <v>Phòng ngủ</v>
       </c>
       <c r="E21" t="str">
         <v>GOOD</v>
@@ -5008,21 +5248,21 @@
         <v>1</v>
       </c>
       <c r="G21" t="str">
-        <v/>
+        <v>Đồ chủ gốc — không tính NT khai thác</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>HD-MTX-12-NORENO-WH-FULL</v>
+        <v>HD-MTX-17-RENO-WH-BASIC</v>
       </c>
       <c r="B22" t="str">
-        <v>Điều hòa</v>
+        <v>Quạt</v>
       </c>
       <c r="C22" t="str">
-        <v>1HP</v>
+        <v>Quạt trần cũ của chủ</v>
       </c>
       <c r="D22" t="str">
-        <v>Phòng ngủ 1</v>
+        <v>Phòng khách</v>
       </c>
       <c r="E22" t="str">
         <v>GOOD</v>
@@ -5031,21 +5271,21 @@
         <v>1</v>
       </c>
       <c r="G22" t="str">
-        <v/>
+        <v>Đồ chủ gốc — không tính NT khai thác</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>HD-MTX-12-NORENO-WH-FULL</v>
+        <v>HD-MTX-19-RENO-WH-BASIC</v>
       </c>
       <c r="B23" t="str">
-        <v>Tủ lạnh</v>
+        <v>Quạt</v>
       </c>
       <c r="C23" t="str">
-        <v>Inverter 200L</v>
+        <v>Quạt trần cũ của chủ</v>
       </c>
       <c r="D23" t="str">
-        <v>Bếp</v>
+        <v>Phòng khách</v>
       </c>
       <c r="E23" t="str">
         <v>GOOD</v>
@@ -5054,21 +5294,21 @@
         <v>1</v>
       </c>
       <c r="G23" t="str">
-        <v/>
+        <v>Đồ chủ gốc — không tính NT khai thác</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>HD-MTX-12-NORENO-WH-FULL</v>
+        <v>HD-MTX-20-RENO-WH-BASIC</v>
       </c>
       <c r="B24" t="str">
-        <v>Máy giặt</v>
+        <v>Quạt</v>
       </c>
       <c r="C24" t="str">
-        <v>Cửa trước 8kg</v>
+        <v>Quạt trần cũ của chủ</v>
       </c>
       <c r="D24" t="str">
-        <v>Sân sau</v>
+        <v>Phòng khách</v>
       </c>
       <c r="E24" t="str">
         <v>GOOD</v>
@@ -5077,44 +5317,44 @@
         <v>1</v>
       </c>
       <c r="G24" t="str">
-        <v/>
+        <v>Đồ chủ gốc — không tính NT khai thác</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>HD-MTX-12-NORENO-WH-FULL</v>
+        <v>HD-MTX-20-RENO-WH-BASIC</v>
       </c>
       <c r="B25" t="str">
-        <v>Nóng lạnh</v>
+        <v>Tủ lạnh</v>
       </c>
       <c r="C25" t="str">
-        <v>15L</v>
+        <v>Tủ 150L cũ</v>
       </c>
       <c r="D25" t="str">
-        <v>WC tầng 1</v>
+        <v>Bếp</v>
       </c>
       <c r="E25" t="str">
-        <v>GOOD</v>
+        <v>DAMAGED</v>
       </c>
       <c r="F25">
         <v>1</v>
       </c>
       <c r="G25" t="str">
-        <v/>
+        <v>Đồ chủ gốc hỏng — đợt 2 mua mới nếu có NT</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>HD-MTX-12-NORENO-WH-FULL</v>
+        <v>HD-MTX-22-RENO-WH-BASIC</v>
       </c>
       <c r="B26" t="str">
-        <v>Giường</v>
+        <v>Quạt</v>
       </c>
       <c r="C26" t="str">
-        <v>Giường gỗ 1m6</v>
+        <v>Quạt trần cũ của chủ</v>
       </c>
       <c r="D26" t="str">
-        <v>Phòng ngủ 1</v>
+        <v>Phòng khách</v>
       </c>
       <c r="E26" t="str">
         <v>GOOD</v>
@@ -5123,41 +5363,41 @@
         <v>1</v>
       </c>
       <c r="G26" t="str">
-        <v/>
+        <v>Đồ chủ gốc — không tính NT khai thác</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>HD-MTX-12-NORENO-WH-FULL</v>
+        <v>HD-MTX-22-RENO-WH-BASIC</v>
       </c>
       <c r="B27" t="str">
-        <v>Giường</v>
+        <v>Tủ lạnh</v>
       </c>
       <c r="C27" t="str">
-        <v>Giường gỗ 1m6</v>
+        <v>Tủ 150L cũ</v>
       </c>
       <c r="D27" t="str">
-        <v>Phòng ngủ 2</v>
+        <v>Bếp</v>
       </c>
       <c r="E27" t="str">
-        <v>GOOD</v>
+        <v>DAMAGED</v>
       </c>
       <c r="F27">
         <v>1</v>
       </c>
       <c r="G27" t="str">
-        <v/>
+        <v>Đồ chủ gốc hỏng — đợt 2 mua mới nếu có NT</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>HD-MTX-12-NORENO-WH-FULL</v>
+        <v>HD-MTX-23-RENO-WH-BASIC</v>
       </c>
       <c r="B28" t="str">
         <v>Quạt</v>
       </c>
       <c r="C28" t="str">
-        <v>Quạt trần</v>
+        <v>Quạt trần cũ của chủ</v>
       </c>
       <c r="D28" t="str">
         <v>Phòng khách</v>
@@ -5169,21 +5409,21 @@
         <v>1</v>
       </c>
       <c r="G28" t="str">
-        <v/>
+        <v>Đồ chủ gốc — không tính NT khai thác</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>HD-MTX-12-NORENO-WH-FULL</v>
+        <v>HD-MTX-25-RENO-WH-BASIC</v>
       </c>
       <c r="B29" t="str">
         <v>Quạt</v>
       </c>
       <c r="C29" t="str">
-        <v>Quạt đứng</v>
+        <v>Quạt trần cũ của chủ</v>
       </c>
       <c r="D29" t="str">
-        <v>Phòng ngủ 1</v>
+        <v>Phòng khách</v>
       </c>
       <c r="E29" t="str">
         <v>GOOD</v>
@@ -5192,18 +5432,18 @@
         <v>1</v>
       </c>
       <c r="G29" t="str">
-        <v/>
+        <v>Đồ chủ gốc — không tính NT khai thác</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>HD-MTX-13-NORENO-WH-FULL</v>
+        <v>HD-MTX-26-RENO-WH-BASIC</v>
       </c>
       <c r="B30" t="str">
-        <v>Điều hòa</v>
+        <v>Quạt</v>
       </c>
       <c r="C30" t="str">
-        <v>1.5HP Inverter</v>
+        <v>Quạt trần cũ của chủ</v>
       </c>
       <c r="D30" t="str">
         <v>Phòng khách</v>
@@ -5215,44 +5455,44 @@
         <v>1</v>
       </c>
       <c r="G30" t="str">
-        <v/>
+        <v>Đồ chủ gốc — không tính NT khai thác</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>HD-MTX-13-NORENO-WH-FULL</v>
+        <v>HD-MTX-26-RENO-WH-BASIC</v>
       </c>
       <c r="B31" t="str">
-        <v>Điều hòa</v>
+        <v>Tủ lạnh</v>
       </c>
       <c r="C31" t="str">
-        <v>1HP</v>
+        <v>Tủ 150L cũ</v>
       </c>
       <c r="D31" t="str">
-        <v>Phòng ngủ 1</v>
+        <v>Bếp</v>
       </c>
       <c r="E31" t="str">
-        <v>GOOD</v>
+        <v>DAMAGED</v>
       </c>
       <c r="F31">
         <v>1</v>
       </c>
       <c r="G31" t="str">
-        <v/>
+        <v>Đồ chủ gốc hỏng — đợt 2 mua mới nếu có NT</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>HD-MTX-13-NORENO-WH-FULL</v>
+        <v>HD-MTX-26-RENO-WH-BASIC</v>
       </c>
       <c r="B32" t="str">
-        <v>Tủ lạnh</v>
+        <v>Giường</v>
       </c>
       <c r="C32" t="str">
-        <v>Inverter 200L</v>
+        <v>Giường sắt cũ</v>
       </c>
       <c r="D32" t="str">
-        <v>Bếp</v>
+        <v>Phòng ngủ</v>
       </c>
       <c r="E32" t="str">
         <v>GOOD</v>
@@ -5261,21 +5501,21 @@
         <v>1</v>
       </c>
       <c r="G32" t="str">
-        <v/>
+        <v>Đồ chủ gốc — không tính NT khai thác</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>HD-MTX-13-NORENO-WH-FULL</v>
+        <v>HD-MTX-28-RENO-WH-NONE</v>
       </c>
       <c r="B33" t="str">
-        <v>Máy giặt</v>
+        <v>Quạt</v>
       </c>
       <c r="C33" t="str">
-        <v>Cửa trước 8kg</v>
+        <v>Quạt trần cũ của chủ</v>
       </c>
       <c r="D33" t="str">
-        <v>Sân sau</v>
+        <v>Phòng khách</v>
       </c>
       <c r="E33" t="str">
         <v>GOOD</v>
@@ -5284,44 +5524,44 @@
         <v>1</v>
       </c>
       <c r="G33" t="str">
-        <v/>
+        <v>Đồ chủ gốc — không tính NT khai thác</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>HD-MTX-13-NORENO-WH-FULL</v>
+        <v>HD-MTX-28-RENO-WH-NONE</v>
       </c>
       <c r="B34" t="str">
-        <v>Nóng lạnh</v>
+        <v>Tủ lạnh</v>
       </c>
       <c r="C34" t="str">
-        <v>15L</v>
+        <v>Tủ 150L cũ</v>
       </c>
       <c r="D34" t="str">
-        <v>WC tầng 1</v>
+        <v>Bếp</v>
       </c>
       <c r="E34" t="str">
-        <v>GOOD</v>
+        <v>DAMAGED</v>
       </c>
       <c r="F34">
         <v>1</v>
       </c>
       <c r="G34" t="str">
-        <v/>
+        <v>Đồ chủ gốc hỏng — đợt 2 mua mới nếu có NT</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>HD-MTX-13-NORENO-WH-FULL</v>
+        <v>HD-MTX-29-RENO-WH-NONE</v>
       </c>
       <c r="B35" t="str">
-        <v>Giường</v>
+        <v>Quạt</v>
       </c>
       <c r="C35" t="str">
-        <v>Giường gỗ 1m6</v>
+        <v>Quạt trần cũ của chủ</v>
       </c>
       <c r="D35" t="str">
-        <v>Phòng ngủ 1</v>
+        <v>Phòng khách</v>
       </c>
       <c r="E35" t="str">
         <v>GOOD</v>
@@ -5330,21 +5570,21 @@
         <v>1</v>
       </c>
       <c r="G35" t="str">
-        <v/>
+        <v>Đồ chủ gốc — không tính NT khai thác</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>HD-MTX-13-NORENO-WH-FULL</v>
+        <v>HD-MTX-31-RENO-WH-NONE</v>
       </c>
       <c r="B36" t="str">
-        <v>Giường</v>
+        <v>Quạt</v>
       </c>
       <c r="C36" t="str">
-        <v>Giường gỗ 1m6</v>
+        <v>Quạt trần cũ của chủ</v>
       </c>
       <c r="D36" t="str">
-        <v>Phòng ngủ 2</v>
+        <v>Phòng khách</v>
       </c>
       <c r="E36" t="str">
         <v>GOOD</v>
@@ -5353,21 +5593,21 @@
         <v>1</v>
       </c>
       <c r="G36" t="str">
-        <v/>
+        <v>Đồ chủ gốc — không tính NT khai thác</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>HD-MTX-13-NORENO-WH-FULL</v>
+        <v>HD-MTX-31-RENO-WH-NONE</v>
       </c>
       <c r="B37" t="str">
-        <v>Quạt</v>
+        <v>Giường</v>
       </c>
       <c r="C37" t="str">
-        <v>Quạt trần</v>
+        <v>Giường sắt cũ</v>
       </c>
       <c r="D37" t="str">
-        <v>Phòng khách</v>
+        <v>Phòng ngủ</v>
       </c>
       <c r="E37" t="str">
         <v>GOOD</v>
@@ -5376,21 +5616,21 @@
         <v>1</v>
       </c>
       <c r="G37" t="str">
-        <v/>
+        <v>Đồ chủ gốc — không tính NT khai thác</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>HD-MTX-13-NORENO-WH-FULL</v>
+        <v>HD-MTX-32-RENO-WH-NONE</v>
       </c>
       <c r="B38" t="str">
         <v>Quạt</v>
       </c>
       <c r="C38" t="str">
-        <v>Quạt đứng</v>
+        <v>Quạt trần cũ của chủ</v>
       </c>
       <c r="D38" t="str">
-        <v>Phòng ngủ 1</v>
+        <v>Phòng khách</v>
       </c>
       <c r="E38" t="str">
         <v>GOOD</v>
@@ -5399,44 +5639,44 @@
         <v>1</v>
       </c>
       <c r="G38" t="str">
-        <v/>
+        <v>Đồ chủ gốc — không tính NT khai thác</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>HD-MTX-14-NORENO-WH-FULL</v>
+        <v>HD-MTX-32-RENO-WH-NONE</v>
       </c>
       <c r="B39" t="str">
-        <v>Điều hòa</v>
+        <v>Tủ lạnh</v>
       </c>
       <c r="C39" t="str">
-        <v>1.5HP Inverter</v>
+        <v>Tủ 150L cũ</v>
       </c>
       <c r="D39" t="str">
-        <v>Phòng khách</v>
+        <v>Bếp</v>
       </c>
       <c r="E39" t="str">
-        <v>GOOD</v>
+        <v>DAMAGED</v>
       </c>
       <c r="F39">
         <v>1</v>
       </c>
       <c r="G39" t="str">
-        <v/>
+        <v>Đồ chủ gốc hỏng — đợt 2 mua mới nếu có NT</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>HD-MTX-14-NORENO-WH-FULL</v>
+        <v>HD-MTX-34-RENO-WH-NONE</v>
       </c>
       <c r="B40" t="str">
-        <v>Điều hòa</v>
+        <v>Quạt</v>
       </c>
       <c r="C40" t="str">
-        <v>1HP</v>
+        <v>Quạt trần cũ của chủ</v>
       </c>
       <c r="D40" t="str">
-        <v>Phòng ngủ 1</v>
+        <v>Phòng khách</v>
       </c>
       <c r="E40" t="str">
         <v>GOOD</v>
@@ -5445,44 +5685,44 @@
         <v>1</v>
       </c>
       <c r="G40" t="str">
-        <v/>
+        <v>Đồ chủ gốc — không tính NT khai thác</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>HD-MTX-14-NORENO-WH-FULL</v>
+        <v>HD-MTX-34-RENO-WH-NONE</v>
       </c>
       <c r="B41" t="str">
         <v>Tủ lạnh</v>
       </c>
       <c r="C41" t="str">
-        <v>Inverter 200L</v>
+        <v>Tủ 150L cũ</v>
       </c>
       <c r="D41" t="str">
         <v>Bếp</v>
       </c>
       <c r="E41" t="str">
-        <v>GOOD</v>
+        <v>DAMAGED</v>
       </c>
       <c r="F41">
         <v>1</v>
       </c>
       <c r="G41" t="str">
-        <v/>
+        <v>Đồ chủ gốc hỏng — đợt 2 mua mới nếu có NT</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>HD-MTX-14-NORENO-WH-FULL</v>
+        <v>HD-MTX-35-RENO-WH-NONE</v>
       </c>
       <c r="B42" t="str">
-        <v>Máy giặt</v>
+        <v>Quạt</v>
       </c>
       <c r="C42" t="str">
-        <v>Cửa trước 8kg</v>
+        <v>Quạt trần cũ của chủ</v>
       </c>
       <c r="D42" t="str">
-        <v>Sân sau</v>
+        <v>Phòng khách</v>
       </c>
       <c r="E42" t="str">
         <v>GOOD</v>
@@ -5491,21 +5731,21 @@
         <v>1</v>
       </c>
       <c r="G42" t="str">
-        <v/>
+        <v>Đồ chủ gốc — không tính NT khai thác</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>HD-MTX-14-NORENO-WH-FULL</v>
+        <v>HD-MTX-37-RENO-WH-NONE</v>
       </c>
       <c r="B43" t="str">
-        <v>Nóng lạnh</v>
+        <v>Quạt</v>
       </c>
       <c r="C43" t="str">
-        <v>15L</v>
+        <v>Quạt trần cũ của chủ</v>
       </c>
       <c r="D43" t="str">
-        <v>WC tầng 1</v>
+        <v>Phòng khách</v>
       </c>
       <c r="E43" t="str">
         <v>GOOD</v>
@@ -5514,21 +5754,21 @@
         <v>1</v>
       </c>
       <c r="G43" t="str">
-        <v/>
+        <v>Đồ chủ gốc — không tính NT khai thác</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>HD-MTX-14-NORENO-WH-FULL</v>
+        <v>HD-MTX-38-RENO-WH-NONE</v>
       </c>
       <c r="B44" t="str">
-        <v>Giường</v>
+        <v>Quạt</v>
       </c>
       <c r="C44" t="str">
-        <v>Giường gỗ 1m6</v>
+        <v>Quạt trần cũ của chủ</v>
       </c>
       <c r="D44" t="str">
-        <v>Phòng ngủ 1</v>
+        <v>Phòng khách</v>
       </c>
       <c r="E44" t="str">
         <v>GOOD</v>
@@ -5537,41 +5777,41 @@
         <v>1</v>
       </c>
       <c r="G44" t="str">
-        <v/>
+        <v>Đồ chủ gốc — không tính NT khai thác</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>HD-MTX-14-NORENO-WH-FULL</v>
+        <v>HD-MTX-38-RENO-WH-NONE</v>
       </c>
       <c r="B45" t="str">
-        <v>Giường</v>
+        <v>Tủ lạnh</v>
       </c>
       <c r="C45" t="str">
-        <v>Giường gỗ 1m6</v>
+        <v>Tủ 150L cũ</v>
       </c>
       <c r="D45" t="str">
-        <v>Phòng ngủ 2</v>
+        <v>Bếp</v>
       </c>
       <c r="E45" t="str">
-        <v>GOOD</v>
+        <v>DAMAGED</v>
       </c>
       <c r="F45">
         <v>1</v>
       </c>
       <c r="G45" t="str">
-        <v/>
+        <v>Đồ chủ gốc hỏng — đợt 2 mua mới nếu có NT</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>HD-MTX-14-NORENO-WH-FULL</v>
+        <v>HD-MTX-40-RENO-WH-NONE</v>
       </c>
       <c r="B46" t="str">
         <v>Quạt</v>
       </c>
       <c r="C46" t="str">
-        <v>Quạt trần</v>
+        <v>Quạt trần cũ của chủ</v>
       </c>
       <c r="D46" t="str">
         <v>Phòng khách</v>
@@ -5583,41 +5823,41 @@
         <v>1</v>
       </c>
       <c r="G46" t="str">
-        <v/>
+        <v>Đồ chủ gốc — không tính NT khai thác</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>HD-MTX-14-NORENO-WH-FULL</v>
+        <v>HD-MTX-40-RENO-WH-NONE</v>
       </c>
       <c r="B47" t="str">
-        <v>Quạt</v>
+        <v>Tủ lạnh</v>
       </c>
       <c r="C47" t="str">
-        <v>Quạt đứng</v>
+        <v>Tủ 150L cũ</v>
       </c>
       <c r="D47" t="str">
-        <v>Phòng ngủ 1</v>
+        <v>Bếp</v>
       </c>
       <c r="E47" t="str">
-        <v>GOOD</v>
+        <v>DAMAGED</v>
       </c>
       <c r="F47">
         <v>1</v>
       </c>
       <c r="G47" t="str">
-        <v/>
+        <v>Đồ chủ gốc hỏng — đợt 2 mua mới nếu có NT</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>HD-MTX-15-NORENO-WH-FULL</v>
+        <v>HD-MTX-41-RENO-RM-FULL</v>
       </c>
       <c r="B48" t="str">
-        <v>Điều hòa</v>
+        <v>Quạt</v>
       </c>
       <c r="C48" t="str">
-        <v>1.5HP Inverter</v>
+        <v>Quạt trần cũ của chủ</v>
       </c>
       <c r="D48" t="str">
         <v>Phòng khách</v>
@@ -5629,21 +5869,21 @@
         <v>1</v>
       </c>
       <c r="G48" t="str">
-        <v/>
+        <v>Đồ chủ gốc — không tính NT khai thác</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>HD-MTX-15-NORENO-WH-FULL</v>
+        <v>HD-MTX-41-RENO-RM-FULL</v>
       </c>
       <c r="B49" t="str">
-        <v>Điều hòa</v>
+        <v>Giường</v>
       </c>
       <c r="C49" t="str">
-        <v>1HP</v>
+        <v>Giường sắt cũ</v>
       </c>
       <c r="D49" t="str">
-        <v>Phòng ngủ 1</v>
+        <v>Phòng ngủ</v>
       </c>
       <c r="E49" t="str">
         <v>GOOD</v>
@@ -5652,21 +5892,21 @@
         <v>1</v>
       </c>
       <c r="G49" t="str">
-        <v/>
+        <v>Đồ chủ gốc — không tính NT khai thác</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>HD-MTX-15-NORENO-WH-FULL</v>
+        <v>HD-MTX-43-RENO-RM-FULL</v>
       </c>
       <c r="B50" t="str">
-        <v>Tủ lạnh</v>
+        <v>Quạt</v>
       </c>
       <c r="C50" t="str">
-        <v>Inverter 200L</v>
+        <v>Quạt trần cũ của chủ</v>
       </c>
       <c r="D50" t="str">
-        <v>Bếp</v>
+        <v>Phòng khách</v>
       </c>
       <c r="E50" t="str">
         <v>GOOD</v>
@@ -5675,21 +5915,21 @@
         <v>1</v>
       </c>
       <c r="G50" t="str">
-        <v/>
+        <v>Đồ chủ gốc — không tính NT khai thác</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>HD-MTX-15-NORENO-WH-FULL</v>
+        <v>HD-MTX-44-RENO-RM-FULL</v>
       </c>
       <c r="B51" t="str">
-        <v>Máy giặt</v>
+        <v>Quạt</v>
       </c>
       <c r="C51" t="str">
-        <v>Cửa trước 8kg</v>
+        <v>Quạt trần cũ của chủ</v>
       </c>
       <c r="D51" t="str">
-        <v>Sân sau</v>
+        <v>Phòng khách</v>
       </c>
       <c r="E51" t="str">
         <v>GOOD</v>
@@ -5698,44 +5938,44 @@
         <v>1</v>
       </c>
       <c r="G51" t="str">
-        <v/>
+        <v>Đồ chủ gốc — không tính NT khai thác</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>HD-MTX-15-NORENO-WH-FULL</v>
+        <v>HD-MTX-44-RENO-RM-FULL</v>
       </c>
       <c r="B52" t="str">
-        <v>Nóng lạnh</v>
+        <v>Tủ lạnh</v>
       </c>
       <c r="C52" t="str">
-        <v>15L</v>
+        <v>Tủ 150L cũ</v>
       </c>
       <c r="D52" t="str">
-        <v>WC tầng 1</v>
+        <v>Bếp</v>
       </c>
       <c r="E52" t="str">
-        <v>GOOD</v>
+        <v>DAMAGED</v>
       </c>
       <c r="F52">
         <v>1</v>
       </c>
       <c r="G52" t="str">
-        <v/>
+        <v>Đồ chủ gốc hỏng — đợt 2 mua mới nếu có NT</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>HD-MTX-15-NORENO-WH-FULL</v>
+        <v>HD-MTX-46-RENO-RM-BASIC</v>
       </c>
       <c r="B53" t="str">
-        <v>Giường</v>
+        <v>Quạt</v>
       </c>
       <c r="C53" t="str">
-        <v>Giường gỗ 1m6</v>
+        <v>Quạt trần cũ của chủ</v>
       </c>
       <c r="D53" t="str">
-        <v>Phòng ngủ 1</v>
+        <v>Phòng khách</v>
       </c>
       <c r="E53" t="str">
         <v>GOOD</v>
@@ -5744,44 +5984,44 @@
         <v>1</v>
       </c>
       <c r="G53" t="str">
-        <v/>
+        <v>Đồ chủ gốc — không tính NT khai thác</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>HD-MTX-15-NORENO-WH-FULL</v>
+        <v>HD-MTX-46-RENO-RM-BASIC</v>
       </c>
       <c r="B54" t="str">
-        <v>Giường</v>
+        <v>Tủ lạnh</v>
       </c>
       <c r="C54" t="str">
-        <v>Giường gỗ 1m6</v>
+        <v>Tủ 150L cũ</v>
       </c>
       <c r="D54" t="str">
-        <v>Phòng ngủ 2</v>
+        <v>Bếp</v>
       </c>
       <c r="E54" t="str">
-        <v>GOOD</v>
+        <v>DAMAGED</v>
       </c>
       <c r="F54">
         <v>1</v>
       </c>
       <c r="G54" t="str">
-        <v/>
+        <v>Đồ chủ gốc hỏng — đợt 2 mua mới nếu có NT</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>HD-MTX-15-NORENO-WH-FULL</v>
+        <v>HD-MTX-46-RENO-RM-BASIC</v>
       </c>
       <c r="B55" t="str">
-        <v>Quạt</v>
+        <v>Giường</v>
       </c>
       <c r="C55" t="str">
-        <v>Quạt trần</v>
+        <v>Giường sắt cũ</v>
       </c>
       <c r="D55" t="str">
-        <v>Phòng khách</v>
+        <v>Phòng ngủ</v>
       </c>
       <c r="E55" t="str">
         <v>GOOD</v>
@@ -5790,21 +6030,21 @@
         <v>1</v>
       </c>
       <c r="G55" t="str">
-        <v/>
+        <v>Đồ chủ gốc — không tính NT khai thác</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>HD-MTX-15-NORENO-WH-FULL</v>
+        <v>HD-MTX-47-RENO-RM-BASIC</v>
       </c>
       <c r="B56" t="str">
         <v>Quạt</v>
       </c>
       <c r="C56" t="str">
-        <v>Quạt đứng</v>
+        <v>Quạt trần cũ của chủ</v>
       </c>
       <c r="D56" t="str">
-        <v>Phòng ngủ 1</v>
+        <v>Phòng khách</v>
       </c>
       <c r="E56" t="str">
         <v>GOOD</v>
@@ -5813,18 +6053,18 @@
         <v>1</v>
       </c>
       <c r="G56" t="str">
-        <v/>
+        <v>Đồ chủ gốc — không tính NT khai thác</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>HD-MTX-19-RENO-WH-BASIC-HO</v>
+        <v>HD-MTX-49-RENO-RM-NONE</v>
       </c>
       <c r="B57" t="str">
-        <v>Điều hòa</v>
+        <v>Quạt</v>
       </c>
       <c r="C57" t="str">
-        <v>Máy 1.5HP</v>
+        <v>Quạt trần cũ của chủ</v>
       </c>
       <c r="D57" t="str">
         <v>Phòng khách</v>
@@ -5836,21 +6076,21 @@
         <v>1</v>
       </c>
       <c r="G57" t="str">
-        <v>NT cơ bản</v>
+        <v>Đồ chủ gốc — không tính NT khai thác</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>HD-MTX-19-RENO-WH-BASIC-HO</v>
+        <v>HD-MTX-50-RENO-RM-NONE</v>
       </c>
       <c r="B58" t="str">
-        <v>Giường</v>
+        <v>Quạt</v>
       </c>
       <c r="C58" t="str">
-        <v>Giường gỗ 1m6</v>
+        <v>Quạt trần cũ của chủ</v>
       </c>
       <c r="D58" t="str">
-        <v>Phòng ngủ</v>
+        <v>Phòng khách</v>
       </c>
       <c r="E58" t="str">
         <v>GOOD</v>
@@ -5859,1300 +6099,35 @@
         <v>1</v>
       </c>
       <c r="G58" t="str">
-        <v/>
+        <v>Đồ chủ gốc — không tính NT khai thác</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>HD-MTX-20-RENO-WH-BASIC-HO</v>
+        <v>HD-MTX-50-RENO-RM-NONE</v>
       </c>
       <c r="B59" t="str">
-        <v>Điều hòa</v>
+        <v>Tủ lạnh</v>
       </c>
       <c r="C59" t="str">
-        <v>Máy 1.5HP</v>
+        <v>Tủ 150L cũ</v>
       </c>
       <c r="D59" t="str">
-        <v>Phòng khách</v>
+        <v>Bếp</v>
       </c>
       <c r="E59" t="str">
-        <v>GOOD</v>
+        <v>DAMAGED</v>
       </c>
       <c r="F59">
         <v>1</v>
       </c>
       <c r="G59" t="str">
-        <v>NT cơ bản</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="str">
-        <v>HD-MTX-20-RENO-WH-BASIC-HO</v>
-      </c>
-      <c r="B60" t="str">
-        <v>Giường</v>
-      </c>
-      <c r="C60" t="str">
-        <v>Giường gỗ 1m6</v>
-      </c>
-      <c r="D60" t="str">
-        <v>Phòng ngủ</v>
-      </c>
-      <c r="E60" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F60">
-        <v>1</v>
-      </c>
-      <c r="G60" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="str">
-        <v>HD-MTX-21-RENO-WH-BASIC-HO</v>
-      </c>
-      <c r="B61" t="str">
-        <v>Điều hòa</v>
-      </c>
-      <c r="C61" t="str">
-        <v>Máy 1.5HP</v>
-      </c>
-      <c r="D61" t="str">
-        <v>Phòng khách</v>
-      </c>
-      <c r="E61" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F61">
-        <v>1</v>
-      </c>
-      <c r="G61" t="str">
-        <v>NT cơ bản</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="str">
-        <v>HD-MTX-21-RENO-WH-BASIC-HO</v>
-      </c>
-      <c r="B62" t="str">
-        <v>Giường</v>
-      </c>
-      <c r="C62" t="str">
-        <v>Giường gỗ 1m6</v>
-      </c>
-      <c r="D62" t="str">
-        <v>Phòng ngủ</v>
-      </c>
-      <c r="E62" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F62">
-        <v>1</v>
-      </c>
-      <c r="G62" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="str">
-        <v>HD-MTX-25-RENO-WH-FULL</v>
-      </c>
-      <c r="B63" t="str">
-        <v>Điều hòa</v>
-      </c>
-      <c r="C63" t="str">
-        <v>1.5HP Inverter</v>
-      </c>
-      <c r="D63" t="str">
-        <v>Phòng khách</v>
-      </c>
-      <c r="E63" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F63">
-        <v>1</v>
-      </c>
-      <c r="G63" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="str">
-        <v>HD-MTX-25-RENO-WH-FULL</v>
-      </c>
-      <c r="B64" t="str">
-        <v>Điều hòa</v>
-      </c>
-      <c r="C64" t="str">
-        <v>1HP</v>
-      </c>
-      <c r="D64" t="str">
-        <v>Phòng ngủ 1</v>
-      </c>
-      <c r="E64" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F64">
-        <v>1</v>
-      </c>
-      <c r="G64" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="str">
-        <v>HD-MTX-25-RENO-WH-FULL</v>
-      </c>
-      <c r="B65" t="str">
-        <v>Tủ lạnh</v>
-      </c>
-      <c r="C65" t="str">
-        <v>Inverter 200L</v>
-      </c>
-      <c r="D65" t="str">
-        <v>Bếp</v>
-      </c>
-      <c r="E65" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F65">
-        <v>1</v>
-      </c>
-      <c r="G65" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="str">
-        <v>HD-MTX-25-RENO-WH-FULL</v>
-      </c>
-      <c r="B66" t="str">
-        <v>Máy giặt</v>
-      </c>
-      <c r="C66" t="str">
-        <v>Cửa trước 8kg</v>
-      </c>
-      <c r="D66" t="str">
-        <v>Sân sau</v>
-      </c>
-      <c r="E66" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F66">
-        <v>1</v>
-      </c>
-      <c r="G66" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="str">
-        <v>HD-MTX-25-RENO-WH-FULL</v>
-      </c>
-      <c r="B67" t="str">
-        <v>Nóng lạnh</v>
-      </c>
-      <c r="C67" t="str">
-        <v>15L</v>
-      </c>
-      <c r="D67" t="str">
-        <v>WC tầng 1</v>
-      </c>
-      <c r="E67" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F67">
-        <v>1</v>
-      </c>
-      <c r="G67" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="str">
-        <v>HD-MTX-25-RENO-WH-FULL</v>
-      </c>
-      <c r="B68" t="str">
-        <v>Giường</v>
-      </c>
-      <c r="C68" t="str">
-        <v>Giường gỗ 1m6</v>
-      </c>
-      <c r="D68" t="str">
-        <v>Phòng ngủ 1</v>
-      </c>
-      <c r="E68" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F68">
-        <v>1</v>
-      </c>
-      <c r="G68" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="str">
-        <v>HD-MTX-25-RENO-WH-FULL</v>
-      </c>
-      <c r="B69" t="str">
-        <v>Giường</v>
-      </c>
-      <c r="C69" t="str">
-        <v>Giường gỗ 1m6</v>
-      </c>
-      <c r="D69" t="str">
-        <v>Phòng ngủ 2</v>
-      </c>
-      <c r="E69" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F69">
-        <v>1</v>
-      </c>
-      <c r="G69" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="str">
-        <v>HD-MTX-25-RENO-WH-FULL</v>
-      </c>
-      <c r="B70" t="str">
-        <v>Quạt</v>
-      </c>
-      <c r="C70" t="str">
-        <v>Quạt trần</v>
-      </c>
-      <c r="D70" t="str">
-        <v>Phòng khách</v>
-      </c>
-      <c r="E70" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F70">
-        <v>1</v>
-      </c>
-      <c r="G70" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="str">
-        <v>HD-MTX-25-RENO-WH-FULL</v>
-      </c>
-      <c r="B71" t="str">
-        <v>Quạt</v>
-      </c>
-      <c r="C71" t="str">
-        <v>Quạt đứng</v>
-      </c>
-      <c r="D71" t="str">
-        <v>Phòng ngủ 1</v>
-      </c>
-      <c r="E71" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F71">
-        <v>1</v>
-      </c>
-      <c r="G71" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="str">
-        <v>HD-MTX-26-RENO-WH-FULL</v>
-      </c>
-      <c r="B72" t="str">
-        <v>Điều hòa</v>
-      </c>
-      <c r="C72" t="str">
-        <v>1.5HP Inverter</v>
-      </c>
-      <c r="D72" t="str">
-        <v>Phòng khách</v>
-      </c>
-      <c r="E72" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F72">
-        <v>1</v>
-      </c>
-      <c r="G72" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="str">
-        <v>HD-MTX-26-RENO-WH-FULL</v>
-      </c>
-      <c r="B73" t="str">
-        <v>Điều hòa</v>
-      </c>
-      <c r="C73" t="str">
-        <v>1HP</v>
-      </c>
-      <c r="D73" t="str">
-        <v>Phòng ngủ 1</v>
-      </c>
-      <c r="E73" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F73">
-        <v>1</v>
-      </c>
-      <c r="G73" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="str">
-        <v>HD-MTX-26-RENO-WH-FULL</v>
-      </c>
-      <c r="B74" t="str">
-        <v>Tủ lạnh</v>
-      </c>
-      <c r="C74" t="str">
-        <v>Inverter 200L</v>
-      </c>
-      <c r="D74" t="str">
-        <v>Bếp</v>
-      </c>
-      <c r="E74" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F74">
-        <v>1</v>
-      </c>
-      <c r="G74" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="str">
-        <v>HD-MTX-26-RENO-WH-FULL</v>
-      </c>
-      <c r="B75" t="str">
-        <v>Máy giặt</v>
-      </c>
-      <c r="C75" t="str">
-        <v>Cửa trước 8kg</v>
-      </c>
-      <c r="D75" t="str">
-        <v>Sân sau</v>
-      </c>
-      <c r="E75" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F75">
-        <v>1</v>
-      </c>
-      <c r="G75" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="str">
-        <v>HD-MTX-26-RENO-WH-FULL</v>
-      </c>
-      <c r="B76" t="str">
-        <v>Nóng lạnh</v>
-      </c>
-      <c r="C76" t="str">
-        <v>15L</v>
-      </c>
-      <c r="D76" t="str">
-        <v>WC tầng 1</v>
-      </c>
-      <c r="E76" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F76">
-        <v>1</v>
-      </c>
-      <c r="G76" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="str">
-        <v>HD-MTX-26-RENO-WH-FULL</v>
-      </c>
-      <c r="B77" t="str">
-        <v>Giường</v>
-      </c>
-      <c r="C77" t="str">
-        <v>Giường gỗ 1m6</v>
-      </c>
-      <c r="D77" t="str">
-        <v>Phòng ngủ 1</v>
-      </c>
-      <c r="E77" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F77">
-        <v>1</v>
-      </c>
-      <c r="G77" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="str">
-        <v>HD-MTX-26-RENO-WH-FULL</v>
-      </c>
-      <c r="B78" t="str">
-        <v>Giường</v>
-      </c>
-      <c r="C78" t="str">
-        <v>Giường gỗ 1m6</v>
-      </c>
-      <c r="D78" t="str">
-        <v>Phòng ngủ 2</v>
-      </c>
-      <c r="E78" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F78">
-        <v>1</v>
-      </c>
-      <c r="G78" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="str">
-        <v>HD-MTX-26-RENO-WH-FULL</v>
-      </c>
-      <c r="B79" t="str">
-        <v>Quạt</v>
-      </c>
-      <c r="C79" t="str">
-        <v>Quạt trần</v>
-      </c>
-      <c r="D79" t="str">
-        <v>Phòng khách</v>
-      </c>
-      <c r="E79" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F79">
-        <v>1</v>
-      </c>
-      <c r="G79" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="str">
-        <v>HD-MTX-26-RENO-WH-FULL</v>
-      </c>
-      <c r="B80" t="str">
-        <v>Quạt</v>
-      </c>
-      <c r="C80" t="str">
-        <v>Quạt đứng</v>
-      </c>
-      <c r="D80" t="str">
-        <v>Phòng ngủ 1</v>
-      </c>
-      <c r="E80" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F80">
-        <v>1</v>
-      </c>
-      <c r="G80" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="str">
-        <v>HD-MTX-27-RENO-WH-FULL</v>
-      </c>
-      <c r="B81" t="str">
-        <v>Điều hòa</v>
-      </c>
-      <c r="C81" t="str">
-        <v>1.5HP Inverter</v>
-      </c>
-      <c r="D81" t="str">
-        <v>Phòng khách</v>
-      </c>
-      <c r="E81" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F81">
-        <v>1</v>
-      </c>
-      <c r="G81" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="str">
-        <v>HD-MTX-27-RENO-WH-FULL</v>
-      </c>
-      <c r="B82" t="str">
-        <v>Điều hòa</v>
-      </c>
-      <c r="C82" t="str">
-        <v>1HP</v>
-      </c>
-      <c r="D82" t="str">
-        <v>Phòng ngủ 1</v>
-      </c>
-      <c r="E82" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F82">
-        <v>1</v>
-      </c>
-      <c r="G82" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="str">
-        <v>HD-MTX-27-RENO-WH-FULL</v>
-      </c>
-      <c r="B83" t="str">
-        <v>Tủ lạnh</v>
-      </c>
-      <c r="C83" t="str">
-        <v>Inverter 200L</v>
-      </c>
-      <c r="D83" t="str">
-        <v>Bếp</v>
-      </c>
-      <c r="E83" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F83">
-        <v>1</v>
-      </c>
-      <c r="G83" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="str">
-        <v>HD-MTX-27-RENO-WH-FULL</v>
-      </c>
-      <c r="B84" t="str">
-        <v>Máy giặt</v>
-      </c>
-      <c r="C84" t="str">
-        <v>Cửa trước 8kg</v>
-      </c>
-      <c r="D84" t="str">
-        <v>Sân sau</v>
-      </c>
-      <c r="E84" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F84">
-        <v>1</v>
-      </c>
-      <c r="G84" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="str">
-        <v>HD-MTX-27-RENO-WH-FULL</v>
-      </c>
-      <c r="B85" t="str">
-        <v>Nóng lạnh</v>
-      </c>
-      <c r="C85" t="str">
-        <v>15L</v>
-      </c>
-      <c r="D85" t="str">
-        <v>WC tầng 1</v>
-      </c>
-      <c r="E85" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F85">
-        <v>1</v>
-      </c>
-      <c r="G85" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="str">
-        <v>HD-MTX-27-RENO-WH-FULL</v>
-      </c>
-      <c r="B86" t="str">
-        <v>Giường</v>
-      </c>
-      <c r="C86" t="str">
-        <v>Giường gỗ 1m6</v>
-      </c>
-      <c r="D86" t="str">
-        <v>Phòng ngủ 1</v>
-      </c>
-      <c r="E86" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F86">
-        <v>1</v>
-      </c>
-      <c r="G86" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="str">
-        <v>HD-MTX-27-RENO-WH-FULL</v>
-      </c>
-      <c r="B87" t="str">
-        <v>Giường</v>
-      </c>
-      <c r="C87" t="str">
-        <v>Giường gỗ 1m6</v>
-      </c>
-      <c r="D87" t="str">
-        <v>Phòng ngủ 2</v>
-      </c>
-      <c r="E87" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F87">
-        <v>1</v>
-      </c>
-      <c r="G87" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="str">
-        <v>HD-MTX-27-RENO-WH-FULL</v>
-      </c>
-      <c r="B88" t="str">
-        <v>Quạt</v>
-      </c>
-      <c r="C88" t="str">
-        <v>Quạt trần</v>
-      </c>
-      <c r="D88" t="str">
-        <v>Phòng khách</v>
-      </c>
-      <c r="E88" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F88">
-        <v>1</v>
-      </c>
-      <c r="G88" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="str">
-        <v>HD-MTX-27-RENO-WH-FULL</v>
-      </c>
-      <c r="B89" t="str">
-        <v>Quạt</v>
-      </c>
-      <c r="C89" t="str">
-        <v>Quạt đứng</v>
-      </c>
-      <c r="D89" t="str">
-        <v>Phòng ngủ 1</v>
-      </c>
-      <c r="E89" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F89">
-        <v>1</v>
-      </c>
-      <c r="G89" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="str">
-        <v>HD-MTX-28-RENO-WH-HO-NOBUY</v>
-      </c>
-      <c r="B90" t="str">
-        <v>Máy giặt</v>
-      </c>
-      <c r="C90" t="str">
-        <v>Máy cũ</v>
-      </c>
-      <c r="D90" t="str">
-        <v>Sân sau</v>
-      </c>
-      <c r="E90" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F90">
-        <v>1</v>
-      </c>
-      <c r="G90" t="str">
-        <v>TB chủ — không NT</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="str">
-        <v>HD-MTX-29-RENO-WH-HO-NOBUY</v>
-      </c>
-      <c r="B91" t="str">
-        <v>Máy giặt</v>
-      </c>
-      <c r="C91" t="str">
-        <v>Máy cũ</v>
-      </c>
-      <c r="D91" t="str">
-        <v>Sân sau</v>
-      </c>
-      <c r="E91" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F91">
-        <v>1</v>
-      </c>
-      <c r="G91" t="str">
-        <v>TB chủ — không NT</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="str">
-        <v>HD-MTX-30-RENO-WH-HO-BUY</v>
-      </c>
-      <c r="B92" t="str">
-        <v>Điều hòa</v>
-      </c>
-      <c r="C92" t="str">
-        <v>Máy 1.5HP</v>
-      </c>
-      <c r="D92" t="str">
-        <v>Phòng khách</v>
-      </c>
-      <c r="E92" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F92">
-        <v>1</v>
-      </c>
-      <c r="G92" t="str">
-        <v>NT cơ bản</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="str">
-        <v>HD-MTX-30-RENO-WH-HO-BUY</v>
-      </c>
-      <c r="B93" t="str">
-        <v>Giường</v>
-      </c>
-      <c r="C93" t="str">
-        <v>Giường gỗ 1m6</v>
-      </c>
-      <c r="D93" t="str">
-        <v>Phòng ngủ</v>
-      </c>
-      <c r="E93" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F93">
-        <v>1</v>
-      </c>
-      <c r="G93" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="str">
-        <v>HD-MTX-31-RENO-WH-HO-BUY</v>
-      </c>
-      <c r="B94" t="str">
-        <v>Điều hòa</v>
-      </c>
-      <c r="C94" t="str">
-        <v>Máy 1.5HP</v>
-      </c>
-      <c r="D94" t="str">
-        <v>Phòng khách</v>
-      </c>
-      <c r="E94" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F94">
-        <v>1</v>
-      </c>
-      <c r="G94" t="str">
-        <v>NT cơ bản</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="str">
-        <v>HD-MTX-31-RENO-WH-HO-BUY</v>
-      </c>
-      <c r="B95" t="str">
-        <v>Giường</v>
-      </c>
-      <c r="C95" t="str">
-        <v>Giường gỗ 1m6</v>
-      </c>
-      <c r="D95" t="str">
-        <v>Phòng ngủ</v>
-      </c>
-      <c r="E95" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F95">
-        <v>1</v>
-      </c>
-      <c r="G95" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="str">
-        <v>HD-MTX-36-RENO-RM-BASIC-HO</v>
-      </c>
-      <c r="B96" t="str">
-        <v>Giường</v>
-      </c>
-      <c r="C96" t="str">
-        <v>Giường sắt cũ</v>
-      </c>
-      <c r="D96" t="str">
-        <v>Tầng 2</v>
-      </c>
-      <c r="E96" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F96">
-        <v>2</v>
-      </c>
-      <c r="G96" t="str">
-        <v>TB chủ</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="str">
-        <v>HD-MTX-36-RENO-RM-BASIC-HO</v>
-      </c>
-      <c r="B97" t="str">
-        <v>Quạt</v>
-      </c>
-      <c r="C97" t="str">
-        <v>Quạt trần</v>
-      </c>
-      <c r="D97" t="str">
-        <v>Hành lang</v>
-      </c>
-      <c r="E97" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F97">
-        <v>1</v>
-      </c>
-      <c r="G97" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="str">
-        <v>HD-MTX-37-RENO-RM-BASIC-HO</v>
-      </c>
-      <c r="B98" t="str">
-        <v>Giường</v>
-      </c>
-      <c r="C98" t="str">
-        <v>Giường sắt cũ</v>
-      </c>
-      <c r="D98" t="str">
-        <v>Tầng 2</v>
-      </c>
-      <c r="E98" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F98">
-        <v>2</v>
-      </c>
-      <c r="G98" t="str">
-        <v>TB chủ</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="str">
-        <v>HD-MTX-38-RENO-RM-BASIC-HO</v>
-      </c>
-      <c r="B99" t="str">
-        <v>Giường</v>
-      </c>
-      <c r="C99" t="str">
-        <v>Giường sắt cũ</v>
-      </c>
-      <c r="D99" t="str">
-        <v>Tầng 2</v>
-      </c>
-      <c r="E99" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F99">
-        <v>2</v>
-      </c>
-      <c r="G99" t="str">
-        <v>TB chủ</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="str">
-        <v>HD-MTX-38-RENO-RM-BASIC-HO</v>
-      </c>
-      <c r="B100" t="str">
-        <v>Quạt</v>
-      </c>
-      <c r="C100" t="str">
-        <v>Quạt trần</v>
-      </c>
-      <c r="D100" t="str">
-        <v>Hành lang</v>
-      </c>
-      <c r="E100" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F100">
-        <v>1</v>
-      </c>
-      <c r="G100" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="str">
-        <v>HD-MTX-39-RENO-RM-BASIC-HO</v>
-      </c>
-      <c r="B101" t="str">
-        <v>Giường</v>
-      </c>
-      <c r="C101" t="str">
-        <v>Giường sắt cũ</v>
-      </c>
-      <c r="D101" t="str">
-        <v>Tầng 2</v>
-      </c>
-      <c r="E101" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F101">
-        <v>2</v>
-      </c>
-      <c r="G101" t="str">
-        <v>TB chủ</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="str">
-        <v>HD-MTX-44-RENO-RM-FULL</v>
-      </c>
-      <c r="B102" t="str">
-        <v>Máy giặt</v>
-      </c>
-      <c r="C102" t="str">
-        <v>Máy cũ chung</v>
-      </c>
-      <c r="D102" t="str">
-        <v>Sân phơi</v>
-      </c>
-      <c r="E102" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F102">
-        <v>1</v>
-      </c>
-      <c r="G102" t="str">
-        <v>TB dùng chung</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="str">
-        <v>HD-MTX-44-RENO-RM-FULL</v>
-      </c>
-      <c r="B103" t="str">
-        <v>Tủ lạnh</v>
-      </c>
-      <c r="C103" t="str">
-        <v>Tủ cũ tầng 1</v>
-      </c>
-      <c r="D103" t="str">
-        <v>Bếp chung</v>
-      </c>
-      <c r="E103" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F103">
-        <v>1</v>
-      </c>
-      <c r="G103" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="str">
-        <v>HD-MTX-45-RENO-RM-FULL</v>
-      </c>
-      <c r="B104" t="str">
-        <v>Máy giặt</v>
-      </c>
-      <c r="C104" t="str">
-        <v>Máy cũ chung</v>
-      </c>
-      <c r="D104" t="str">
-        <v>Sân phơi</v>
-      </c>
-      <c r="E104" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F104">
-        <v>1</v>
-      </c>
-      <c r="G104" t="str">
-        <v>TB dùng chung</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="str">
-        <v>HD-MTX-45-RENO-RM-FULL</v>
-      </c>
-      <c r="B105" t="str">
-        <v>Tủ lạnh</v>
-      </c>
-      <c r="C105" t="str">
-        <v>Tủ cũ tầng 1</v>
-      </c>
-      <c r="D105" t="str">
-        <v>Bếp chung</v>
-      </c>
-      <c r="E105" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F105">
-        <v>1</v>
-      </c>
-      <c r="G105" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="str">
-        <v>HD-MTX-46-RENO-RM-FULL</v>
-      </c>
-      <c r="B106" t="str">
-        <v>Máy giặt</v>
-      </c>
-      <c r="C106" t="str">
-        <v>Máy cũ chung</v>
-      </c>
-      <c r="D106" t="str">
-        <v>Sân phơi</v>
-      </c>
-      <c r="E106" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F106">
-        <v>1</v>
-      </c>
-      <c r="G106" t="str">
-        <v>TB dùng chung</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="str">
-        <v>HD-MTX-46-RENO-RM-FULL</v>
-      </c>
-      <c r="B107" t="str">
-        <v>Tủ lạnh</v>
-      </c>
-      <c r="C107" t="str">
-        <v>Tủ cũ tầng 1</v>
-      </c>
-      <c r="D107" t="str">
-        <v>Bếp chung</v>
-      </c>
-      <c r="E107" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F107">
-        <v>1</v>
-      </c>
-      <c r="G107" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="str">
-        <v>HD-MTX-47-RENO-RM-FULL</v>
-      </c>
-      <c r="B108" t="str">
-        <v>Máy giặt</v>
-      </c>
-      <c r="C108" t="str">
-        <v>Máy cũ chung</v>
-      </c>
-      <c r="D108" t="str">
-        <v>Sân phơi</v>
-      </c>
-      <c r="E108" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F108">
-        <v>1</v>
-      </c>
-      <c r="G108" t="str">
-        <v>TB dùng chung</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="str">
-        <v>HD-MTX-47-RENO-RM-FULL</v>
-      </c>
-      <c r="B109" t="str">
-        <v>Tủ lạnh</v>
-      </c>
-      <c r="C109" t="str">
-        <v>Tủ cũ tầng 1</v>
-      </c>
-      <c r="D109" t="str">
-        <v>Bếp chung</v>
-      </c>
-      <c r="E109" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F109">
-        <v>1</v>
-      </c>
-      <c r="G109" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="str">
-        <v>HD-MTX-48-RENO-RM-HO-BUY</v>
-      </c>
-      <c r="B110" t="str">
-        <v>Giường</v>
-      </c>
-      <c r="C110" t="str">
-        <v>Giường sắt cũ</v>
-      </c>
-      <c r="D110" t="str">
-        <v>Tầng 2</v>
-      </c>
-      <c r="E110" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F110">
-        <v>2</v>
-      </c>
-      <c r="G110" t="str">
-        <v>TB chủ</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="str">
-        <v>HD-MTX-48-RENO-RM-HO-BUY</v>
-      </c>
-      <c r="B111" t="str">
-        <v>Quạt</v>
-      </c>
-      <c r="C111" t="str">
-        <v>Quạt trần</v>
-      </c>
-      <c r="D111" t="str">
-        <v>Hành lang</v>
-      </c>
-      <c r="E111" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F111">
-        <v>1</v>
-      </c>
-      <c r="G111" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="str">
-        <v>HD-MTX-49-RENO-RM-HO-BUY</v>
-      </c>
-      <c r="B112" t="str">
-        <v>Giường</v>
-      </c>
-      <c r="C112" t="str">
-        <v>Giường sắt cũ</v>
-      </c>
-      <c r="D112" t="str">
-        <v>Tầng 2</v>
-      </c>
-      <c r="E112" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F112">
-        <v>2</v>
-      </c>
-      <c r="G112" t="str">
-        <v>TB chủ</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="str">
-        <v>HD-MTX-50-RENO-RM-HO-BUY</v>
-      </c>
-      <c r="B113" t="str">
-        <v>Giường</v>
-      </c>
-      <c r="C113" t="str">
-        <v>Giường sắt cũ</v>
-      </c>
-      <c r="D113" t="str">
-        <v>Tầng 2</v>
-      </c>
-      <c r="E113" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F113">
-        <v>2</v>
-      </c>
-      <c r="G113" t="str">
-        <v>TB chủ</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="str">
-        <v>HD-MTX-50-RENO-RM-HO-BUY</v>
-      </c>
-      <c r="B114" t="str">
-        <v>Quạt</v>
-      </c>
-      <c r="C114" t="str">
-        <v>Quạt trần</v>
-      </c>
-      <c r="D114" t="str">
-        <v>Hành lang</v>
-      </c>
-      <c r="E114" t="str">
-        <v>GOOD</v>
-      </c>
-      <c r="F114">
-        <v>1</v>
-      </c>
-      <c r="G114" t="str">
-        <v/>
+        <v>Đồ chủ gốc hỏng — đợt 2 mua mới nếu có NT</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G114"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G59"/>
   </ignoredErrors>
 </worksheet>
 </file>